--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -649,6 +649,9 @@
     <t>['53']</t>
   </si>
   <si>
+    <t>['29', '45+2']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -815,6 +818,9 @@
   </si>
   <si>
     <t>['30']</t>
+  </si>
+  <si>
+    <t>['6', '56']</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP179"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1638,7 +1644,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1844,7 +1850,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2668,7 +2674,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3286,7 +3292,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3492,7 +3498,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3573,7 +3579,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3698,7 +3704,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3779,7 +3785,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ13">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3904,7 +3910,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4728,7 +4734,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4934,7 +4940,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5218,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ20">
         <v>0.67</v>
@@ -5424,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ21">
         <v>0.78</v>
@@ -5758,7 +5764,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6376,7 +6382,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6994,7 +7000,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7072,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7406,7 +7412,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8642,7 +8648,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8723,7 +8729,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ37">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR37">
         <v>2.41</v>
@@ -8929,7 +8935,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ38">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9132,7 +9138,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ39">
         <v>1.5</v>
@@ -9672,7 +9678,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10908,7 +10914,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11114,7 +11120,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11526,7 +11532,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11604,7 +11610,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ51">
         <v>1.78</v>
@@ -12016,7 +12022,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ53">
         <v>0.25</v>
@@ -12637,7 +12643,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ56">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.78</v>
@@ -12762,7 +12768,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13255,7 +13261,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ59">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.57</v>
@@ -13586,7 +13592,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14616,7 +14622,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14822,7 +14828,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -15028,7 +15034,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15106,7 +15112,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ68">
         <v>1.33</v>
@@ -15234,7 +15240,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15518,7 +15524,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ70">
         <v>0.89</v>
@@ -15646,7 +15652,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15933,7 +15939,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR72">
         <v>2.1</v>
@@ -16676,7 +16682,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17169,7 +17175,7 @@
         <v>2</v>
       </c>
       <c r="AQ78">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR78">
         <v>1.76</v>
@@ -18402,7 +18408,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ84">
         <v>0.3</v>
@@ -18530,7 +18536,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19148,7 +19154,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19432,7 +19438,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ89">
         <v>0.6</v>
@@ -19766,7 +19772,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19972,7 +19978,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20178,7 +20184,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20465,7 +20471,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ94">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.37</v>
@@ -20590,7 +20596,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20796,7 +20802,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21907,7 +21913,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ101">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -22110,7 +22116,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ102">
         <v>1.5</v>
@@ -22650,7 +22656,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23268,7 +23274,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23552,7 +23558,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ109">
         <v>0.78</v>
@@ -24092,7 +24098,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24710,7 +24716,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24916,7 +24922,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25534,7 +25540,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25946,7 +25952,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26027,7 +26033,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ121">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>2.18</v>
@@ -26230,7 +26236,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ122">
         <v>1.11</v>
@@ -26439,7 +26445,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ123">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR123">
         <v>1.83</v>
@@ -26564,7 +26570,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26848,7 +26854,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -28006,7 +28012,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28212,7 +28218,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28418,7 +28424,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28499,7 +28505,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ133">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>2.05</v>
@@ -28830,7 +28836,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29242,7 +29248,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29654,7 +29660,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q139">
         <v>3.02</v>
@@ -30762,7 +30768,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ144">
         <v>1</v>
@@ -31302,7 +31308,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31586,7 +31592,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ148">
         <v>1.25</v>
@@ -31714,7 +31720,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31920,7 +31926,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32207,7 +32213,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ151">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.53</v>
@@ -32950,7 +32956,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33855,7 +33861,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ159">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.73</v>
@@ -34058,7 +34064,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ160">
         <v>0.3</v>
@@ -34392,7 +34398,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34598,7 +34604,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34676,7 +34682,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ163">
         <v>1.25</v>
@@ -34804,7 +34810,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -34885,7 +34891,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR164">
         <v>1.95</v>
@@ -35010,7 +35016,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35216,7 +35222,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35422,7 +35428,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35628,7 +35634,7 @@
         <v>202</v>
       </c>
       <c r="P168" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35834,7 +35840,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -36246,7 +36252,7 @@
         <v>97</v>
       </c>
       <c r="P171" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q171">
         <v>2.4</v>
@@ -36864,7 +36870,7 @@
         <v>199</v>
       </c>
       <c r="P174" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37276,7 +37282,7 @@
         <v>207</v>
       </c>
       <c r="P176" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q176">
         <v>2.8</v>
@@ -37688,7 +37694,7 @@
         <v>209</v>
       </c>
       <c r="P178" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q178">
         <v>2.93</v>
@@ -37894,7 +37900,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q179">
         <v>3.1</v>
@@ -38051,6 +38057,418 @@
       </c>
       <c r="BP179">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7841211</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45862.79166666666</v>
+      </c>
+      <c r="F180">
+        <v>18</v>
+      </c>
+      <c r="G180" t="s">
+        <v>89</v>
+      </c>
+      <c r="H180" t="s">
+        <v>72</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>2</v>
+      </c>
+      <c r="N180">
+        <v>2</v>
+      </c>
+      <c r="O180" t="s">
+        <v>97</v>
+      </c>
+      <c r="P180" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q180">
+        <v>3.55</v>
+      </c>
+      <c r="R180">
+        <v>1.85</v>
+      </c>
+      <c r="S180">
+        <v>3.45</v>
+      </c>
+      <c r="T180">
+        <v>1.65</v>
+      </c>
+      <c r="U180">
+        <v>2.1</v>
+      </c>
+      <c r="V180">
+        <v>3.8</v>
+      </c>
+      <c r="W180">
+        <v>1.22</v>
+      </c>
+      <c r="X180">
+        <v>10</v>
+      </c>
+      <c r="Y180">
+        <v>1.02</v>
+      </c>
+      <c r="Z180">
+        <v>2.95</v>
+      </c>
+      <c r="AA180">
+        <v>2.83</v>
+      </c>
+      <c r="AB180">
+        <v>2.84</v>
+      </c>
+      <c r="AC180">
+        <v>1.07</v>
+      </c>
+      <c r="AD180">
+        <v>5.5</v>
+      </c>
+      <c r="AE180">
+        <v>1.61</v>
+      </c>
+      <c r="AF180">
+        <v>2.2</v>
+      </c>
+      <c r="AG180">
+        <v>3.1</v>
+      </c>
+      <c r="AH180">
+        <v>1.36</v>
+      </c>
+      <c r="AI180">
+        <v>2.25</v>
+      </c>
+      <c r="AJ180">
+        <v>1.58</v>
+      </c>
+      <c r="AK180">
+        <v>1.41</v>
+      </c>
+      <c r="AL180">
+        <v>1.38</v>
+      </c>
+      <c r="AM180">
+        <v>1.4</v>
+      </c>
+      <c r="AN180">
+        <v>1.22</v>
+      </c>
+      <c r="AO180">
+        <v>1.13</v>
+      </c>
+      <c r="AP180">
+        <v>1.1</v>
+      </c>
+      <c r="AQ180">
+        <v>1.33</v>
+      </c>
+      <c r="AR180">
+        <v>1.42</v>
+      </c>
+      <c r="AS180">
+        <v>1.26</v>
+      </c>
+      <c r="AT180">
+        <v>2.68</v>
+      </c>
+      <c r="AU180">
+        <v>6</v>
+      </c>
+      <c r="AV180">
+        <v>5</v>
+      </c>
+      <c r="AW180">
+        <v>12</v>
+      </c>
+      <c r="AX180">
+        <v>5</v>
+      </c>
+      <c r="AY180">
+        <v>18</v>
+      </c>
+      <c r="AZ180">
+        <v>10</v>
+      </c>
+      <c r="BA180">
+        <v>6</v>
+      </c>
+      <c r="BB180">
+        <v>5</v>
+      </c>
+      <c r="BC180">
+        <v>11</v>
+      </c>
+      <c r="BD180">
+        <v>2.21</v>
+      </c>
+      <c r="BE180">
+        <v>7.5</v>
+      </c>
+      <c r="BF180">
+        <v>2.02</v>
+      </c>
+      <c r="BG180">
+        <v>1.19</v>
+      </c>
+      <c r="BH180">
+        <v>4.1</v>
+      </c>
+      <c r="BI180">
+        <v>1.33</v>
+      </c>
+      <c r="BJ180">
+        <v>3.2</v>
+      </c>
+      <c r="BK180">
+        <v>1.5</v>
+      </c>
+      <c r="BL180">
+        <v>2.4</v>
+      </c>
+      <c r="BM180">
+        <v>1.8</v>
+      </c>
+      <c r="BN180">
+        <v>1.91</v>
+      </c>
+      <c r="BO180">
+        <v>2.25</v>
+      </c>
+      <c r="BP180">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7841205</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45862.89930555555</v>
+      </c>
+      <c r="F181">
+        <v>18</v>
+      </c>
+      <c r="G181" t="s">
+        <v>88</v>
+      </c>
+      <c r="H181" t="s">
+        <v>78</v>
+      </c>
+      <c r="I181">
+        <v>2</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181">
+        <v>3</v>
+      </c>
+      <c r="L181">
+        <v>2</v>
+      </c>
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>3</v>
+      </c>
+      <c r="O181" t="s">
+        <v>211</v>
+      </c>
+      <c r="P181" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q181">
+        <v>3.25</v>
+      </c>
+      <c r="R181">
+        <v>1.67</v>
+      </c>
+      <c r="S181">
+        <v>3.87</v>
+      </c>
+      <c r="T181">
+        <v>1.53</v>
+      </c>
+      <c r="U181">
+        <v>2.35</v>
+      </c>
+      <c r="V181">
+        <v>3.6</v>
+      </c>
+      <c r="W181">
+        <v>1.27</v>
+      </c>
+      <c r="X181">
+        <v>7.5</v>
+      </c>
+      <c r="Y181">
+        <v>1.04</v>
+      </c>
+      <c r="Z181">
+        <v>2.35</v>
+      </c>
+      <c r="AA181">
+        <v>2.9</v>
+      </c>
+      <c r="AB181">
+        <v>2.87</v>
+      </c>
+      <c r="AC181">
+        <v>1.11</v>
+      </c>
+      <c r="AD181">
+        <v>6.25</v>
+      </c>
+      <c r="AE181">
+        <v>1.46</v>
+      </c>
+      <c r="AF181">
+        <v>2.36</v>
+      </c>
+      <c r="AG181">
+        <v>2.2</v>
+      </c>
+      <c r="AH181">
+        <v>1.53</v>
+      </c>
+      <c r="AI181">
+        <v>2.16</v>
+      </c>
+      <c r="AJ181">
+        <v>1.66</v>
+      </c>
+      <c r="AK181">
+        <v>1.36</v>
+      </c>
+      <c r="AL181">
+        <v>1.34</v>
+      </c>
+      <c r="AM181">
+        <v>1.5</v>
+      </c>
+      <c r="AN181">
+        <v>2</v>
+      </c>
+      <c r="AO181">
+        <v>1.13</v>
+      </c>
+      <c r="AP181">
+        <v>2.1</v>
+      </c>
+      <c r="AQ181">
+        <v>1</v>
+      </c>
+      <c r="AR181">
+        <v>1.31</v>
+      </c>
+      <c r="AS181">
+        <v>1.27</v>
+      </c>
+      <c r="AT181">
+        <v>2.58</v>
+      </c>
+      <c r="AU181">
+        <v>8</v>
+      </c>
+      <c r="AV181">
+        <v>7</v>
+      </c>
+      <c r="AW181">
+        <v>6</v>
+      </c>
+      <c r="AX181">
+        <v>11</v>
+      </c>
+      <c r="AY181">
+        <v>14</v>
+      </c>
+      <c r="AZ181">
+        <v>18</v>
+      </c>
+      <c r="BA181">
+        <v>7</v>
+      </c>
+      <c r="BB181">
+        <v>2</v>
+      </c>
+      <c r="BC181">
+        <v>9</v>
+      </c>
+      <c r="BD181">
+        <v>1.88</v>
+      </c>
+      <c r="BE181">
+        <v>7</v>
+      </c>
+      <c r="BF181">
+        <v>2.47</v>
+      </c>
+      <c r="BG181">
+        <v>1.09</v>
+      </c>
+      <c r="BH181">
+        <v>4.5</v>
+      </c>
+      <c r="BI181">
+        <v>1.3</v>
+      </c>
+      <c r="BJ181">
+        <v>3.2</v>
+      </c>
+      <c r="BK181">
+        <v>1.45</v>
+      </c>
+      <c r="BL181">
+        <v>2.4</v>
+      </c>
+      <c r="BM181">
+        <v>1.8</v>
+      </c>
+      <c r="BN181">
+        <v>1.91</v>
+      </c>
+      <c r="BO181">
+        <v>2.12</v>
+      </c>
+      <c r="BP181">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -652,6 +652,9 @@
     <t>['29', '45+2']</t>
   </si>
   <si>
+    <t>['37', '66', '54', '51']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1182,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1644,7 +1647,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1850,7 +1853,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1931,7 +1934,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ4">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2340,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ6">
         <v>1.11</v>
@@ -2674,7 +2677,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2752,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -3167,7 +3170,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ10">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3292,7 +3295,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3498,7 +3501,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3704,7 +3707,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3910,7 +3913,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4734,7 +4737,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4940,7 +4943,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5764,7 +5767,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6051,7 +6054,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ24">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6257,7 +6260,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ25">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -6382,7 +6385,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6872,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ28">
         <v>0.3</v>
@@ -7000,7 +7003,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7284,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ30">
         <v>0.78</v>
@@ -7412,7 +7415,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8648,7 +8651,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9678,7 +9681,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10377,7 +10380,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ45">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR45">
         <v>1.46</v>
@@ -10914,7 +10917,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11120,7 +11123,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11532,7 +11535,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11816,7 +11819,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ52">
         <v>1.5</v>
@@ -12437,7 +12440,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ55">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR55">
         <v>1.76</v>
@@ -12768,7 +12771,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13464,7 +13467,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13592,7 +13595,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14622,7 +14625,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14703,7 +14706,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ66">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR66">
         <v>1.58</v>
@@ -14828,7 +14831,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -15034,7 +15037,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15240,7 +15243,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15652,7 +15655,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15936,7 +15939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -16682,7 +16685,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16763,7 +16766,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR76">
         <v>1.64</v>
@@ -17172,7 +17175,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ78">
         <v>1.33</v>
@@ -18536,7 +18539,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19029,7 +19032,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ87">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR87">
         <v>1.81</v>
@@ -19154,7 +19157,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19772,7 +19775,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19978,7 +19981,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20056,7 +20059,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ92">
         <v>0.88</v>
@@ -20184,7 +20187,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20265,7 +20268,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ93">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR93">
         <v>1.7</v>
@@ -20596,7 +20599,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20802,7 +20805,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21292,7 +21295,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ98">
         <v>1</v>
@@ -22656,7 +22659,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23274,7 +23277,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23561,7 +23564,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ109">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR109">
         <v>1.3</v>
@@ -24098,7 +24101,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24588,7 +24591,7 @@
         <v>2</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ114">
         <v>1.78</v>
@@ -24716,7 +24719,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24922,7 +24925,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25003,7 +25006,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ116">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR116">
         <v>1.63</v>
@@ -25540,7 +25543,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25952,7 +25955,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26570,7 +26573,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -27060,7 +27063,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ126">
         <v>0.6</v>
@@ -27887,7 +27890,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR130">
         <v>1.68</v>
@@ -28012,7 +28015,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28218,7 +28221,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28296,7 +28299,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ132">
         <v>0.67</v>
@@ -28424,7 +28427,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28836,7 +28839,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29123,7 +29126,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ136">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR136">
         <v>2.25</v>
@@ -29248,7 +29251,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29660,7 +29663,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q139">
         <v>3.02</v>
@@ -31308,7 +31311,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31386,7 +31389,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ147">
         <v>0.89</v>
@@ -31595,7 +31598,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ148">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR148">
         <v>1.37</v>
@@ -31720,7 +31723,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31926,7 +31929,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32416,7 +32419,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ152">
         <v>1.5</v>
@@ -32625,7 +32628,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ153">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR153">
         <v>1.55</v>
@@ -32956,7 +32959,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -34398,7 +34401,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34604,7 +34607,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34685,7 +34688,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ163">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR163">
         <v>1.33</v>
@@ -34810,7 +34813,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -35016,7 +35019,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35094,7 +35097,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ165">
         <v>1.33</v>
@@ -35222,7 +35225,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35428,7 +35431,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35634,7 +35637,7 @@
         <v>202</v>
       </c>
       <c r="P168" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35840,7 +35843,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -36252,7 +36255,7 @@
         <v>97</v>
       </c>
       <c r="P171" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q171">
         <v>2.4</v>
@@ -36870,7 +36873,7 @@
         <v>199</v>
       </c>
       <c r="P174" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37282,7 +37285,7 @@
         <v>207</v>
       </c>
       <c r="P176" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q176">
         <v>2.8</v>
@@ -37694,7 +37697,7 @@
         <v>209</v>
       </c>
       <c r="P178" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q178">
         <v>2.93</v>
@@ -37900,7 +37903,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q179">
         <v>3.1</v>
@@ -38106,7 +38109,7 @@
         <v>97</v>
       </c>
       <c r="P180" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q180">
         <v>3.55</v>
@@ -38469,6 +38472,418 @@
       </c>
       <c r="BP181">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="182" spans="1:68">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>7841220</v>
+      </c>
+      <c r="C182" t="s">
+        <v>68</v>
+      </c>
+      <c r="D182" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45864.77083333334</v>
+      </c>
+      <c r="F182">
+        <v>19</v>
+      </c>
+      <c r="G182" t="s">
+        <v>76</v>
+      </c>
+      <c r="H182" t="s">
+        <v>86</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="N182">
+        <v>0</v>
+      </c>
+      <c r="O182" t="s">
+        <v>97</v>
+      </c>
+      <c r="P182" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q182">
+        <v>3.44</v>
+      </c>
+      <c r="R182">
+        <v>1.9</v>
+      </c>
+      <c r="S182">
+        <v>3.75</v>
+      </c>
+      <c r="T182">
+        <v>1.57</v>
+      </c>
+      <c r="U182">
+        <v>2.2</v>
+      </c>
+      <c r="V182">
+        <v>3.9</v>
+      </c>
+      <c r="W182">
+        <v>1.25</v>
+      </c>
+      <c r="X182">
+        <v>12</v>
+      </c>
+      <c r="Y182">
+        <v>1.04</v>
+      </c>
+      <c r="Z182">
+        <v>2.52</v>
+      </c>
+      <c r="AA182">
+        <v>2.89</v>
+      </c>
+      <c r="AB182">
+        <v>2.92</v>
+      </c>
+      <c r="AC182">
+        <v>1.09</v>
+      </c>
+      <c r="AD182">
+        <v>5.8</v>
+      </c>
+      <c r="AE182">
+        <v>1.57</v>
+      </c>
+      <c r="AF182">
+        <v>2.35</v>
+      </c>
+      <c r="AG182">
+        <v>2.55</v>
+      </c>
+      <c r="AH182">
+        <v>1.44</v>
+      </c>
+      <c r="AI182">
+        <v>2.1</v>
+      </c>
+      <c r="AJ182">
+        <v>1.7</v>
+      </c>
+      <c r="AK182">
+        <v>1.35</v>
+      </c>
+      <c r="AL182">
+        <v>1.4</v>
+      </c>
+      <c r="AM182">
+        <v>1.44</v>
+      </c>
+      <c r="AN182">
+        <v>1.5</v>
+      </c>
+      <c r="AO182">
+        <v>0.78</v>
+      </c>
+      <c r="AP182">
+        <v>1.44</v>
+      </c>
+      <c r="AQ182">
+        <v>0.8</v>
+      </c>
+      <c r="AR182">
+        <v>1.78</v>
+      </c>
+      <c r="AS182">
+        <v>1.29</v>
+      </c>
+      <c r="AT182">
+        <v>3.07</v>
+      </c>
+      <c r="AU182">
+        <v>4</v>
+      </c>
+      <c r="AV182">
+        <v>6</v>
+      </c>
+      <c r="AW182">
+        <v>4</v>
+      </c>
+      <c r="AX182">
+        <v>20</v>
+      </c>
+      <c r="AY182">
+        <v>8</v>
+      </c>
+      <c r="AZ182">
+        <v>26</v>
+      </c>
+      <c r="BA182">
+        <v>4</v>
+      </c>
+      <c r="BB182">
+        <v>16</v>
+      </c>
+      <c r="BC182">
+        <v>20</v>
+      </c>
+      <c r="BD182">
+        <v>2.1</v>
+      </c>
+      <c r="BE182">
+        <v>6.75</v>
+      </c>
+      <c r="BF182">
+        <v>2.15</v>
+      </c>
+      <c r="BG182">
+        <v>1.22</v>
+      </c>
+      <c r="BH182">
+        <v>3.58</v>
+      </c>
+      <c r="BI182">
+        <v>1.43</v>
+      </c>
+      <c r="BJ182">
+        <v>2.47</v>
+      </c>
+      <c r="BK182">
+        <v>1.73</v>
+      </c>
+      <c r="BL182">
+        <v>2</v>
+      </c>
+      <c r="BM182">
+        <v>2.25</v>
+      </c>
+      <c r="BN182">
+        <v>1.56</v>
+      </c>
+      <c r="BO182">
+        <v>2.9</v>
+      </c>
+      <c r="BP182">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="183" spans="1:68">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>7841218</v>
+      </c>
+      <c r="C183" t="s">
+        <v>68</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45864.85416666666</v>
+      </c>
+      <c r="F183">
+        <v>19</v>
+      </c>
+      <c r="G183" t="s">
+        <v>74</v>
+      </c>
+      <c r="H183" t="s">
+        <v>85</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>4</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>4</v>
+      </c>
+      <c r="O183" t="s">
+        <v>212</v>
+      </c>
+      <c r="P183" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q183">
+        <v>3.18</v>
+      </c>
+      <c r="R183">
+        <v>1.88</v>
+      </c>
+      <c r="S183">
+        <v>4.2</v>
+      </c>
+      <c r="T183">
+        <v>1.55</v>
+      </c>
+      <c r="U183">
+        <v>2.2</v>
+      </c>
+      <c r="V183">
+        <v>3.6</v>
+      </c>
+      <c r="W183">
+        <v>1.25</v>
+      </c>
+      <c r="X183">
+        <v>13.5</v>
+      </c>
+      <c r="Y183">
+        <v>1.02</v>
+      </c>
+      <c r="Z183">
+        <v>2.36</v>
+      </c>
+      <c r="AA183">
+        <v>2.88</v>
+      </c>
+      <c r="AB183">
+        <v>3.25</v>
+      </c>
+      <c r="AC183">
+        <v>1.13</v>
+      </c>
+      <c r="AD183">
+        <v>5.55</v>
+      </c>
+      <c r="AE183">
+        <v>1.55</v>
+      </c>
+      <c r="AF183">
+        <v>2.25</v>
+      </c>
+      <c r="AG183">
+        <v>3.1</v>
+      </c>
+      <c r="AH183">
+        <v>1.4</v>
+      </c>
+      <c r="AI183">
+        <v>2.48</v>
+      </c>
+      <c r="AJ183">
+        <v>1.54</v>
+      </c>
+      <c r="AK183">
+        <v>1.33</v>
+      </c>
+      <c r="AL183">
+        <v>1.37</v>
+      </c>
+      <c r="AM183">
+        <v>1.6</v>
+      </c>
+      <c r="AN183">
+        <v>2</v>
+      </c>
+      <c r="AO183">
+        <v>1.25</v>
+      </c>
+      <c r="AP183">
+        <v>2.11</v>
+      </c>
+      <c r="AQ183">
+        <v>1.11</v>
+      </c>
+      <c r="AR183">
+        <v>2.02</v>
+      </c>
+      <c r="AS183">
+        <v>1.24</v>
+      </c>
+      <c r="AT183">
+        <v>3.26</v>
+      </c>
+      <c r="AU183">
+        <v>7</v>
+      </c>
+      <c r="AV183">
+        <v>7</v>
+      </c>
+      <c r="AW183">
+        <v>9</v>
+      </c>
+      <c r="AX183">
+        <v>13</v>
+      </c>
+      <c r="AY183">
+        <v>16</v>
+      </c>
+      <c r="AZ183">
+        <v>20</v>
+      </c>
+      <c r="BA183">
+        <v>3</v>
+      </c>
+      <c r="BB183">
+        <v>10</v>
+      </c>
+      <c r="BC183">
+        <v>13</v>
+      </c>
+      <c r="BD183">
+        <v>1.65</v>
+      </c>
+      <c r="BE183">
+        <v>6.75</v>
+      </c>
+      <c r="BF183">
+        <v>2.43</v>
+      </c>
+      <c r="BG183">
+        <v>1.16</v>
+      </c>
+      <c r="BH183">
+        <v>4</v>
+      </c>
+      <c r="BI183">
+        <v>1.34</v>
+      </c>
+      <c r="BJ183">
+        <v>2.78</v>
+      </c>
+      <c r="BK183">
+        <v>1.66</v>
+      </c>
+      <c r="BL183">
+        <v>2.08</v>
+      </c>
+      <c r="BM183">
+        <v>2.07</v>
+      </c>
+      <c r="BN183">
+        <v>1.67</v>
+      </c>
+      <c r="BO183">
+        <v>2.67</v>
+      </c>
+      <c r="BP183">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,7 +538,7 @@
     <t>['29', '90+5']</t>
   </si>
   <si>
-    <t>['82', '90+7', '21']</t>
+    <t>['21', '82', '90+7']</t>
   </si>
   <si>
     <t>['19', '47', '90+2']</t>
@@ -565,7 +565,7 @@
     <t>['32', '71']</t>
   </si>
   <si>
-    <t>['62', '31']</t>
+    <t>['31', '62']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -595,7 +595,7 @@
     <t>['49']</t>
   </si>
   <si>
-    <t>['45', '90+2', '71']</t>
+    <t>['45', '71', '90+2']</t>
   </si>
   <si>
     <t>['41', '47']</t>
@@ -607,10 +607,10 @@
     <t>['46']</t>
   </si>
   <si>
-    <t>['20', '9', '57', '84']</t>
+    <t>['9', '20', '57', '84']</t>
   </si>
   <si>
-    <t>['74', '29', '35']</t>
+    <t>['29', '35', '74']</t>
   </si>
   <si>
     <t>['18']</t>
@@ -625,25 +625,25 @@
     <t>['72']</t>
   </si>
   <si>
-    <t>['81', '55', '67']</t>
+    <t>['55', '67', '81']</t>
   </si>
   <si>
     <t>['3', '52', '60']</t>
   </si>
   <si>
-    <t>['87', '90+11', '67']</t>
+    <t>['67', '87', '90+11']</t>
   </si>
   <si>
     <t>['19', '47']</t>
   </si>
   <si>
-    <t>['11', '40', '36', '72']</t>
+    <t>['11', '36', '40', '72']</t>
   </si>
   <si>
     <t>['21']</t>
   </si>
   <si>
-    <t>['85', '50', '45+6']</t>
+    <t>['45+6', '50', '85']</t>
   </si>
   <si>
     <t>['53']</t>
@@ -652,7 +652,16 @@
     <t>['29', '45+2']</t>
   </si>
   <si>
-    <t>['37', '66', '54', '51']</t>
+    <t>['37', '51', '54', '66']</t>
+  </si>
+  <si>
+    <t>['28', '55']</t>
+  </si>
+  <si>
+    <t>['53', '90+7']</t>
+  </si>
+  <si>
+    <t>['9', '13', '39', '45+2', '88']</t>
   </si>
   <si>
     <t>['33', '72']</t>
@@ -751,7 +760,7 @@
     <t>['-1']</t>
   </si>
   <si>
-    <t>['90+4', '81', '60']</t>
+    <t>['60', '81', '90+4']</t>
   </si>
   <si>
     <t>['1']</t>
@@ -778,7 +787,7 @@
     <t>['78', '90+4']</t>
   </si>
   <si>
-    <t>['90+7', '89']</t>
+    <t>['89', '90+7']</t>
   </si>
   <si>
     <t>['3', '61', '90+9']</t>
@@ -790,7 +799,7 @@
     <t>['17']</t>
   </si>
   <si>
-    <t>['45+11', '27']</t>
+    <t>['27', '45+11']</t>
   </si>
   <si>
     <t>['2']</t>
@@ -802,7 +811,7 @@
     <t>['50']</t>
   </si>
   <si>
-    <t>['44', '28', '31', '69', '87']</t>
+    <t>['28', '31', '44', '69', '87']</t>
   </si>
   <si>
     <t>['87']</t>
@@ -824,6 +833,12 @@
   </si>
   <si>
     <t>['6', '56']</t>
+  </si>
+  <si>
+    <t>['36', '67']</t>
+  </si>
+  <si>
+    <t>['24']</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1522,7 +1537,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ2">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1647,7 +1662,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1725,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1853,7 +1868,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2137,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ5">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2346,7 +2361,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2549,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2677,7 +2692,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2961,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3167,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ10">
         <v>1.11</v>
@@ -3295,7 +3310,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3373,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3501,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3707,7 +3722,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3913,7 +3928,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4737,7 +4752,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4943,7 +4958,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5642,7 +5657,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR22">
         <v>1.69</v>
@@ -5767,7 +5782,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5845,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ23">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR23">
         <v>1.37</v>
@@ -6051,7 +6066,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ24">
         <v>0.8</v>
@@ -6257,7 +6272,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ25">
         <v>1.11</v>
@@ -6385,7 +6400,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6466,7 +6481,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ26">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6672,7 +6687,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR27">
         <v>1.99</v>
@@ -7003,7 +7018,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7415,7 +7430,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7493,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR31">
         <v>2.07</v>
@@ -7908,7 +7923,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ33">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR33">
         <v>1.59</v>
@@ -8114,7 +8129,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR34">
         <v>2.24</v>
@@ -8523,7 +8538,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>1.78</v>
@@ -8651,7 +8666,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9347,7 +9362,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9553,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
         <v>0.7</v>
@@ -9681,7 +9696,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9762,7 +9777,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR42">
         <v>2.49</v>
@@ -10174,7 +10189,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ44">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR44">
         <v>1.73</v>
@@ -10377,7 +10392,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ45">
         <v>0.8</v>
@@ -10583,7 +10598,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ46">
         <v>0.67</v>
@@ -10917,7 +10932,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11123,7 +11138,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11201,7 +11216,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ49">
         <v>0.6</v>
@@ -11535,7 +11550,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -12028,7 +12043,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ53">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR53">
         <v>1.06</v>
@@ -12231,7 +12246,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12437,7 +12452,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ55">
         <v>1.11</v>
@@ -12771,7 +12786,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12852,7 +12867,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ57">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13595,7 +13610,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13676,7 +13691,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ61">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -13882,7 +13897,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ62">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14085,7 +14100,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ63">
         <v>0.78</v>
@@ -14625,7 +14640,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14831,7 +14846,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -15037,7 +15052,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15118,7 +15133,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15243,7 +15258,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15530,7 +15545,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ70">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR70">
         <v>1.26</v>
@@ -15655,7 +15670,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15733,7 +15748,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -16354,7 +16369,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ74">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR74">
         <v>1.6</v>
@@ -16560,7 +16575,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -16685,7 +16700,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16969,7 +16984,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17381,7 +17396,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ79">
         <v>1.78</v>
@@ -17587,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR80">
         <v>1.86</v>
@@ -17793,7 +17808,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ81">
         <v>0.67</v>
@@ -18208,7 +18223,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ83">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR83">
         <v>1.64</v>
@@ -18539,7 +18554,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18617,10 +18632,10 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ85">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR85">
         <v>1.73</v>
@@ -19157,7 +19172,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19650,7 +19665,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ90">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR90">
         <v>1.68</v>
@@ -19775,7 +19790,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19853,7 +19868,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>0.78</v>
@@ -19981,7 +19996,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20062,7 +20077,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ92">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20187,7 +20202,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20471,7 +20486,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20599,7 +20614,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20677,7 +20692,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ95">
         <v>1.78</v>
@@ -20805,7 +20820,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21092,7 +21107,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ97">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR97">
         <v>1.76</v>
@@ -21501,7 +21516,7 @@
         <v>0</v>
       </c>
       <c r="AP99">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>0.67</v>
@@ -21710,7 +21725,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ100">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR100">
         <v>1.63</v>
@@ -21913,7 +21928,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ101">
         <v>1.33</v>
@@ -22328,7 +22343,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ103">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR103">
         <v>2.14</v>
@@ -22659,7 +22674,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22737,7 +22752,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
         <v>0.7</v>
@@ -22943,7 +22958,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ106">
         <v>0.6</v>
@@ -23277,7 +23292,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23770,7 +23785,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ110">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR110">
         <v>2.01</v>
@@ -23976,7 +23991,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -24101,7 +24116,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24385,10 +24400,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ113">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR113">
         <v>1.9</v>
@@ -24719,7 +24734,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24925,7 +24940,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25209,7 +25224,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ117">
         <v>1.5</v>
@@ -25543,7 +25558,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25624,7 +25639,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ119">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR119">
         <v>1.99</v>
@@ -25955,7 +25970,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26033,7 +26048,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26242,7 +26257,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR122">
         <v>1.2</v>
@@ -26445,7 +26460,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
         <v>1.33</v>
@@ -26573,7 +26588,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26651,10 +26666,10 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ124">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR124">
         <v>1.84</v>
@@ -27269,7 +27284,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ127">
         <v>1</v>
@@ -27475,7 +27490,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ128">
         <v>0.3</v>
@@ -27684,7 +27699,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ129">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR129">
         <v>1.61</v>
@@ -28015,7 +28030,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28096,7 +28111,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ131">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR131">
         <v>1.55</v>
@@ -28221,7 +28236,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28427,7 +28442,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28839,7 +28854,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29123,7 +29138,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
         <v>0.8</v>
@@ -29251,7 +29266,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29538,7 +29553,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ138">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR138">
         <v>1.83</v>
@@ -29663,7 +29678,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q139">
         <v>3.02</v>
@@ -29947,7 +29962,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ140">
         <v>0.7</v>
@@ -30156,7 +30171,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ141">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR141">
         <v>1.78</v>
@@ -30359,7 +30374,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ142">
         <v>0.6</v>
@@ -30565,7 +30580,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ143">
         <v>0.3</v>
@@ -30977,7 +30992,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ145">
         <v>1</v>
@@ -31186,7 +31201,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ146">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR146">
         <v>1.55</v>
@@ -31311,7 +31326,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31392,7 +31407,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ147">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR147">
         <v>1.83</v>
@@ -31723,7 +31738,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31804,7 +31819,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ149">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR149">
         <v>1.71</v>
@@ -31929,7 +31944,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32007,10 +32022,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR150">
         <v>1.79</v>
@@ -32959,7 +32974,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33037,7 +33052,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ155">
         <v>0.78</v>
@@ -34276,7 +34291,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ161">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR161">
         <v>1.76</v>
@@ -34401,7 +34416,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34607,7 +34622,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34813,7 +34828,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -34891,7 +34906,7 @@
         <v>0.86</v>
       </c>
       <c r="AP164">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ164">
         <v>1.33</v>
@@ -35019,7 +35034,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35100,7 +35115,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ165">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR165">
         <v>1.86</v>
@@ -35225,7 +35240,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35431,7 +35446,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35509,7 +35524,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AQ167">
         <v>1</v>
@@ -35637,7 +35652,7 @@
         <v>202</v>
       </c>
       <c r="P168" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35715,10 +35730,10 @@
         <v>0.88</v>
       </c>
       <c r="AP168">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ168">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR168">
         <v>1.94</v>
@@ -35843,7 +35858,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -35921,10 +35936,10 @@
         <v>1.43</v>
       </c>
       <c r="AP169">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ169">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR169">
         <v>2.17</v>
@@ -36130,7 +36145,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ170">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR170">
         <v>1.48</v>
@@ -36255,7 +36270,7 @@
         <v>97</v>
       </c>
       <c r="P171" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q171">
         <v>2.4</v>
@@ -36333,10 +36348,10 @@
         <v>0.88</v>
       </c>
       <c r="AP171">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ171">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR171">
         <v>1.79</v>
@@ -36873,7 +36888,7 @@
         <v>199</v>
       </c>
       <c r="P174" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37285,7 +37300,7 @@
         <v>207</v>
       </c>
       <c r="P176" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q176">
         <v>2.8</v>
@@ -37697,7 +37712,7 @@
         <v>209</v>
       </c>
       <c r="P178" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q178">
         <v>2.93</v>
@@ -37903,7 +37918,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q179">
         <v>3.1</v>
@@ -38109,7 +38124,7 @@
         <v>97</v>
       </c>
       <c r="P180" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q180">
         <v>3.55</v>
@@ -38884,6 +38899,1242 @@
       </c>
       <c r="BP183">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="184" spans="1:68">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>7841221</v>
+      </c>
+      <c r="C184" t="s">
+        <v>68</v>
+      </c>
+      <c r="D184" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45865.66666666666</v>
+      </c>
+      <c r="F184">
+        <v>19</v>
+      </c>
+      <c r="G184" t="s">
+        <v>77</v>
+      </c>
+      <c r="H184" t="s">
+        <v>83</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184">
+        <v>2</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>3</v>
+      </c>
+      <c r="O184" t="s">
+        <v>213</v>
+      </c>
+      <c r="P184" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q184">
+        <v>2.95</v>
+      </c>
+      <c r="R184">
+        <v>1.83</v>
+      </c>
+      <c r="S184">
+        <v>4.33</v>
+      </c>
+      <c r="T184">
+        <v>1.57</v>
+      </c>
+      <c r="U184">
+        <v>2.44</v>
+      </c>
+      <c r="V184">
+        <v>3.66</v>
+      </c>
+      <c r="W184">
+        <v>1.22</v>
+      </c>
+      <c r="X184">
+        <v>11</v>
+      </c>
+      <c r="Y184">
+        <v>1.02</v>
+      </c>
+      <c r="Z184">
+        <v>2.24</v>
+      </c>
+      <c r="AA184">
+        <v>2.95</v>
+      </c>
+      <c r="AB184">
+        <v>3.55</v>
+      </c>
+      <c r="AC184">
+        <v>1.12</v>
+      </c>
+      <c r="AD184">
+        <v>6</v>
+      </c>
+      <c r="AE184">
+        <v>1.5</v>
+      </c>
+      <c r="AF184">
+        <v>2.55</v>
+      </c>
+      <c r="AG184">
+        <v>2.73</v>
+      </c>
+      <c r="AH184">
+        <v>1.41</v>
+      </c>
+      <c r="AI184">
+        <v>2.1</v>
+      </c>
+      <c r="AJ184">
+        <v>1.65</v>
+      </c>
+      <c r="AK184">
+        <v>1.3</v>
+      </c>
+      <c r="AL184">
+        <v>1.37</v>
+      </c>
+      <c r="AM184">
+        <v>1.62</v>
+      </c>
+      <c r="AN184">
+        <v>1.88</v>
+      </c>
+      <c r="AO184">
+        <v>0.89</v>
+      </c>
+      <c r="AP184">
+        <v>2</v>
+      </c>
+      <c r="AQ184">
+        <v>0.8</v>
+      </c>
+      <c r="AR184">
+        <v>2.1</v>
+      </c>
+      <c r="AS184">
+        <v>1.33</v>
+      </c>
+      <c r="AT184">
+        <v>3.43</v>
+      </c>
+      <c r="AU184">
+        <v>7</v>
+      </c>
+      <c r="AV184">
+        <v>5</v>
+      </c>
+      <c r="AW184">
+        <v>10</v>
+      </c>
+      <c r="AX184">
+        <v>7</v>
+      </c>
+      <c r="AY184">
+        <v>17</v>
+      </c>
+      <c r="AZ184">
+        <v>12</v>
+      </c>
+      <c r="BA184">
+        <v>4</v>
+      </c>
+      <c r="BB184">
+        <v>6</v>
+      </c>
+      <c r="BC184">
+        <v>10</v>
+      </c>
+      <c r="BD184">
+        <v>1.54</v>
+      </c>
+      <c r="BE184">
+        <v>8</v>
+      </c>
+      <c r="BF184">
+        <v>3.26</v>
+      </c>
+      <c r="BG184">
+        <v>1.22</v>
+      </c>
+      <c r="BH184">
+        <v>3.8</v>
+      </c>
+      <c r="BI184">
+        <v>1.36</v>
+      </c>
+      <c r="BJ184">
+        <v>2.95</v>
+      </c>
+      <c r="BK184">
+        <v>1.59</v>
+      </c>
+      <c r="BL184">
+        <v>2.2</v>
+      </c>
+      <c r="BM184">
+        <v>1.95</v>
+      </c>
+      <c r="BN184">
+        <v>1.76</v>
+      </c>
+      <c r="BO184">
+        <v>2.54</v>
+      </c>
+      <c r="BP184">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="185" spans="1:68">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>7841212</v>
+      </c>
+      <c r="C185" t="s">
+        <v>68</v>
+      </c>
+      <c r="D185" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45865.66666666666</v>
+      </c>
+      <c r="F185">
+        <v>19</v>
+      </c>
+      <c r="G185" t="s">
+        <v>73</v>
+      </c>
+      <c r="H185" t="s">
+        <v>84</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="M185">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>2</v>
+      </c>
+      <c r="O185" t="s">
+        <v>178</v>
+      </c>
+      <c r="P185" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q185">
+        <v>2.05</v>
+      </c>
+      <c r="R185">
+        <v>1.98</v>
+      </c>
+      <c r="S185">
+        <v>7.99</v>
+      </c>
+      <c r="T185">
+        <v>1.48</v>
+      </c>
+      <c r="U185">
+        <v>2.55</v>
+      </c>
+      <c r="V185">
+        <v>3.34</v>
+      </c>
+      <c r="W185">
+        <v>1.3</v>
+      </c>
+      <c r="X185">
+        <v>9.5</v>
+      </c>
+      <c r="Y185">
+        <v>1.05</v>
+      </c>
+      <c r="Z185">
+        <v>1.48</v>
+      </c>
+      <c r="AA185">
+        <v>3.6</v>
+      </c>
+      <c r="AB185">
+        <v>6</v>
+      </c>
+      <c r="AC185">
+        <v>1.03</v>
+      </c>
+      <c r="AD185">
+        <v>9.5</v>
+      </c>
+      <c r="AE185">
+        <v>1.44</v>
+      </c>
+      <c r="AF185">
+        <v>2.63</v>
+      </c>
+      <c r="AG185">
+        <v>2.3</v>
+      </c>
+      <c r="AH185">
+        <v>1.57</v>
+      </c>
+      <c r="AI185">
+        <v>2.55</v>
+      </c>
+      <c r="AJ185">
+        <v>1.5</v>
+      </c>
+      <c r="AK185">
+        <v>1.24</v>
+      </c>
+      <c r="AL185">
+        <v>1.25</v>
+      </c>
+      <c r="AM185">
+        <v>2.63</v>
+      </c>
+      <c r="AN185">
+        <v>2.38</v>
+      </c>
+      <c r="AO185">
+        <v>0.25</v>
+      </c>
+      <c r="AP185">
+        <v>2.22</v>
+      </c>
+      <c r="AQ185">
+        <v>0.33</v>
+      </c>
+      <c r="AR185">
+        <v>1.46</v>
+      </c>
+      <c r="AS185">
+        <v>1.21</v>
+      </c>
+      <c r="AT185">
+        <v>2.67</v>
+      </c>
+      <c r="AU185">
+        <v>5</v>
+      </c>
+      <c r="AV185">
+        <v>3</v>
+      </c>
+      <c r="AW185">
+        <v>6</v>
+      </c>
+      <c r="AX185">
+        <v>4</v>
+      </c>
+      <c r="AY185">
+        <v>11</v>
+      </c>
+      <c r="AZ185">
+        <v>7</v>
+      </c>
+      <c r="BA185">
+        <v>8</v>
+      </c>
+      <c r="BB185">
+        <v>2</v>
+      </c>
+      <c r="BC185">
+        <v>10</v>
+      </c>
+      <c r="BD185">
+        <v>1.24</v>
+      </c>
+      <c r="BE185">
+        <v>8</v>
+      </c>
+      <c r="BF185">
+        <v>3.9</v>
+      </c>
+      <c r="BG185">
+        <v>1.13</v>
+      </c>
+      <c r="BH185">
+        <v>4</v>
+      </c>
+      <c r="BI185">
+        <v>1.35</v>
+      </c>
+      <c r="BJ185">
+        <v>2.91</v>
+      </c>
+      <c r="BK185">
+        <v>1.56</v>
+      </c>
+      <c r="BL185">
+        <v>2.17</v>
+      </c>
+      <c r="BM185">
+        <v>1.91</v>
+      </c>
+      <c r="BN185">
+        <v>1.74</v>
+      </c>
+      <c r="BO185">
+        <v>2.33</v>
+      </c>
+      <c r="BP185">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7841219</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45865.77083333334</v>
+      </c>
+      <c r="F186">
+        <v>19</v>
+      </c>
+      <c r="G186" t="s">
+        <v>75</v>
+      </c>
+      <c r="H186" t="s">
+        <v>80</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>2</v>
+      </c>
+      <c r="M186">
+        <v>2</v>
+      </c>
+      <c r="N186">
+        <v>4</v>
+      </c>
+      <c r="O186" t="s">
+        <v>214</v>
+      </c>
+      <c r="P186" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q186">
+        <v>3.34</v>
+      </c>
+      <c r="R186">
+        <v>1.95</v>
+      </c>
+      <c r="S186">
+        <v>3.45</v>
+      </c>
+      <c r="T186">
+        <v>1.5</v>
+      </c>
+      <c r="U186">
+        <v>2.5</v>
+      </c>
+      <c r="V186">
+        <v>3.3</v>
+      </c>
+      <c r="W186">
+        <v>1.28</v>
+      </c>
+      <c r="X186">
+        <v>8.5</v>
+      </c>
+      <c r="Y186">
+        <v>1.04</v>
+      </c>
+      <c r="Z186">
+        <v>2.29</v>
+      </c>
+      <c r="AA186">
+        <v>3</v>
+      </c>
+      <c r="AB186">
+        <v>3.1</v>
+      </c>
+      <c r="AC186">
+        <v>1.1</v>
+      </c>
+      <c r="AD186">
+        <v>7.43</v>
+      </c>
+      <c r="AE186">
+        <v>1.44</v>
+      </c>
+      <c r="AF186">
+        <v>2.7</v>
+      </c>
+      <c r="AG186">
+        <v>2.3</v>
+      </c>
+      <c r="AH186">
+        <v>1.55</v>
+      </c>
+      <c r="AI186">
+        <v>1.95</v>
+      </c>
+      <c r="AJ186">
+        <v>1.7</v>
+      </c>
+      <c r="AK186">
+        <v>1.36</v>
+      </c>
+      <c r="AL186">
+        <v>1.35</v>
+      </c>
+      <c r="AM186">
+        <v>1.47</v>
+      </c>
+      <c r="AN186">
+        <v>1.56</v>
+      </c>
+      <c r="AO186">
+        <v>1.25</v>
+      </c>
+      <c r="AP186">
+        <v>1.5</v>
+      </c>
+      <c r="AQ186">
+        <v>1.22</v>
+      </c>
+      <c r="AR186">
+        <v>1.92</v>
+      </c>
+      <c r="AS186">
+        <v>1.4</v>
+      </c>
+      <c r="AT186">
+        <v>3.32</v>
+      </c>
+      <c r="AU186">
+        <v>4</v>
+      </c>
+      <c r="AV186">
+        <v>6</v>
+      </c>
+      <c r="AW186">
+        <v>6</v>
+      </c>
+      <c r="AX186">
+        <v>4</v>
+      </c>
+      <c r="AY186">
+        <v>10</v>
+      </c>
+      <c r="AZ186">
+        <v>10</v>
+      </c>
+      <c r="BA186">
+        <v>4</v>
+      </c>
+      <c r="BB186">
+        <v>2</v>
+      </c>
+      <c r="BC186">
+        <v>6</v>
+      </c>
+      <c r="BD186">
+        <v>1.9</v>
+      </c>
+      <c r="BE186">
+        <v>6.75</v>
+      </c>
+      <c r="BF186">
+        <v>2.23</v>
+      </c>
+      <c r="BG186">
+        <v>1.22</v>
+      </c>
+      <c r="BH186">
+        <v>4.22</v>
+      </c>
+      <c r="BI186">
+        <v>1.34</v>
+      </c>
+      <c r="BJ186">
+        <v>2.92</v>
+      </c>
+      <c r="BK186">
+        <v>1.65</v>
+      </c>
+      <c r="BL186">
+        <v>2.1</v>
+      </c>
+      <c r="BM186">
+        <v>2</v>
+      </c>
+      <c r="BN186">
+        <v>1.72</v>
+      </c>
+      <c r="BO186">
+        <v>2.56</v>
+      </c>
+      <c r="BP186">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7841214</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45865.79166666666</v>
+      </c>
+      <c r="F187">
+        <v>19</v>
+      </c>
+      <c r="G187" t="s">
+        <v>79</v>
+      </c>
+      <c r="H187" t="s">
+        <v>82</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187" t="s">
+        <v>97</v>
+      </c>
+      <c r="P187" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q187">
+        <v>2.69</v>
+      </c>
+      <c r="R187">
+        <v>1.97</v>
+      </c>
+      <c r="S187">
+        <v>4.8</v>
+      </c>
+      <c r="T187">
+        <v>1.5</v>
+      </c>
+      <c r="U187">
+        <v>2.45</v>
+      </c>
+      <c r="V187">
+        <v>3.3</v>
+      </c>
+      <c r="W187">
+        <v>1.29</v>
+      </c>
+      <c r="X187">
+        <v>9</v>
+      </c>
+      <c r="Y187">
+        <v>1.03</v>
+      </c>
+      <c r="Z187">
+        <v>2.1</v>
+      </c>
+      <c r="AA187">
+        <v>2.93</v>
+      </c>
+      <c r="AB187">
+        <v>3.3</v>
+      </c>
+      <c r="AC187">
+        <v>1.1</v>
+      </c>
+      <c r="AD187">
+        <v>6.5</v>
+      </c>
+      <c r="AE187">
+        <v>1.5</v>
+      </c>
+      <c r="AF187">
+        <v>2.6</v>
+      </c>
+      <c r="AG187">
+        <v>2.3</v>
+      </c>
+      <c r="AH187">
+        <v>1.5</v>
+      </c>
+      <c r="AI187">
+        <v>2.14</v>
+      </c>
+      <c r="AJ187">
+        <v>1.7</v>
+      </c>
+      <c r="AK187">
+        <v>1.36</v>
+      </c>
+      <c r="AL187">
+        <v>1.32</v>
+      </c>
+      <c r="AM187">
+        <v>1.75</v>
+      </c>
+      <c r="AN187">
+        <v>1.67</v>
+      </c>
+      <c r="AO187">
+        <v>1.11</v>
+      </c>
+      <c r="AP187">
+        <v>1.6</v>
+      </c>
+      <c r="AQ187">
+        <v>1.1</v>
+      </c>
+      <c r="AR187">
+        <v>1.87</v>
+      </c>
+      <c r="AS187">
+        <v>1.45</v>
+      </c>
+      <c r="AT187">
+        <v>3.32</v>
+      </c>
+      <c r="AU187">
+        <v>4</v>
+      </c>
+      <c r="AV187">
+        <v>3</v>
+      </c>
+      <c r="AW187">
+        <v>11</v>
+      </c>
+      <c r="AX187">
+        <v>5</v>
+      </c>
+      <c r="AY187">
+        <v>15</v>
+      </c>
+      <c r="AZ187">
+        <v>8</v>
+      </c>
+      <c r="BA187">
+        <v>3</v>
+      </c>
+      <c r="BB187">
+        <v>3</v>
+      </c>
+      <c r="BC187">
+        <v>6</v>
+      </c>
+      <c r="BD187">
+        <v>1.42</v>
+      </c>
+      <c r="BE187">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF187">
+        <v>3.4</v>
+      </c>
+      <c r="BG187">
+        <v>1.2</v>
+      </c>
+      <c r="BH187">
+        <v>3.9</v>
+      </c>
+      <c r="BI187">
+        <v>1.35</v>
+      </c>
+      <c r="BJ187">
+        <v>2.9</v>
+      </c>
+      <c r="BK187">
+        <v>1.83</v>
+      </c>
+      <c r="BL187">
+        <v>2.2</v>
+      </c>
+      <c r="BM187">
+        <v>1.91</v>
+      </c>
+      <c r="BN187">
+        <v>1.75</v>
+      </c>
+      <c r="BO187">
+        <v>2.35</v>
+      </c>
+      <c r="BP187">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7841216</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45866.79166666666</v>
+      </c>
+      <c r="F188">
+        <v>19</v>
+      </c>
+      <c r="G188" t="s">
+        <v>78</v>
+      </c>
+      <c r="H188" t="s">
+        <v>89</v>
+      </c>
+      <c r="I188">
+        <v>4</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>4</v>
+      </c>
+      <c r="L188">
+        <v>5</v>
+      </c>
+      <c r="M188">
+        <v>0</v>
+      </c>
+      <c r="N188">
+        <v>5</v>
+      </c>
+      <c r="O188" t="s">
+        <v>215</v>
+      </c>
+      <c r="P188" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q188">
+        <v>2.47</v>
+      </c>
+      <c r="R188">
+        <v>1.94</v>
+      </c>
+      <c r="S188">
+        <v>5.5</v>
+      </c>
+      <c r="T188">
+        <v>1.5</v>
+      </c>
+      <c r="U188">
+        <v>2.5</v>
+      </c>
+      <c r="V188">
+        <v>3.4</v>
+      </c>
+      <c r="W188">
+        <v>1.26</v>
+      </c>
+      <c r="X188">
+        <v>10</v>
+      </c>
+      <c r="Y188">
+        <v>1.05</v>
+      </c>
+      <c r="Z188">
+        <v>1.67</v>
+      </c>
+      <c r="AA188">
+        <v>3.48</v>
+      </c>
+      <c r="AB188">
+        <v>6.1</v>
+      </c>
+      <c r="AC188">
+        <v>1.1</v>
+      </c>
+      <c r="AD188">
+        <v>6.5</v>
+      </c>
+      <c r="AE188">
+        <v>1.5</v>
+      </c>
+      <c r="AF188">
+        <v>2.55</v>
+      </c>
+      <c r="AG188">
+        <v>2.55</v>
+      </c>
+      <c r="AH188">
+        <v>1.5</v>
+      </c>
+      <c r="AI188">
+        <v>2.4</v>
+      </c>
+      <c r="AJ188">
+        <v>1.53</v>
+      </c>
+      <c r="AK188">
+        <v>1.32</v>
+      </c>
+      <c r="AL188">
+        <v>1.3</v>
+      </c>
+      <c r="AM188">
+        <v>2.33</v>
+      </c>
+      <c r="AN188">
+        <v>1.78</v>
+      </c>
+      <c r="AO188">
+        <v>0.88</v>
+      </c>
+      <c r="AP188">
+        <v>1.9</v>
+      </c>
+      <c r="AQ188">
+        <v>0.78</v>
+      </c>
+      <c r="AR188">
+        <v>1.95</v>
+      </c>
+      <c r="AS188">
+        <v>1.27</v>
+      </c>
+      <c r="AT188">
+        <v>3.22</v>
+      </c>
+      <c r="AU188">
+        <v>9</v>
+      </c>
+      <c r="AV188">
+        <v>3</v>
+      </c>
+      <c r="AW188">
+        <v>4</v>
+      </c>
+      <c r="AX188">
+        <v>11</v>
+      </c>
+      <c r="AY188">
+        <v>13</v>
+      </c>
+      <c r="AZ188">
+        <v>14</v>
+      </c>
+      <c r="BA188">
+        <v>3</v>
+      </c>
+      <c r="BB188">
+        <v>4</v>
+      </c>
+      <c r="BC188">
+        <v>7</v>
+      </c>
+      <c r="BD188">
+        <v>1.49</v>
+      </c>
+      <c r="BE188">
+        <v>6.75</v>
+      </c>
+      <c r="BF188">
+        <v>3.66</v>
+      </c>
+      <c r="BG188">
+        <v>1.19</v>
+      </c>
+      <c r="BH188">
+        <v>4</v>
+      </c>
+      <c r="BI188">
+        <v>1.33</v>
+      </c>
+      <c r="BJ188">
+        <v>3</v>
+      </c>
+      <c r="BK188">
+        <v>1.57</v>
+      </c>
+      <c r="BL188">
+        <v>2.25</v>
+      </c>
+      <c r="BM188">
+        <v>1.91</v>
+      </c>
+      <c r="BN188">
+        <v>1.8</v>
+      </c>
+      <c r="BO188">
+        <v>2.43</v>
+      </c>
+      <c r="BP188">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7841215</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45866.89583333334</v>
+      </c>
+      <c r="F189">
+        <v>19</v>
+      </c>
+      <c r="G189" t="s">
+        <v>71</v>
+      </c>
+      <c r="H189" t="s">
+        <v>87</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>2</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>2</v>
+      </c>
+      <c r="O189" t="s">
+        <v>111</v>
+      </c>
+      <c r="P189" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q189">
+        <v>2.91</v>
+      </c>
+      <c r="R189">
+        <v>1.9</v>
+      </c>
+      <c r="S189">
+        <v>3.56</v>
+      </c>
+      <c r="T189">
+        <v>1.52</v>
+      </c>
+      <c r="U189">
+        <v>2.38</v>
+      </c>
+      <c r="V189">
+        <v>3.2</v>
+      </c>
+      <c r="W189">
+        <v>1.29</v>
+      </c>
+      <c r="X189">
+        <v>10</v>
+      </c>
+      <c r="Y189">
+        <v>1.04</v>
+      </c>
+      <c r="Z189">
+        <v>2.3</v>
+      </c>
+      <c r="AA189">
+        <v>2.98</v>
+      </c>
+      <c r="AB189">
+        <v>3.2</v>
+      </c>
+      <c r="AC189">
+        <v>1.04</v>
+      </c>
+      <c r="AD189">
+        <v>7.1</v>
+      </c>
+      <c r="AE189">
+        <v>1.44</v>
+      </c>
+      <c r="AF189">
+        <v>2.6</v>
+      </c>
+      <c r="AG189">
+        <v>2.3</v>
+      </c>
+      <c r="AH189">
+        <v>1.51</v>
+      </c>
+      <c r="AI189">
+        <v>2.12</v>
+      </c>
+      <c r="AJ189">
+        <v>1.75</v>
+      </c>
+      <c r="AK189">
+        <v>1.31</v>
+      </c>
+      <c r="AL189">
+        <v>1.33</v>
+      </c>
+      <c r="AM189">
+        <v>1.52</v>
+      </c>
+      <c r="AN189">
+        <v>1.13</v>
+      </c>
+      <c r="AO189">
+        <v>1.33</v>
+      </c>
+      <c r="AP189">
+        <v>1.11</v>
+      </c>
+      <c r="AQ189">
+        <v>1.3</v>
+      </c>
+      <c r="AR189">
+        <v>1.84</v>
+      </c>
+      <c r="AS189">
+        <v>1.31</v>
+      </c>
+      <c r="AT189">
+        <v>3.15</v>
+      </c>
+      <c r="AU189">
+        <v>6</v>
+      </c>
+      <c r="AV189">
+        <v>7</v>
+      </c>
+      <c r="AW189">
+        <v>11</v>
+      </c>
+      <c r="AX189">
+        <v>8</v>
+      </c>
+      <c r="AY189">
+        <v>17</v>
+      </c>
+      <c r="AZ189">
+        <v>15</v>
+      </c>
+      <c r="BA189">
+        <v>6</v>
+      </c>
+      <c r="BB189">
+        <v>6</v>
+      </c>
+      <c r="BC189">
+        <v>12</v>
+      </c>
+      <c r="BD189">
+        <v>1.75</v>
+      </c>
+      <c r="BE189">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF189">
+        <v>2.72</v>
+      </c>
+      <c r="BG189">
+        <v>1.1</v>
+      </c>
+      <c r="BH189">
+        <v>4.8</v>
+      </c>
+      <c r="BI189">
+        <v>1.22</v>
+      </c>
+      <c r="BJ189">
+        <v>3.7</v>
+      </c>
+      <c r="BK189">
+        <v>1.66</v>
+      </c>
+      <c r="BL189">
+        <v>2.55</v>
+      </c>
+      <c r="BM189">
+        <v>1.73</v>
+      </c>
+      <c r="BN189">
+        <v>1.93</v>
+      </c>
+      <c r="BO189">
+        <v>2.2</v>
+      </c>
+      <c r="BP189">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.8</v>
@@ -2440,7 +2440,7 @@
         <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.3</v>
@@ -9198,7 +9198,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR40" t="n">
         <v>1.82</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ43" t="n">
         <v>1</v>
@@ -13558,7 +13558,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR60" t="n">
         <v>1.78</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.3</v>
@@ -16392,7 +16392,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR73" t="n">
         <v>1.75</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.5</v>
@@ -21406,7 +21406,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR96" t="n">
         <v>1.76</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.8</v>
@@ -26202,7 +26202,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR118" t="n">
         <v>2</v>
@@ -26417,7 +26417,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.33</v>
@@ -28164,7 +28164,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR127" t="n">
         <v>1.46</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -31870,7 +31870,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR144" t="n">
         <v>1.33</v>
@@ -34701,7 +34701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.7</v>
@@ -36666,7 +36666,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR166" t="n">
         <v>1.5</v>
@@ -41474,22 +41474,22 @@
         <v>3.22</v>
       </c>
       <c r="AU188" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV188" t="n">
         <v>3</v>
       </c>
       <c r="AW188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX188" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY188" t="n">
         <v>11</v>
       </c>
-      <c r="AY188" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ188" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA188" t="n">
         <v>3</v>
@@ -41692,22 +41692,22 @@
         <v>3.15</v>
       </c>
       <c r="AU189" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV189" t="n">
         <v>7</v>
       </c>
       <c r="AW189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY189" t="n">
         <v>11</v>
       </c>
-      <c r="AX189" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY189" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ189" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA189" t="n">
         <v>6</v>
@@ -41756,6 +41756,224 @@
       </c>
       <c r="BP189" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>7841217</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45867.85416666666</v>
+      </c>
+      <c r="F190" t="n">
+        <v>19</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>1</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R190" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S190" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V190" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X190" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.33</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.8</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.5</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.7</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.3</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.3</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.33</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.9</v>
@@ -41474,22 +41474,22 @@
         <v>3.22</v>
       </c>
       <c r="AU188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV188" t="n">
         <v>3</v>
       </c>
       <c r="AW188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX188" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY188" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ188" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA188" t="n">
         <v>3</v>
@@ -41692,22 +41692,22 @@
         <v>3.15</v>
       </c>
       <c r="AU189" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV189" t="n">
         <v>7</v>
       </c>
       <c r="AW189" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AX189" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY189" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ189" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA189" t="n">
         <v>6</v>
@@ -41910,22 +41910,22 @@
         <v>3.55</v>
       </c>
       <c r="AU190" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV190" t="n">
         <v>0</v>
       </c>
       <c r="AW190" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX190" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY190" t="n">
         <v>9</v>
       </c>
       <c r="AZ190" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA190" t="n">
         <v>1</v>
@@ -41974,6 +41974,224 @@
       </c>
       <c r="BP190" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>7841213</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45867.89930555555</v>
+      </c>
+      <c r="F191" t="n">
+        <v>19</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>1</v>
+      </c>
+      <c r="N191" t="n">
+        <v>2</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S191" t="n">
+        <v>6</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X191" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -42029,7 +42029,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3530,7 +3530,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15" t="n">
         <v>1</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.78</v>
@@ -8980,7 +8980,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR39" t="n">
         <v>1.19</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.1</v>
@@ -11814,7 +11814,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR52" t="n">
         <v>2.26</v>
@@ -14430,7 +14430,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR64" t="n">
         <v>1.84</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.22</v>
@@ -19662,7 +19662,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR88" t="n">
         <v>2.01</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.11</v>
@@ -22714,7 +22714,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR102" t="n">
         <v>1.3</v>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.67</v>
@@ -25984,7 +25984,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR117" t="n">
         <v>1.9</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.78</v>
@@ -29908,7 +29908,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR135" t="n">
         <v>1.89</v>
@@ -33614,7 +33614,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR152" t="n">
         <v>1.82</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.8</v>
@@ -38410,7 +38410,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AR174" t="n">
         <v>1.7</v>
@@ -38625,7 +38625,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.6</v>
@@ -42192,6 +42192,224 @@
       </c>
       <c r="BP191" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>7841223</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45869.89930555555</v>
+      </c>
+      <c r="F192" t="n">
+        <v>20</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="n">
+        <v>3</v>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>2</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['14', '45+2']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S192" t="n">
+        <v>4</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V192" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X192" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3094,7 +3094,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.78</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.67</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
         <v>1</v>
@@ -8762,7 +8762,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR38" t="n">
         <v>1.97</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.64</v>
@@ -9416,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR41" t="n">
         <v>1.74</v>
@@ -11378,7 +11378,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR50" t="n">
         <v>1.55</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.33</v>
@@ -12686,7 +12686,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
         <v>1.78</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.67</v>
@@ -15084,7 +15084,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR67" t="n">
         <v>2.23</v>
@@ -15735,7 +15735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.8</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.78</v>
@@ -17482,7 +17482,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR78" t="n">
         <v>1.76</v>
@@ -18354,7 +18354,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR82" t="n">
         <v>1.86</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.3</v>
@@ -21621,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.22</v>
@@ -22496,7 +22496,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR101" t="n">
         <v>1.81</v>
@@ -23368,7 +23368,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR105" t="n">
         <v>1.85</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.8</v>
@@ -26638,7 +26638,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR120" t="n">
         <v>1.66</v>
@@ -27292,7 +27292,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR123" t="n">
         <v>1.83</v>
@@ -27725,7 +27725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ125" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.11</v>
@@ -30998,7 +30998,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR140" t="n">
         <v>1.87</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.9</v>
@@ -32957,7 +32957,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.1</v>
@@ -33396,7 +33396,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR151" t="n">
         <v>1.53</v>
@@ -34704,7 +34704,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR157" t="n">
         <v>2.02</v>
@@ -35791,7 +35791,7 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.6</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.11</v>
@@ -36230,7 +36230,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR164" t="n">
         <v>1.95</v>
@@ -37971,7 +37971,7 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.78</v>
@@ -38192,7 +38192,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR173" t="n">
         <v>1.9</v>
@@ -39718,7 +39718,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR180" t="n">
         <v>1.42</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -42410,6 +42410,442 @@
       </c>
       <c r="BP192" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>7841225</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45870.79166666666</v>
+      </c>
+      <c r="F193" t="n">
+        <v>20</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" t="n">
+        <v>1</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>2</v>
+      </c>
+      <c r="N193" t="n">
+        <v>2</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>['45+4', '54']</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R193" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S193" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V193" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X193" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>7841227</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>45870.89583333334</v>
+      </c>
+      <c r="F194" t="n">
+        <v>20</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S194" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X194" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP194"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
@@ -938,10 +938,10 @@
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA2" t="n">
         <v>8</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -1156,10 +1156,10 @@
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA3" t="n">
         <v>5</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
         <v>7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>11</v>
@@ -1374,10 +1374,10 @@
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>11</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
         <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA6" t="n">
         <v>3</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>11</v>
@@ -2028,10 +2028,10 @@
         <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>2</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>18</v>
@@ -2246,10 +2246,10 @@
         <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
         <v>11</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
         <v>14</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2682,10 +2682,10 @@
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>4</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
         <v>6</v>
@@ -2900,10 +2900,10 @@
         <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA11" t="n">
         <v>7</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -3118,10 +3118,10 @@
         <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="n">
         <v>7</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
         <v>13</v>
@@ -3336,10 +3336,10 @@
         <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV14" t="n">
         <v>5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6</v>
       </c>
       <c r="AW14" t="n">
         <v>20</v>
@@ -3554,10 +3554,10 @@
         <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3760,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.91</v>
@@ -3978,10 +3978,10 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>9</v>
@@ -3990,10 +3990,10 @@
         <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -4205,13 +4205,13 @@
         <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -4402,7 +4402,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4414,10 +4414,10 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW18" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
         <v>3</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA18" t="n">
         <v>7</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW19" t="n">
         <v>13</v>
@@ -4644,10 +4644,10 @@
         <v>15</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
         <v>7</v>
@@ -4838,7 +4838,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -4850,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4862,10 +4862,10 @@
         <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
         <v>2</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.78</v>
@@ -5068,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
         <v>5</v>
@@ -5080,10 +5080,10 @@
         <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA21" t="n">
         <v>6</v>
@@ -5277,19 +5277,19 @@
         <v>1.22</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AU22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV22" t="n">
         <v>4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>5</v>
       </c>
       <c r="AW22" t="n">
         <v>9</v>
@@ -5298,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="AY22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA22" t="n">
         <v>9</v>
@@ -5495,19 +5495,19 @@
         <v>1.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.22</v>
+        <v>3.95</v>
       </c>
       <c r="AU23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
         <v>11</v>
@@ -5516,10 +5516,10 @@
         <v>3</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>6</v>
@@ -5713,19 +5713,19 @@
         <v>0.8</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
         <v>7</v>
@@ -5734,10 +5734,10 @@
         <v>11</v>
       </c>
       <c r="AY24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>15</v>
       </c>
       <c r="BA24" t="n">
         <v>4</v>
@@ -5931,19 +5931,19 @@
         <v>1.11</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
@@ -5952,10 +5952,10 @@
         <v>2</v>
       </c>
       <c r="AY25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA25" t="n">
         <v>6</v>
@@ -6149,19 +6149,19 @@
         <v>0.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AU26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV26" t="n">
         <v>4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>12</v>
@@ -6170,10 +6170,10 @@
         <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
@@ -6367,19 +6367,19 @@
         <v>1.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW27" t="n">
         <v>16</v>
@@ -6388,10 +6388,10 @@
         <v>1</v>
       </c>
       <c r="AY27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA27" t="n">
         <v>5</v>
@@ -6585,19 +6585,19 @@
         <v>0.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AU28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW28" t="n">
         <v>13</v>
@@ -6606,10 +6606,10 @@
         <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
         <v>4</v>
@@ -6797,25 +6797,25 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="AU29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV29" t="n">
         <v>3</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>4</v>
@@ -6824,10 +6824,10 @@
         <v>14</v>
       </c>
       <c r="AY29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
         <v>3</v>
@@ -7021,19 +7021,19 @@
         <v>0.78</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.04</v>
+        <v>4.76</v>
       </c>
       <c r="AU30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -7042,10 +7042,10 @@
         <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA30" t="n">
         <v>6</v>
@@ -7239,19 +7239,19 @@
         <v>0.33</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW31" t="n">
         <v>8</v>
@@ -7260,10 +7260,10 @@
         <v>5</v>
       </c>
       <c r="AY31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA31" t="n">
         <v>4</v>
@@ -7457,19 +7457,19 @@
         <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AU32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW32" t="n">
         <v>13</v>
@@ -7478,10 +7478,10 @@
         <v>7</v>
       </c>
       <c r="AY32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA32" t="n">
         <v>6</v>
@@ -7675,19 +7675,19 @@
         <v>0.78</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW33" t="n">
         <v>13</v>
@@ -7696,10 +7696,10 @@
         <v>4</v>
       </c>
       <c r="AY33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA33" t="n">
         <v>5</v>
@@ -7893,19 +7893,19 @@
         <v>1.3</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW34" t="n">
         <v>7</v>
@@ -7914,10 +7914,10 @@
         <v>14</v>
       </c>
       <c r="AY34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA34" t="n">
         <v>3</v>
@@ -8111,19 +8111,19 @@
         <v>0.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.49</v>
+        <v>3.22</v>
       </c>
       <c r="AU35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW35" t="n">
         <v>7</v>
@@ -8132,10 +8132,10 @@
         <v>6</v>
       </c>
       <c r="AY35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA35" t="n">
         <v>4</v>
@@ -8326,22 +8326,22 @@
         <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AS36" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.95</v>
+        <v>2.67</v>
       </c>
       <c r="AU36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
         <v>8</v>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="AY36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA36" t="n">
         <v>10</v>
@@ -8541,25 +8541,25 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="AU37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW37" t="n">
         <v>8</v>
@@ -8568,10 +8568,10 @@
         <v>6</v>
       </c>
       <c r="AY37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA37" t="n">
         <v>4</v>
@@ -8765,19 +8765,19 @@
         <v>1.2</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="AU38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW38" t="n">
         <v>18</v>
@@ -8786,10 +8786,10 @@
         <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA38" t="n">
         <v>8</v>
@@ -8983,19 +8983,19 @@
         <v>1.64</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW39" t="n">
         <v>2</v>
@@ -9004,10 +9004,10 @@
         <v>14</v>
       </c>
       <c r="AY39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA39" t="n">
         <v>1</v>
@@ -9201,19 +9201,19 @@
         <v>0.9</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
         <v>10</v>
@@ -9222,10 +9222,10 @@
         <v>12</v>
       </c>
       <c r="AY40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA40" t="n">
         <v>2</v>
@@ -9419,16 +9419,16 @@
         <v>0.91</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV41" t="n">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         <v>11</v>
       </c>
       <c r="AX41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY41" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA41" t="n">
         <v>6</v>
@@ -9637,19 +9637,19 @@
         <v>1.22</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="AU42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW42" t="n">
         <v>12</v>
@@ -9658,10 +9658,10 @@
         <v>8</v>
       </c>
       <c r="AY42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
         <v>7</v>
@@ -9855,19 +9855,19 @@
         <v>1</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AU43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW43" t="n">
         <v>11</v>
@@ -9876,10 +9876,10 @@
         <v>7</v>
       </c>
       <c r="AY43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA43" t="n">
         <v>8</v>
@@ -10073,19 +10073,19 @@
         <v>1.1</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.72</v>
+        <v>3.46</v>
       </c>
       <c r="AU44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW44" t="n">
         <v>11</v>
@@ -10094,10 +10094,10 @@
         <v>12</v>
       </c>
       <c r="AY44" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA44" t="n">
         <v>7</v>
@@ -10291,19 +10291,19 @@
         <v>0.8</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AU45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW45" t="n">
         <v>5</v>
@@ -10312,10 +10312,10 @@
         <v>6</v>
       </c>
       <c r="AY45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA45" t="n">
         <v>5</v>
@@ -10506,22 +10506,22 @@
         <v>1.9</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW46" t="n">
         <v>7</v>
@@ -10530,10 +10530,10 @@
         <v>11</v>
       </c>
       <c r="AY46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>17</v>
       </c>
       <c r="BA46" t="n">
         <v>5</v>
@@ -10727,19 +10727,19 @@
         <v>0.3</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="AU47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW47" t="n">
         <v>3</v>
@@ -10748,10 +10748,10 @@
         <v>11</v>
       </c>
       <c r="AY47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ47" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA47" t="n">
         <v>6</v>
@@ -10939,25 +10939,25 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.78</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.68</v>
+        <v>3.41</v>
       </c>
       <c r="AU48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW48" t="n">
         <v>11</v>
@@ -10966,10 +10966,10 @@
         <v>6</v>
       </c>
       <c r="AY48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA48" t="n">
         <v>7</v>
@@ -11163,19 +11163,19 @@
         <v>0.6</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW49" t="n">
         <v>13</v>
@@ -11184,10 +11184,10 @@
         <v>16</v>
       </c>
       <c r="AY49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA49" t="n">
         <v>8</v>
@@ -11381,19 +11381,19 @@
         <v>0.91</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AU50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW50" t="n">
         <v>10</v>
@@ -11402,10 +11402,10 @@
         <v>11</v>
       </c>
       <c r="AY50" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ50" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA50" t="n">
         <v>8</v>
@@ -11593,25 +11593,25 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW51" t="n">
         <v>11</v>
@@ -11620,10 +11620,10 @@
         <v>5</v>
       </c>
       <c r="AY51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA51" t="n">
         <v>5</v>
@@ -11817,19 +11817,19 @@
         <v>1.64</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AT52" t="n">
-        <v>4.11</v>
+        <v>3.85</v>
       </c>
       <c r="AU52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW52" t="n">
         <v>7</v>
@@ -11838,10 +11838,10 @@
         <v>6</v>
       </c>
       <c r="AY52" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA52" t="n">
         <v>2</v>
@@ -12035,19 +12035,19 @@
         <v>0.33</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="AU53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW53" t="n">
         <v>12</v>
@@ -12056,10 +12056,10 @@
         <v>12</v>
       </c>
       <c r="AY53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA53" t="n">
         <v>3</v>
@@ -12253,16 +12253,16 @@
         <v>1</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
         <v>0</v>
@@ -12271,13 +12271,13 @@
         <v>19</v>
       </c>
       <c r="AX54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA54" t="n">
         <v>8</v>
@@ -12471,19 +12471,19 @@
         <v>1.11</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW55" t="n">
         <v>7</v>
@@ -12492,10 +12492,10 @@
         <v>10</v>
       </c>
       <c r="AY55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA55" t="n">
         <v>6</v>
@@ -12689,19 +12689,19 @@
         <v>1.2</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW56" t="n">
         <v>13</v>
@@ -12710,10 +12710,10 @@
         <v>10</v>
       </c>
       <c r="AY56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ56" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA56" t="n">
         <v>2</v>
@@ -12907,19 +12907,19 @@
         <v>0.78</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AU57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV57" t="n">
         <v>5</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>6</v>
       </c>
       <c r="AW57" t="n">
         <v>6</v>
@@ -12928,10 +12928,10 @@
         <v>5</v>
       </c>
       <c r="AY57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA57" t="n">
         <v>4</v>
@@ -13122,22 +13122,22 @@
         <v>1.8</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AU58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW58" t="n">
         <v>14</v>
@@ -13146,10 +13146,10 @@
         <v>7</v>
       </c>
       <c r="AY58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ58" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA58" t="n">
         <v>5</v>
@@ -13343,19 +13343,19 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW59" t="n">
         <v>18</v>
@@ -13364,10 +13364,10 @@
         <v>9</v>
       </c>
       <c r="AY59" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA59" t="n">
         <v>13</v>
@@ -13561,19 +13561,19 @@
         <v>0.9</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="AU60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW60" t="n">
         <v>8</v>
@@ -13582,10 +13582,10 @@
         <v>7</v>
       </c>
       <c r="AY60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA60" t="n">
         <v>7</v>
@@ -13779,31 +13779,31 @@
         <v>0.8</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AS61" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="AU61" t="n">
         <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX61" t="n">
         <v>6</v>
       </c>
       <c r="AY61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA61" t="n">
         <v>5</v>
@@ -13997,19 +13997,19 @@
         <v>1.1</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW62" t="n">
         <v>15</v>
@@ -14018,10 +14018,10 @@
         <v>4</v>
       </c>
       <c r="AY62" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA62" t="n">
         <v>10</v>
@@ -14215,19 +14215,19 @@
         <v>0.78</v>
       </c>
       <c r="AR63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS63" t="n">
         <v>1.64</v>
       </c>
-      <c r="AS63" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AT63" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AU63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW63" t="n">
         <v>11</v>
@@ -14236,10 +14236,10 @@
         <v>8</v>
       </c>
       <c r="AY63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA63" t="n">
         <v>6</v>
@@ -14433,16 +14433,16 @@
         <v>1.64</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV64" t="n">
         <v>0</v>
@@ -14451,13 +14451,13 @@
         <v>11</v>
       </c>
       <c r="AX64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA64" t="n">
         <v>5</v>
@@ -14651,19 +14651,19 @@
         <v>0.3</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="AU65" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV65" t="n">
         <v>4</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>5</v>
       </c>
       <c r="AW65" t="n">
         <v>13</v>
@@ -14672,10 +14672,10 @@
         <v>10</v>
       </c>
       <c r="AY65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA65" t="n">
         <v>9</v>
@@ -14869,19 +14869,19 @@
         <v>0.8</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT66" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AU66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW66" t="n">
         <v>7</v>
@@ -14890,10 +14890,10 @@
         <v>3</v>
       </c>
       <c r="AY66" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA66" t="n">
         <v>6</v>
@@ -15087,19 +15087,19 @@
         <v>0.91</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.36</v>
+        <v>3.11</v>
       </c>
       <c r="AU67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV67" t="n">
         <v>4</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>5</v>
       </c>
       <c r="AW67" t="n">
         <v>11</v>
@@ -15108,10 +15108,10 @@
         <v>9</v>
       </c>
       <c r="AY67" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA67" t="n">
         <v>8</v>
@@ -15299,25 +15299,25 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.3</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AU68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV68" t="n">
         <v>4</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>5</v>
       </c>
       <c r="AW68" t="n">
         <v>7</v>
@@ -15326,10 +15326,10 @@
         <v>8</v>
       </c>
       <c r="AY68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA68" t="n">
         <v>7</v>
@@ -15517,25 +15517,25 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.6</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AT69" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="AU69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW69" t="n">
         <v>10</v>
@@ -15544,10 +15544,10 @@
         <v>10</v>
       </c>
       <c r="AY69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA69" t="n">
         <v>7</v>
@@ -15741,19 +15741,19 @@
         <v>0.8</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="AU70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV70" t="n">
         <v>5</v>
-      </c>
-      <c r="AV70" t="n">
-        <v>6</v>
       </c>
       <c r="AW70" t="n">
         <v>6</v>
@@ -15762,10 +15762,10 @@
         <v>16</v>
       </c>
       <c r="AY70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA70" t="n">
         <v>5</v>
@@ -15959,19 +15959,19 @@
         <v>1</v>
       </c>
       <c r="AR71" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="AT71" t="n">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="AU71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV71" t="n">
         <v>5</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>6</v>
       </c>
       <c r="AW71" t="n">
         <v>11</v>
@@ -15980,10 +15980,10 @@
         <v>5</v>
       </c>
       <c r="AY71" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA71" t="n">
         <v>7</v>
@@ -16177,19 +16177,19 @@
         <v>1</v>
       </c>
       <c r="AR72" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.49</v>
+        <v>3.22</v>
       </c>
       <c r="AU72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW72" t="n">
         <v>11</v>
@@ -16198,10 +16198,10 @@
         <v>11</v>
       </c>
       <c r="AY72" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA72" t="n">
         <v>3</v>
@@ -16395,19 +16395,19 @@
         <v>0.9</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.59</v>
+        <v>3.33</v>
       </c>
       <c r="AU73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW73" t="n">
         <v>6</v>
@@ -16416,10 +16416,10 @@
         <v>15</v>
       </c>
       <c r="AY73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
@@ -16613,19 +16613,19 @@
         <v>0.78</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="AU74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW74" t="n">
         <v>13</v>
@@ -16634,10 +16634,10 @@
         <v>3</v>
       </c>
       <c r="AY74" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA74" t="n">
         <v>6</v>
@@ -16831,19 +16831,19 @@
         <v>1.22</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW75" t="n">
         <v>6</v>
@@ -16852,10 +16852,10 @@
         <v>6</v>
       </c>
       <c r="AY75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA75" t="n">
         <v>5</v>
@@ -17049,19 +17049,19 @@
         <v>1.11</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="AU76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW76" t="n">
         <v>8</v>
@@ -17070,10 +17070,10 @@
         <v>6</v>
       </c>
       <c r="AY76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA76" t="n">
         <v>10</v>
@@ -17267,19 +17267,19 @@
         <v>1</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT77" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW77" t="n">
         <v>15</v>
@@ -17288,10 +17288,10 @@
         <v>3</v>
       </c>
       <c r="AY77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA77" t="n">
         <v>8</v>
@@ -17485,19 +17485,19 @@
         <v>1.2</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="AU78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW78" t="n">
         <v>12</v>
@@ -17506,10 +17506,10 @@
         <v>11</v>
       </c>
       <c r="AY78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ78" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA78" t="n">
         <v>1</v>
@@ -17700,22 +17700,22 @@
         <v>1.11</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="AU79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW79" t="n">
         <v>15</v>
@@ -17724,10 +17724,10 @@
         <v>10</v>
       </c>
       <c r="AY79" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA79" t="n">
         <v>5</v>
@@ -17921,19 +17921,19 @@
         <v>0.33</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW80" t="n">
         <v>27</v>
@@ -17942,10 +17942,10 @@
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AZ80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA80" t="n">
         <v>7</v>
@@ -18136,22 +18136,22 @@
         <v>2.22</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AT81" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW81" t="n">
         <v>3</v>
@@ -18160,10 +18160,10 @@
         <v>6</v>
       </c>
       <c r="AY81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA81" t="n">
         <v>9</v>
@@ -18357,19 +18357,19 @@
         <v>0.91</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="AU82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW82" t="n">
         <v>5</v>
@@ -18378,10 +18378,10 @@
         <v>14</v>
       </c>
       <c r="AY82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA82" t="n">
         <v>4</v>
@@ -18575,19 +18575,19 @@
         <v>1.3</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="AU83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW83" t="n">
         <v>9</v>
@@ -18596,10 +18596,10 @@
         <v>5</v>
       </c>
       <c r="AY83" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA83" t="n">
         <v>5</v>
@@ -18793,19 +18793,19 @@
         <v>0.3</v>
       </c>
       <c r="AR84" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS84" t="n">
         <v>1.23</v>
       </c>
-      <c r="AS84" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AT84" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="AU84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW84" t="n">
         <v>10</v>
@@ -18814,10 +18814,10 @@
         <v>8</v>
       </c>
       <c r="AY84" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ84" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>16</v>
       </c>
       <c r="BA84" t="n">
         <v>3</v>
@@ -19011,19 +19011,19 @@
         <v>1.1</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT85" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW85" t="n">
         <v>15</v>
@@ -19032,10 +19032,10 @@
         <v>13</v>
       </c>
       <c r="AY85" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ85" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA85" t="n">
         <v>5</v>
@@ -19229,19 +19229,19 @@
         <v>1</v>
       </c>
       <c r="AR86" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="AU86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW86" t="n">
         <v>16</v>
@@ -19250,10 +19250,10 @@
         <v>4</v>
       </c>
       <c r="AY86" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA86" t="n">
         <v>8</v>
@@ -19441,25 +19441,25 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.8</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="AU87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW87" t="n">
         <v>8</v>
@@ -19468,10 +19468,10 @@
         <v>10</v>
       </c>
       <c r="AY87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ87" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA87" t="n">
         <v>4</v>
@@ -19665,19 +19665,19 @@
         <v>1.64</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="AU88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW88" t="n">
         <v>12</v>
@@ -19686,10 +19686,10 @@
         <v>6</v>
       </c>
       <c r="AY88" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA88" t="n">
         <v>9</v>
@@ -19877,25 +19877,25 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.6</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW89" t="n">
         <v>9</v>
@@ -19904,10 +19904,10 @@
         <v>11</v>
       </c>
       <c r="AY89" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ89" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA89" t="n">
         <v>1</v>
@@ -20101,19 +20101,19 @@
         <v>0.8</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="AU90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW90" t="n">
         <v>8</v>
@@ -20122,10 +20122,10 @@
         <v>5</v>
       </c>
       <c r="AY90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20319,19 +20319,19 @@
         <v>0.78</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AU91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW91" t="n">
         <v>7</v>
@@ -20340,10 +20340,10 @@
         <v>8</v>
       </c>
       <c r="AY91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA91" t="n">
         <v>6</v>
@@ -20537,19 +20537,19 @@
         <v>0.78</v>
       </c>
       <c r="AR92" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AS92" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="AT92" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW92" t="n">
         <v>16</v>
@@ -20558,10 +20558,10 @@
         <v>9</v>
       </c>
       <c r="AY92" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA92" t="n">
         <v>2</v>
@@ -20755,19 +20755,19 @@
         <v>1.11</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW93" t="n">
         <v>9</v>
@@ -20776,10 +20776,10 @@
         <v>6</v>
       </c>
       <c r="AY93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA93" t="n">
         <v>13</v>
@@ -20973,19 +20973,19 @@
         <v>1</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AU94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW94" t="n">
         <v>7</v>
@@ -20994,10 +20994,10 @@
         <v>4</v>
       </c>
       <c r="AY94" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ94" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA94" t="n">
         <v>4</v>
@@ -21188,22 +21188,22 @@
         <v>1.6</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT95" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW95" t="n">
         <v>10</v>
@@ -21212,10 +21212,10 @@
         <v>3</v>
       </c>
       <c r="AY95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA95" t="n">
         <v>6</v>
@@ -21409,19 +21409,19 @@
         <v>0.9</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.53</v>
+        <v>3.28</v>
       </c>
       <c r="AU96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW96" t="n">
         <v>8</v>
@@ -21430,10 +21430,10 @@
         <v>8</v>
       </c>
       <c r="AY96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ96" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA96" t="n">
         <v>3</v>
@@ -21627,19 +21627,19 @@
         <v>1.22</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.09</v>
+        <v>2.81</v>
       </c>
       <c r="AU97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW97" t="n">
         <v>8</v>
@@ -21648,10 +21648,10 @@
         <v>5</v>
       </c>
       <c r="AY97" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA97" t="n">
         <v>1</v>
@@ -21845,19 +21845,19 @@
         <v>1</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW98" t="n">
         <v>10</v>
@@ -21866,10 +21866,10 @@
         <v>12</v>
       </c>
       <c r="AY98" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ98" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA98" t="n">
         <v>5</v>
@@ -22060,22 +22060,22 @@
         <v>2</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AT99" t="n">
-        <v>4.11</v>
+        <v>3.85</v>
       </c>
       <c r="AU99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW99" t="n">
         <v>6</v>
@@ -22084,10 +22084,10 @@
         <v>7</v>
       </c>
       <c r="AY99" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA99" t="n">
         <v>6</v>
@@ -22281,19 +22281,19 @@
         <v>0.33</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.1</v>
+        <v>0.96</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.73</v>
+        <v>2.46</v>
       </c>
       <c r="AU100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW100" t="n">
         <v>12</v>
@@ -22302,10 +22302,10 @@
         <v>9</v>
       </c>
       <c r="AY100" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ100" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA100" t="n">
         <v>9</v>
@@ -22499,19 +22499,19 @@
         <v>1.2</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="AU101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV101" t="n">
         <v>6</v>
-      </c>
-      <c r="AV101" t="n">
-        <v>7</v>
       </c>
       <c r="AW101" t="n">
         <v>18</v>
@@ -22520,10 +22520,10 @@
         <v>2</v>
       </c>
       <c r="AY101" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA101" t="n">
         <v>11</v>
@@ -22711,25 +22711,25 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.64</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="AU102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW102" t="n">
         <v>4</v>
@@ -22738,10 +22738,10 @@
         <v>3</v>
       </c>
       <c r="AY102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA102" t="n">
         <v>3</v>
@@ -22935,19 +22935,19 @@
         <v>1.1</v>
       </c>
       <c r="AR103" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.75</v>
+        <v>3.49</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW103" t="n">
         <v>6</v>
@@ -22956,10 +22956,10 @@
         <v>6</v>
       </c>
       <c r="AY103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA103" t="n">
         <v>5</v>
@@ -23153,19 +23153,19 @@
         <v>1</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW104" t="n">
         <v>16</v>
@@ -23174,10 +23174,10 @@
         <v>5</v>
       </c>
       <c r="AY104" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA104" t="n">
         <v>9</v>
@@ -23371,19 +23371,19 @@
         <v>0.91</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AU105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW105" t="n">
         <v>12</v>
@@ -23392,10 +23392,10 @@
         <v>9</v>
       </c>
       <c r="AY105" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ105" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA105" t="n">
         <v>9</v>
@@ -23589,19 +23589,19 @@
         <v>0.6</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="AU106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW106" t="n">
         <v>7</v>
@@ -23610,10 +23610,10 @@
         <v>11</v>
       </c>
       <c r="AY106" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ106" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23807,19 +23807,19 @@
         <v>0.3</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="AU107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW107" t="n">
         <v>3</v>
@@ -23828,10 +23828,10 @@
         <v>6</v>
       </c>
       <c r="AY107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA107" t="n">
         <v>2</v>
@@ -24025,13 +24025,13 @@
         <v>0.78</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU108" t="n">
         <v>-1</v>
@@ -24243,19 +24243,19 @@
         <v>0.8</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW109" t="n">
         <v>8</v>
@@ -24264,10 +24264,10 @@
         <v>6</v>
       </c>
       <c r="AY109" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA109" t="n">
         <v>6</v>
@@ -24461,16 +24461,16 @@
         <v>0.8</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="AU110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV110" t="n">
         <v>0</v>
@@ -24479,13 +24479,13 @@
         <v>13</v>
       </c>
       <c r="AX110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY110" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ110" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA110" t="n">
         <v>13</v>
@@ -24673,25 +24673,25 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.3</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AU111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW111" t="n">
         <v>3</v>
@@ -24700,10 +24700,10 @@
         <v>10</v>
       </c>
       <c r="AY111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ111" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA111" t="n">
         <v>2</v>
@@ -24894,22 +24894,22 @@
         <v>1.9</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AU112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW112" t="n">
         <v>6</v>
@@ -24918,10 +24918,10 @@
         <v>4</v>
       </c>
       <c r="AY112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA112" t="n">
         <v>4</v>
@@ -25115,19 +25115,19 @@
         <v>0.78</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.06</v>
+        <v>2.78</v>
       </c>
       <c r="AU113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW113" t="n">
         <v>14</v>
@@ -25136,10 +25136,10 @@
         <v>5</v>
       </c>
       <c r="AY113" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ113" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA113" t="n">
         <v>8</v>
@@ -25330,22 +25330,22 @@
         <v>2.11</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="AU114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV114" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW114" t="n">
         <v>11</v>
@@ -25354,10 +25354,10 @@
         <v>10</v>
       </c>
       <c r="AY114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA114" t="n">
         <v>1</v>
@@ -25551,19 +25551,19 @@
         <v>1</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="AU115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW115" t="n">
         <v>15</v>
@@ -25572,10 +25572,10 @@
         <v>5</v>
       </c>
       <c r="AY115" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA115" t="n">
         <v>13</v>
@@ -25769,19 +25769,19 @@
         <v>0.8</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AU116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW116" t="n">
         <v>7</v>
@@ -25790,10 +25790,10 @@
         <v>9</v>
       </c>
       <c r="AY116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA116" t="n">
         <v>5</v>
@@ -25987,19 +25987,19 @@
         <v>1.64</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AT117" t="n">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="AU117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW117" t="n">
         <v>9</v>
@@ -26008,10 +26008,10 @@
         <v>7</v>
       </c>
       <c r="AY117" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26205,19 +26205,19 @@
         <v>0.9</v>
       </c>
       <c r="AR118" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU118" t="n">
         <v>2</v>
       </c>
-      <c r="AS118" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AT118" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AU118" t="n">
-        <v>3</v>
-      </c>
       <c r="AV118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW118" t="n">
         <v>4</v>
@@ -26226,10 +26226,10 @@
         <v>5</v>
       </c>
       <c r="AY118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ118" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA118" t="n">
         <v>2</v>
@@ -26423,19 +26423,19 @@
         <v>0.33</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW119" t="n">
         <v>8</v>
@@ -26444,10 +26444,10 @@
         <v>7</v>
       </c>
       <c r="AY119" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ119" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA119" t="n">
         <v>5</v>
@@ -26641,19 +26641,19 @@
         <v>0.91</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT120" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="AU120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW120" t="n">
         <v>4</v>
@@ -26662,10 +26662,10 @@
         <v>12</v>
       </c>
       <c r="AY120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ120" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA120" t="n">
         <v>1</v>
@@ -26859,19 +26859,19 @@
         <v>1</v>
       </c>
       <c r="AR121" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.57</v>
+        <v>3.31</v>
       </c>
       <c r="AU121" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW121" t="n">
         <v>8</v>
@@ -26880,10 +26880,10 @@
         <v>5</v>
       </c>
       <c r="AY121" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA121" t="n">
         <v>12</v>
@@ -27071,25 +27071,25 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.1</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW122" t="n">
         <v>17</v>
@@ -27098,10 +27098,10 @@
         <v>6</v>
       </c>
       <c r="AY122" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA122" t="n">
         <v>13</v>
@@ -27295,19 +27295,19 @@
         <v>1.2</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="AU123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV123" t="n">
         <v>3</v>
-      </c>
-      <c r="AV123" t="n">
-        <v>4</v>
       </c>
       <c r="AW123" t="n">
         <v>14</v>
@@ -27316,10 +27316,10 @@
         <v>7</v>
       </c>
       <c r="AY123" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA123" t="n">
         <v>7</v>
@@ -27513,19 +27513,19 @@
         <v>1.22</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW124" t="n">
         <v>10</v>
@@ -27534,10 +27534,10 @@
         <v>6</v>
       </c>
       <c r="AY124" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ124" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA124" t="n">
         <v>4</v>
@@ -27731,19 +27731,19 @@
         <v>1</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AU125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV125" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW125" t="n">
         <v>15</v>
@@ -27752,10 +27752,10 @@
         <v>14</v>
       </c>
       <c r="AY125" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ125" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA125" t="n">
         <v>7</v>
@@ -27949,19 +27949,19 @@
         <v>0.6</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AU126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW126" t="n">
         <v>8</v>
@@ -27970,10 +27970,10 @@
         <v>16</v>
       </c>
       <c r="AY126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ126" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA126" t="n">
         <v>2</v>
@@ -28167,19 +28167,19 @@
         <v>0.9</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW127" t="n">
         <v>8</v>
@@ -28188,10 +28188,10 @@
         <v>6</v>
       </c>
       <c r="AY127" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ127" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA127" t="n">
         <v>5</v>
@@ -28385,16 +28385,16 @@
         <v>0.3</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AU128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV128" t="n">
         <v>0</v>
@@ -28403,13 +28403,13 @@
         <v>15</v>
       </c>
       <c r="AX128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY128" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA128" t="n">
         <v>8</v>
@@ -28597,25 +28597,25 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.8</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AU129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW129" t="n">
         <v>8</v>
@@ -28624,10 +28624,10 @@
         <v>11</v>
       </c>
       <c r="AY129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ129" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA129" t="n">
         <v>8</v>
@@ -28821,19 +28821,19 @@
         <v>1.11</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW130" t="n">
         <v>13</v>
@@ -28842,10 +28842,10 @@
         <v>10</v>
       </c>
       <c r="AY130" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ130" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA130" t="n">
         <v>2</v>
@@ -29039,19 +29039,19 @@
         <v>1.3</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW131" t="n">
         <v>10</v>
@@ -29060,10 +29060,10 @@
         <v>12</v>
       </c>
       <c r="AY131" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ131" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA131" t="n">
         <v>4</v>
@@ -29254,22 +29254,22 @@
         <v>2.11</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW132" t="n">
         <v>19</v>
@@ -29278,10 +29278,10 @@
         <v>6</v>
       </c>
       <c r="AY132" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA132" t="n">
         <v>14</v>
@@ -29475,19 +29475,19 @@
         <v>1</v>
       </c>
       <c r="AR133" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AU133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW133" t="n">
         <v>14</v>
@@ -29496,10 +29496,10 @@
         <v>4</v>
       </c>
       <c r="AY133" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA133" t="n">
         <v>6</v>
@@ -29693,19 +29693,19 @@
         <v>0.78</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.18</v>
+        <v>2.91</v>
       </c>
       <c r="AU134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW134" t="n">
         <v>7</v>
@@ -29714,10 +29714,10 @@
         <v>8</v>
       </c>
       <c r="AY134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA134" t="n">
         <v>5</v>
@@ -29911,19 +29911,19 @@
         <v>1.64</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AT135" t="n">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AU135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV135" t="n">
         <v>5</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>6</v>
       </c>
       <c r="AW135" t="n">
         <v>15</v>
@@ -29932,10 +29932,10 @@
         <v>3</v>
       </c>
       <c r="AY135" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ135" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA135" t="n">
         <v>7</v>
@@ -30129,16 +30129,16 @@
         <v>0.8</v>
       </c>
       <c r="AR136" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.64</v>
+        <v>3.37</v>
       </c>
       <c r="AU136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV136" t="n">
         <v>0</v>
@@ -30147,13 +30147,13 @@
         <v>12</v>
       </c>
       <c r="AX136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY136" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30347,19 +30347,19 @@
         <v>1</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW137" t="n">
         <v>12</v>
@@ -30368,10 +30368,10 @@
         <v>3</v>
       </c>
       <c r="AY137" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA137" t="n">
         <v>10</v>
@@ -30565,19 +30565,19 @@
         <v>0.33</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.99</v>
+        <v>2.71</v>
       </c>
       <c r="AU138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW138" t="n">
         <v>12</v>
@@ -30586,10 +30586,10 @@
         <v>6</v>
       </c>
       <c r="AY138" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ138" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA138" t="n">
         <v>6</v>
@@ -30780,22 +30780,22 @@
         <v>2.11</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW139" t="n">
         <v>7</v>
@@ -30804,10 +30804,10 @@
         <v>12</v>
       </c>
       <c r="AY139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ139" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA139" t="n">
         <v>5</v>
@@ -31001,19 +31001,19 @@
         <v>0.91</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AU140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW140" t="n">
         <v>8</v>
@@ -31022,10 +31022,10 @@
         <v>8</v>
       </c>
       <c r="AY140" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA140" t="n">
         <v>5</v>
@@ -31219,19 +31219,19 @@
         <v>0.78</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="AU141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW141" t="n">
         <v>12</v>
@@ -31240,10 +31240,10 @@
         <v>12</v>
       </c>
       <c r="AY141" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ141" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA141" t="n">
         <v>5</v>
@@ -31437,19 +31437,19 @@
         <v>0.6</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="AU142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW142" t="n">
         <v>8</v>
@@ -31458,10 +31458,10 @@
         <v>15</v>
       </c>
       <c r="AY142" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ142" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA142" t="n">
         <v>2</v>
@@ -31655,19 +31655,19 @@
         <v>0.3</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AU143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW143" t="n">
         <v>7</v>
@@ -31676,10 +31676,10 @@
         <v>10</v>
       </c>
       <c r="AY143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ143" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA143" t="n">
         <v>2</v>
@@ -31873,19 +31873,19 @@
         <v>0.9</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW144" t="n">
         <v>5</v>
@@ -31894,10 +31894,10 @@
         <v>4</v>
       </c>
       <c r="AY144" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ144" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA144" t="n">
         <v>7</v>
@@ -32091,19 +32091,19 @@
         <v>1</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AT145" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW145" t="n">
         <v>9</v>
@@ -32112,10 +32112,10 @@
         <v>3</v>
       </c>
       <c r="AY145" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ145" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA145" t="n">
         <v>2</v>
@@ -32303,25 +32303,25 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.22</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AU146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV146" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW146" t="n">
         <v>8</v>
@@ -32330,10 +32330,10 @@
         <v>8</v>
       </c>
       <c r="AY146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ146" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA146" t="n">
         <v>3</v>
@@ -32527,19 +32527,19 @@
         <v>0.8</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AT147" t="n">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="AU147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW147" t="n">
         <v>12</v>
@@ -32548,10 +32548,10 @@
         <v>6</v>
       </c>
       <c r="AY147" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ147" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA147" t="n">
         <v>7</v>
@@ -32739,25 +32739,25 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.11</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AU148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW148" t="n">
         <v>12</v>
@@ -32766,10 +32766,10 @@
         <v>2</v>
       </c>
       <c r="AY148" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA148" t="n">
         <v>8</v>
@@ -32963,19 +32963,19 @@
         <v>1.1</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT149" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU149" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV149" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW149" t="n">
         <v>12</v>
@@ -32984,10 +32984,10 @@
         <v>6</v>
       </c>
       <c r="AY149" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ149" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA149" t="n">
         <v>1</v>
@@ -33181,19 +33181,19 @@
         <v>1.3</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV150" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW150" t="n">
         <v>17</v>
@@ -33202,10 +33202,10 @@
         <v>7</v>
       </c>
       <c r="AY150" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ150" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA150" t="n">
         <v>8</v>
@@ -33399,19 +33399,19 @@
         <v>1.2</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW151" t="n">
         <v>8</v>
@@ -33420,10 +33420,10 @@
         <v>13</v>
       </c>
       <c r="AY151" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ151" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA151" t="n">
         <v>8</v>
@@ -33617,19 +33617,19 @@
         <v>1.64</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT152" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV152" t="n">
         <v>3</v>
-      </c>
-      <c r="AU152" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV152" t="n">
-        <v>4</v>
       </c>
       <c r="AW152" t="n">
         <v>20</v>
@@ -33638,10 +33638,10 @@
         <v>2</v>
       </c>
       <c r="AY152" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AZ152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA152" t="n">
         <v>10</v>
@@ -33835,19 +33835,19 @@
         <v>0.8</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
         <v>5</v>
@@ -33856,10 +33856,10 @@
         <v>3</v>
       </c>
       <c r="AY153" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA153" t="n">
         <v>5</v>
@@ -34050,22 +34050,22 @@
         <v>2.4</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU154" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV154" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW154" t="n">
         <v>10</v>
@@ -34074,10 +34074,10 @@
         <v>11</v>
       </c>
       <c r="AY154" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ154" t="n">
         <v>18</v>
-      </c>
-      <c r="AZ154" t="n">
-        <v>19</v>
       </c>
       <c r="BA154" t="n">
         <v>2</v>
@@ -34271,19 +34271,19 @@
         <v>0.78</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.35</v>
+        <v>3.09</v>
       </c>
       <c r="AU155" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW155" t="n">
         <v>8</v>
@@ -34292,10 +34292,10 @@
         <v>11</v>
       </c>
       <c r="AY155" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA155" t="n">
         <v>10</v>
@@ -34486,22 +34486,22 @@
         <v>1.4</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="AU156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW156" t="n">
         <v>18</v>
@@ -34510,10 +34510,10 @@
         <v>2</v>
       </c>
       <c r="AY156" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA156" t="n">
         <v>8</v>
@@ -34707,19 +34707,19 @@
         <v>0.91</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AU157" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW157" t="n">
         <v>10</v>
@@ -34728,10 +34728,10 @@
         <v>9</v>
       </c>
       <c r="AY157" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ157" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA157" t="n">
         <v>12</v>
@@ -34925,19 +34925,19 @@
         <v>1</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="AU158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW158" t="n">
         <v>7</v>
@@ -34946,10 +34946,10 @@
         <v>8</v>
       </c>
       <c r="AY158" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ158" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA158" t="n">
         <v>6</v>
@@ -35143,19 +35143,19 @@
         <v>1</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT159" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="AU159" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW159" t="n">
         <v>1</v>
@@ -35164,10 +35164,10 @@
         <v>8</v>
       </c>
       <c r="AY159" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ159" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ159" t="n">
-        <v>10</v>
       </c>
       <c r="BA159" t="n">
         <v>5</v>
@@ -35355,25 +35355,25 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.3</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
       <c r="AU160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV160" t="n">
         <v>3</v>
-      </c>
-      <c r="AV160" t="n">
-        <v>4</v>
       </c>
       <c r="AW160" t="n">
         <v>10</v>
@@ -35382,10 +35382,10 @@
         <v>12</v>
       </c>
       <c r="AY160" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ160" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA160" t="n">
         <v>6</v>
@@ -35579,19 +35579,19 @@
         <v>0.33</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AU161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW161" t="n">
         <v>4</v>
@@ -35600,10 +35600,10 @@
         <v>9</v>
       </c>
       <c r="AY161" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ161" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA161" t="n">
         <v>1</v>
@@ -35797,19 +35797,19 @@
         <v>0.6</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AU162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW162" t="n">
         <v>15</v>
@@ -35818,10 +35818,10 @@
         <v>6</v>
       </c>
       <c r="AY162" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ162" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA162" t="n">
         <v>5</v>
@@ -36015,19 +36015,19 @@
         <v>1.11</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="AU163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW163" t="n">
         <v>8</v>
@@ -36036,10 +36036,10 @@
         <v>15</v>
       </c>
       <c r="AY163" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ163" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA163" t="n">
         <v>5</v>
@@ -36233,19 +36233,19 @@
         <v>1.2</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT164" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="AU164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW164" t="n">
         <v>7</v>
@@ -36254,10 +36254,10 @@
         <v>7</v>
       </c>
       <c r="AY164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
@@ -36451,19 +36451,19 @@
         <v>1.3</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="AU165" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW165" t="n">
         <v>4</v>
@@ -36472,10 +36472,10 @@
         <v>2</v>
       </c>
       <c r="AY165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA165" t="n">
         <v>2</v>
@@ -36669,19 +36669,19 @@
         <v>0.9</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT166" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW166" t="n">
         <v>10</v>
@@ -36690,10 +36690,10 @@
         <v>4</v>
       </c>
       <c r="AY166" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ166" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA166" t="n">
         <v>2</v>
@@ -36887,19 +36887,19 @@
         <v>1</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AU167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV167" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW167" t="n">
         <v>16</v>
@@ -36908,10 +36908,10 @@
         <v>7</v>
       </c>
       <c r="AY167" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ167" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA167" t="n">
         <v>10</v>
@@ -37105,19 +37105,19 @@
         <v>0.8</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU168" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW168" t="n">
         <v>10</v>
@@ -37126,10 +37126,10 @@
         <v>7</v>
       </c>
       <c r="AY168" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ168" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA168" t="n">
         <v>10</v>
@@ -37323,19 +37323,19 @@
         <v>1.22</v>
       </c>
       <c r="AR169" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT169" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="AU169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW169" t="n">
         <v>8</v>
@@ -37344,10 +37344,10 @@
         <v>9</v>
       </c>
       <c r="AY169" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ169" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA169" t="n">
         <v>3</v>
@@ -37535,25 +37535,25 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.78</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW170" t="n">
         <v>9</v>
@@ -37562,10 +37562,10 @@
         <v>5</v>
       </c>
       <c r="AY170" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ170" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA170" t="n">
         <v>1</v>
@@ -37759,19 +37759,19 @@
         <v>1.1</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT171" t="n">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="AU171" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW171" t="n">
         <v>19</v>
@@ -37780,10 +37780,10 @@
         <v>6</v>
       </c>
       <c r="AY171" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ171" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA171" t="n">
         <v>7</v>
@@ -37977,19 +37977,19 @@
         <v>0.78</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT172" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW172" t="n">
         <v>6</v>
@@ -37998,10 +37998,10 @@
         <v>1</v>
       </c>
       <c r="AY172" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA172" t="n">
         <v>3</v>
@@ -38195,19 +38195,19 @@
         <v>0.91</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.37</v>
+        <v>3.12</v>
       </c>
       <c r="AU173" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW173" t="n">
         <v>19</v>
@@ -38216,10 +38216,10 @@
         <v>5</v>
       </c>
       <c r="AY173" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ173" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA173" t="n">
         <v>11</v>
@@ -38413,19 +38413,19 @@
         <v>1.64</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="AU174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV174" t="n">
         <v>6</v>
-      </c>
-      <c r="AV174" t="n">
-        <v>7</v>
       </c>
       <c r="AW174" t="n">
         <v>3</v>
@@ -38434,10 +38434,10 @@
         <v>1</v>
       </c>
       <c r="AY174" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ174" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA174" t="n">
         <v>5</v>
@@ -38631,19 +38631,19 @@
         <v>0.6</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT175" t="n">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AU175" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW175" t="n">
         <v>7</v>
@@ -38652,10 +38652,10 @@
         <v>19</v>
       </c>
       <c r="AY175" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ175" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA175" t="n">
         <v>5</v>
@@ -38849,19 +38849,19 @@
         <v>0.3</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU176" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV176" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW176" t="n">
         <v>16</v>
@@ -38870,10 +38870,10 @@
         <v>13</v>
       </c>
       <c r="AY176" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ176" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA176" t="n">
         <v>7</v>
@@ -39064,22 +39064,22 @@
         <v>2.4</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT177" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV177" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW177" t="n">
         <v>10</v>
@@ -39088,10 +39088,10 @@
         <v>9</v>
       </c>
       <c r="AY177" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ177" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ177" t="n">
-        <v>15</v>
       </c>
       <c r="BA177" t="n">
         <v>3</v>
@@ -39282,22 +39282,22 @@
         <v>2.11</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT178" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW178" t="n">
         <v>3</v>
@@ -39306,10 +39306,10 @@
         <v>7</v>
       </c>
       <c r="AY178" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ178" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA178" t="n">
         <v>2</v>
@@ -39497,25 +39497,25 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ179" t="n">
         <v>1</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="AU179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW179" t="n">
         <v>19</v>
@@ -39524,10 +39524,10 @@
         <v>9</v>
       </c>
       <c r="AY179" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ179" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA179" t="n">
         <v>13</v>
@@ -39715,25 +39715,25 @@
         <v>1.13</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.2</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW180" t="n">
         <v>12</v>
@@ -39742,10 +39742,10 @@
         <v>5</v>
       </c>
       <c r="AY180" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ180" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA180" t="n">
         <v>6</v>
@@ -39939,19 +39939,19 @@
         <v>1</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AU181" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW181" t="n">
         <v>6</v>
@@ -39960,10 +39960,10 @@
         <v>11</v>
       </c>
       <c r="AY181" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ181" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA181" t="n">
         <v>7</v>
@@ -40157,19 +40157,19 @@
         <v>0.8</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT182" t="n">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="AU182" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW182" t="n">
         <v>4</v>
@@ -40178,10 +40178,10 @@
         <v>20</v>
       </c>
       <c r="AY182" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ182" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
@@ -40375,19 +40375,19 @@
         <v>1.11</v>
       </c>
       <c r="AR183" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AT183" t="n">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="AU183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW183" t="n">
         <v>9</v>
@@ -40396,10 +40396,10 @@
         <v>13</v>
       </c>
       <c r="AY183" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ183" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA183" t="n">
         <v>3</v>
@@ -40593,19 +40593,19 @@
         <v>0.8</v>
       </c>
       <c r="AR184" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AT184" t="n">
-        <v>3.43</v>
+        <v>3.19</v>
       </c>
       <c r="AU184" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV184" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW184" t="n">
         <v>10</v>
@@ -40614,10 +40614,10 @@
         <v>7</v>
       </c>
       <c r="AY184" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ184" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA184" t="n">
         <v>4</v>
@@ -40811,19 +40811,19 @@
         <v>0.33</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AU185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW185" t="n">
         <v>6</v>
@@ -40832,10 +40832,10 @@
         <v>4</v>
       </c>
       <c r="AY185" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ185" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA185" t="n">
         <v>8</v>
@@ -41029,19 +41029,19 @@
         <v>1.22</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT186" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="AU186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW186" t="n">
         <v>6</v>
@@ -41050,10 +41050,10 @@
         <v>4</v>
       </c>
       <c r="AY186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ186" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA186" t="n">
         <v>4</v>
@@ -41247,19 +41247,19 @@
         <v>1.1</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT187" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="AU187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW187" t="n">
         <v>11</v>
@@ -41268,10 +41268,10 @@
         <v>5</v>
       </c>
       <c r="AY187" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ187" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA187" t="n">
         <v>3</v>
@@ -41465,19 +41465,19 @@
         <v>0.78</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT188" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="AU188" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV188" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW188" t="n">
         <v>4</v>
@@ -41486,10 +41486,10 @@
         <v>11</v>
       </c>
       <c r="AY188" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ188" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ188" t="n">
-        <v>14</v>
       </c>
       <c r="BA188" t="n">
         <v>3</v>
@@ -41683,19 +41683,19 @@
         <v>1.3</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT189" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV189" t="n">
         <v>6</v>
-      </c>
-      <c r="AV189" t="n">
-        <v>7</v>
       </c>
       <c r="AW189" t="n">
         <v>11</v>
@@ -41704,10 +41704,10 @@
         <v>8</v>
       </c>
       <c r="AY189" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ189" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA189" t="n">
         <v>6</v>
@@ -41901,16 +41901,16 @@
         <v>0.9</v>
       </c>
       <c r="AR190" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT190" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="AU190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV190" t="n">
         <v>0</v>
@@ -41919,13 +41919,13 @@
         <v>5</v>
       </c>
       <c r="AX190" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY190" t="n">
         <v>8</v>
       </c>
-      <c r="AY190" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ190" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA190" t="n">
         <v>1</v>
@@ -42119,19 +42119,19 @@
         <v>1</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU191" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW191" t="n">
         <v>21</v>
@@ -42140,10 +42140,10 @@
         <v>6</v>
       </c>
       <c r="AY191" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ191" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA191" t="n">
         <v>11</v>
@@ -42337,19 +42337,19 @@
         <v>1.64</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AU192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW192" t="n">
         <v>16</v>
@@ -42358,10 +42358,10 @@
         <v>11</v>
       </c>
       <c r="AY192" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ192" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA192" t="n">
         <v>3</v>
@@ -42555,19 +42555,19 @@
         <v>0.91</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="AU193" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV193" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW193" t="n">
         <v>11</v>
@@ -42576,10 +42576,10 @@
         <v>10</v>
       </c>
       <c r="AY193" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ193" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA193" t="n">
         <v>7</v>
@@ -42773,16 +42773,16 @@
         <v>1.2</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV194" t="n">
         <v>0</v>
@@ -42791,13 +42791,13 @@
         <v>10</v>
       </c>
       <c r="AX194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY194" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA194" t="n">
         <v>8</v>
@@ -42846,6 +42846,442 @@
       </c>
       <c r="BP194" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>7841231</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45871.77083333334</v>
+      </c>
+      <c r="F195" t="n">
+        <v>20</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
+        <v>2</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="n">
+        <v>1</v>
+      </c>
+      <c r="N195" t="n">
+        <v>3</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>['20', '70']</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>4</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2</v>
+      </c>
+      <c r="S195" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X195" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>7841228</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45871.85416666666</v>
+      </c>
+      <c r="F196" t="n">
+        <v>20</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>2</v>
+      </c>
+      <c r="K196" t="n">
+        <v>3</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2</v>
+      </c>
+      <c r="M196" t="n">
+        <v>2</v>
+      </c>
+      <c r="N196" t="n">
+        <v>4</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>['16', '73']</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['11', '32']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R196" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S196" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V196" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X196" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.2</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.64</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.3</v>
@@ -4620,7 +4620,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.3</v>
@@ -8105,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR35" t="n">
         <v>1.53</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.2</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.22</v>
@@ -11160,7 +11160,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.2</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.78</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.1</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.91</v>
@@ -15520,7 +15520,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -16389,7 +16389,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.9</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.3</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -19880,7 +19880,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR89" t="n">
         <v>1.18</v>
@@ -22275,7 +22275,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.33</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.1</v>
@@ -23586,7 +23586,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -24019,7 +24019,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.78</v>
@@ -25545,7 +25545,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ115" t="n">
         <v>1</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.9</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.91</v>
@@ -27946,7 +27946,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR126" t="n">
         <v>1.86</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.64</v>
@@ -30559,7 +30559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.33</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.7</v>
@@ -31434,7 +31434,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR142" t="n">
         <v>1.81</v>
@@ -34047,7 +34047,7 @@
         <v>0.86</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.6</v>
@@ -34483,7 +34483,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.7</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ158" t="n">
         <v>1</v>
@@ -35794,7 +35794,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR162" t="n">
         <v>1.61</v>
@@ -38189,7 +38189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ173" t="n">
         <v>0.91</v>
@@ -38628,7 +38628,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AR175" t="n">
         <v>1.41</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.3</v>
@@ -39061,7 +39061,7 @@
         <v>2</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.7</v>
@@ -43282,6 +43282,660 @@
       </c>
       <c r="BP196" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>7841226</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45872.66666666666</v>
+      </c>
+      <c r="F197" t="n">
+        <v>20</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>3</v>
+      </c>
+      <c r="L197" t="n">
+        <v>3</v>
+      </c>
+      <c r="M197" t="n">
+        <v>2</v>
+      </c>
+      <c r="N197" t="n">
+        <v>5</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>['6', '27', '37']</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['67', '73']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R197" t="n">
+        <v>2</v>
+      </c>
+      <c r="S197" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X197" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>7841230</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45872.66666666666</v>
+      </c>
+      <c r="F198" t="n">
+        <v>20</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="n">
+        <v>2</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S198" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X198" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>7841222</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45872.77083333334</v>
+      </c>
+      <c r="F199" t="n">
+        <v>20</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S199" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X199" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -4184,7 +4184,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.55</v>
@@ -5056,7 +5056,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.22</v>
@@ -6582,7 +6582,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -7018,7 +7018,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR30" t="n">
         <v>2.72</v>
@@ -10721,10 +10721,10 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -10942,7 +10942,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR48" t="n">
         <v>1.9</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.91</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.8</v>
@@ -14212,7 +14212,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR63" t="n">
         <v>1.5</v>
@@ -14648,7 +14648,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR65" t="n">
         <v>2</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.8</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.11</v>
@@ -18790,7 +18790,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR84" t="n">
         <v>1.1</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.8</v>
@@ -20316,7 +20316,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR91" t="n">
         <v>1.83</v>
@@ -21403,7 +21403,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.9</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ104" t="n">
         <v>1</v>
@@ -23804,7 +23804,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR107" t="n">
         <v>1.6</v>
@@ -24022,7 +24022,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR108" t="n">
         <v>1.5</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.8</v>
@@ -28382,7 +28382,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR128" t="n">
         <v>1.71</v>
@@ -29690,7 +29690,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR134" t="n">
         <v>1.51</v>
@@ -30341,7 +30341,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ137" t="n">
         <v>1</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.78</v>
@@ -31652,7 +31652,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR143" t="n">
         <v>1.3</v>
@@ -34268,7 +34268,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR155" t="n">
         <v>1.73</v>
@@ -35137,7 +35137,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ159" t="n">
         <v>1</v>
@@ -35358,7 +35358,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR160" t="n">
         <v>1.31</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.33</v>
@@ -37974,7 +37974,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR172" t="n">
         <v>1.62</v>
@@ -38407,7 +38407,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.64</v>
@@ -38846,7 +38846,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR176" t="n">
         <v>1.37</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.6</v>
@@ -43936,6 +43936,442 @@
       </c>
       <c r="BP199" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>7841229</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45873.79166666666</v>
+      </c>
+      <c r="F200" t="n">
+        <v>20</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>2</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" t="n">
+        <v>2</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R200" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S200" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U200" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V200" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X200" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7841224</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45873.89583333334</v>
+      </c>
+      <c r="F201" t="n">
+        <v>20</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['20', '59']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R201" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S201" t="n">
+        <v>5</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U201" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V201" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X201" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -44096,16 +44096,16 @@
         <v>4</v>
       </c>
       <c r="AW200" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ200" t="n">
         <v>8</v>
-      </c>
-      <c r="AY200" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ200" t="n">
-        <v>12</v>
       </c>
       <c r="BA200" t="n">
         <v>4</v>
@@ -44314,16 +44314,16 @@
         <v>2</v>
       </c>
       <c r="AW201" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AX201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY201" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA201" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -44096,16 +44096,16 @@
         <v>4</v>
       </c>
       <c r="AW200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX200" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY200" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ200" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA200" t="n">
         <v>4</v>
@@ -44314,16 +44314,16 @@
         <v>2</v>
       </c>
       <c r="AW201" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY201" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ201" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA201" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.3</v>
@@ -1350,7 +1350,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.78</v>
@@ -2222,7 +2222,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.8</v>
@@ -6800,7 +6800,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.3</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.7</v>
@@ -9852,7 +9852,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR43" t="n">
         <v>2.12</v>
@@ -10288,7 +10288,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR45" t="n">
         <v>1.33</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.64</v>
@@ -14866,7 +14866,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR66" t="n">
         <v>1.45</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71" t="n">
         <v>1</v>
@@ -17264,7 +17264,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.91</v>
@@ -19444,7 +19444,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR87" t="n">
         <v>1.68</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.8</v>
@@ -21842,7 +21842,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR98" t="n">
         <v>1.61</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.91</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.27</v>
@@ -24240,7 +24240,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR109" t="n">
         <v>1.17</v>
@@ -25548,7 +25548,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR115" t="n">
         <v>1.5</v>
@@ -25766,7 +25766,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR116" t="n">
         <v>1.51</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.2</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.3</v>
@@ -30126,7 +30126,7 @@
         <v>2</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR136" t="n">
         <v>2.12</v>
@@ -30344,7 +30344,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR137" t="n">
         <v>1.49</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.3</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.2</v>
@@ -33832,7 +33832,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR153" t="n">
         <v>1.42</v>
@@ -34922,7 +34922,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR158" t="n">
         <v>1.34</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.9</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.09</v>
@@ -40154,7 +40154,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR182" t="n">
         <v>1.65</v>
@@ -41023,7 +41023,7 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.22</v>
@@ -42113,10 +42113,10 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR191" t="n">
         <v>1.39</v>
@@ -44532,16 +44532,16 @@
         <v>3</v>
       </c>
       <c r="AW202" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ202" t="n">
         <v>6</v>
-      </c>
-      <c r="AY202" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ202" t="n">
-        <v>9</v>
       </c>
       <c r="BA202" t="n">
         <v>9</v>
@@ -44808,6 +44808,442 @@
       </c>
       <c r="BP203" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>7841239</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45878.66666666666</v>
+      </c>
+      <c r="F204" t="n">
+        <v>21</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>1</v>
+      </c>
+      <c r="N204" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S204" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X204" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>7841233</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45878.77083333334</v>
+      </c>
+      <c r="F205" t="n">
+        <v>21</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>2</v>
+      </c>
+      <c r="L205" t="n">
+        <v>2</v>
+      </c>
+      <c r="M205" t="n">
+        <v>1</v>
+      </c>
+      <c r="N205" t="n">
+        <v>3</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['25', '59']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R205" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S205" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V205" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X205" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.9</v>
@@ -2658,7 +2658,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.91</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ54" t="n">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -17046,7 +17046,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.3</v>
@@ -20752,7 +20752,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR93" t="n">
         <v>1.57</v>
@@ -22057,7 +22057,7 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.6</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ121" t="n">
         <v>1</v>
@@ -28818,7 +28818,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR130" t="n">
         <v>1.55</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.73</v>
@@ -32742,7 +32742,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR148" t="n">
         <v>1.24</v>
@@ -36012,7 +36012,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR163" t="n">
         <v>1.2</v>
@@ -37317,7 +37317,7 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.22</v>
@@ -40372,7 +40372,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR183" t="n">
         <v>1.89</v>
@@ -40587,7 +40587,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.8</v>
@@ -44532,16 +44532,16 @@
         <v>3</v>
       </c>
       <c r="AW202" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX202" t="n">
         <v>6</v>
       </c>
-      <c r="AX202" t="n">
-        <v>3</v>
-      </c>
       <c r="AY202" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ202" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA202" t="n">
         <v>9</v>
@@ -44962,22 +44962,22 @@
         <v>2.85</v>
       </c>
       <c r="AU204" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV204" t="n">
         <v>2</v>
       </c>
       <c r="AW204" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX204" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY204" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ204" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BA204" t="n">
         <v>9</v>
@@ -45186,16 +45186,16 @@
         <v>1</v>
       </c>
       <c r="AW205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX205" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY205" t="n">
         <v>12</v>
       </c>
-      <c r="AY205" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ205" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA205" t="n">
         <v>4</v>
@@ -45244,6 +45244,224 @@
       </c>
       <c r="BP205" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>7841241</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45878.85416666666</v>
+      </c>
+      <c r="F206" t="n">
+        <v>21</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="R206" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S206" t="n">
+        <v>4</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V206" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X206" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.1</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.3</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.73</v>
@@ -7672,7 +7672,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR40" t="n">
         <v>1.69</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.6</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.1</v>
@@ -12904,7 +12904,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR57" t="n">
         <v>1.36</v>
@@ -13558,7 +13558,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR60" t="n">
         <v>1.65</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.8</v>
@@ -16392,7 +16392,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR73" t="n">
         <v>1.62</v>
@@ -16610,7 +16610,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.2</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.09</v>
@@ -20534,7 +20534,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR92" t="n">
         <v>1.93</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.7</v>
@@ -21406,7 +21406,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR96" t="n">
         <v>1.65</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.55</v>
@@ -25112,7 +25112,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR113" t="n">
         <v>1.76</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.64</v>
@@ -26202,7 +26202,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR118" t="n">
         <v>1.86</v>
@@ -27507,7 +27507,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.22</v>
@@ -28164,7 +28164,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR127" t="n">
         <v>1.32</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.27</v>
@@ -31216,7 +31216,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31431,7 +31431,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.55</v>
@@ -31870,7 +31870,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR144" t="n">
         <v>1.2</v>
@@ -32085,7 +32085,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ145" t="n">
         <v>1</v>
@@ -36227,7 +36227,7 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.2</v>
@@ -36666,7 +36666,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR166" t="n">
         <v>1.37</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.8</v>
@@ -37538,7 +37538,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR170" t="n">
         <v>1.35</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.09</v>
@@ -41459,10 +41459,10 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR188" t="n">
         <v>1.82</v>
@@ -41898,7 +41898,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AR190" t="n">
         <v>1.95</v>
@@ -45462,6 +45462,442 @@
       </c>
       <c r="BP206" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>7841236</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45879.66666666666</v>
+      </c>
+      <c r="F207" t="n">
+        <v>21</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>2</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>2</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>2</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>['21', '35']</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R207" t="n">
+        <v>2</v>
+      </c>
+      <c r="S207" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V207" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X207" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>7841234</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45879.77083333334</v>
+      </c>
+      <c r="F208" t="n">
+        <v>21</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>2</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>2</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['64', '88']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S208" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U208" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V208" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X208" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.73</v>
@@ -1568,7 +1568,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.09</v>
@@ -6146,7 +6146,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>1.36</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.3</v>
@@ -9634,7 +9634,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR42" t="n">
         <v>2.35</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.2</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.55</v>
@@ -13776,7 +13776,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR61" t="n">
         <v>1.62</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.27</v>
@@ -15738,7 +15738,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR70" t="n">
         <v>1.12</v>
@@ -16828,7 +16828,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17697,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.7</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.64</v>
@@ -20098,7 +20098,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -21624,7 +21624,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.2</v>
@@ -24455,10 +24455,10 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR110" t="n">
         <v>1.88</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.7</v>
@@ -26417,7 +26417,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.3</v>
@@ -27510,7 +27510,7 @@
         <v>2</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR124" t="n">
         <v>1.71</v>
@@ -28600,7 +28600,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR129" t="n">
         <v>1.48</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -30995,7 +30995,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.91</v>
@@ -32306,7 +32306,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR146" t="n">
         <v>1.42</v>
@@ -32524,7 +32524,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR147" t="n">
         <v>1.7</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.8</v>
@@ -34701,7 +34701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.91</v>
@@ -37102,7 +37102,7 @@
         <v>2</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR168" t="n">
         <v>1.8</v>
@@ -37320,7 +37320,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR169" t="n">
         <v>2.04</v>
@@ -40590,7 +40590,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR184" t="n">
         <v>1.97</v>
@@ -41026,7 +41026,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR186" t="n">
         <v>1.78</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.3</v>
@@ -41895,7 +41895,7 @@
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.82</v>
@@ -45622,16 +45622,16 @@
         <v>5</v>
       </c>
       <c r="AW207" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX207" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY207" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ207" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA207" t="n">
         <v>1</v>
@@ -45840,16 +45840,16 @@
         <v>2</v>
       </c>
       <c r="AW208" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AX208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY208" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AZ208" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA208" t="n">
         <v>5</v>
@@ -45898,6 +45898,442 @@
       </c>
       <c r="BP208" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>7841237</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45880.79166666666</v>
+      </c>
+      <c r="F209" t="n">
+        <v>21</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>4</v>
+      </c>
+      <c r="M209" t="n">
+        <v>2</v>
+      </c>
+      <c r="N209" t="n">
+        <v>6</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['-1', '-1', '-1', '-1']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S209" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U209" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V209" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X209" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>7841235</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45880.89583333334</v>
+      </c>
+      <c r="F210" t="n">
+        <v>21</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R210" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S210" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V210" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X210" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -44245,16 +44245,16 @@
         <v>3</v>
       </c>
       <c r="AW209">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX209">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY209">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ209">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA209">
         <v>4</v>
@@ -44451,16 +44451,16 @@
         <v>2</v>
       </c>
       <c r="AW210">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX210">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY210">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AZ210">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA210">
         <v>9</v>
@@ -44657,16 +44657,16 @@
         <v>3</v>
       </c>
       <c r="AW211">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX211">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY211">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AZ211">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA211">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3530,7 +3530,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.27</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.2</v>
@@ -8980,7 +8980,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.1</v>
@@ -11814,7 +11814,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR52" t="n">
         <v>2.13</v>
@@ -14430,7 +14430,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR64" t="n">
         <v>1.71</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.91</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -19662,7 +19662,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR88" t="n">
         <v>1.88</v>
@@ -22714,7 +22714,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR102" t="n">
         <v>1.16</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.09</v>
@@ -25984,7 +25984,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR117" t="n">
         <v>1.77</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.82</v>
@@ -29908,7 +29908,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR135" t="n">
         <v>1.76</v>
@@ -30559,7 +30559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.3</v>
@@ -33614,7 +33614,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR152" t="n">
         <v>1.68</v>
@@ -34047,7 +34047,7 @@
         <v>0.86</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.6</v>
@@ -38410,7 +38410,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR174" t="n">
         <v>1.58</v>
@@ -39061,7 +39061,7 @@
         <v>2</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.7</v>
@@ -42334,7 +42334,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR192" t="n">
         <v>1.42</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ198" t="n">
         <v>1</v>
@@ -46552,6 +46552,224 @@
       </c>
       <c r="BP211" t="n">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>7841250</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45883.89930555555</v>
+      </c>
+      <c r="F212" t="n">
+        <v>22</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['18', '88']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R212" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S212" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V212" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X212" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -46712,16 +46712,16 @@
         <v>4</v>
       </c>
       <c r="AW212" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ212" t="n">
         <v>9</v>
-      </c>
-      <c r="AX212" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY212" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ212" t="n">
-        <v>8</v>
       </c>
       <c r="BA212" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.91</v>
@@ -4838,7 +4838,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>2</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR46" t="n">
         <v>1.4</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.8</v>
@@ -13122,7 +13122,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.55</v>
@@ -18136,7 +18136,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR81" t="n">
         <v>1.26</v>
@@ -19441,7 +19441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.73</v>
@@ -22060,7 +22060,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR99" t="n">
         <v>2.15</v>
@@ -24673,7 +24673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.18</v>
@@ -24894,7 +24894,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR112" t="n">
         <v>1.67</v>
@@ -28597,7 +28597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
         <v>1</v>
@@ -29254,7 +29254,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR132" t="n">
         <v>1.56</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.1</v>
@@ -34050,7 +34050,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR154" t="n">
         <v>1.71</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.7</v>
@@ -39282,7 +39282,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR178" t="n">
         <v>1.57</v>
@@ -39497,7 +39497,7 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
         <v>1</v>
@@ -42988,7 +42988,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR195" t="n">
         <v>1.33</v>
@@ -43203,7 +43203,7 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.7</v>
@@ -46770,6 +46770,224 @@
       </c>
       <c r="BP212" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>7841248</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45884.83333333334</v>
+      </c>
+      <c r="F213" t="n">
+        <v>22</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="n">
+        <v>2</v>
+      </c>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['38', '55']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['79', '90+9']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R213" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S213" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V213" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X213" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.2</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>1</v>
@@ -4402,7 +4402,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.64</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.55</v>
@@ -8326,7 +8326,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.75</v>
@@ -9198,7 +9198,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR40" t="n">
         <v>1.69</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.09</v>
@@ -11596,7 +11596,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.3</v>
@@ -12901,10 +12901,10 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR57" t="n">
         <v>1.36</v>
@@ -13558,7 +13558,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR60" t="n">
         <v>1.65</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.09</v>
@@ -15735,7 +15735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -16392,7 +16392,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR73" t="n">
         <v>1.62</v>
@@ -16610,7 +16610,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.1</v>
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.18</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.27</v>
@@ -20534,7 +20534,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR92" t="n">
         <v>1.93</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.1</v>
@@ -21188,7 +21188,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR95" t="n">
         <v>1.8</v>
@@ -21406,7 +21406,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR96" t="n">
         <v>1.65</v>
@@ -24019,7 +24019,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.8</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.73</v>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.64</v>
@@ -25112,7 +25112,7 @@
         <v>1</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR113" t="n">
         <v>1.76</v>
@@ -25330,7 +25330,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -25545,7 +25545,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.2</v>
@@ -26202,7 +26202,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR118" t="n">
         <v>1.86</v>
@@ -27725,7 +27725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ125" t="n">
         <v>1</v>
@@ -28164,7 +28164,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR127" t="n">
         <v>1.32</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.8</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.75</v>
@@ -30780,7 +30780,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR139" t="n">
         <v>1.44</v>
@@ -31216,7 +31216,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31867,10 +31867,10 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR144" t="n">
         <v>1.2</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.73</v>
@@ -34483,10 +34483,10 @@
         <v>1.86</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR156" t="n">
         <v>1.76</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.1</v>
@@ -36666,7 +36666,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR166" t="n">
         <v>1.37</v>
@@ -37538,7 +37538,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR170" t="n">
         <v>1.35</v>
@@ -38189,7 +38189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ173" t="n">
         <v>0.91</v>
@@ -38625,7 +38625,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.55</v>
@@ -39064,7 +39064,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR177" t="n">
         <v>1.73</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -41462,7 +41462,7 @@
         <v>2</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR188" t="n">
         <v>1.82</v>
@@ -41898,7 +41898,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR190" t="n">
         <v>1.95</v>
@@ -42331,7 +42331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.75</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.91</v>
@@ -43206,7 +43206,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR196" t="n">
         <v>1.41</v>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ199" t="n">
         <v>1</v>
@@ -45604,7 +45604,7 @@
         <v>2</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR207" t="n">
         <v>1.81</v>
@@ -45822,7 +45822,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR208" t="n">
         <v>1.71</v>
@@ -46930,16 +46930,16 @@
         <v>5</v>
       </c>
       <c r="AW213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX213" t="n">
         <v>7</v>
       </c>
-      <c r="AX213" t="n">
+      <c r="AY213" t="n">
         <v>11</v>
       </c>
-      <c r="AY213" t="n">
+      <c r="AZ213" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ213" t="n">
-        <v>16</v>
       </c>
       <c r="BA213" t="n">
         <v>5</v>
@@ -46988,6 +46988,660 @@
       </c>
       <c r="BP213" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>7841245</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45885.66666666666</v>
+      </c>
+      <c r="F214" t="n">
+        <v>22</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" t="n">
+        <v>2</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S214" t="n">
+        <v>6</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U214" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V214" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X214" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>7841243</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45885.77083333334</v>
+      </c>
+      <c r="F215" t="n">
+        <v>22</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>2</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['1', '80']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S215" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V215" t="n">
+        <v>4</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X215" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>7841242</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>45885.85416666666</v>
+      </c>
+      <c r="F216" t="n">
+        <v>22</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
+        <v>2</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R216" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S216" t="n">
+        <v>5</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U216" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V216" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X216" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -46930,16 +46930,16 @@
         <v>5</v>
       </c>
       <c r="AW213" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX213" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY213" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ213" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA213" t="n">
         <v>5</v>
@@ -47148,16 +47148,16 @@
         <v>2</v>
       </c>
       <c r="AW214" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX214" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY214" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ214" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA214" t="n">
         <v>3</v>
@@ -47333,7 +47333,7 @@
         <v>1.4</v>
       </c>
       <c r="AL215" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AM215" t="n">
         <v>1.4</v>
@@ -47366,16 +47366,16 @@
         <v>3</v>
       </c>
       <c r="AW215" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX215" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY215" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ215" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA215" t="n">
         <v>1</v>
@@ -47584,16 +47584,16 @@
         <v>2</v>
       </c>
       <c r="AW216" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ216" t="n">
         <v>9</v>
-      </c>
-      <c r="AX216" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY216" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ216" t="n">
-        <v>8</v>
       </c>
       <c r="BA216" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -1601,10 +1601,10 @@
         <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
         <v>1.37</v>
@@ -4650,13 +4650,13 @@
         <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
         <v>1.58</v>
@@ -4871,10 +4871,10 @@
         <v>2</v>
       </c>
       <c r="BB20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>1.74</v>
@@ -5525,10 +5525,10 @@
         <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD23" t="n">
         <v>1.29</v>
@@ -6833,10 +6833,10 @@
         <v>3</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD29" t="n">
         <v>1.71</v>
@@ -7705,10 +7705,10 @@
         <v>5</v>
       </c>
       <c r="BB33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD33" t="n">
         <v>1.6</v>
@@ -9013,10 +9013,10 @@
         <v>1</v>
       </c>
       <c r="BB39" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC39" t="n">
         <v>13</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>14</v>
       </c>
       <c r="BD39" t="n">
         <v>1.79</v>
@@ -12501,10 +12501,10 @@
         <v>6</v>
       </c>
       <c r="BB55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD55" t="n">
         <v>1.82</v>
@@ -13373,10 +13373,10 @@
         <v>13</v>
       </c>
       <c r="BB59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD59" t="n">
         <v>1.54</v>
@@ -17076,13 +17076,13 @@
         <v>9</v>
       </c>
       <c r="BA76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB76" t="n">
         <v>1</v>
       </c>
       <c r="BC76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD76" t="n">
         <v>2.33</v>
@@ -19913,10 +19913,10 @@
         <v>1</v>
       </c>
       <c r="BB89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD89" t="n">
         <v>1.81</v>
@@ -21218,13 +21218,13 @@
         <v>8</v>
       </c>
       <c r="BA95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB95" t="n">
         <v>3</v>
       </c>
       <c r="BC95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD95" t="n">
         <v>1.62</v>
@@ -21439,10 +21439,10 @@
         <v>3</v>
       </c>
       <c r="BB96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD96" t="n">
         <v>1.79</v>
@@ -23837,10 +23837,10 @@
         <v>2</v>
       </c>
       <c r="BB107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD107" t="n">
         <v>1.6</v>
@@ -23919,10 +23919,10 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -24034,31 +24034,31 @@
         <v>2.9</v>
       </c>
       <c r="AU108" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW108" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AX108" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY108" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ108" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BA108" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB108" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC108" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BD108" t="n">
         <v>1.5</v>
@@ -24488,13 +24488,13 @@
         <v>13</v>
       </c>
       <c r="BA110" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BB110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC110" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BD110" t="n">
         <v>1.54</v>
@@ -25551,13 +25551,13 @@
         <v>1.2</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AS115" t="n">
         <v>1.36</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AU115" t="n">
         <v>12</v>
@@ -26017,10 +26017,10 @@
         <v>4</v>
       </c>
       <c r="BB117" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC117" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD117" t="n">
         <v>1.67</v>
@@ -27758,13 +27758,13 @@
         <v>21</v>
       </c>
       <c r="BA125" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC125" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD125" t="n">
         <v>1.9</v>
@@ -29696,10 +29696,10 @@
         <v>1.51</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="AU134" t="n">
         <v>1</v>
@@ -29911,13 +29911,13 @@
         <v>1.75</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AS135" t="n">
         <v>1.07</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="AU135" t="n">
         <v>4</v>
@@ -31682,13 +31682,13 @@
         <v>17</v>
       </c>
       <c r="BA143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB143" t="n">
         <v>5</v>
       </c>
       <c r="BC143" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD143" t="n">
         <v>1.49</v>
@@ -34274,10 +34274,10 @@
         <v>1.73</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AU155" t="n">
         <v>6</v>
@@ -34298,13 +34298,13 @@
         <v>20</v>
       </c>
       <c r="BA155" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB155" t="n">
         <v>6</v>
       </c>
       <c r="BC155" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD155" t="n">
         <v>1.73</v>
@@ -34489,13 +34489,13 @@
         <v>1.55</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AS156" t="n">
         <v>1.33</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="AU156" t="n">
         <v>3</v>
@@ -35173,10 +35173,10 @@
         <v>5</v>
       </c>
       <c r="BB159" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC159" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD159" t="n">
         <v>1.57</v>
@@ -36914,13 +36914,13 @@
         <v>13</v>
       </c>
       <c r="BA167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB167" t="n">
         <v>2</v>
       </c>
       <c r="BC167" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD167" t="n">
         <v>1.44</v>
@@ -37571,10 +37571,10 @@
         <v>1</v>
       </c>
       <c r="BB170" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC170" t="n">
         <v>7</v>
-      </c>
-      <c r="BC170" t="n">
-        <v>8</v>
       </c>
       <c r="BD170" t="n">
         <v>1.69</v>
@@ -37980,10 +37980,10 @@
         <v>1.62</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AT172" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AU172" t="n">
         <v>5</v>
@@ -38195,13 +38195,13 @@
         <v>0.91</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AS173" t="n">
         <v>1.35</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="AU173" t="n">
         <v>8</v>
@@ -39315,10 +39315,10 @@
         <v>2</v>
       </c>
       <c r="BB178" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD178" t="n">
         <v>1.58</v>
@@ -43454,13 +43454,13 @@
         <v>17</v>
       </c>
       <c r="BA197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB197" t="n">
         <v>6</v>
       </c>
       <c r="BC197" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD197" t="n">
         <v>1.9</v>
@@ -43863,13 +43863,13 @@
         <v>1</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AS199" t="n">
         <v>1.08</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AU199" t="n">
         <v>4</v>
@@ -43890,13 +43890,13 @@
         <v>7</v>
       </c>
       <c r="BA199" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB199" t="n">
         <v>2</v>
       </c>
       <c r="BC199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD199" t="n">
         <v>1.3</v>
@@ -44084,10 +44084,10 @@
         <v>1.53</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU200" t="n">
         <v>6</v>
@@ -47569,13 +47569,13 @@
         <v>0.83</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AS216" t="n">
         <v>1.34</v>
       </c>
       <c r="AT216" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AU216" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -47148,16 +47148,16 @@
         <v>2</v>
       </c>
       <c r="AW214" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX214" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY214" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ214" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA214" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.18</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.75</v>
@@ -3748,7 +3748,7 @@
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.18</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.83</v>
@@ -9416,7 +9416,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR41" t="n">
         <v>1.61</v>
@@ -11378,7 +11378,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR50" t="n">
         <v>1.42</v>
@@ -12250,7 +12250,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR54" t="n">
         <v>1.59</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.1</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.2</v>
@@ -15084,7 +15084,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR67" t="n">
         <v>2.09</v>
@@ -15956,7 +15956,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR71" t="n">
         <v>1.88</v>
@@ -16389,7 +16389,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.83</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.2</v>
@@ -18354,7 +18354,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR82" t="n">
         <v>1.73</v>
@@ -19226,7 +19226,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR86" t="n">
         <v>1.94</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.55</v>
@@ -22275,7 +22275,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.3</v>
@@ -23150,7 +23150,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR104" t="n">
         <v>1.54</v>
@@ -23368,7 +23368,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR105" t="n">
         <v>1.72</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.75</v>
@@ -26635,10 +26635,10 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR120" t="n">
         <v>1.53</v>
@@ -27728,7 +27728,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR125" t="n">
         <v>1.16</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.27</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.55</v>
@@ -30998,7 +30998,7 @@
         <v>1</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR140" t="n">
         <v>1.74</v>
@@ -31431,7 +31431,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.55</v>
@@ -32088,7 +32088,7 @@
         <v>2</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR145" t="n">
         <v>1.69</v>
@@ -34704,7 +34704,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR157" t="n">
         <v>1.89</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.2</v>
@@ -36227,7 +36227,7 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.2</v>
@@ -36884,7 +36884,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR167" t="n">
         <v>1.24</v>
@@ -38192,7 +38192,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR173" t="n">
         <v>1.72</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.27</v>
@@ -39500,7 +39500,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR179" t="n">
         <v>1.33</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.09</v>
@@ -42552,7 +42552,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR193" t="n">
         <v>1.22</v>
@@ -43421,7 +43421,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.55</v>
@@ -43860,7 +43860,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR199" t="n">
         <v>1.81</v>
@@ -45819,7 +45819,7 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.73</v>
@@ -47366,16 +47366,16 @@
         <v>3</v>
       </c>
       <c r="AW215" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX215" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY215" t="n">
         <v>7</v>
       </c>
-      <c r="AY215" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ215" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA215" t="n">
         <v>1</v>
@@ -47584,16 +47584,16 @@
         <v>2</v>
       </c>
       <c r="AW216" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX216" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY216" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ216" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA216" t="n">
         <v>8</v>
@@ -47642,6 +47642,442 @@
       </c>
       <c r="BP216" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>7841246</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45886.66666666666</v>
+      </c>
+      <c r="F217" t="n">
+        <v>22</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" t="n">
+        <v>2</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['20', '56']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R217" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U217" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V217" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X217" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>7841244</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>45886.77083333334</v>
+      </c>
+      <c r="F218" t="n">
+        <v>22</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>3</v>
+      </c>
+      <c r="N218" t="n">
+        <v>4</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>['21', '56', '90+9']</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S218" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X218" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -47148,16 +47148,16 @@
         <v>2</v>
       </c>
       <c r="AW214" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX214" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY214" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ214" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA214" t="n">
         <v>3</v>
@@ -47366,16 +47366,16 @@
         <v>3</v>
       </c>
       <c r="AW215" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX215" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY215" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ215" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA215" t="n">
         <v>1</v>
@@ -47584,16 +47584,16 @@
         <v>2</v>
       </c>
       <c r="AW216" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ216" t="n">
         <v>9</v>
-      </c>
-      <c r="AX216" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY216" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ216" t="n">
-        <v>8</v>
       </c>
       <c r="BA216" t="n">
         <v>8</v>
@@ -47802,16 +47802,16 @@
         <v>3</v>
       </c>
       <c r="AW217" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX217" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AY217" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ217" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BA217" t="n">
         <v>7</v>
@@ -48020,16 +48020,16 @@
         <v>4</v>
       </c>
       <c r="AW218" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX218" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY218" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ218" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA218" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -47802,16 +47802,16 @@
         <v>3</v>
       </c>
       <c r="AW217" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX217" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AY217" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ217" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BA217" t="n">
         <v>7</v>
@@ -48020,16 +48020,16 @@
         <v>4</v>
       </c>
       <c r="AW218" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AX218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY218" t="n">
         <v>10</v>
       </c>
-      <c r="AY218" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ218" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA218" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP218"/>
+  <dimension ref="A1:BP219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.83</v>
@@ -4620,7 +4620,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -8108,7 +8108,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR35" t="n">
         <v>1.53</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.08</v>
@@ -11160,7 +11160,7 @@
         <v>1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.92</v>
@@ -15520,7 +15520,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.3</v>
@@ -19880,7 +19880,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR89" t="n">
         <v>1.18</v>
@@ -22057,7 +22057,7 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.64</v>
@@ -23586,7 +23586,7 @@
         <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ121" t="n">
         <v>1</v>
@@ -27946,7 +27946,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR126" t="n">
         <v>1.86</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.73</v>
@@ -31434,7 +31434,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR142" t="n">
         <v>1.81</v>
@@ -35794,7 +35794,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR162" t="n">
         <v>1.61</v>
@@ -37317,7 +37317,7 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.1</v>
@@ -38628,7 +38628,7 @@
         <v>2</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR175" t="n">
         <v>1.41</v>
@@ -40587,7 +40587,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ184" t="n">
         <v>1</v>
@@ -43424,7 +43424,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -45383,7 +45383,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.1</v>
@@ -48078,6 +48078,224 @@
       </c>
       <c r="BP218" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>7841251</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>45887.79166666666</v>
+      </c>
+      <c r="F219" t="n">
+        <v>22</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R219" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S219" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V219" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X219" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3094,7 +3094,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.75</v>
@@ -8762,7 +8762,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.27</v>
@@ -12686,7 +12686,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ61" t="n">
         <v>1</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.1</v>
@@ -17482,7 +17482,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -21403,7 +21403,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.83</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR101" t="n">
         <v>1.68</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.73</v>
@@ -27292,7 +27292,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR123" t="n">
         <v>1.69</v>
@@ -30341,7 +30341,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.2</v>
@@ -33396,7 +33396,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR151" t="n">
         <v>1.4</v>
@@ -35137,7 +35137,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ159" t="n">
         <v>1</v>
@@ -36230,7 +36230,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR164" t="n">
         <v>1.82</v>
@@ -38407,7 +38407,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.75</v>
@@ -39718,7 +39718,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR180" t="n">
         <v>1.29</v>
@@ -42770,7 +42770,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR194" t="n">
         <v>1.58</v>
@@ -44075,7 +44075,7 @@
         <v>0.78</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.8</v>
@@ -47802,16 +47802,16 @@
         <v>3</v>
       </c>
       <c r="AW217" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX217" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AY217" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ217" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="BA217" t="n">
         <v>7</v>
@@ -48020,16 +48020,16 @@
         <v>4</v>
       </c>
       <c r="AW218" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX218" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY218" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ218" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA218" t="n">
         <v>6</v>
@@ -48238,16 +48238,16 @@
         <v>4</v>
       </c>
       <c r="AW219" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX219" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY219" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ219" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA219" t="n">
         <v>3</v>
@@ -48296,6 +48296,224 @@
       </c>
       <c r="BP219" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>7841249</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>45887.875</v>
+      </c>
+      <c r="F220" t="n">
+        <v>22</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R220" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S220" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V220" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X220" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP220"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.55</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.92</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.64</v>
@@ -15314,7 +15314,7 @@
         <v>2.3</v>
       </c>
       <c r="AU68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV68" t="n">
         <v>4</v>
@@ -15323,13 +15323,13 @@
         <v>7</v>
       </c>
       <c r="AX68" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ68" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA68" t="n">
         <v>7</v>
@@ -15532,22 +15532,22 @@
         <v>3.35</v>
       </c>
       <c r="AU69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX69" t="n">
         <v>5</v>
       </c>
-      <c r="AV69" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW69" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX69" t="n">
-        <v>10</v>
-      </c>
       <c r="AY69" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ69" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA69" t="n">
         <v>7</v>
@@ -15756,16 +15756,16 @@
         <v>5</v>
       </c>
       <c r="AW70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AY70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ70" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA70" t="n">
         <v>5</v>
@@ -15971,19 +15971,19 @@
         <v>4</v>
       </c>
       <c r="AV71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW71" t="n">
         <v>5</v>
-      </c>
-      <c r="AW71" t="n">
-        <v>11</v>
       </c>
       <c r="AX71" t="n">
         <v>5</v>
       </c>
       <c r="AY71" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA71" t="n">
         <v>7</v>
@@ -16189,19 +16189,19 @@
         <v>6</v>
       </c>
       <c r="AV72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW72" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AX72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AY72" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ72" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA72" t="n">
         <v>3</v>
@@ -16410,16 +16410,16 @@
         <v>1</v>
       </c>
       <c r="AW73" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AX73" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AY73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AZ73" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.73</v>
@@ -16628,13 +16628,13 @@
         <v>1</v>
       </c>
       <c r="AW74" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX74" t="n">
         <v>3</v>
       </c>
       <c r="AY74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ74" t="n">
         <v>4</v>
@@ -16840,22 +16840,22 @@
         <v>3</v>
       </c>
       <c r="AU75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX75" t="n">
         <v>4</v>
       </c>
-      <c r="AV75" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW75" t="n">
+      <c r="AY75" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ75" t="n">
         <v>6</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>8</v>
       </c>
       <c r="BA75" t="n">
         <v>5</v>
@@ -17058,31 +17058,31 @@
         <v>2.73</v>
       </c>
       <c r="AU76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ76" t="n">
         <v>8</v>
       </c>
-      <c r="AV76" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>9</v>
-      </c>
       <c r="BA76" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC76" t="n">
         <v>11</v>
-      </c>
-      <c r="BB76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>12</v>
       </c>
       <c r="BD76" t="n">
         <v>2.33</v>
@@ -17276,22 +17276,22 @@
         <v>2.79</v>
       </c>
       <c r="AU77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW77" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AX77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY77" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AZ77" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA77" t="n">
         <v>8</v>
@@ -17494,22 +17494,22 @@
         <v>2.67</v>
       </c>
       <c r="AU78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW78" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ78" t="n">
         <v>12</v>
-      </c>
-      <c r="AX78" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY78" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ78" t="n">
-        <v>15</v>
       </c>
       <c r="BA78" t="n">
         <v>1</v>
@@ -17718,16 +17718,16 @@
         <v>3</v>
       </c>
       <c r="AW79" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AX79" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ79" t="n">
         <v>10</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>13</v>
       </c>
       <c r="BA79" t="n">
         <v>5</v>
@@ -17930,22 +17930,22 @@
         <v>2.89</v>
       </c>
       <c r="AU80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AX80" t="n">
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA80" t="n">
         <v>7</v>
@@ -18154,16 +18154,16 @@
         <v>10</v>
       </c>
       <c r="AW81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ81" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA81" t="n">
         <v>9</v>
@@ -18366,22 +18366,22 @@
         <v>2.82</v>
       </c>
       <c r="AU82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV82" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX82" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ82" t="n">
         <v>14</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>22</v>
       </c>
       <c r="BA82" t="n">
         <v>4</v>
@@ -18578,25 +18578,25 @@
         <v>1.51</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AU83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV83" t="n">
         <v>2</v>
       </c>
       <c r="AW83" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX83" t="n">
         <v>5</v>
       </c>
       <c r="AY83" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ83" t="n">
         <v>7</v>
@@ -18793,31 +18793,31 @@
         <v>0.27</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AS84" t="n">
         <v>1.23</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AU84" t="n">
         <v>4</v>
       </c>
       <c r="AV84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ84" t="n">
         <v>10</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>15</v>
       </c>
       <c r="BA84" t="n">
         <v>3</v>
@@ -19020,22 +19020,22 @@
         <v>3.1</v>
       </c>
       <c r="AU85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV85" t="n">
         <v>2</v>
       </c>
       <c r="AW85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY85" t="n">
         <v>15</v>
       </c>
-      <c r="AX85" t="n">
+      <c r="AZ85" t="n">
         <v>13</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>15</v>
       </c>
       <c r="BA85" t="n">
         <v>5</v>
@@ -19232,10 +19232,10 @@
         <v>1.94</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AU86" t="n">
         <v>6</v>
@@ -19244,16 +19244,16 @@
         <v>4</v>
       </c>
       <c r="AW86" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY86" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA86" t="n">
         <v>8</v>
@@ -19447,31 +19447,31 @@
         <v>0.73</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AS87" t="n">
         <v>1.41</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV87" t="n">
         <v>1</v>
       </c>
       <c r="AW87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AY87" t="n">
         <v>11</v>
       </c>
       <c r="AZ87" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BA87" t="n">
         <v>4</v>
@@ -19680,16 +19680,16 @@
         <v>4</v>
       </c>
       <c r="AW88" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY88" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA88" t="n">
         <v>9</v>
@@ -19883,31 +19883,31 @@
         <v>0.75</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AU89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX89" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA89" t="n">
         <v>1</v>
@@ -20104,28 +20104,28 @@
         <v>1.55</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AT90" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="AU90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV90" t="n">
         <v>2</v>
       </c>
       <c r="AW90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ90" t="n">
         <v>8</v>
-      </c>
-      <c r="AX90" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY90" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ90" t="n">
-        <v>7</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20319,31 +20319,31 @@
         <v>0.8</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS91" t="n">
         <v>1.45</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AU91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV91" t="n">
         <v>3</v>
       </c>
       <c r="AW91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY91" t="n">
         <v>7</v>
       </c>
-      <c r="AX91" t="n">
+      <c r="AZ91" t="n">
         <v>8</v>
-      </c>
-      <c r="AY91" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ91" t="n">
-        <v>11</v>
       </c>
       <c r="BA91" t="n">
         <v>6</v>
@@ -20537,31 +20537,31 @@
         <v>0.73</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AS92" t="n">
         <v>0.84</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="AU92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW92" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AX92" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY92" t="n">
         <v>9</v>
       </c>
-      <c r="AY92" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ92" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA92" t="n">
         <v>2</v>
@@ -20755,13 +20755,13 @@
         <v>1.1</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AU93" t="n">
         <v>7</v>
@@ -20770,13 +20770,13 @@
         <v>1</v>
       </c>
       <c r="AW93" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX93" t="n">
         <v>6</v>
       </c>
       <c r="AY93" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ93" t="n">
         <v>7</v>
@@ -20973,28 +20973,28 @@
         <v>1</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AU94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY94" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ94" t="n">
         <v>8</v>
@@ -21191,13 +21191,13 @@
         <v>1.55</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AU95" t="n">
         <v>5</v>
@@ -21206,16 +21206,16 @@
         <v>5</v>
       </c>
       <c r="AW95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA95" t="n">
         <v>7</v>
@@ -21324,7 +21324,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>['12', '87']</t>
+          <t>['13', '87']</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -21409,31 +21409,31 @@
         <v>0.83</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="AU96" t="n">
         <v>1</v>
       </c>
       <c r="AV96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY96" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ96" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA96" t="n">
         <v>3</v>
@@ -21621,19 +21621,19 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.1</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="AU97" t="n">
         <v>4</v>
@@ -21642,16 +21642,16 @@
         <v>4</v>
       </c>
       <c r="AW97" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY97" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA97" t="n">
         <v>1</v>
@@ -21755,7 +21755,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>['9', '62']</t>
+          <t>['10', '61']</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -21845,31 +21845,31 @@
         <v>1.2</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AU98" t="n">
         <v>4</v>
       </c>
       <c r="AV98" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AW98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX98" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AY98" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ98" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA98" t="n">
         <v>5</v>
@@ -22063,31 +22063,31 @@
         <v>0.64</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.85</v>
+        <v>3.61</v>
       </c>
       <c r="AU99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY99" t="n">
         <v>7</v>
       </c>
-      <c r="AV99" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW99" t="n">
+      <c r="AZ99" t="n">
         <v>6</v>
-      </c>
-      <c r="AX99" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY99" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ99" t="n">
-        <v>10</v>
       </c>
       <c r="BA99" t="n">
         <v>6</v>
@@ -22281,13 +22281,13 @@
         <v>0.3</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AS100" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AU100" t="n">
         <v>5</v>
@@ -22296,16 +22296,16 @@
         <v>2</v>
       </c>
       <c r="AW100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY100" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ100" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA100" t="n">
         <v>9</v>
@@ -22499,31 +22499,31 @@
         <v>1.18</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS101" t="n">
         <v>1.18</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="AU101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ101" t="n">
         <v>6</v>
-      </c>
-      <c r="AW101" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX101" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY101" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ101" t="n">
-        <v>8</v>
       </c>
       <c r="BA101" t="n">
         <v>11</v>
@@ -22717,31 +22717,31 @@
         <v>1.75</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AU102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW102" t="n">
         <v>4</v>
       </c>
       <c r="AX102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA102" t="n">
         <v>3</v>
@@ -22935,13 +22935,13 @@
         <v>1.09</v>
       </c>
       <c r="AR103" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="AU103" t="n">
         <v>4</v>
@@ -23153,13 +23153,13 @@
         <v>0.92</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU104" t="n">
         <v>6</v>
@@ -23168,16 +23168,16 @@
         <v>3</v>
       </c>
       <c r="AW104" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY104" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA104" t="n">
         <v>9</v>
@@ -23371,31 +23371,31 @@
         <v>1.08</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.04</v>
+        <v>2.72</v>
       </c>
       <c r="AU105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV105" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW105" t="n">
         <v>5</v>
       </c>
-      <c r="AW105" t="n">
-        <v>12</v>
-      </c>
       <c r="AX105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY105" t="n">
         <v>9</v>
       </c>
-      <c r="AY105" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ105" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA105" t="n">
         <v>9</v>
@@ -23589,31 +23589,31 @@
         <v>0.75</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AU106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX106" t="n">
         <v>8</v>
       </c>
-      <c r="AV106" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW106" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX106" t="n">
-        <v>11</v>
-      </c>
       <c r="AY106" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ106" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23807,40 +23807,40 @@
         <v>0.27</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="AU107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX107" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB107" t="n">
         <v>6</v>
       </c>
-      <c r="AY107" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ107" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA107" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB107" t="n">
-        <v>7</v>
-      </c>
       <c r="BC107" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD107" t="n">
         <v>1.6</v>
@@ -24025,31 +24025,31 @@
         <v>0.8</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AU108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW108" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY108" t="n">
         <v>11</v>
       </c>
-      <c r="AX108" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY108" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ108" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA108" t="n">
         <v>5</v>
@@ -24118,7 +24118,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>45816.85416666666</v>
+        <v>45816.79166666666</v>
       </c>
       <c r="F109" t="n">
         <v>11</v>
@@ -24243,31 +24243,31 @@
         <v>0.73</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="AU109" t="n">
         <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW109" t="n">
         <v>8</v>
       </c>
       <c r="AX109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY109" t="n">
         <v>11</v>
       </c>
       <c r="AZ109" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA109" t="n">
         <v>6</v>
@@ -24461,31 +24461,31 @@
         <v>1</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AU110" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV110" t="n">
         <v>0</v>
       </c>
       <c r="AW110" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY110" t="n">
         <v>13</v>
       </c>
-      <c r="AX110" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY110" t="n">
-        <v>18</v>
-      </c>
       <c r="AZ110" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA110" t="n">
         <v>16</v>
@@ -24679,31 +24679,31 @@
         <v>1.18</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AU111" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" t="n">
         <v>4</v>
       </c>
-      <c r="AV111" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW111" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX111" t="n">
-        <v>10</v>
-      </c>
       <c r="AY111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ111" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BA111" t="n">
         <v>2</v>
@@ -24775,7 +24775,7 @@
         <v>45821.79166666666</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -24897,31 +24897,31 @@
         <v>0.64</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="AU112" t="n">
         <v>1</v>
       </c>
       <c r="AV112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW112" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY112" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ112" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA112" t="n">
         <v>4</v>
@@ -24993,7 +24993,7 @@
         <v>45821.89930555555</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -25115,13 +25115,13 @@
         <v>0.73</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="AU113" t="n">
         <v>3</v>
@@ -25130,16 +25130,16 @@
         <v>6</v>
       </c>
       <c r="AW113" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AX113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY113" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ113" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA113" t="n">
         <v>8</v>
@@ -25211,7 +25211,7 @@
         <v>45822.66666666666</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -25333,31 +25333,31 @@
         <v>1.55</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AU114" t="n">
         <v>4</v>
       </c>
       <c r="AV114" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW114" t="n">
         <v>7</v>
       </c>
-      <c r="AW114" t="n">
+      <c r="AX114" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY114" t="n">
         <v>11</v>
       </c>
-      <c r="AX114" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY114" t="n">
+      <c r="AZ114" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ114" t="n">
-        <v>17</v>
       </c>
       <c r="BA114" t="n">
         <v>1</v>
@@ -25429,7 +25429,7 @@
         <v>45822.77083333334</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -25551,31 +25551,31 @@
         <v>1.2</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="AU115" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV115" t="n">
         <v>3</v>
       </c>
       <c r="AW115" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ115" t="n">
         <v>5</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>8</v>
       </c>
       <c r="BA115" t="n">
         <v>13</v>
@@ -25647,7 +25647,7 @@
         <v>45822.85416666666</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -25769,13 +25769,13 @@
         <v>0.73</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="AU116" t="n">
         <v>5</v>
@@ -25784,16 +25784,16 @@
         <v>3</v>
       </c>
       <c r="AW116" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX116" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ116" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA116" t="n">
         <v>5</v>
@@ -25865,7 +25865,7 @@
         <v>45823.66666666666</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -25987,31 +25987,31 @@
         <v>1.75</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="AU117" t="n">
         <v>4</v>
       </c>
       <c r="AV117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY117" t="n">
         <v>9</v>
       </c>
-      <c r="AX117" t="n">
+      <c r="AZ117" t="n">
         <v>7</v>
-      </c>
-      <c r="AY117" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ117" t="n">
-        <v>8</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26083,7 +26083,7 @@
         <v>45823.66666666666</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -26205,31 +26205,31 @@
         <v>0.83</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.39</v>
+        <v>3.24</v>
       </c>
       <c r="AU118" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV118" t="n">
         <v>9</v>
       </c>
       <c r="AW118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY118" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA118" t="n">
         <v>2</v>
@@ -26301,7 +26301,7 @@
         <v>45823.85416666666</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -26423,31 +26423,31 @@
         <v>0.3</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AS119" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AU119" t="n">
         <v>11</v>
       </c>
       <c r="AV119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW119" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ119" t="n">
         <v>8</v>
-      </c>
-      <c r="AX119" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY119" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ119" t="n">
-        <v>11</v>
       </c>
       <c r="BA119" t="n">
         <v>5</v>
@@ -26519,7 +26519,7 @@
         <v>45824.79166666666</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -26641,31 +26641,31 @@
         <v>1.08</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AU120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY120" t="n">
         <v>6</v>
       </c>
-      <c r="AW120" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX120" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY120" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ120" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA120" t="n">
         <v>1</v>
@@ -26737,7 +26737,7 @@
         <v>45825.8125</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -26859,31 +26859,31 @@
         <v>1</v>
       </c>
       <c r="AR121" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.31</v>
+        <v>2.91</v>
       </c>
       <c r="AU121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW121" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY121" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA121" t="n">
         <v>12</v>
@@ -26955,7 +26955,7 @@
         <v>45828.79166666666</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -27077,31 +27077,31 @@
         <v>1.09</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AU122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW122" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY122" t="n">
         <v>17</v>
       </c>
-      <c r="AX122" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY122" t="n">
-        <v>23</v>
-      </c>
       <c r="AZ122" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA122" t="n">
         <v>13</v>
@@ -27173,7 +27173,7 @@
         <v>45828.89930555555</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -27295,13 +27295,13 @@
         <v>1.18</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="AU123" t="n">
         <v>2</v>
@@ -27310,16 +27310,16 @@
         <v>3</v>
       </c>
       <c r="AW123" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY123" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA123" t="n">
         <v>7</v>
@@ -27391,7 +27391,7 @@
         <v>45829.66666666666</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -27513,31 +27513,31 @@
         <v>1.1</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="AU124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV124" t="n">
         <v>4</v>
       </c>
       <c r="AW124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX124" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY124" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA124" t="n">
         <v>4</v>
@@ -27609,7 +27609,7 @@
         <v>45829.77083333334</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -27731,40 +27731,40 @@
         <v>0.92</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AS125" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AU125" t="n">
         <v>2</v>
       </c>
       <c r="AV125" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA125" t="n">
         <v>7</v>
       </c>
-      <c r="AW125" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX125" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY125" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ125" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA125" t="n">
-        <v>8</v>
-      </c>
       <c r="BB125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC125" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD125" t="n">
         <v>1.9</v>
@@ -27827,7 +27827,7 @@
         <v>45829.85416666666</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -27949,13 +27949,13 @@
         <v>0.75</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AU126" t="n">
         <v>2</v>
@@ -27964,16 +27964,16 @@
         <v>5</v>
       </c>
       <c r="AW126" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX126" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AY126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ126" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA126" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         <v>45830.66666666666</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -28167,31 +28167,31 @@
         <v>0.83</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AU127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV127" t="n">
         <v>2</v>
       </c>
       <c r="AW127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY127" t="n">
         <v>8</v>
       </c>
-      <c r="AX127" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY127" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ127" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA127" t="n">
         <v>5</v>
@@ -28263,7 +28263,7 @@
         <v>45830.66666666666</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -28385,13 +28385,13 @@
         <v>0.27</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AT128" t="n">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AU128" t="n">
         <v>6</v>
@@ -28400,13 +28400,13 @@
         <v>0</v>
       </c>
       <c r="AW128" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX128" t="n">
         <v>6</v>
       </c>
       <c r="AY128" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ128" t="n">
         <v>6</v>
@@ -28481,7 +28481,7 @@
         <v>45830.75</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="Q129" t="n">
@@ -28603,31 +28603,31 @@
         <v>1</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="AU129" t="n">
         <v>2</v>
       </c>
       <c r="AV129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW129" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ129" t="n">
         <v>8</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>13</v>
       </c>
       <c r="BA129" t="n">
         <v>8</v>
@@ -28699,7 +28699,7 @@
         <v>45831.79166666666</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -28815,37 +28815,37 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.1</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AU130" t="n">
         <v>5</v>
       </c>
       <c r="AV130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW130" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX130" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ130" t="n">
         <v>10</v>
-      </c>
-      <c r="AY130" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ130" t="n">
-        <v>12</v>
       </c>
       <c r="BA130" t="n">
         <v>2</v>
@@ -28917,7 +28917,7 @@
         <v>45831.875</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -29039,31 +29039,31 @@
         <v>1.18</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AU131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV131" t="n">
         <v>4</v>
       </c>
       <c r="AW131" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY131" t="n">
         <v>10</v>
       </c>
-      <c r="AX131" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY131" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ131" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="BA131" t="n">
         <v>4</v>
@@ -29135,7 +29135,7 @@
         <v>45834.89930555555</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -29257,31 +29257,31 @@
         <v>0.64</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="AU132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW132" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AX132" t="n">
         <v>6</v>
       </c>
       <c r="AY132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AZ132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA132" t="n">
         <v>14</v>
@@ -29353,7 +29353,7 @@
         <v>45835.85416666666</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -29475,31 +29475,31 @@
         <v>1</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AU133" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW133" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX133" t="n">
         <v>4</v>
       </c>
       <c r="AY133" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA133" t="n">
         <v>6</v>
@@ -29571,7 +29571,7 @@
         <v>45836.66666666666</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -29693,13 +29693,13 @@
         <v>0.8</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU134" t="n">
         <v>1</v>
@@ -29708,16 +29708,16 @@
         <v>3</v>
       </c>
       <c r="AW134" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX134" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY134" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AZ134" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA134" t="n">
         <v>5</v>
@@ -29789,7 +29789,7 @@
         <v>45836.77083333334</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -29911,28 +29911,28 @@
         <v>1.75</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AU135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV135" t="n">
         <v>4</v>
       </c>
-      <c r="AV135" t="n">
-        <v>5</v>
-      </c>
       <c r="AW135" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY135" t="n">
         <v>15</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>19</v>
       </c>
       <c r="AZ135" t="n">
         <v>8</v>
@@ -30007,7 +30007,7 @@
         <v>45837.66666666666</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -30129,31 +30129,31 @@
         <v>0.73</v>
       </c>
       <c r="AR136" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.37</v>
+        <v>2.92</v>
       </c>
       <c r="AU136" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW136" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY136" t="n">
         <v>12</v>
       </c>
-      <c r="AX136" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY136" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ136" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30225,7 +30225,7 @@
         <v>45837.66666666666</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -30347,13 +30347,13 @@
         <v>1.2</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="AU137" t="n">
         <v>9</v>
@@ -30362,13 +30362,13 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX137" t="n">
         <v>3</v>
       </c>
       <c r="AY137" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AZ137" t="n">
         <v>6</v>
@@ -30443,7 +30443,7 @@
         <v>45837.79166666666</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -30565,31 +30565,31 @@
         <v>0.3</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="AU138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX138" t="n">
         <v>4</v>
       </c>
-      <c r="AV138" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW138" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX138" t="n">
-        <v>6</v>
-      </c>
       <c r="AY138" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ138" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA138" t="n">
         <v>6</v>
@@ -30661,7 +30661,7 @@
         <v>45837.79166666666</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -30783,31 +30783,31 @@
         <v>1.55</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="AU139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW139" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX139" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY139" t="n">
         <v>8</v>
       </c>
       <c r="AZ139" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA139" t="n">
         <v>5</v>
@@ -30879,7 +30879,7 @@
         <v>45838.79166666666</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -31001,13 +31001,13 @@
         <v>1.08</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="AU140" t="n">
         <v>5</v>
@@ -31016,16 +31016,16 @@
         <v>2</v>
       </c>
       <c r="AW140" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX140" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY140" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA140" t="n">
         <v>5</v>
@@ -31097,7 +31097,7 @@
         <v>45838.875</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -31219,31 +31219,31 @@
         <v>0.73</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.07</v>
+        <v>0.96</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="AU141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW141" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY141" t="n">
         <v>12</v>
       </c>
-      <c r="AX141" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY141" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ141" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA141" t="n">
         <v>5</v>
@@ -31315,7 +31315,7 @@
         <v>45841.89930555555</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -31437,31 +31437,31 @@
         <v>0.75</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="AU142" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV142" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW142" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AY142" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ142" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ142" t="n">
-        <v>21</v>
       </c>
       <c r="BA142" t="n">
         <v>2</v>
@@ -31533,7 +31533,7 @@
         <v>45842.79166666666</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -31655,31 +31655,31 @@
         <v>0.27</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AU143" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV143" t="n">
         <v>7</v>
       </c>
       <c r="AW143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX143" t="n">
         <v>7</v>
       </c>
-      <c r="AX143" t="n">
-        <v>10</v>
-      </c>
       <c r="AY143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ143" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA143" t="n">
         <v>3</v>
@@ -31751,7 +31751,7 @@
         <v>45843.66666666666</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -31873,31 +31873,31 @@
         <v>0.83</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="AU144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW144" t="n">
         <v>4</v>
       </c>
-      <c r="AW144" t="n">
-        <v>5</v>
-      </c>
       <c r="AX144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ144" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA144" t="n">
         <v>7</v>
@@ -31969,7 +31969,7 @@
         <v>45843.8125</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -32091,31 +32091,31 @@
         <v>0.92</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="AU145" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AV145" t="n">
         <v>1</v>
       </c>
       <c r="AW145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY145" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ145" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA145" t="n">
         <v>2</v>
@@ -32187,7 +32187,7 @@
         <v>45843.85416666666</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -32309,31 +32309,31 @@
         <v>1.1</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AU146" t="n">
         <v>1</v>
       </c>
       <c r="AV146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY146" t="n">
         <v>7</v>
       </c>
-      <c r="AW146" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX146" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY146" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ146" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BA146" t="n">
         <v>3</v>
@@ -32405,7 +32405,7 @@
         <v>45844.66666666666</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -32527,31 +32527,31 @@
         <v>1</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="AU147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV147" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW147" t="n">
         <v>8</v>
       </c>
-      <c r="AW147" t="n">
-        <v>12</v>
-      </c>
       <c r="AX147" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY147" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ147" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA147" t="n">
         <v>7</v>
@@ -32623,7 +32623,7 @@
         <v>45844.77083333334</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -32745,13 +32745,13 @@
         <v>1.1</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AU148" t="n">
         <v>6</v>
@@ -32841,7 +32841,7 @@
         <v>45845.79166666666</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -32957,37 +32957,37 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.09</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="AU149" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV149" t="n">
         <v>6</v>
       </c>
       <c r="AW149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX149" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY149" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ149" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA149" t="n">
         <v>1</v>
@@ -33059,7 +33059,7 @@
         <v>45845.875</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -33181,31 +33181,31 @@
         <v>1.18</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.84</v>
+        <v>2.43</v>
       </c>
       <c r="AU150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV150" t="n">
         <v>6</v>
       </c>
       <c r="AW150" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AX150" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY150" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ150" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA150" t="n">
         <v>8</v>
@@ -33277,7 +33277,7 @@
         <v>45846.8125</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -33399,31 +33399,31 @@
         <v>1.18</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="AU151" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV151" t="n">
         <v>2</v>
       </c>
       <c r="AW151" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX151" t="n">
         <v>8</v>
-      </c>
-      <c r="AX151" t="n">
-        <v>13</v>
       </c>
       <c r="AY151" t="n">
         <v>10</v>
       </c>
       <c r="AZ151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA151" t="n">
         <v>8</v>
@@ -33495,7 +33495,7 @@
         <v>45848.89930555555</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -33617,31 +33617,31 @@
         <v>1.75</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="AU152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV152" t="n">
         <v>3</v>
       </c>
       <c r="AW152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY152" t="n">
         <v>20</v>
       </c>
-      <c r="AX152" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY152" t="n">
-        <v>31</v>
-      </c>
       <c r="AZ152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA152" t="n">
         <v>10</v>
@@ -33713,7 +33713,7 @@
         <v>45849.79166666666</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -33835,13 +33835,13 @@
         <v>0.73</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AU153" t="n">
         <v>5</v>
@@ -33850,16 +33850,16 @@
         <v>3</v>
       </c>
       <c r="AW153" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY153" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ153" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA153" t="n">
         <v>5</v>
@@ -33931,7 +33931,7 @@
         <v>45850.66666666666</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -34053,31 +34053,31 @@
         <v>0.64</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AU154" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV154" t="n">
         <v>7</v>
       </c>
       <c r="AW154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX154" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY154" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ154" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA154" t="n">
         <v>2</v>
@@ -34149,7 +34149,7 @@
         <v>45850.77083333334</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -34271,31 +34271,31 @@
         <v>0.8</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.07</v>
+        <v>2.71</v>
       </c>
       <c r="AU155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV155" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY155" t="n">
         <v>9</v>
       </c>
-      <c r="AW155" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ155" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA155" t="n">
         <v>11</v>
@@ -34367,7 +34367,7 @@
         <v>45850.85416666666</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="Q156" t="n">
@@ -34489,31 +34489,31 @@
         <v>1.55</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.03</v>
+        <v>2.81</v>
       </c>
       <c r="AU156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX156" t="n">
         <v>3</v>
       </c>
-      <c r="AV156" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW156" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX156" t="n">
-        <v>2</v>
-      </c>
       <c r="AY156" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AZ156" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA156" t="n">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>45851.66666666666</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -34707,31 +34707,31 @@
         <v>1.08</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU157" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV157" t="n">
         <v>3</v>
       </c>
       <c r="AW157" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AX157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY157" t="n">
         <v>9</v>
       </c>
-      <c r="AY157" t="n">
-        <v>20</v>
-      </c>
       <c r="AZ157" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA157" t="n">
         <v>12</v>
@@ -34803,7 +34803,7 @@
         <v>45851.77083333334</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -34925,13 +34925,13 @@
         <v>1.2</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AU158" t="n">
         <v>8</v>
@@ -34940,16 +34940,16 @@
         <v>3</v>
       </c>
       <c r="AW158" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX158" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY158" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ158" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA158" t="n">
         <v>6</v>
@@ -35021,7 +35021,7 @@
         <v>45852.79166666666</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -35143,31 +35143,31 @@
         <v>1</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="AU159" t="n">
         <v>7</v>
       </c>
       <c r="AV159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX159" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ159" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BA159" t="n">
         <v>5</v>
@@ -35239,7 +35239,7 @@
         <v>45852.89583333334</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -35361,13 +35361,13 @@
         <v>0.27</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AU160" t="n">
         <v>2</v>
@@ -35457,7 +35457,7 @@
         <v>45853.8125</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -35579,31 +35579,31 @@
         <v>0.3</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="AU161" t="n">
         <v>4</v>
       </c>
       <c r="AV161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX161" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY161" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ161" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA161" t="n">
         <v>1</v>
@@ -35675,7 +35675,7 @@
         <v>45855.8125</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -35791,37 +35791,37 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.75</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AU162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV162" t="n">
         <v>2</v>
       </c>
       <c r="AW162" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY162" t="n">
         <v>15</v>
       </c>
-      <c r="AX162" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY162" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA162" t="n">
         <v>5</v>
@@ -35893,7 +35893,7 @@
         <v>45855.89930555555</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -36015,13 +36015,13 @@
         <v>1.1</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AU163" t="n">
         <v>2</v>
@@ -36030,16 +36030,16 @@
         <v>4</v>
       </c>
       <c r="AW163" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX163" t="n">
         <v>8</v>
       </c>
-      <c r="AX163" t="n">
-        <v>15</v>
-      </c>
       <c r="AY163" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ163" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA163" t="n">
         <v>5</v>
@@ -36111,7 +36111,7 @@
         <v>45856.79166666666</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -36233,13 +36233,13 @@
         <v>1.18</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.97</v>
+        <v>2.67</v>
       </c>
       <c r="AU164" t="n">
         <v>2</v>
@@ -36248,16 +36248,16 @@
         <v>2</v>
       </c>
       <c r="AW164" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX164" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY164" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ164" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
@@ -36329,7 +36329,7 @@
         <v>45856.89583333334</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -36451,13 +36451,13 @@
         <v>1.18</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="AU165" t="n">
         <v>5</v>
@@ -36466,16 +36466,16 @@
         <v>2</v>
       </c>
       <c r="AW165" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY165" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA165" t="n">
         <v>2</v>
@@ -36547,7 +36547,7 @@
         <v>45857.66666666666</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -36669,31 +36669,31 @@
         <v>0.83</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="AU166" t="n">
         <v>4</v>
       </c>
       <c r="AV166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW166" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX166" t="n">
         <v>4</v>
       </c>
       <c r="AY166" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA166" t="n">
         <v>2</v>
@@ -36765,7 +36765,7 @@
         <v>45857.77083333334</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -36887,40 +36887,40 @@
         <v>0.92</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="AU167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV167" t="n">
         <v>6</v>
       </c>
       <c r="AW167" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX167" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY167" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ167" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA167" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB167" t="n">
         <v>2</v>
       </c>
       <c r="BC167" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD167" t="n">
         <v>1.44</v>
@@ -36983,7 +36983,7 @@
         <v>45857.77083333334</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -37105,16 +37105,16 @@
         <v>1</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT168" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AU168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV168" t="n">
         <v>5</v>
@@ -37123,13 +37123,13 @@
         <v>10</v>
       </c>
       <c r="AX168" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY168" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ168" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA168" t="n">
         <v>10</v>
@@ -37201,7 +37201,7 @@
         <v>45857.85416666666</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -37323,13 +37323,13 @@
         <v>1.1</v>
       </c>
       <c r="AR169" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AT169" t="n">
-        <v>3.29</v>
+        <v>2.72</v>
       </c>
       <c r="AU169" t="n">
         <v>6</v>
@@ -37338,13 +37338,13 @@
         <v>4</v>
       </c>
       <c r="AW169" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX169" t="n">
         <v>9</v>
       </c>
       <c r="AY169" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ169" t="n">
         <v>13</v>
@@ -37541,40 +37541,40 @@
         <v>0.73</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AU170" t="n">
         <v>3</v>
       </c>
       <c r="AV170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW170" t="n">
         <v>5</v>
       </c>
-      <c r="AW170" t="n">
+      <c r="AX170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ170" t="n">
         <v>9</v>
       </c>
-      <c r="AX170" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY170" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ170" t="n">
-        <v>10</v>
-      </c>
       <c r="BA170" t="n">
         <v>1</v>
       </c>
       <c r="BB170" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC170" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD170" t="n">
         <v>1.69</v>
@@ -37759,31 +37759,31 @@
         <v>1.09</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.99</v>
+        <v>2.66</v>
       </c>
       <c r="AU171" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ171" t="n">
         <v>8</v>
-      </c>
-      <c r="AV171" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW171" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX171" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY171" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ171" t="n">
-        <v>11</v>
       </c>
       <c r="BA171" t="n">
         <v>7</v>
@@ -37971,19 +37971,19 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.8</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AT172" t="n">
-        <v>3.06</v>
+        <v>2.81</v>
       </c>
       <c r="AU172" t="n">
         <v>5</v>
@@ -37992,16 +37992,16 @@
         <v>3</v>
       </c>
       <c r="AW172" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY172" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA172" t="n">
         <v>3</v>
@@ -38195,31 +38195,31 @@
         <v>1.08</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.07</v>
+        <v>2.68</v>
       </c>
       <c r="AU173" t="n">
         <v>8</v>
       </c>
       <c r="AV173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX173" t="n">
         <v>3</v>
       </c>
-      <c r="AW173" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX173" t="n">
+      <c r="AY173" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ173" t="n">
         <v>5</v>
-      </c>
-      <c r="AY173" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ173" t="n">
-        <v>8</v>
       </c>
       <c r="BA173" t="n">
         <v>11</v>
@@ -38413,31 +38413,31 @@
         <v>1.75</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AU174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV174" t="n">
         <v>5</v>
       </c>
-      <c r="AV174" t="n">
-        <v>6</v>
-      </c>
       <c r="AW174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY174" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ174" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA174" t="n">
         <v>5</v>
@@ -38631,31 +38631,31 @@
         <v>0.75</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AT175" t="n">
-        <v>3.04</v>
+        <v>2.76</v>
       </c>
       <c r="AU175" t="n">
         <v>6</v>
       </c>
       <c r="AV175" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX175" t="n">
         <v>7</v>
       </c>
-      <c r="AX175" t="n">
-        <v>19</v>
-      </c>
       <c r="AY175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ175" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ175" t="n">
-        <v>23</v>
       </c>
       <c r="BA175" t="n">
         <v>5</v>
@@ -38849,31 +38849,31 @@
         <v>0.27</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="AU176" t="n">
         <v>8</v>
       </c>
       <c r="AV176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW176" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX176" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AY176" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ176" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA176" t="n">
         <v>7</v>
@@ -39067,31 +39067,31 @@
         <v>1.55</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="AU177" t="n">
         <v>3</v>
       </c>
       <c r="AV177" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX177" t="n">
         <v>5</v>
       </c>
-      <c r="AW177" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX177" t="n">
-        <v>9</v>
-      </c>
       <c r="AY177" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ177" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA177" t="n">
         <v>3</v>
@@ -39195,7 +39195,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>['45+6', '50', '85']</t>
+          <t>['45+6', '51', '85']</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -39285,31 +39285,31 @@
         <v>0.64</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AT178" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AU178" t="n">
         <v>5</v>
       </c>
       <c r="AV178" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX178" t="n">
         <v>5</v>
       </c>
-      <c r="AW178" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX178" t="n">
+      <c r="AY178" t="n">
         <v>7</v>
       </c>
-      <c r="AY178" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ178" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA178" t="n">
         <v>2</v>
@@ -39503,31 +39503,31 @@
         <v>0.92</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="AU179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV179" t="n">
         <v>2</v>
       </c>
       <c r="AW179" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AX179" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY179" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ179" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA179" t="n">
         <v>13</v>
@@ -39721,31 +39721,31 @@
         <v>1.18</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AU180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV180" t="n">
         <v>5</v>
       </c>
-      <c r="AV180" t="n">
-        <v>4</v>
-      </c>
       <c r="AW180" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX180" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY180" t="n">
         <v>17</v>
       </c>
       <c r="AZ180" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA180" t="n">
         <v>6</v>
@@ -39939,13 +39939,13 @@
         <v>1</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="AU181" t="n">
         <v>7</v>
@@ -39954,16 +39954,16 @@
         <v>6</v>
       </c>
       <c r="AW181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY181" t="n">
         <v>11</v>
       </c>
-      <c r="AY181" t="n">
+      <c r="AZ181" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ181" t="n">
-        <v>17</v>
       </c>
       <c r="BA181" t="n">
         <v>7</v>
@@ -40157,31 +40157,31 @@
         <v>0.73</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="AU182" t="n">
         <v>3</v>
       </c>
       <c r="AV182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW182" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX182" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AY182" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ182" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
@@ -40375,31 +40375,31 @@
         <v>1.1</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="AU183" t="n">
         <v>6</v>
       </c>
       <c r="AV183" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW183" t="n">
         <v>6</v>
       </c>
-      <c r="AW183" t="n">
+      <c r="AX183" t="n">
         <v>9</v>
       </c>
-      <c r="AX183" t="n">
-        <v>13</v>
-      </c>
       <c r="AY183" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ183" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA183" t="n">
         <v>3</v>
@@ -40593,31 +40593,31 @@
         <v>1</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT184" t="n">
-        <v>3.19</v>
+        <v>2.67</v>
       </c>
       <c r="AU184" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX184" t="n">
         <v>6</v>
       </c>
-      <c r="AV184" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW184" t="n">
+      <c r="AY184" t="n">
         <v>10</v>
       </c>
-      <c r="AX184" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY184" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ184" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA184" t="n">
         <v>4</v>
@@ -40811,13 +40811,13 @@
         <v>0.3</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AU185" t="n">
         <v>4</v>
@@ -40826,16 +40826,16 @@
         <v>2</v>
       </c>
       <c r="AW185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ185" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA185" t="n">
         <v>8</v>
@@ -41029,13 +41029,13 @@
         <v>1.1</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AT186" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="AU186" t="n">
         <v>3</v>
@@ -41047,13 +41047,13 @@
         <v>6</v>
       </c>
       <c r="AX186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY186" t="n">
         <v>9</v>
       </c>
       <c r="AZ186" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA186" t="n">
         <v>4</v>
@@ -41247,31 +41247,31 @@
         <v>1.09</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AT187" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AU187" t="n">
         <v>3</v>
       </c>
       <c r="AV187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY187" t="n">
         <v>11</v>
       </c>
-      <c r="AX187" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY187" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ187" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA187" t="n">
         <v>3</v>
@@ -41465,31 +41465,31 @@
         <v>0.73</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AT188" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="AU188" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX188" t="n">
         <v>8</v>
       </c>
-      <c r="AV188" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW188" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX188" t="n">
-        <v>11</v>
-      </c>
       <c r="AY188" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ188" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA188" t="n">
         <v>3</v>
@@ -41683,31 +41683,31 @@
         <v>1.18</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="AU189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV189" t="n">
         <v>6</v>
       </c>
       <c r="AW189" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AX189" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY189" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ189" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA189" t="n">
         <v>6</v>
@@ -41901,31 +41901,31 @@
         <v>0.83</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AT190" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AU190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV190" t="n">
         <v>0</v>
       </c>
       <c r="AW190" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX190" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ190" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA190" t="n">
         <v>1</v>
@@ -42119,28 +42119,28 @@
         <v>1.2</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AU191" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW191" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY191" t="n">
         <v>21</v>
-      </c>
-      <c r="AX191" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY191" t="n">
-        <v>28</v>
       </c>
       <c r="AZ191" t="n">
         <v>7</v>
@@ -42337,31 +42337,31 @@
         <v>1.75</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AU192" t="n">
         <v>4</v>
       </c>
       <c r="AV192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW192" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX192" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY192" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA192" t="n">
         <v>3</v>
@@ -42555,31 +42555,31 @@
         <v>1.08</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="AU193" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV193" t="n">
         <v>7</v>
       </c>
-      <c r="AV193" t="n">
+      <c r="AW193" t="n">
         <v>6</v>
       </c>
-      <c r="AW193" t="n">
-        <v>11</v>
-      </c>
       <c r="AX193" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY193" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ193" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA193" t="n">
         <v>7</v>
@@ -42767,34 +42767,34 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.18</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV194" t="n">
         <v>0</v>
       </c>
       <c r="AW194" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX194" t="n">
         <v>6</v>
       </c>
       <c r="AY194" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ194" t="n">
         <v>6</v>
@@ -42991,31 +42991,31 @@
         <v>0.64</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="AU195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV195" t="n">
         <v>6</v>
       </c>
       <c r="AW195" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY195" t="n">
         <v>10</v>
       </c>
-      <c r="AX195" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY195" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ195" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA195" t="n">
         <v>1</v>
@@ -43209,31 +43209,31 @@
         <v>1.55</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="AU196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW196" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX196" t="n">
         <v>5</v>
       </c>
       <c r="AY196" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ196" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA196" t="n">
         <v>1</v>
@@ -43427,13 +43427,13 @@
         <v>0.75</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AT197" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
@@ -43442,16 +43442,16 @@
         <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX197" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AY197" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ197" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA197" t="n">
         <v>4</v>
@@ -43645,31 +43645,31 @@
         <v>1</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AU198" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV198" t="n">
         <v>6</v>
       </c>
       <c r="AW198" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY198" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ198" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA198" t="n">
         <v>7</v>
@@ -43863,31 +43863,31 @@
         <v>0.92</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="AU199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV199" t="n">
         <v>3</v>
       </c>
       <c r="AW199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY199" t="n">
         <v>13</v>
       </c>
-      <c r="AX199" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY199" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA199" t="n">
         <v>6</v>
@@ -44081,13 +44081,13 @@
         <v>0.8</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="AU200" t="n">
         <v>6</v>
@@ -44096,16 +44096,16 @@
         <v>4</v>
       </c>
       <c r="AW200" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ200" t="n">
         <v>8</v>
-      </c>
-      <c r="AY200" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ200" t="n">
-        <v>12</v>
       </c>
       <c r="BA200" t="n">
         <v>4</v>
@@ -44299,13 +44299,13 @@
         <v>0.27</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU201" t="n">
         <v>6</v>
@@ -44314,16 +44314,16 @@
         <v>2</v>
       </c>
       <c r="AW201" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AX201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY201" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA201" t="n">
         <v>5</v>
@@ -44517,13 +44517,13 @@
         <v>0.3</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.58</v>
+        <v>2.21</v>
       </c>
       <c r="AU202" t="n">
         <v>4</v>
@@ -44532,16 +44532,16 @@
         <v>3</v>
       </c>
       <c r="AW202" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ202" t="n">
         <v>6</v>
-      </c>
-      <c r="AY202" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ202" t="n">
-        <v>9</v>
       </c>
       <c r="BA202" t="n">
         <v>9</v>
@@ -44735,13 +44735,13 @@
         <v>1.09</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="AU203" t="n">
         <v>5</v>
@@ -44750,16 +44750,16 @@
         <v>0</v>
       </c>
       <c r="AW203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY203" t="n">
         <v>11</v>
       </c>
-      <c r="AX203" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY203" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ203" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA203" t="n">
         <v>4</v>
@@ -44953,31 +44953,31 @@
         <v>1.2</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="AU204" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ204" t="n">
         <v>5</v>
-      </c>
-      <c r="AV204" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW204" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX204" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY204" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ204" t="n">
-        <v>6</v>
       </c>
       <c r="BA204" t="n">
         <v>9</v>
@@ -45171,13 +45171,13 @@
         <v>0.73</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AU205" t="n">
         <v>3</v>
@@ -45186,16 +45186,16 @@
         <v>1</v>
       </c>
       <c r="AW205" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX205" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY205" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ205" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA205" t="n">
         <v>4</v>
@@ -45389,13 +45389,13 @@
         <v>1.1</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT206" t="n">
-        <v>3.12</v>
+        <v>2.61</v>
       </c>
       <c r="AU206" t="n">
         <v>6</v>
@@ -45404,16 +45404,16 @@
         <v>3</v>
       </c>
       <c r="AW206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY206" t="n">
         <v>9</v>
       </c>
-      <c r="AX206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ206" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA206" t="n">
         <v>11</v>
@@ -45607,13 +45607,13 @@
         <v>0.83</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AT207" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="AU207" t="n">
         <v>5</v>
@@ -45622,16 +45622,16 @@
         <v>5</v>
       </c>
       <c r="AW207" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX207" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY207" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ207" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA207" t="n">
         <v>1</v>
@@ -45825,13 +45825,13 @@
         <v>0.73</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="AU208" t="n">
         <v>7</v>
@@ -45840,16 +45840,16 @@
         <v>2</v>
       </c>
       <c r="AW208" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AX208" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY208" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AZ208" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA208" t="n">
         <v>5</v>
@@ -46043,13 +46043,13 @@
         <v>1.1</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AT209" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="AU209" t="n">
         <v>9</v>
@@ -46058,16 +46058,16 @@
         <v>3</v>
       </c>
       <c r="AW209" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY209" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ209" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA209" t="n">
         <v>4</v>
@@ -46261,13 +46261,13 @@
         <v>1</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.92</v>
+        <v>2.53</v>
       </c>
       <c r="AU210" t="n">
         <v>1</v>
@@ -46276,16 +46276,16 @@
         <v>2</v>
       </c>
       <c r="AW210" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AX210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY210" t="n">
         <v>4</v>
       </c>
-      <c r="AY210" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ210" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA210" t="n">
         <v>9</v>
@@ -46479,13 +46479,13 @@
         <v>1.18</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AT211" t="n">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="AU211" t="n">
         <v>6</v>
@@ -46494,16 +46494,16 @@
         <v>3</v>
       </c>
       <c r="AW211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY211" t="n">
         <v>14</v>
       </c>
-      <c r="AX211" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY211" t="n">
-        <v>20</v>
-      </c>
       <c r="AZ211" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA211" t="n">
         <v>8</v>
@@ -46697,13 +46697,13 @@
         <v>1.75</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="AU212" t="n">
         <v>3</v>
@@ -46712,16 +46712,16 @@
         <v>4</v>
       </c>
       <c r="AW212" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX212" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY212" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA212" t="n">
         <v>4</v>
@@ -46915,13 +46915,13 @@
         <v>0.64</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="AU213" t="n">
         <v>5</v>
@@ -46930,16 +46930,16 @@
         <v>5</v>
       </c>
       <c r="AW213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX213" t="n">
         <v>7</v>
       </c>
-      <c r="AX213" t="n">
+      <c r="AY213" t="n">
         <v>11</v>
       </c>
-      <c r="AY213" t="n">
+      <c r="AZ213" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ213" t="n">
-        <v>16</v>
       </c>
       <c r="BA213" t="n">
         <v>5</v>
@@ -47133,13 +47133,13 @@
         <v>0.73</v>
       </c>
       <c r="AR214" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AS214" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AU214" t="n">
         <v>5</v>
@@ -47351,13 +47351,13 @@
         <v>1.55</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AU215" t="n">
         <v>3</v>
@@ -47569,13 +47569,13 @@
         <v>0.83</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT216" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AU216" t="n">
         <v>4</v>
@@ -47787,13 +47787,13 @@
         <v>0.92</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AU217" t="n">
         <v>7</v>
@@ -48005,13 +48005,13 @@
         <v>1.08</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AT218" t="n">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
       <c r="AU218" t="n">
         <v>5</v>
@@ -48223,13 +48223,13 @@
         <v>0.75</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AT219" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AU219" t="n">
         <v>4</v>
@@ -48441,13 +48441,13 @@
         <v>1.18</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.61</v>
+        <v>2.28</v>
       </c>
       <c r="AU220" t="n">
         <v>4</v>
@@ -48514,6 +48514,224 @@
       </c>
       <c r="BP220" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>7841247</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>45888.8125</v>
+      </c>
+      <c r="F221" t="n">
+        <v>22</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R221" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S221" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V221" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X221" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -48671,19 +48671,19 @@
         <v>5</v>
       </c>
       <c r="AV221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW221" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX221" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AY221" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ221" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA221" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.75</v>
@@ -5492,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR23" t="n">
         <v>1.23</v>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR44" t="n">
         <v>1.6</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.27</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ61" t="n">
         <v>1</v>
@@ -13994,7 +13994,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR62" t="n">
         <v>1.27</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.1</v>
@@ -19008,7 +19008,7 @@
         <v>2</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR85" t="n">
         <v>1.6</v>
@@ -21403,7 +21403,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.83</v>
@@ -22932,7 +22932,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR103" t="n">
         <v>1.97</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.73</v>
@@ -27074,7 +27074,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR122" t="n">
         <v>1.11</v>
@@ -30341,7 +30341,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.2</v>
@@ -32960,7 +32960,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR149" t="n">
         <v>1.48</v>
@@ -35137,7 +35137,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ159" t="n">
         <v>1</v>
@@ -37756,7 +37756,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR171" t="n">
         <v>1.41</v>
@@ -38407,7 +38407,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.75</v>
@@ -41244,7 +41244,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR187" t="n">
         <v>1.53</v>
@@ -44075,7 +44075,7 @@
         <v>0.78</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.8</v>
@@ -44732,7 +44732,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR203" t="n">
         <v>1.2</v>
@@ -48435,7 +48435,7 @@
         <v>1.2</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.18</v>
@@ -48732,6 +48732,224 @@
       </c>
       <c r="BP221" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>7841259</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>45891.79166666666</v>
+      </c>
+      <c r="F222" t="n">
+        <v>23</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>4</v>
+      </c>
+      <c r="N222" t="n">
+        <v>4</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>['53', '58', '68', '80']</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2</v>
+      </c>
+      <c r="S222" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V222" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X222" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.73</v>
@@ -2658,7 +2658,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.18</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.2</v>
@@ -12468,7 +12468,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.27</v>
@@ -17046,7 +17046,7 @@
         <v>1</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.75</v>
@@ -20752,7 +20752,7 @@
         <v>2</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR93" t="n">
         <v>1.65</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ110" t="n">
         <v>1</v>
@@ -26417,7 +26417,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.3</v>
@@ -28818,7 +28818,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR130" t="n">
         <v>1.46</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -32742,7 +32742,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR148" t="n">
         <v>1.21</v>
@@ -34701,7 +34701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.08</v>
@@ -36012,7 +36012,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR163" t="n">
         <v>1.08</v>
@@ -40372,7 +40372,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR183" t="n">
         <v>1.6</v>
@@ -41895,7 +41895,7 @@
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.83</v>
@@ -45386,7 +45386,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR206" t="n">
         <v>1.55</v>
@@ -46037,7 +46037,7 @@
         <v>1.22</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.1</v>
@@ -48950,6 +48950,224 @@
       </c>
       <c r="BP222" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>7841257</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>45891.89930555555</v>
+      </c>
+      <c r="F223" t="n">
+        <v>23</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>2</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>['63', '79']</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R223" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S223" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V223" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X223" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.3</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -6800,7 +6800,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -9852,7 +9852,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR43" t="n">
         <v>2.12</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.73</v>
@@ -10506,7 +10506,7 @@
         <v>2</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR46" t="n">
         <v>1.4</v>
@@ -13122,7 +13122,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.75</v>
@@ -17264,7 +17264,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -18133,10 +18133,10 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR81" t="n">
         <v>1.26</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.08</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>1</v>
@@ -21842,7 +21842,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR98" t="n">
         <v>1.5</v>
@@ -22060,7 +22060,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR99" t="n">
         <v>1.94</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.27</v>
@@ -24894,7 +24894,7 @@
         <v>2</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR112" t="n">
         <v>1.71</v>
@@ -25548,7 +25548,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR115" t="n">
         <v>1.38</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.83</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.18</v>
@@ -29254,7 +29254,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR132" t="n">
         <v>1.39</v>
@@ -30344,7 +30344,7 @@
         <v>1</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR137" t="n">
         <v>1.22</v>
@@ -31649,7 +31649,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.27</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.18</v>
@@ -34050,7 +34050,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR154" t="n">
         <v>1.7</v>
@@ -34922,7 +34922,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR158" t="n">
         <v>1.27</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.83</v>
@@ -36881,7 +36881,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.92</v>
@@ -39282,7 +39282,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR178" t="n">
         <v>1.47</v>
@@ -40805,7 +40805,7 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.3</v>
@@ -42113,10 +42113,10 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR191" t="n">
         <v>1.45</v>
@@ -42988,7 +42988,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR195" t="n">
         <v>1.31</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.25</v>
@@ -44950,7 +44950,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR204" t="n">
         <v>1.43</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.73</v>
@@ -46912,7 +46912,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR213" t="n">
         <v>1.3</v>
@@ -49168,6 +49168,442 @@
       </c>
       <c r="BP223" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>7841252</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>45892.66666666666</v>
+      </c>
+      <c r="F224" t="n">
+        <v>23</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S224" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U224" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V224" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X224" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>7841253</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>45892.75</v>
+      </c>
+      <c r="F225" t="n">
+        <v>23</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>1</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R225" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S225" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U225" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V225" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X225" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.25</v>
@@ -5274,7 +5274,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.27</v>
@@ -9634,7 +9634,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR42" t="n">
         <v>2.35</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.83</v>
@@ -16828,7 +16828,7 @@
         <v>2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17479,7 +17479,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.18</v>
@@ -21624,7 +21624,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR97" t="n">
         <v>1.55</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.18</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.55</v>
@@ -27510,7 +27510,7 @@
         <v>2</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR124" t="n">
         <v>1.56</v>
@@ -29251,7 +29251,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.58</v>
@@ -32306,7 +32306,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR146" t="n">
         <v>1.39</v>
@@ -33611,7 +33611,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.75</v>
@@ -37320,7 +37320,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR169" t="n">
         <v>1.65</v>
@@ -40369,7 +40369,7 @@
         <v>1.25</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ183" t="n">
         <v>1</v>
@@ -41026,7 +41026,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR186" t="n">
         <v>1.47</v>
@@ -46040,7 +46040,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AR209" t="n">
         <v>1.67</v>
@@ -46473,7 +46473,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.18</v>
@@ -49604,6 +49604,224 @@
       </c>
       <c r="BP225" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>7841258</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>45892.85416666666</v>
+      </c>
+      <c r="F226" t="n">
+        <v>23</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>1</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2</v>
+      </c>
+      <c r="S226" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U226" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V226" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X226" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -16410,16 +16410,16 @@
         <v>1</v>
       </c>
       <c r="AW73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX73" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY73" t="n">
         <v>8</v>
       </c>
-      <c r="AY73" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ73" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
@@ -16628,16 +16628,16 @@
         <v>1</v>
       </c>
       <c r="AW74" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AZ74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA74" t="n">
         <v>6</v>
@@ -16846,16 +16846,16 @@
         <v>2</v>
       </c>
       <c r="AW75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY75" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA75" t="n">
         <v>5</v>
@@ -17064,16 +17064,16 @@
         <v>4</v>
       </c>
       <c r="AW76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY76" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA76" t="n">
         <v>10</v>
@@ -17282,16 +17282,16 @@
         <v>2</v>
       </c>
       <c r="AW77" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ77" t="n">
         <v>7</v>
-      </c>
-      <c r="AX77" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY77" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ77" t="n">
-        <v>6</v>
       </c>
       <c r="BA77" t="n">
         <v>8</v>
@@ -17500,16 +17500,16 @@
         <v>7</v>
       </c>
       <c r="AW78" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY78" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ78" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BA78" t="n">
         <v>1</v>
@@ -17718,16 +17718,16 @@
         <v>3</v>
       </c>
       <c r="AW79" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY79" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ79" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA79" t="n">
         <v>5</v>
@@ -17936,16 +17936,16 @@
         <v>1</v>
       </c>
       <c r="AW80" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY80" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA80" t="n">
         <v>7</v>
@@ -18154,16 +18154,16 @@
         <v>10</v>
       </c>
       <c r="AW81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ81" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA81" t="n">
         <v>9</v>
@@ -18372,16 +18372,16 @@
         <v>5</v>
       </c>
       <c r="AW82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX82" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AY82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ82" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BA82" t="n">
         <v>4</v>
@@ -18590,16 +18590,16 @@
         <v>2</v>
       </c>
       <c r="AW83" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX83" t="n">
         <v>6</v>
       </c>
-      <c r="AX83" t="n">
-        <v>5</v>
-      </c>
       <c r="AY83" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA83" t="n">
         <v>5</v>
@@ -18808,16 +18808,16 @@
         <v>6</v>
       </c>
       <c r="AW84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY84" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ84" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BA84" t="n">
         <v>3</v>
@@ -19026,16 +19026,16 @@
         <v>2</v>
       </c>
       <c r="AW85" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX85" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY85" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ85" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA85" t="n">
         <v>5</v>
@@ -19244,16 +19244,16 @@
         <v>4</v>
       </c>
       <c r="AW86" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY86" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ86" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA86" t="n">
         <v>8</v>
@@ -19462,16 +19462,16 @@
         <v>1</v>
       </c>
       <c r="AW87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX87" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AY87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ87" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BA87" t="n">
         <v>4</v>
@@ -19680,16 +19680,16 @@
         <v>4</v>
       </c>
       <c r="AW88" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY88" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ88" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA88" t="n">
         <v>9</v>
@@ -19898,16 +19898,16 @@
         <v>6</v>
       </c>
       <c r="AW89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX89" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AY89" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ89" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BA89" t="n">
         <v>1</v>
@@ -20116,13 +20116,13 @@
         <v>2</v>
       </c>
       <c r="AW90" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX90" t="n">
         <v>6</v>
       </c>
       <c r="AY90" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ90" t="n">
         <v>8</v>
@@ -20334,16 +20334,16 @@
         <v>3</v>
       </c>
       <c r="AW91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY91" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ91" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA91" t="n">
         <v>6</v>
@@ -20540,10 +20540,10 @@
         <v>1.81</v>
       </c>
       <c r="AS92" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AU92" t="n">
         <v>2</v>
@@ -20552,16 +20552,16 @@
         <v>4</v>
       </c>
       <c r="AW92" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AX92" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY92" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AZ92" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA92" t="n">
         <v>2</v>
@@ -20755,13 +20755,13 @@
         <v>1</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AU93" t="n">
         <v>7</v>
@@ -20770,16 +20770,16 @@
         <v>1</v>
       </c>
       <c r="AW93" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX93" t="n">
         <v>7</v>
       </c>
-      <c r="AX93" t="n">
-        <v>6</v>
-      </c>
       <c r="AY93" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA93" t="n">
         <v>13</v>
@@ -20973,13 +20973,13 @@
         <v>1</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AS94" t="n">
         <v>1.2</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AU94" t="n">
         <v>6</v>
@@ -20988,13 +20988,13 @@
         <v>5</v>
       </c>
       <c r="AW94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX94" t="n">
         <v>3</v>
       </c>
       <c r="AY94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ94" t="n">
         <v>8</v>
@@ -21191,13 +21191,13 @@
         <v>1.55</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AS95" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AU95" t="n">
         <v>5</v>
@@ -21206,16 +21206,16 @@
         <v>5</v>
       </c>
       <c r="AW95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY95" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ95" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA95" t="n">
         <v>7</v>
@@ -21409,13 +21409,13 @@
         <v>0.83</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AU96" t="n">
         <v>1</v>
@@ -21424,16 +21424,16 @@
         <v>4</v>
       </c>
       <c r="AW96" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX96" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY96" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA96" t="n">
         <v>3</v>
@@ -21627,13 +21627,13 @@
         <v>1.27</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="AU97" t="n">
         <v>4</v>
@@ -21642,16 +21642,16 @@
         <v>4</v>
       </c>
       <c r="AW97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY97" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA97" t="n">
         <v>1</v>
@@ -21845,13 +21845,13 @@
         <v>1.18</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AU98" t="n">
         <v>4</v>
@@ -21860,16 +21860,16 @@
         <v>11</v>
       </c>
       <c r="AW98" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY98" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ98" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA98" t="n">
         <v>5</v>
@@ -22063,13 +22063,13 @@
         <v>0.58</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.61</v>
+        <v>3.87</v>
       </c>
       <c r="AU99" t="n">
         <v>3</v>
@@ -22078,16 +22078,16 @@
         <v>2</v>
       </c>
       <c r="AW99" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY99" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ99" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA99" t="n">
         <v>6</v>
@@ -22281,13 +22281,13 @@
         <v>0.3</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AS100" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AU100" t="n">
         <v>5</v>
@@ -22296,16 +22296,16 @@
         <v>2</v>
       </c>
       <c r="AW100" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX100" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY100" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ100" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA100" t="n">
         <v>9</v>
@@ -22499,13 +22499,13 @@
         <v>1.18</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="AU101" t="n">
         <v>6</v>
@@ -22514,13 +22514,13 @@
         <v>4</v>
       </c>
       <c r="AW101" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AX101" t="n">
         <v>2</v>
       </c>
       <c r="AY101" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AZ101" t="n">
         <v>6</v>
@@ -22717,13 +22717,13 @@
         <v>1.75</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AU102" t="n">
         <v>3</v>
@@ -22735,13 +22735,13 @@
         <v>4</v>
       </c>
       <c r="AX102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY102" t="n">
         <v>7</v>
       </c>
       <c r="AZ102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA102" t="n">
         <v>3</v>
@@ -22935,13 +22935,13 @@
         <v>1.25</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AU103" t="n">
         <v>4</v>
@@ -22950,16 +22950,16 @@
         <v>3</v>
       </c>
       <c r="AW103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ103" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA103" t="n">
         <v>5</v>
@@ -23153,13 +23153,13 @@
         <v>0.92</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS104" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AU104" t="n">
         <v>6</v>
@@ -23168,16 +23168,16 @@
         <v>3</v>
       </c>
       <c r="AW104" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY104" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA104" t="n">
         <v>9</v>
@@ -23371,13 +23371,13 @@
         <v>1.08</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="AU105" t="n">
         <v>4</v>
@@ -23386,16 +23386,16 @@
         <v>6</v>
       </c>
       <c r="AW105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX105" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY105" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ105" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA105" t="n">
         <v>9</v>
@@ -23589,13 +23589,13 @@
         <v>0.75</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="AU106" t="n">
         <v>6</v>
@@ -23604,16 +23604,16 @@
         <v>2</v>
       </c>
       <c r="AW106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX106" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY106" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ106" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23807,13 +23807,13 @@
         <v>0.27</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="AU107" t="n">
         <v>6</v>
@@ -23822,16 +23822,16 @@
         <v>4</v>
       </c>
       <c r="AW107" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX107" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AY107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ107" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BA107" t="n">
         <v>2</v>
@@ -24025,13 +24025,13 @@
         <v>0.8</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="AU108" t="n">
         <v>1</v>
@@ -24040,16 +24040,16 @@
         <v>4</v>
       </c>
       <c r="AW108" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AX108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY108" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA108" t="n">
         <v>5</v>
@@ -24243,13 +24243,13 @@
         <v>0.73</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AU109" t="n">
         <v>3</v>
@@ -24258,16 +24258,16 @@
         <v>5</v>
       </c>
       <c r="AW109" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX109" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY109" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ109" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA109" t="n">
         <v>6</v>
@@ -24461,13 +24461,13 @@
         <v>1</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AS110" t="n">
         <v>1.05</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AU110" t="n">
         <v>7</v>
@@ -24476,16 +24476,16 @@
         <v>0</v>
       </c>
       <c r="AW110" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX110" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY110" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AZ110" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA110" t="n">
         <v>16</v>
@@ -24679,13 +24679,13 @@
         <v>1.18</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU111" t="n">
         <v>5</v>
@@ -24694,16 +24694,16 @@
         <v>2</v>
       </c>
       <c r="AW111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY111" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ111" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BA111" t="n">
         <v>2</v>
@@ -24897,13 +24897,13 @@
         <v>0.58</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="AU112" t="n">
         <v>1</v>
@@ -24912,16 +24912,16 @@
         <v>5</v>
       </c>
       <c r="AW112" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX112" t="n">
         <v>4</v>
       </c>
-      <c r="AX112" t="n">
-        <v>3</v>
-      </c>
       <c r="AY112" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AZ112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA112" t="n">
         <v>4</v>
@@ -25115,13 +25115,13 @@
         <v>0.73</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="AU113" t="n">
         <v>3</v>
@@ -25130,16 +25130,16 @@
         <v>6</v>
       </c>
       <c r="AW113" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY113" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ113" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA113" t="n">
         <v>8</v>
@@ -25333,13 +25333,13 @@
         <v>1.55</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="AU114" t="n">
         <v>4</v>
@@ -25348,16 +25348,16 @@
         <v>6</v>
       </c>
       <c r="AW114" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX114" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY114" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ114" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA114" t="n">
         <v>1</v>
@@ -25551,13 +25551,13 @@
         <v>1.18</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AU115" t="n">
         <v>11</v>
@@ -25566,16 +25566,16 @@
         <v>3</v>
       </c>
       <c r="AW115" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY115" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AZ115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA115" t="n">
         <v>13</v>
@@ -25769,13 +25769,13 @@
         <v>0.73</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AU116" t="n">
         <v>5</v>
@@ -25784,16 +25784,16 @@
         <v>3</v>
       </c>
       <c r="AW116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX116" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ116" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA116" t="n">
         <v>5</v>
@@ -25987,13 +25987,13 @@
         <v>1.75</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="AU117" t="n">
         <v>4</v>
@@ -26002,16 +26002,16 @@
         <v>2</v>
       </c>
       <c r="AW117" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX117" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY117" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AZ117" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26205,13 +26205,13 @@
         <v>0.83</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.24</v>
+        <v>3.43</v>
       </c>
       <c r="AU118" t="n">
         <v>6</v>
@@ -26220,16 +26220,16 @@
         <v>9</v>
       </c>
       <c r="AW118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX118" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY118" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ118" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA118" t="n">
         <v>2</v>
@@ -26423,13 +26423,13 @@
         <v>0.3</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AS119" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AU119" t="n">
         <v>11</v>
@@ -26438,16 +26438,16 @@
         <v>3</v>
       </c>
       <c r="AW119" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX119" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY119" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA119" t="n">
         <v>5</v>
@@ -26641,13 +26641,13 @@
         <v>1.08</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="AU120" t="n">
         <v>3</v>
@@ -26656,16 +26656,16 @@
         <v>7</v>
       </c>
       <c r="AW120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX120" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY120" t="n">
         <v>7</v>
       </c>
-      <c r="AY120" t="n">
-        <v>6</v>
-      </c>
       <c r="AZ120" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA120" t="n">
         <v>1</v>
@@ -26859,13 +26859,13 @@
         <v>1</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AS121" t="n">
         <v>1.21</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="AU121" t="n">
         <v>10</v>
@@ -26874,16 +26874,16 @@
         <v>3</v>
       </c>
       <c r="AW121" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY121" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA121" t="n">
         <v>12</v>
@@ -27077,13 +27077,13 @@
         <v>1.25</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AU122" t="n">
         <v>5</v>
@@ -27092,16 +27092,16 @@
         <v>1</v>
       </c>
       <c r="AW122" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY122" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AZ122" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA122" t="n">
         <v>13</v>
@@ -27295,13 +27295,13 @@
         <v>1.18</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AU123" t="n">
         <v>2</v>
@@ -27310,16 +27310,16 @@
         <v>3</v>
       </c>
       <c r="AW123" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY123" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ123" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>9</v>
       </c>
       <c r="BA123" t="n">
         <v>7</v>
@@ -27513,13 +27513,13 @@
         <v>1.27</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="AU124" t="n">
         <v>4</v>
@@ -27528,16 +27528,16 @@
         <v>4</v>
       </c>
       <c r="AW124" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY124" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ124" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA124" t="n">
         <v>4</v>
@@ -27731,13 +27731,13 @@
         <v>0.92</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AS125" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="AU125" t="n">
         <v>2</v>
@@ -27746,16 +27746,16 @@
         <v>8</v>
       </c>
       <c r="AW125" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AX125" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY125" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ125" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA125" t="n">
         <v>7</v>
@@ -27949,13 +27949,13 @@
         <v>0.75</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="AU126" t="n">
         <v>2</v>
@@ -27964,16 +27964,16 @@
         <v>5</v>
       </c>
       <c r="AW126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX126" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY126" t="n">
         <v>10</v>
       </c>
-      <c r="AY126" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ126" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BA126" t="n">
         <v>2</v>
@@ -28167,13 +28167,13 @@
         <v>0.83</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AU127" t="n">
         <v>2</v>
@@ -28182,16 +28182,16 @@
         <v>2</v>
       </c>
       <c r="AW127" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX127" t="n">
         <v>6</v>
       </c>
-      <c r="AX127" t="n">
-        <v>2</v>
-      </c>
       <c r="AY127" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ127" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ127" t="n">
-        <v>4</v>
       </c>
       <c r="BA127" t="n">
         <v>5</v>
@@ -28385,13 +28385,13 @@
         <v>0.27</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AT128" t="n">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="AU128" t="n">
         <v>6</v>
@@ -28400,13 +28400,13 @@
         <v>0</v>
       </c>
       <c r="AW128" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX128" t="n">
         <v>6</v>
       </c>
       <c r="AY128" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ128" t="n">
         <v>6</v>
@@ -28603,13 +28603,13 @@
         <v>1</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AS129" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AU129" t="n">
         <v>2</v>
@@ -28618,16 +28618,16 @@
         <v>3</v>
       </c>
       <c r="AW129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX129" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ129" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA129" t="n">
         <v>8</v>
@@ -28821,13 +28821,13 @@
         <v>1</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AU130" t="n">
         <v>5</v>
@@ -28836,16 +28836,16 @@
         <v>1</v>
       </c>
       <c r="AW130" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX130" t="n">
         <v>11</v>
       </c>
-      <c r="AX130" t="n">
-        <v>9</v>
-      </c>
       <c r="AY130" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ130" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA130" t="n">
         <v>2</v>
@@ -29039,13 +29039,13 @@
         <v>1.18</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AS131" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AU131" t="n">
         <v>4</v>
@@ -29054,16 +29054,16 @@
         <v>4</v>
       </c>
       <c r="AW131" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX131" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ131" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BA131" t="n">
         <v>4</v>
@@ -29257,13 +29257,13 @@
         <v>0.58</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.79</v>
+        <v>3.06</v>
       </c>
       <c r="AU132" t="n">
         <v>7</v>
@@ -29272,16 +29272,16 @@
         <v>5</v>
       </c>
       <c r="AW132" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AX132" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY132" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AZ132" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA132" t="n">
         <v>14</v>
@@ -29475,13 +29475,13 @@
         <v>1</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="AU133" t="n">
         <v>6</v>
@@ -29490,16 +29490,16 @@
         <v>5</v>
       </c>
       <c r="AW133" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY133" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA133" t="n">
         <v>6</v>
@@ -29693,13 +29693,13 @@
         <v>0.8</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.79</v>
+        <v>2.93</v>
       </c>
       <c r="AU134" t="n">
         <v>1</v>
@@ -29708,16 +29708,16 @@
         <v>3</v>
       </c>
       <c r="AW134" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX134" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY134" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AZ134" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA134" t="n">
         <v>5</v>
@@ -29911,13 +29911,13 @@
         <v>1.75</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AU135" t="n">
         <v>3</v>
@@ -29926,16 +29926,16 @@
         <v>4</v>
       </c>
       <c r="AW135" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX135" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY135" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ135" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA135" t="n">
         <v>7</v>
@@ -30129,13 +30129,13 @@
         <v>0.73</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AU136" t="n">
         <v>2</v>
@@ -30144,16 +30144,16 @@
         <v>1</v>
       </c>
       <c r="AW136" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ136" t="n">
         <v>10</v>
-      </c>
-      <c r="AX136" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY136" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ136" t="n">
-        <v>6</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30347,13 +30347,13 @@
         <v>1.18</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AU137" t="n">
         <v>9</v>
@@ -30362,13 +30362,13 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX137" t="n">
         <v>3</v>
       </c>
       <c r="AY137" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AZ137" t="n">
         <v>6</v>
@@ -30565,13 +30565,13 @@
         <v>0.3</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AS138" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AU138" t="n">
         <v>3</v>
@@ -30580,16 +30580,16 @@
         <v>3</v>
       </c>
       <c r="AW138" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX138" t="n">
         <v>7</v>
       </c>
-      <c r="AX138" t="n">
-        <v>4</v>
-      </c>
       <c r="AY138" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ138" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ138" t="n">
-        <v>7</v>
       </c>
       <c r="BA138" t="n">
         <v>6</v>
@@ -30783,13 +30783,13 @@
         <v>1.55</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AU139" t="n">
         <v>3</v>
@@ -30798,16 +30798,16 @@
         <v>5</v>
       </c>
       <c r="AW139" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX139" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY139" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ139" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA139" t="n">
         <v>5</v>
@@ -31001,13 +31001,13 @@
         <v>1.08</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="AU140" t="n">
         <v>5</v>
@@ -31016,16 +31016,16 @@
         <v>2</v>
       </c>
       <c r="AW140" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX140" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY140" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ140" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ140" t="n">
-        <v>7</v>
       </c>
       <c r="BA140" t="n">
         <v>5</v>
@@ -31219,13 +31219,13 @@
         <v>0.73</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AS141" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AU141" t="n">
         <v>3</v>
@@ -31234,16 +31234,16 @@
         <v>3</v>
       </c>
       <c r="AW141" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX141" t="n">
         <v>9</v>
       </c>
-      <c r="AX141" t="n">
-        <v>7</v>
-      </c>
       <c r="AY141" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ141" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ141" t="n">
-        <v>10</v>
       </c>
       <c r="BA141" t="n">
         <v>5</v>
@@ -31437,13 +31437,13 @@
         <v>0.75</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="AU142" t="n">
         <v>4</v>
@@ -31452,16 +31452,16 @@
         <v>4</v>
       </c>
       <c r="AW142" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX142" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AY142" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ142" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA142" t="n">
         <v>2</v>
@@ -31655,13 +31655,13 @@
         <v>0.27</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
@@ -31670,16 +31670,16 @@
         <v>7</v>
       </c>
       <c r="AW143" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX143" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY143" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ143" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA143" t="n">
         <v>3</v>
@@ -31873,13 +31873,13 @@
         <v>0.83</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="AU144" t="n">
         <v>4</v>
@@ -31888,16 +31888,16 @@
         <v>3</v>
       </c>
       <c r="AW144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY144" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ144" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ144" t="n">
-        <v>6</v>
       </c>
       <c r="BA144" t="n">
         <v>7</v>
@@ -32091,13 +32091,13 @@
         <v>0.92</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="AU145" t="n">
         <v>5</v>
@@ -32106,16 +32106,16 @@
         <v>1</v>
       </c>
       <c r="AW145" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY145" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA145" t="n">
         <v>2</v>
@@ -32309,13 +32309,13 @@
         <v>1.27</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="AU146" t="n">
         <v>1</v>
@@ -32324,16 +32324,16 @@
         <v>4</v>
       </c>
       <c r="AW146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX146" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AY146" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ146" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BA146" t="n">
         <v>3</v>
@@ -32527,13 +32527,13 @@
         <v>1</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="AS147" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="AU147" t="n">
         <v>3</v>
@@ -32542,16 +32542,16 @@
         <v>9</v>
       </c>
       <c r="AW147" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX147" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY147" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ147" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA147" t="n">
         <v>7</v>
@@ -32745,13 +32745,13 @@
         <v>1</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AU148" t="n">
         <v>6</v>
@@ -32963,13 +32963,13 @@
         <v>1.25</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="AU149" t="n">
         <v>7</v>
@@ -32978,16 +32978,16 @@
         <v>6</v>
       </c>
       <c r="AW149" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX149" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY149" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ149" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA149" t="n">
         <v>1</v>
@@ -33181,13 +33181,13 @@
         <v>1.18</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS150" t="n">
-        <v>0.98</v>
+        <v>1.1</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="AU150" t="n">
         <v>1</v>
@@ -33196,16 +33196,16 @@
         <v>6</v>
       </c>
       <c r="AW150" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AX150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY150" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>10</v>
       </c>
       <c r="BA150" t="n">
         <v>8</v>
@@ -33399,13 +33399,13 @@
         <v>1.18</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="AU151" t="n">
         <v>3</v>
@@ -33414,16 +33414,16 @@
         <v>2</v>
       </c>
       <c r="AW151" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX151" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY151" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ151" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA151" t="n">
         <v>8</v>
@@ -33617,13 +33617,13 @@
         <v>1.75</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="AU152" t="n">
         <v>10</v>
@@ -33632,16 +33632,16 @@
         <v>3</v>
       </c>
       <c r="AW152" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AX152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY152" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AZ152" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA152" t="n">
         <v>10</v>
@@ -33835,13 +33835,13 @@
         <v>0.73</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="AU153" t="n">
         <v>5</v>
@@ -33850,16 +33850,16 @@
         <v>3</v>
       </c>
       <c r="AW153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX153" t="n">
         <v>3</v>
       </c>
-      <c r="AX153" t="n">
-        <v>1</v>
-      </c>
       <c r="AY153" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ153" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA153" t="n">
         <v>5</v>
@@ -34053,13 +34053,13 @@
         <v>0.58</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="AU154" t="n">
         <v>5</v>
@@ -34068,16 +34068,16 @@
         <v>7</v>
       </c>
       <c r="AW154" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY154" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ154" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA154" t="n">
         <v>2</v>
@@ -34271,13 +34271,13 @@
         <v>0.8</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="AU155" t="n">
         <v>5</v>
@@ -34286,16 +34286,16 @@
         <v>8</v>
       </c>
       <c r="AW155" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX155" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY155" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ155" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA155" t="n">
         <v>11</v>
@@ -34489,13 +34489,13 @@
         <v>1.55</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AU156" t="n">
         <v>2</v>
@@ -34504,13 +34504,13 @@
         <v>4</v>
       </c>
       <c r="AW156" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AX156" t="n">
         <v>3</v>
       </c>
       <c r="AY156" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ156" t="n">
         <v>7</v>
@@ -34707,13 +34707,13 @@
         <v>1.08</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="AU157" t="n">
         <v>8</v>
@@ -34722,16 +34722,16 @@
         <v>3</v>
       </c>
       <c r="AW157" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX157" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY157" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AZ157" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA157" t="n">
         <v>12</v>
@@ -34925,13 +34925,13 @@
         <v>1.18</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AU158" t="n">
         <v>8</v>
@@ -34940,16 +34940,16 @@
         <v>3</v>
       </c>
       <c r="AW158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX158" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY158" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ158" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA158" t="n">
         <v>6</v>
@@ -35143,13 +35143,13 @@
         <v>1</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AU159" t="n">
         <v>7</v>
@@ -35161,13 +35161,13 @@
         <v>2</v>
       </c>
       <c r="AX159" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY159" t="n">
         <v>9</v>
       </c>
       <c r="AZ159" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA159" t="n">
         <v>5</v>
@@ -35361,13 +35361,13 @@
         <v>0.27</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AU160" t="n">
         <v>2</v>
@@ -35579,13 +35579,13 @@
         <v>0.3</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AS161" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="AU161" t="n">
         <v>4</v>
@@ -35594,16 +35594,16 @@
         <v>5</v>
       </c>
       <c r="AW161" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX161" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ161" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA161" t="n">
         <v>1</v>
@@ -35797,13 +35797,13 @@
         <v>0.75</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AT162" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AU162" t="n">
         <v>3</v>
@@ -35812,16 +35812,16 @@
         <v>2</v>
       </c>
       <c r="AW162" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX162" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY162" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ162" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA162" t="n">
         <v>5</v>
@@ -36015,13 +36015,13 @@
         <v>1</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AS163" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AU163" t="n">
         <v>2</v>
@@ -36030,16 +36030,16 @@
         <v>4</v>
       </c>
       <c r="AW163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX163" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY163" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ163" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA163" t="n">
         <v>5</v>
@@ -36233,13 +36233,13 @@
         <v>1.18</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AU164" t="n">
         <v>2</v>
@@ -36248,16 +36248,16 @@
         <v>2</v>
       </c>
       <c r="AW164" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX164" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA164" t="n">
         <v>4</v>
@@ -36451,13 +36451,13 @@
         <v>1.18</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="AU165" t="n">
         <v>5</v>
@@ -36466,16 +36466,16 @@
         <v>2</v>
       </c>
       <c r="AW165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX165" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY165" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ165" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA165" t="n">
         <v>2</v>
@@ -36669,13 +36669,13 @@
         <v>0.83</v>
       </c>
       <c r="AR166" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS166" t="n">
         <v>1.46</v>
       </c>
-      <c r="AS166" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AT166" t="n">
-        <v>2.76</v>
+        <v>3.02</v>
       </c>
       <c r="AU166" t="n">
         <v>4</v>
@@ -36684,13 +36684,13 @@
         <v>3</v>
       </c>
       <c r="AW166" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX166" t="n">
         <v>4</v>
       </c>
       <c r="AY166" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ166" t="n">
         <v>7</v>
@@ -36887,13 +36887,13 @@
         <v>0.92</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AS167" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AU167" t="n">
         <v>3</v>
@@ -36902,16 +36902,16 @@
         <v>6</v>
       </c>
       <c r="AW167" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AX167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY167" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ167" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ167" t="n">
-        <v>11</v>
       </c>
       <c r="BA167" t="n">
         <v>10</v>
@@ -37105,13 +37105,13 @@
         <v>1</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="AU168" t="n">
         <v>6</v>
@@ -37120,16 +37120,16 @@
         <v>5</v>
       </c>
       <c r="AW168" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX168" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY168" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ168" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA168" t="n">
         <v>10</v>
@@ -37323,13 +37323,13 @@
         <v>1.27</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.72</v>
+        <v>3.09</v>
       </c>
       <c r="AU169" t="n">
         <v>6</v>
@@ -37338,16 +37338,16 @@
         <v>4</v>
       </c>
       <c r="AW169" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY169" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ169" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA169" t="n">
         <v>3</v>
@@ -37541,13 +37541,13 @@
         <v>0.73</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AS170" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="AU170" t="n">
         <v>3</v>
@@ -37556,13 +37556,13 @@
         <v>3</v>
       </c>
       <c r="AW170" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX170" t="n">
         <v>6</v>
       </c>
       <c r="AY170" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AZ170" t="n">
         <v>9</v>
@@ -37759,13 +37759,13 @@
         <v>1.25</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AU171" t="n">
         <v>7</v>
@@ -37774,16 +37774,16 @@
         <v>4</v>
       </c>
       <c r="AW171" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX171" t="n">
         <v>7</v>
       </c>
-      <c r="AX171" t="n">
-        <v>4</v>
-      </c>
       <c r="AY171" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AZ171" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA171" t="n">
         <v>7</v>
@@ -37977,13 +37977,13 @@
         <v>0.8</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.81</v>
+        <v>3.03</v>
       </c>
       <c r="AU172" t="n">
         <v>5</v>
@@ -37992,13 +37992,13 @@
         <v>3</v>
       </c>
       <c r="AW172" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX172" t="n">
         <v>0</v>
       </c>
       <c r="AY172" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ172" t="n">
         <v>3</v>
@@ -38195,13 +38195,13 @@
         <v>1.08</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.68</v>
+        <v>3.01</v>
       </c>
       <c r="AU173" t="n">
         <v>8</v>
@@ -38210,16 +38210,16 @@
         <v>2</v>
       </c>
       <c r="AW173" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AX173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY173" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AZ173" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA173" t="n">
         <v>11</v>
@@ -38413,13 +38413,13 @@
         <v>1.75</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="AU174" t="n">
         <v>3</v>
@@ -38428,13 +38428,13 @@
         <v>5</v>
       </c>
       <c r="AW174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX174" t="n">
         <v>0</v>
       </c>
       <c r="AY174" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ174" t="n">
         <v>5</v>
@@ -38631,13 +38631,13 @@
         <v>0.75</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.76</v>
+        <v>3.03</v>
       </c>
       <c r="AU175" t="n">
         <v>6</v>
@@ -38646,16 +38646,16 @@
         <v>6</v>
       </c>
       <c r="AW175" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX175" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AY175" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ175" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BA175" t="n">
         <v>5</v>
@@ -38849,13 +38849,13 @@
         <v>0.27</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="AU176" t="n">
         <v>8</v>
@@ -38864,16 +38864,16 @@
         <v>4</v>
       </c>
       <c r="AW176" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX176" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY176" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AZ176" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA176" t="n">
         <v>7</v>
@@ -39067,13 +39067,13 @@
         <v>1.55</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="AU177" t="n">
         <v>3</v>
@@ -39082,16 +39082,16 @@
         <v>6</v>
       </c>
       <c r="AW177" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX177" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY177" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ177" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA177" t="n">
         <v>3</v>
@@ -39285,13 +39285,13 @@
         <v>0.58</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AT178" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AU178" t="n">
         <v>5</v>
@@ -39300,16 +39300,16 @@
         <v>6</v>
       </c>
       <c r="AW178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX178" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ178" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA178" t="n">
         <v>2</v>
@@ -39503,13 +39503,13 @@
         <v>0.92</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AU179" t="n">
         <v>4</v>
@@ -39518,16 +39518,16 @@
         <v>2</v>
       </c>
       <c r="AW179" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AX179" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY179" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ179" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA179" t="n">
         <v>13</v>
@@ -39721,13 +39721,13 @@
         <v>1.18</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU180" t="n">
         <v>4</v>
@@ -39736,16 +39736,16 @@
         <v>5</v>
       </c>
       <c r="AW180" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ180" t="n">
         <v>13</v>
-      </c>
-      <c r="AX180" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY180" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ180" t="n">
-        <v>12</v>
       </c>
       <c r="BA180" t="n">
         <v>6</v>
@@ -39939,13 +39939,13 @@
         <v>1</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="AU181" t="n">
         <v>7</v>
@@ -39954,16 +39954,16 @@
         <v>6</v>
       </c>
       <c r="AW181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX181" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY181" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ181" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA181" t="n">
         <v>7</v>
@@ -40157,13 +40157,13 @@
         <v>0.73</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="AU182" t="n">
         <v>3</v>
@@ -40172,16 +40172,16 @@
         <v>6</v>
       </c>
       <c r="AW182" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX182" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AY182" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ182" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
@@ -40375,13 +40375,13 @@
         <v>1</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AS183" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AU183" t="n">
         <v>6</v>
@@ -40390,16 +40390,16 @@
         <v>5</v>
       </c>
       <c r="AW183" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX183" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AY183" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ183" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BA183" t="n">
         <v>3</v>
@@ -40593,13 +40593,13 @@
         <v>1</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.67</v>
+        <v>3.04</v>
       </c>
       <c r="AU184" t="n">
         <v>5</v>
@@ -40608,16 +40608,16 @@
         <v>3</v>
       </c>
       <c r="AW184" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX184" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY184" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ184" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA184" t="n">
         <v>4</v>
@@ -40811,13 +40811,13 @@
         <v>0.3</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AS185" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AU185" t="n">
         <v>4</v>
@@ -40826,16 +40826,16 @@
         <v>2</v>
       </c>
       <c r="AW185" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ185" t="n">
         <v>5</v>
-      </c>
-      <c r="AX185" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY185" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ185" t="n">
-        <v>3</v>
       </c>
       <c r="BA185" t="n">
         <v>8</v>
@@ -41029,13 +41029,13 @@
         <v>1.27</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AT186" t="n">
-        <v>2.58</v>
+        <v>2.93</v>
       </c>
       <c r="AU186" t="n">
         <v>3</v>
@@ -41044,16 +41044,16 @@
         <v>5</v>
       </c>
       <c r="AW186" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX186" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY186" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ186" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ186" t="n">
-        <v>7</v>
       </c>
       <c r="BA186" t="n">
         <v>4</v>
@@ -41247,13 +41247,13 @@
         <v>1.25</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT187" t="n">
-        <v>2.74</v>
+        <v>3.06</v>
       </c>
       <c r="AU187" t="n">
         <v>3</v>
@@ -41262,16 +41262,16 @@
         <v>1</v>
       </c>
       <c r="AW187" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX187" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY187" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ187" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA187" t="n">
         <v>3</v>
@@ -41465,13 +41465,13 @@
         <v>0.73</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AS188" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AT188" t="n">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="AU188" t="n">
         <v>7</v>
@@ -41480,16 +41480,16 @@
         <v>2</v>
       </c>
       <c r="AW188" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX188" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ188" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA188" t="n">
         <v>3</v>
@@ -41683,13 +41683,13 @@
         <v>1.18</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="AU189" t="n">
         <v>6</v>
@@ -41698,16 +41698,16 @@
         <v>6</v>
       </c>
       <c r="AW189" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX189" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY189" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AZ189" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA189" t="n">
         <v>6</v>
@@ -41901,13 +41901,13 @@
         <v>0.83</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AT190" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AU190" t="n">
         <v>2</v>
@@ -41916,16 +41916,16 @@
         <v>0</v>
       </c>
       <c r="AW190" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX190" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY190" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ190" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA190" t="n">
         <v>1</v>
@@ -42119,13 +42119,13 @@
         <v>1.18</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AU191" t="n">
         <v>9</v>
@@ -42134,13 +42134,13 @@
         <v>2</v>
       </c>
       <c r="AW191" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AX191" t="n">
         <v>5</v>
       </c>
       <c r="AY191" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AZ191" t="n">
         <v>7</v>
@@ -42337,13 +42337,13 @@
         <v>1.75</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AU192" t="n">
         <v>4</v>
@@ -42352,16 +42352,16 @@
         <v>3</v>
       </c>
       <c r="AW192" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AX192" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY192" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ192" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ192" t="n">
-        <v>10</v>
       </c>
       <c r="BA192" t="n">
         <v>3</v>
@@ -42555,13 +42555,13 @@
         <v>1.08</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="AU193" t="n">
         <v>6</v>
@@ -42570,16 +42570,16 @@
         <v>7</v>
       </c>
       <c r="AW193" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX193" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY193" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ193" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA193" t="n">
         <v>7</v>
@@ -42773,13 +42773,13 @@
         <v>1.18</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AU194" t="n">
         <v>3</v>
@@ -42788,13 +42788,13 @@
         <v>0</v>
       </c>
       <c r="AW194" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX194" t="n">
         <v>6</v>
       </c>
       <c r="AY194" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ194" t="n">
         <v>6</v>
@@ -42991,13 +42991,13 @@
         <v>0.58</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="AU195" t="n">
         <v>3</v>
@@ -43006,16 +43006,16 @@
         <v>6</v>
       </c>
       <c r="AW195" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX195" t="n">
         <v>7</v>
       </c>
-      <c r="AX195" t="n">
-        <v>4</v>
-      </c>
       <c r="AY195" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ195" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA195" t="n">
         <v>1</v>
@@ -43209,13 +43209,13 @@
         <v>1.55</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="AU196" t="n">
         <v>3</v>
@@ -43224,13 +43224,13 @@
         <v>5</v>
       </c>
       <c r="AW196" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX196" t="n">
         <v>5</v>
       </c>
       <c r="AY196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ196" t="n">
         <v>10</v>
@@ -43427,13 +43427,13 @@
         <v>0.75</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="AU197" t="n">
         <v>6</v>
@@ -43442,16 +43442,16 @@
         <v>4</v>
       </c>
       <c r="AW197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX197" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AY197" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ197" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA197" t="n">
         <v>4</v>
@@ -43645,13 +43645,13 @@
         <v>1</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="AU198" t="n">
         <v>7</v>
@@ -43660,16 +43660,16 @@
         <v>6</v>
       </c>
       <c r="AW198" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY198" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ198" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA198" t="n">
         <v>7</v>
@@ -43863,13 +43863,13 @@
         <v>0.92</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AS199" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.57</v>
+        <v>2.87</v>
       </c>
       <c r="AU199" t="n">
         <v>5</v>
@@ -43878,16 +43878,16 @@
         <v>3</v>
       </c>
       <c r="AW199" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AX199" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY199" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AZ199" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA199" t="n">
         <v>6</v>
@@ -44081,13 +44081,13 @@
         <v>0.8</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="AU200" t="n">
         <v>6</v>
@@ -44096,16 +44096,16 @@
         <v>4</v>
       </c>
       <c r="AW200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX200" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY200" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ200" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA200" t="n">
         <v>4</v>
@@ -44299,13 +44299,13 @@
         <v>0.27</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="AU201" t="n">
         <v>6</v>
@@ -44314,16 +44314,16 @@
         <v>2</v>
       </c>
       <c r="AW201" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AX201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY201" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AZ201" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA201" t="n">
         <v>5</v>
@@ -44517,13 +44517,13 @@
         <v>0.3</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AS202" t="n">
-        <v>0.89</v>
+        <v>1.01</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="AU202" t="n">
         <v>4</v>
@@ -44532,16 +44532,16 @@
         <v>3</v>
       </c>
       <c r="AW202" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX202" t="n">
         <v>6</v>
       </c>
-      <c r="AX202" t="n">
-        <v>3</v>
-      </c>
       <c r="AY202" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ202" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA202" t="n">
         <v>9</v>
@@ -44735,13 +44735,13 @@
         <v>1.25</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AU203" t="n">
         <v>5</v>
@@ -44750,16 +44750,16 @@
         <v>0</v>
       </c>
       <c r="AW203" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX203" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY203" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ203" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA203" t="n">
         <v>4</v>
@@ -44953,13 +44953,13 @@
         <v>1.18</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="AU204" t="n">
         <v>7</v>
@@ -44968,16 +44968,16 @@
         <v>2</v>
       </c>
       <c r="AW204" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX204" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY204" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ204" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA204" t="n">
         <v>9</v>
@@ -45171,13 +45171,13 @@
         <v>0.73</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AU205" t="n">
         <v>3</v>
@@ -45186,16 +45186,16 @@
         <v>1</v>
       </c>
       <c r="AW205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX205" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY205" t="n">
         <v>12</v>
       </c>
-      <c r="AY205" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ205" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA205" t="n">
         <v>4</v>
@@ -45389,13 +45389,13 @@
         <v>1</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.61</v>
+        <v>2.99</v>
       </c>
       <c r="AU206" t="n">
         <v>6</v>
@@ -45404,13 +45404,13 @@
         <v>3</v>
       </c>
       <c r="AW206" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX206" t="n">
         <v>2</v>
       </c>
       <c r="AY206" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ206" t="n">
         <v>5</v>
@@ -45607,13 +45607,13 @@
         <v>0.83</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="AU207" t="n">
         <v>5</v>
@@ -45622,16 +45622,16 @@
         <v>5</v>
       </c>
       <c r="AW207" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX207" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AY207" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ207" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BA207" t="n">
         <v>1</v>
@@ -45825,13 +45825,13 @@
         <v>0.73</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="AU208" t="n">
         <v>7</v>
@@ -45840,16 +45840,16 @@
         <v>2</v>
       </c>
       <c r="AW208" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AX208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY208" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AZ208" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA208" t="n">
         <v>5</v>
@@ -46043,13 +46043,13 @@
         <v>1.27</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="AU209" t="n">
         <v>9</v>
@@ -46058,16 +46058,16 @@
         <v>3</v>
       </c>
       <c r="AW209" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX209" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY209" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ209" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA209" t="n">
         <v>4</v>
@@ -46261,13 +46261,13 @@
         <v>1</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="AU210" t="n">
         <v>1</v>
@@ -46276,16 +46276,16 @@
         <v>2</v>
       </c>
       <c r="AW210" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AX210" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY210" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AZ210" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA210" t="n">
         <v>9</v>
@@ -46479,13 +46479,13 @@
         <v>1.18</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="AU211" t="n">
         <v>6</v>
@@ -46494,16 +46494,16 @@
         <v>3</v>
       </c>
       <c r="AW211" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY211" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AZ211" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA211" t="n">
         <v>8</v>
@@ -46697,13 +46697,13 @@
         <v>1.75</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AU212" t="n">
         <v>3</v>
@@ -46712,16 +46712,16 @@
         <v>4</v>
       </c>
       <c r="AW212" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ212" t="n">
         <v>9</v>
-      </c>
-      <c r="AX212" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY212" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ212" t="n">
-        <v>8</v>
       </c>
       <c r="BA212" t="n">
         <v>4</v>
@@ -46915,13 +46915,13 @@
         <v>0.58</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="AU213" t="n">
         <v>5</v>
@@ -46930,16 +46930,16 @@
         <v>5</v>
       </c>
       <c r="AW213" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX213" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY213" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ213" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA213" t="n">
         <v>5</v>
@@ -47133,13 +47133,13 @@
         <v>0.73</v>
       </c>
       <c r="AR214" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AS214" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AU214" t="n">
         <v>5</v>
@@ -47351,13 +47351,13 @@
         <v>1.55</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="AU215" t="n">
         <v>3</v>
@@ -47569,13 +47569,13 @@
         <v>0.83</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AT216" t="n">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="AU216" t="n">
         <v>4</v>
@@ -47584,13 +47584,13 @@
         <v>2</v>
       </c>
       <c r="AW216" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX216" t="n">
         <v>7</v>
       </c>
       <c r="AY216" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ216" t="n">
         <v>9</v>
@@ -47787,13 +47787,13 @@
         <v>0.92</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AS217" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AU217" t="n">
         <v>7</v>
@@ -48005,13 +48005,13 @@
         <v>1.08</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="AU218" t="n">
         <v>5</v>
@@ -48223,13 +48223,13 @@
         <v>0.75</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.95</v>
+        <v>3.46</v>
       </c>
       <c r="AU219" t="n">
         <v>4</v>
@@ -48238,13 +48238,13 @@
         <v>4</v>
       </c>
       <c r="AW219" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX219" t="n">
         <v>11</v>
       </c>
       <c r="AY219" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ219" t="n">
         <v>15</v>
@@ -48441,28 +48441,28 @@
         <v>1.18</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AU220" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV220" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW220" t="n">
         <v>16</v>
       </c>
       <c r="AX220" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY220" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ220" t="n">
         <v>9</v>
@@ -48659,31 +48659,31 @@
         <v>1</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="AU221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV221" t="n">
         <v>3</v>
       </c>
       <c r="AW221" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX221" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY221" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ221" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA221" t="n">
         <v>7</v>
@@ -48877,13 +48877,13 @@
         <v>1.25</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT222" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AU222" t="n">
         <v>2</v>
@@ -49095,13 +49095,13 @@
         <v>1</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AU223" t="n">
         <v>4</v>
@@ -49313,13 +49313,13 @@
         <v>1.18</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="AU224" t="n">
         <v>5</v>
@@ -49531,13 +49531,13 @@
         <v>0.58</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AU225" t="n">
         <v>1</v>
@@ -49749,13 +49749,13 @@
         <v>1.27</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.65</v>
+        <v>3.09</v>
       </c>
       <c r="AU226" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.27</v>
@@ -1350,7 +1350,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.18</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -4184,7 +4184,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.27</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.25</v>
@@ -5710,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -6582,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR30" t="n">
         <v>2.72</v>
@@ -10288,7 +10288,7 @@
         <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR45" t="n">
         <v>1.33</v>
@@ -10724,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -10942,7 +10942,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR48" t="n">
         <v>1.9</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.75</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.08</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.75</v>
@@ -14212,7 +14212,7 @@
         <v>2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR63" t="n">
         <v>1.5</v>
@@ -14648,7 +14648,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR65" t="n">
         <v>2</v>
@@ -14863,10 +14863,10 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR66" t="n">
         <v>1.45</v>
@@ -16171,7 +16171,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -17697,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.55</v>
@@ -18790,7 +18790,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19444,7 +19444,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR87" t="n">
         <v>1.6</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ90" t="n">
         <v>1</v>
@@ -20316,7 +20316,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR91" t="n">
         <v>1.69</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.73</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.18</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.92</v>
@@ -23804,7 +23804,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR107" t="n">
         <v>1.65</v>
@@ -24022,7 +24022,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR108" t="n">
         <v>1.47</v>
@@ -24240,7 +24240,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR109" t="n">
         <v>1.15</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.73</v>
@@ -25766,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR116" t="n">
         <v>1.33</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.75</v>
@@ -28382,7 +28382,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR128" t="n">
         <v>1.74</v>
@@ -29690,7 +29690,7 @@
         <v>2</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -30126,7 +30126,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR136" t="n">
         <v>1.97</v>
@@ -30995,7 +30995,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.08</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.73</v>
@@ -31652,7 +31652,7 @@
         <v>2</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -32521,7 +32521,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ147" t="n">
         <v>1</v>
@@ -33832,7 +33832,7 @@
         <v>2</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR153" t="n">
         <v>1.49</v>
@@ -34265,10 +34265,10 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -35358,7 +35358,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR160" t="n">
         <v>1.33</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.3</v>
@@ -36445,7 +36445,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.18</v>
@@ -37974,7 +37974,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR172" t="n">
         <v>1.66</v>
@@ -38846,7 +38846,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR176" t="n">
         <v>1.38</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.58</v>
@@ -40151,10 +40151,10 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR182" t="n">
         <v>1.54</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.18</v>
@@ -44078,7 +44078,7 @@
         <v>1</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -44293,10 +44293,10 @@
         <v>0.3</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR201" t="n">
         <v>1.52</v>
@@ -44511,7 +44511,7 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.3</v>
@@ -45168,7 +45168,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR205" t="n">
         <v>1.71</v>
@@ -46255,7 +46255,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ210" t="n">
         <v>1</v>
@@ -49822,6 +49822,660 @@
       </c>
       <c r="BP226" t="n">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>7841255</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>45893.66666666666</v>
+      </c>
+      <c r="F227" t="n">
+        <v>23</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="n">
+        <v>2</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="n">
+        <v>2</v>
+      </c>
+      <c r="N227" t="n">
+        <v>3</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>['40', '50']</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R227" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S227" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V227" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X227" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>7841260</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>45893.77083333334</v>
+      </c>
+      <c r="F228" t="n">
+        <v>23</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R228" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S228" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U228" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V228" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X228" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>7841254</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>45893.85416666666</v>
+      </c>
+      <c r="F229" t="n">
+        <v>23</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="n">
+        <v>2</v>
+      </c>
+      <c r="L229" t="n">
+        <v>2</v>
+      </c>
+      <c r="M229" t="n">
+        <v>2</v>
+      </c>
+      <c r="N229" t="n">
+        <v>4</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>['19', '47']</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['14', '90']</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R229" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S229" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V229" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X229" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
         <v>1</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.82</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.92</v>
@@ -6146,7 +6146,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR26" t="n">
         <v>1.36</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.18</v>
@@ -7236,7 +7236,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR31" t="n">
         <v>1.94</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.58</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.55</v>
@@ -12032,7 +12032,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR53" t="n">
         <v>0.93</v>
@@ -13776,7 +13776,7 @@
         <v>1</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR61" t="n">
         <v>1.62</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.82</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.18</v>
@@ -15738,7 +15738,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR70" t="n">
         <v>1.12</v>
@@ -17918,7 +17918,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR80" t="n">
         <v>1.73</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.25</v>
@@ -19877,7 +19877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.75</v>
@@ -20098,7 +20098,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -22278,7 +22278,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR100" t="n">
         <v>1.47</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.75</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.75</v>
@@ -24458,7 +24458,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR110" t="n">
         <v>1.88</v>
@@ -26420,7 +26420,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR119" t="n">
         <v>1.9</v>
@@ -27071,7 +27071,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.25</v>
@@ -27507,7 +27507,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.27</v>
@@ -28600,7 +28600,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -30562,7 +30562,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR138" t="n">
         <v>1.81</v>
@@ -32085,7 +32085,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.92</v>
@@ -32524,7 +32524,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR147" t="n">
         <v>1.59</v>
@@ -32739,7 +32739,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ148" t="n">
         <v>1</v>
@@ -35355,7 +35355,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.33</v>
@@ -35576,7 +35576,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR161" t="n">
         <v>1.65</v>
@@ -37099,10 +37099,10 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR168" t="n">
         <v>1.68</v>
@@ -39715,7 +39715,7 @@
         <v>1.13</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.18</v>
@@ -40590,7 +40590,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR184" t="n">
         <v>1.84</v>
@@ -40808,7 +40808,7 @@
         <v>2</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR185" t="n">
         <v>1.35</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.73</v>
@@ -42985,7 +42985,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.58</v>
@@ -44514,7 +44514,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR202" t="n">
         <v>1.45</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.83</v>
@@ -46258,7 +46258,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR210" t="n">
         <v>1.66</v>
@@ -49113,13 +49113,13 @@
         <v>11</v>
       </c>
       <c r="AX223" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY223" t="n">
         <v>15</v>
       </c>
       <c r="AZ223" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA223" t="n">
         <v>4</v>
@@ -49761,13 +49761,13 @@
         <v>2</v>
       </c>
       <c r="AV226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW226" t="n">
         <v>11</v>
       </c>
       <c r="AX226" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY226" t="n">
         <v>13</v>
@@ -49976,19 +49976,19 @@
         <v>2.99</v>
       </c>
       <c r="AU227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV227" t="n">
         <v>4</v>
       </c>
       <c r="AW227" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX227" t="n">
         <v>2</v>
       </c>
       <c r="AY227" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ227" t="n">
         <v>6</v>
@@ -50476,6 +50476,442 @@
       </c>
       <c r="BP229" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>7841261</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>45894.79166666666</v>
+      </c>
+      <c r="F230" t="n">
+        <v>23</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>2</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>2</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['59', '87']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S230" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V230" t="n">
+        <v>4</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X230" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>7841256</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>45894.89583333334</v>
+      </c>
+      <c r="F231" t="n">
+        <v>23</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
+        <v>2</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>['55', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2</v>
+      </c>
+      <c r="S231" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U231" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V231" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X231" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -50866,13 +50866,13 @@
         <v>8</v>
       </c>
       <c r="BA231" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB231" t="n">
         <v>2</v>
       </c>
       <c r="BC231" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD231" t="n">
         <v>1.49</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -50854,13 +50854,13 @@
         <v>4</v>
       </c>
       <c r="AW231" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX231" t="n">
         <v>4</v>
       </c>
       <c r="AY231" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ231" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3094,7 +3094,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.58</v>
@@ -8762,7 +8762,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.75</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.55</v>
@@ -12686,7 +12686,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -15735,7 +15735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.92</v>
@@ -17482,7 +17482,7 @@
         <v>2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.33</v>
@@ -22496,7 +22496,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.92</v>
@@ -27292,7 +27292,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -27725,7 +27725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.92</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.83</v>
@@ -33396,7 +33396,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ163" t="n">
         <v>1</v>
@@ -36230,7 +36230,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -39718,7 +39718,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.08</v>
@@ -42770,7 +42770,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -47127,7 +47127,7 @@
         <v>0.7</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.73</v>
@@ -48438,7 +48438,7 @@
         <v>1</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -50911,6 +50911,224 @@
         <v>2.41</v>
       </c>
       <c r="BP231" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>7841265</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>45897.89930555555</v>
+      </c>
+      <c r="F232" t="n">
+        <v>24</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
+        <v>1</v>
+      </c>
+      <c r="N232" t="n">
+        <v>1</v>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>['90+11']</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R232" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S232" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="T232" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U232" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V232" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X232" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT232" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU232" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW232" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX232" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY232" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ232" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA232" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB232" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC232" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE232" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF232" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG232" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH232" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BI232" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ232" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK232" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL232" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM232" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN232" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO232" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP232" t="n">
         <v>1.48</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3530,7 +3530,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.55</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.92</v>
@@ -8980,7 +8980,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -11814,7 +11814,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR52" t="n">
         <v>2.13</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.58</v>
@@ -14430,7 +14430,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR64" t="n">
         <v>1.71</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.73</v>
@@ -19662,7 +19662,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR88" t="n">
         <v>1.88</v>
@@ -21621,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.27</v>
@@ -22714,7 +22714,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR102" t="n">
         <v>1.21</v>
@@ -25984,7 +25984,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR117" t="n">
         <v>1.74</v>
@@ -28815,7 +28815,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ130" t="n">
         <v>1</v>
@@ -29908,7 +29908,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR135" t="n">
         <v>1.69</v>
@@ -32957,7 +32957,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.25</v>
@@ -33614,7 +33614,7 @@
         <v>2</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR152" t="n">
         <v>1.73</v>
@@ -35791,7 +35791,7 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.75</v>
@@ -37971,7 +37971,7 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.82</v>
@@ -38410,7 +38410,7 @@
         <v>1</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR174" t="n">
         <v>1.43</v>
@@ -42334,7 +42334,7 @@
         <v>2</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR192" t="n">
         <v>1.47</v>
@@ -42767,7 +42767,7 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.33</v>
@@ -46694,7 +46694,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR212" t="n">
         <v>1.78</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ221" t="n">
         <v>1</v>
@@ -51130,6 +51130,224 @@
       </c>
       <c r="BP232" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>7841267</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>45898.79166666666</v>
+      </c>
+      <c r="F233" t="n">
+        <v>24</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>1</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R233" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S233" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U233" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V233" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X233" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT233" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU233" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW233" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX233" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY233" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA233" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE233" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF233" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG233" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH233" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI233" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ233" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK233" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL233" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM233" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN233" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO233" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP233" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.55</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.25</v>
@@ -2004,7 +2004,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.33</v>
@@ -3748,7 +3748,7 @@
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.92</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.33</v>
@@ -7454,7 +7454,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -7672,7 +7672,7 @@
         <v>2</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.75</v>
@@ -12250,7 +12250,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR54" t="n">
         <v>1.59</v>
@@ -12468,7 +12468,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -12901,10 +12901,10 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR57" t="n">
         <v>1.36</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.83</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.25</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.62</v>
@@ -15956,7 +15956,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR71" t="n">
         <v>1.88</v>
@@ -16610,7 +16610,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -17046,7 +17046,7 @@
         <v>1</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -17479,7 +17479,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.33</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.08</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.18</v>
@@ -19226,7 +19226,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR86" t="n">
         <v>1.94</v>
@@ -20534,7 +20534,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR92" t="n">
         <v>1.81</v>
@@ -20752,7 +20752,7 @@
         <v>2</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR93" t="n">
         <v>1.68</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.18</v>
@@ -23150,7 +23150,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR104" t="n">
         <v>1.55</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.33</v>
@@ -24019,7 +24019,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.82</v>
@@ -25112,7 +25112,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.55</v>
@@ -25545,7 +25545,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.18</v>
@@ -27728,7 +27728,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR125" t="n">
         <v>1.2</v>
@@ -28818,7 +28818,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR130" t="n">
         <v>1.56</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.18</v>
@@ -29251,7 +29251,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.58</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.62</v>
@@ -31216,7 +31216,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -32088,7 +32088,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR145" t="n">
         <v>1.63</v>
@@ -32742,7 +32742,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.33</v>
@@ -33611,7 +33611,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.62</v>
@@ -34483,7 +34483,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.55</v>
@@ -36012,7 +36012,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR163" t="n">
         <v>1.21</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.83</v>
@@ -36884,7 +36884,7 @@
         <v>2</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR167" t="n">
         <v>1.26</v>
@@ -37538,7 +37538,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR170" t="n">
         <v>1.36</v>
@@ -38189,7 +38189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.08</v>
@@ -39500,7 +39500,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR179" t="n">
         <v>1.34</v>
@@ -40369,10 +40369,10 @@
         <v>1.25</v>
       </c>
       <c r="AP183" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR183" t="n">
         <v>1.91</v>
@@ -41462,7 +41462,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR188" t="n">
         <v>1.72</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.18</v>
@@ -43857,10 +43857,10 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR199" t="n">
         <v>1.8</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.92</v>
@@ -45386,7 +45386,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR206" t="n">
         <v>1.82</v>
@@ -45822,7 +45822,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR208" t="n">
         <v>1.71</v>
@@ -46473,7 +46473,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.18</v>
@@ -47130,7 +47130,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -47563,7 +47563,7 @@
         <v>0.82</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.83</v>
@@ -47784,7 +47784,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR217" t="n">
         <v>1.47</v>
@@ -49092,7 +49092,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR223" t="n">
         <v>1.87</v>
@@ -49525,7 +49525,7 @@
         <v>0.64</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.58</v>
@@ -49743,7 +49743,7 @@
         <v>1.1</v>
       </c>
       <c r="AP226" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ226" t="n">
         <v>1.27</v>
@@ -51348,6 +51348,660 @@
       </c>
       <c r="BP233" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>7841268</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>45899.66666666666</v>
+      </c>
+      <c r="F234" t="n">
+        <v>24</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>2</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>2</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>['49', '90+7']</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R234" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S234" t="n">
+        <v>5</v>
+      </c>
+      <c r="T234" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U234" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V234" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X234" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY234" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE234" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="BI234" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO234" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>7841263</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>45899.77083333334</v>
+      </c>
+      <c r="F235" t="n">
+        <v>24</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>1</v>
+      </c>
+      <c r="J235" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" t="n">
+        <v>2</v>
+      </c>
+      <c r="L235" t="n">
+        <v>2</v>
+      </c>
+      <c r="M235" t="n">
+        <v>3</v>
+      </c>
+      <c r="N235" t="n">
+        <v>5</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>['1', '82']</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>['8', '71', '85']</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R235" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S235" t="n">
+        <v>7</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U235" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V235" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W235" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X235" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT235" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU235" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV235" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW235" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX235" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY235" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ235" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA235" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB235" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE235" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF235" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG235" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH235" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI235" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ235" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK235" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL235" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM235" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN235" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO235" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP235" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>7841262</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>45899.85416666666</v>
+      </c>
+      <c r="F236" t="n">
+        <v>24</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>1</v>
+      </c>
+      <c r="J236" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" t="n">
+        <v>2</v>
+      </c>
+      <c r="L236" t="n">
+        <v>2</v>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
+      <c r="N236" t="n">
+        <v>3</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>['29', '49']</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R236" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S236" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T236" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U236" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V236" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W236" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X236" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT236" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU236" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV236" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW236" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX236" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY236" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ236" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA236" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB236" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE236" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF236" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="BG236" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH236" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="BI236" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ236" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK236" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL236" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM236" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN236" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO236" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP236" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -51520,13 +51520,13 @@
         <v>16</v>
       </c>
       <c r="BA234" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB234" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC234" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD234" t="n">
         <v>1.51</v>
@@ -51959,10 +51959,10 @@
         <v>4</v>
       </c>
       <c r="BB236" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC236" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD236" t="n">
         <v>1.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -51075,13 +51075,13 @@
         <v>9</v>
       </c>
       <c r="AX232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY232" t="n">
         <v>15</v>
       </c>
       <c r="AZ232" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA232" t="n">
         <v>5</v>
@@ -51520,13 +51520,13 @@
         <v>16</v>
       </c>
       <c r="BA234" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC234" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD234" t="n">
         <v>1.51</v>
@@ -51959,10 +51959,10 @@
         <v>4</v>
       </c>
       <c r="BB236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC236" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD236" t="n">
         <v>1.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP236"/>
+  <dimension ref="A1:BP237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.18</v>
@@ -7236,7 +7236,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR31" t="n">
         <v>1.94</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.83</v>
@@ -12032,7 +12032,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR53" t="n">
         <v>0.93</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.92</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.18</v>
@@ -17918,7 +17918,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR80" t="n">
         <v>1.73</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.55</v>
@@ -22278,7 +22278,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR100" t="n">
         <v>1.47</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.62</v>
@@ -26420,7 +26420,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR119" t="n">
         <v>1.9</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.33</v>
@@ -30562,7 +30562,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR138" t="n">
         <v>1.81</v>
@@ -31431,7 +31431,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.75</v>
@@ -35576,7 +35576,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR161" t="n">
         <v>1.65</v>
@@ -36227,7 +36227,7 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.33</v>
@@ -40808,7 +40808,7 @@
         <v>2</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR185" t="n">
         <v>1.35</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.25</v>
@@ -44514,7 +44514,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR202" t="n">
         <v>1.45</v>
@@ -45819,7 +45819,7 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.92</v>
@@ -47999,7 +47999,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.08</v>
@@ -50836,7 +50836,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR231" t="n">
         <v>1.66</v>
@@ -52002,6 +52002,224 @@
       </c>
       <c r="BP236" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>7841264</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>45900.66666666666</v>
+      </c>
+      <c r="F237" t="n">
+        <v>24</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" t="n">
+        <v>2</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>2</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>['45', '56']</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R237" t="n">
+        <v>2</v>
+      </c>
+      <c r="S237" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U237" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V237" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W237" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X237" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT237" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU237" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW237" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX237" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY237" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ237" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA237" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB237" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC237" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD237" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE237" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF237" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG237" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH237" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI237" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ237" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK237" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL237" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM237" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN237" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO237" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP237" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP237"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.83</v>
@@ -2876,7 +2876,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR27" t="n">
         <v>1.86</v>
@@ -7890,7 +7890,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.08</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.85</v>
@@ -15302,7 +15302,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.5</v>
@@ -18572,7 +18572,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -22057,7 +22057,7 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.58</v>
@@ -24676,7 +24676,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ121" t="n">
         <v>1</v>
@@ -29036,7 +29036,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.92</v>
@@ -33178,7 +33178,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -36448,7 +36448,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -37317,7 +37317,7 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.27</v>
@@ -40587,7 +40587,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.92</v>
@@ -41680,7 +41680,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -45383,7 +45383,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.92</v>
@@ -46476,7 +46476,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -48217,7 +48217,7 @@
         <v>0.55</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.75</v>
@@ -52220,6 +52220,224 @@
       </c>
       <c r="BP237" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>7841271</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>45900.77083333334</v>
+      </c>
+      <c r="F238" t="n">
+        <v>24</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
+        <v>2</v>
+      </c>
+      <c r="N238" t="n">
+        <v>2</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>['63', '78']</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>3</v>
+      </c>
+      <c r="R238" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S238" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T238" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U238" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V238" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W238" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X238" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT238" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU238" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV238" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW238" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY238" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ238" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA238" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB238" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC238" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE238" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BF238" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG238" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH238" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BI238" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ238" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK238" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL238" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM238" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN238" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO238" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP238" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -51293,13 +51293,13 @@
         <v>14</v>
       </c>
       <c r="AX233" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY233" t="n">
         <v>17</v>
       </c>
       <c r="AZ233" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA233" t="n">
         <v>4</v>
@@ -51511,13 +51511,13 @@
         <v>9</v>
       </c>
       <c r="AX234" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY234" t="n">
         <v>13</v>
       </c>
       <c r="AZ234" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA234" t="n">
         <v>7</v>
@@ -51947,22 +51947,22 @@
         <v>13</v>
       </c>
       <c r="AX236" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY236" t="n">
         <v>20</v>
       </c>
       <c r="AZ236" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA236" t="n">
         <v>4</v>
       </c>
       <c r="BB236" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC236" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD236" t="n">
         <v>1.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.18</v>
@@ -2440,7 +2440,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.62</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.82</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.33</v>
@@ -9198,7 +9198,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR40" t="n">
         <v>1.69</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.62</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.33</v>
@@ -13558,7 +13558,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR60" t="n">
         <v>1.65</v>
@@ -16171,7 +16171,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72" t="n">
         <v>1</v>
@@ -16389,10 +16389,10 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR73" t="n">
         <v>1.62</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.92</v>
@@ -21406,7 +21406,7 @@
         <v>1</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR96" t="n">
         <v>1.47</v>
@@ -22275,7 +22275,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.5</v>
@@ -26202,7 +26202,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR118" t="n">
         <v>1.88</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.08</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.75</v>
@@ -28164,7 +28164,7 @@
         <v>2</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR127" t="n">
         <v>1.31</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.55</v>
@@ -31870,7 +31870,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -32521,7 +32521,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.92</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.18</v>
@@ -36445,7 +36445,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.33</v>
@@ -36666,7 +36666,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR166" t="n">
         <v>1.56</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.33</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.92</v>
@@ -41898,7 +41898,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR190" t="n">
         <v>1.94</v>
@@ -43421,7 +43421,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.75</v>
@@ -44511,7 +44511,7 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.5</v>
@@ -45604,7 +45604,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR207" t="n">
         <v>1.71</v>
@@ -47566,7 +47566,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR216" t="n">
         <v>1.83</v>
@@ -47781,7 +47781,7 @@
         <v>1</v>
       </c>
       <c r="AP217" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.85</v>
@@ -50179,7 +50179,7 @@
         <v>0.27</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.33</v>
@@ -52438,6 +52438,442 @@
       </c>
       <c r="BP238" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>7841266</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>45901.79166666666</v>
+      </c>
+      <c r="F239" t="n">
+        <v>24</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" t="n">
+        <v>2</v>
+      </c>
+      <c r="L239" t="n">
+        <v>2</v>
+      </c>
+      <c r="M239" t="n">
+        <v>2</v>
+      </c>
+      <c r="N239" t="n">
+        <v>4</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>['41', '62']</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>['45+10', '64']</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R239" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S239" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U239" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V239" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X239" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX239" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY239" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ239" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA239" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB239" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ239" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK239" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL239" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM239" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN239" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO239" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP239" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>7841270</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>45901.89583333334</v>
+      </c>
+      <c r="F240" t="n">
+        <v>24</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>2</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>2</v>
+      </c>
+      <c r="L240" t="n">
+        <v>2</v>
+      </c>
+      <c r="M240" t="n">
+        <v>2</v>
+      </c>
+      <c r="N240" t="n">
+        <v>4</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>['30', '43']</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>['71', '77']</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" t="n">
+        <v>0</v>
+      </c>
+      <c r="W240" t="n">
+        <v>0</v>
+      </c>
+      <c r="X240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT240" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX240" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ240" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA240" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB240" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO240" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP240" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -51944,13 +51944,13 @@
         <v>3</v>
       </c>
       <c r="AW236" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX236" t="n">
         <v>10</v>
       </c>
       <c r="AY236" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ236" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.92</v>
@@ -3312,7 +3312,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.5</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.55</v>
@@ -8544,7 +8544,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR37" t="n">
         <v>2.28</v>
@@ -13340,7 +13340,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR59" t="n">
         <v>1.44</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.85</v>
@@ -16174,7 +16174,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR72" t="n">
         <v>1.97</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.82</v>
@@ -20970,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.08</v>
@@ -26856,7 +26856,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR121" t="n">
         <v>1.92</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.33</v>
@@ -29472,7 +29472,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR133" t="n">
         <v>1.92</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.33</v>
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR159" t="n">
         <v>1.43</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.25</v>
@@ -39936,7 +39936,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR181" t="n">
         <v>1.18</v>
@@ -41023,7 +41023,7 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.27</v>
@@ -43642,7 +43642,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR198" t="n">
         <v>1.74</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.18</v>
@@ -48656,7 +48656,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR221" t="n">
         <v>1.61</v>
@@ -52162,13 +52162,13 @@
         <v>0</v>
       </c>
       <c r="AW237" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX237" t="n">
         <v>4</v>
       </c>
       <c r="AY237" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ237" t="n">
         <v>4</v>
@@ -52610,13 +52610,13 @@
         <v>10</v>
       </c>
       <c r="BA239" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB239" t="n">
         <v>0</v>
       </c>
       <c r="BC239" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD239" t="n">
         <v>1.55</v>
@@ -52874,6 +52874,224 @@
       </c>
       <c r="BP240" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>7841269</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>45902.8125</v>
+      </c>
+      <c r="F241" t="n">
+        <v>24</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" t="n">
+        <v>2</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>2</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>['34', '53']</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R241" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S241" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T241" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U241" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V241" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W241" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X241" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ241" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR241" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS241" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT241" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW241" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY241" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA241" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB241" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC241" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD241" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE241" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="BF241" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BG241" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH241" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI241" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ241" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BK241" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL241" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BM241" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN241" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO241" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP241" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.27</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.92</v>
@@ -2222,7 +2222,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.25</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.92</v>
@@ -6582,7 +6582,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -6800,7 +6800,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.92</v>
@@ -9416,7 +9416,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR41" t="n">
         <v>1.61</v>
@@ -9852,7 +9852,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR43" t="n">
         <v>2.12</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.92</v>
@@ -10724,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.82</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.75</v>
@@ -11378,7 +11378,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR50" t="n">
         <v>1.42</v>
@@ -14648,7 +14648,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR65" t="n">
         <v>2</v>
@@ -15084,7 +15084,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR67" t="n">
         <v>2.09</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.75</v>
@@ -17264,7 +17264,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -17697,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.55</v>
@@ -18133,7 +18133,7 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.58</v>
@@ -18354,7 +18354,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR82" t="n">
         <v>1.73</v>
@@ -18790,7 +18790,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19441,7 +19441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.92</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.92</v>
@@ -21842,7 +21842,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR98" t="n">
         <v>1.59</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.33</v>
@@ -23368,7 +23368,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.6</v>
@@ -23804,7 +23804,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR107" t="n">
         <v>1.65</v>
@@ -24673,7 +24673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.33</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.92</v>
@@ -25548,7 +25548,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -26638,7 +26638,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR120" t="n">
         <v>1.52</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.85</v>
@@ -28382,7 +28382,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR128" t="n">
         <v>1.74</v>
@@ -28597,7 +28597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.92</v>
@@ -30344,7 +30344,7 @@
         <v>1</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR137" t="n">
         <v>1.3</v>
@@ -30995,10 +30995,10 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR140" t="n">
         <v>1.7</v>
@@ -31649,10 +31649,10 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.27</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.82</v>
@@ -34704,7 +34704,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR157" t="n">
         <v>1.92</v>
@@ -34922,7 +34922,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR158" t="n">
         <v>1.35</v>
@@ -35358,7 +35358,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR160" t="n">
         <v>1.33</v>
@@ -36881,7 +36881,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.85</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.92</v>
@@ -38192,7 +38192,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR173" t="n">
         <v>1.7</v>
@@ -38846,7 +38846,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR176" t="n">
         <v>1.38</v>
@@ -39497,7 +39497,7 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ179" t="n">
         <v>0.85</v>
@@ -40805,7 +40805,7 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.5</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.33</v>
@@ -42116,7 +42116,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR191" t="n">
         <v>1.56</v>
@@ -42552,7 +42552,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR193" t="n">
         <v>1.23</v>
@@ -43203,7 +43203,7 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.55</v>
@@ -44296,7 +44296,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR201" t="n">
         <v>1.52</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.25</v>
@@ -44950,7 +44950,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR204" t="n">
         <v>1.65</v>
@@ -46255,7 +46255,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.92</v>
@@ -46909,7 +46909,7 @@
         <v>0.6</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.58</v>
@@ -48002,7 +48002,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR218" t="n">
         <v>1.79</v>
@@ -49307,10 +49307,10 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR224" t="n">
         <v>1.36</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.92</v>
@@ -50182,7 +50182,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="AR228" t="n">
         <v>1.44</v>
@@ -53092,6 +53092,660 @@
       </c>
       <c r="BP241" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>7841278</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>45905.70833333334</v>
+      </c>
+      <c r="F242" t="n">
+        <v>25</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
+        <v>3</v>
+      </c>
+      <c r="N242" t="n">
+        <v>4</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>['25', '67', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R242" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S242" t="n">
+        <v>4</v>
+      </c>
+      <c r="T242" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U242" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V242" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X242" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ242" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR242" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS242" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT242" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU242" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW242" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX242" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY242" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ242" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA242" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB242" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC242" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE242" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF242" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BG242" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH242" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="BI242" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ242" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BK242" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL242" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM242" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN242" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BO242" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP242" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>7841275</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>45905.79166666666</v>
+      </c>
+      <c r="F243" t="n">
+        <v>25</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>1</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
+        <v>2</v>
+      </c>
+      <c r="N243" t="n">
+        <v>3</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>['90', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R243" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S243" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T243" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U243" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V243" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W243" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X243" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ243" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR243" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS243" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT243" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU243" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX243" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY243" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ243" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA243" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB243" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC243" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE243" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF243" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG243" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH243" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI243" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ243" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK243" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM243" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN243" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO243" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP243" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>7841272</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>45905.89583333334</v>
+      </c>
+      <c r="F244" t="n">
+        <v>25</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>4</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>4</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>['47', '59', '73', '88']</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R244" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S244" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T244" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U244" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V244" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W244" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X244" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR244" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS244" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT244" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU244" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX244" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY244" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ244" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA244" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB244" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC244" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BE244" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF244" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="BG244" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI244" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ244" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BK244" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL244" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM244" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN244" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BO244" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP244" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.82</v>
@@ -5274,7 +5274,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.33</v>
@@ -9634,7 +9634,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
         <v>2.35</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.55</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.33</v>
@@ -16828,7 +16828,7 @@
         <v>2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -19877,7 +19877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.75</v>
@@ -21624,7 +21624,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.62</v>
@@ -27071,7 +27071,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.25</v>
@@ -27510,7 +27510,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -32306,7 +32306,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -32739,7 +32739,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.92</v>
@@ -35355,7 +35355,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.54</v>
@@ -37320,7 +37320,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -39715,7 +39715,7 @@
         <v>1.13</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.33</v>
@@ -41026,7 +41026,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -42985,7 +42985,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.58</v>
@@ -46040,7 +46040,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR209" t="n">
         <v>1.85</v>
@@ -49746,7 +49746,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR226" t="n">
         <v>1.91</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.92</v>
@@ -53746,6 +53746,224 @@
       </c>
       <c r="BP244" t="n">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>7841281</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>45906.66666666666</v>
+      </c>
+      <c r="F245" t="n">
+        <v>25</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="n">
+        <v>1</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="n">
+        <v>3</v>
+      </c>
+      <c r="N245" t="n">
+        <v>4</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>['16', '90+1', '90+14']</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="R245" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S245" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T245" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V245" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W245" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X245" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE245" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BI245" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM245" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN245" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO245" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP245" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP245"/>
+  <dimension ref="A1:BP246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.92</v>
@@ -1786,7 +1786,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR23" t="n">
         <v>1.23</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.33</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.33</v>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR44" t="n">
         <v>1.6</v>
@@ -13994,7 +13994,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR62" t="n">
         <v>1.27</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.54</v>
@@ -19008,7 +19008,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR85" t="n">
         <v>1.6</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.62</v>
@@ -22932,7 +22932,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR103" t="n">
         <v>2.01</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.92</v>
@@ -26417,7 +26417,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.5</v>
@@ -27074,7 +27074,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR122" t="n">
         <v>1.13</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.92</v>
@@ -32960,7 +32960,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -34701,7 +34701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -37756,7 +37756,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -41244,7 +41244,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR187" t="n">
         <v>1.74</v>
@@ -41895,7 +41895,7 @@
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.85</v>
@@ -44732,7 +44732,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR203" t="n">
         <v>1.34</v>
@@ -46037,7 +46037,7 @@
         <v>1.22</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.42</v>
@@ -48874,7 +48874,7 @@
         <v>1</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR222" t="n">
         <v>1.5</v>
@@ -49089,7 +49089,7 @@
         <v>1.1</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.92</v>
@@ -53964,6 +53964,224 @@
       </c>
       <c r="BP245" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>7841277</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>45907.66666666666</v>
+      </c>
+      <c r="F246" t="n">
+        <v>25</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>2</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>2</v>
+      </c>
+      <c r="L246" t="n">
+        <v>2</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="n">
+        <v>2</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>['10', '14']</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R246" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S246" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U246" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V246" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W246" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X246" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB246" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC246" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE246" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF246" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI246" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ246" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BK246" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM246" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN246" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO246" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP246" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP246"/>
+  <dimension ref="A1:BP248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.92</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.92</v>
@@ -4402,7 +4402,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.92</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.5</v>
@@ -8323,10 +8323,10 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.58</v>
@@ -11596,7 +11596,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.82</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.85</v>
@@ -17700,7 +17700,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.15</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.82</v>
@@ -21188,7 +21188,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR95" t="n">
         <v>1.75</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.75</v>
@@ -25330,7 +25330,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.33</v>
@@ -27507,7 +27507,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.42</v>
@@ -30780,7 +30780,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -32085,7 +32085,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.85</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.33</v>
@@ -34486,7 +34486,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR156" t="n">
         <v>1.7</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.92</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.15</v>
@@ -39064,7 +39064,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR177" t="n">
         <v>1.8</v>
@@ -41023,7 +41023,7 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.42</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.92</v>
@@ -43206,7 +43206,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.33</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.85</v>
@@ -47348,7 +47348,7 @@
         <v>2</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR215" t="n">
         <v>1.54</v>
@@ -50833,7 +50833,7 @@
         <v>0.3</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.5</v>
@@ -53013,7 +53013,7 @@
         <v>1</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ241" t="n">
         <v>0.92</v>
@@ -54182,6 +54182,442 @@
       </c>
       <c r="BP246" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>7841279</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>45907.77083333334</v>
+      </c>
+      <c r="F247" t="n">
+        <v>25</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>1</v>
+      </c>
+      <c r="J247" t="n">
+        <v>1</v>
+      </c>
+      <c r="K247" t="n">
+        <v>2</v>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="n">
+        <v>1</v>
+      </c>
+      <c r="N247" t="n">
+        <v>2</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R247" t="n">
+        <v>2</v>
+      </c>
+      <c r="S247" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T247" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U247" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V247" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W247" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X247" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY247" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA247" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB247" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC247" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE247" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF247" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG247" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH247" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI247" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ247" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK247" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL247" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM247" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN247" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO247" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP247" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>7841276</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>45907.85416666666</v>
+      </c>
+      <c r="F248" t="n">
+        <v>25</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" t="n">
+        <v>2</v>
+      </c>
+      <c r="M248" t="n">
+        <v>1</v>
+      </c>
+      <c r="N248" t="n">
+        <v>3</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>['17', '52']</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R248" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S248" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T248" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U248" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V248" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W248" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X248" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO248" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ248" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY248" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA248" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB248" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC248" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD248" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE248" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF248" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG248" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH248" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI248" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ248" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK248" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL248" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM248" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN248" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO248" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP248" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -53255,22 +53255,22 @@
         <v>16</v>
       </c>
       <c r="AX242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY242" t="n">
         <v>19</v>
       </c>
       <c r="AZ242" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA242" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB242" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC242" t="n">
         <v>9</v>
-      </c>
-      <c r="BA242" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB242" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC242" t="n">
-        <v>8</v>
       </c>
       <c r="BD242" t="n">
         <v>1.65</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP248"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.92</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.85</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.54</v>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.42</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR27" t="n">
         <v>1.86</v>
@@ -7018,7 +7018,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR30" t="n">
         <v>2.72</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.92</v>
@@ -7890,7 +7890,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -8108,7 +8108,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR35" t="n">
         <v>1.53</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.33</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.42</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.15</v>
@@ -10942,7 +10942,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR48" t="n">
         <v>1.9</v>
@@ -11160,7 +11160,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -14212,7 +14212,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR63" t="n">
         <v>1.5</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.92</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ67" t="n">
         <v>1</v>
@@ -15302,7 +15302,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -15520,7 +15520,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.42</v>
@@ -18572,7 +18572,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.85</v>
@@ -19880,7 +19880,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.92</v>
@@ -20316,7 +20316,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR91" t="n">
         <v>1.69</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.92</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.15</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.85</v>
@@ -23586,7 +23586,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR106" t="n">
         <v>1.68</v>
@@ -24022,7 +24022,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR108" t="n">
         <v>1.47</v>
@@ -24676,7 +24676,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.58</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.85</v>
@@ -27946,7 +27946,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -29036,7 +29036,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -29687,10 +29687,10 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -30559,7 +30559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.5</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.92</v>
@@ -31434,7 +31434,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR142" t="n">
         <v>1.84</v>
@@ -33178,7 +33178,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.92</v>
@@ -34047,7 +34047,7 @@
         <v>0.86</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.58</v>
@@ -34268,7 +34268,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.5</v>
@@ -35794,7 +35794,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR162" t="n">
         <v>1.64</v>
@@ -36448,7 +36448,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -37974,7 +37974,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR172" t="n">
         <v>1.66</v>
@@ -38625,10 +38625,10 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR175" t="n">
         <v>1.47</v>
@@ -39061,7 +39061,7 @@
         <v>2</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.42</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.58</v>
@@ -41680,7 +41680,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -42331,7 +42331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP192" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.62</v>
@@ -43424,7 +43424,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.92</v>
@@ -44078,7 +44078,7 @@
         <v>1</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -44293,7 +44293,7 @@
         <v>0.3</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.54</v>
@@ -46476,7 +46476,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -46691,7 +46691,7 @@
         <v>1.64</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.62</v>
@@ -47345,7 +47345,7 @@
         <v>1.7</v>
       </c>
       <c r="AP215" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.42</v>
@@ -48220,7 +48220,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR219" t="n">
         <v>1.8</v>
@@ -50397,10 +50397,10 @@
         <v>0.8</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AR229" t="n">
         <v>1.56</v>
@@ -52362,7 +52362,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
@@ -53682,7 +53682,7 @@
         <v>2.7</v>
       </c>
       <c r="AU244" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV244" t="n">
         <v>1</v>
@@ -53694,7 +53694,7 @@
         <v>8</v>
       </c>
       <c r="AY244" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ244" t="n">
         <v>9</v>
@@ -54618,6 +54618,660 @@
       </c>
       <c r="BP248" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>7841280</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>45908.8125</v>
+      </c>
+      <c r="F249" t="n">
+        <v>25</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" t="n">
+        <v>1</v>
+      </c>
+      <c r="N249" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R249" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S249" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="T249" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V249" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W249" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X249" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO249" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ249" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY249" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA249" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB249" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC249" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD249" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE249" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF249" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG249" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH249" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI249" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ249" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK249" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL249" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM249" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN249" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO249" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP249" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>7841274</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>45908.83333333334</v>
+      </c>
+      <c r="F250" t="n">
+        <v>25</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R250" t="n">
+        <v>2</v>
+      </c>
+      <c r="S250" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="T250" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U250" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V250" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W250" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X250" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ250" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AU250" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY250" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA250" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB250" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC250" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE250" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF250" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG250" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH250" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI250" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ250" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK250" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL250" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM250" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN250" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO250" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP250" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>7841273</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>45908.89583333334</v>
+      </c>
+      <c r="F251" t="n">
+        <v>25</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="n">
+        <v>1</v>
+      </c>
+      <c r="N251" t="n">
+        <v>2</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S251" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T251" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U251" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V251" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W251" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X251" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ251" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU251" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY251" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA251" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB251" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC251" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE251" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BF251" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BG251" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH251" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI251" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ251" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK251" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM251" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN251" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO251" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP251" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.85</v>
@@ -3094,7 +3094,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ41" t="n">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.85</v>
@@ -12686,7 +12686,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -17482,7 +17482,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.5</v>
@@ -22057,7 +22057,7 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.58</v>
@@ -22496,7 +22496,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.92</v>
@@ -27292,7 +27292,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.92</v>
@@ -33396,7 +33396,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -36230,7 +36230,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -37317,7 +37317,7 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.42</v>
@@ -39718,7 +39718,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -40587,7 +40587,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.92</v>
@@ -42770,7 +42770,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -45383,7 +45383,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ206" t="n">
         <v>0.92</v>
@@ -48217,7 +48217,7 @@
         <v>0.55</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.6899999999999999</v>
@@ -48438,7 +48438,7 @@
         <v>1</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -51054,7 +51054,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
@@ -52359,7 +52359,7 @@
         <v>1.18</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.31</v>
@@ -55272,6 +55272,224 @@
       </c>
       <c r="BP251" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>7841291</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>45912.79166666666</v>
+      </c>
+      <c r="F252" t="n">
+        <v>26</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R252" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S252" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T252" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U252" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V252" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W252" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X252" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ252" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA252" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB252" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC252" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD252" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE252" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF252" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG252" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH252" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI252" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ252" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK252" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN252" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO252" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.92</v>
@@ -4402,7 +4402,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.92</v>
@@ -8326,7 +8326,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.92</v>
@@ -11596,7 +11596,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -17700,7 +17700,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -18133,7 +18133,7 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.58</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.92</v>
@@ -21188,7 +21188,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR95" t="n">
         <v>1.75</v>
@@ -25330,7 +25330,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.85</v>
@@ -30780,7 +30780,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -31649,7 +31649,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.54</v>
@@ -34486,7 +34486,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR156" t="n">
         <v>1.7</v>
@@ -36881,7 +36881,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.85</v>
@@ -39064,7 +39064,7 @@
         <v>2</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR177" t="n">
         <v>1.8</v>
@@ -40805,7 +40805,7 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.5</v>
@@ -43206,7 +43206,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.15</v>
@@ -47348,7 +47348,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR215" t="n">
         <v>1.54</v>
@@ -49307,7 +49307,7 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.33</v>
@@ -53667,7 +53667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ244" t="n">
         <v>1</v>
@@ -54542,7 +54542,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR248" t="n">
         <v>1.67</v>
@@ -55490,6 +55490,224 @@
       </c>
       <c r="BP252" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>7841282</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>45912.89583333334</v>
+      </c>
+      <c r="F253" t="n">
+        <v>26</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R253" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S253" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T253" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V253" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="W253" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X253" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ253" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU253" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY253" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB253" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC253" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE253" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF253" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI253" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ253" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK253" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM253" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN253" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO253" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP253" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.42</v>
@@ -2004,7 +2004,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.85</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.38</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.6899999999999999</v>
@@ -4838,7 +4838,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.15</v>
@@ -6800,7 +6800,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.85</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -9198,7 +9198,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR40" t="n">
         <v>1.69</v>
@@ -9852,7 +9852,7 @@
         <v>2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR43" t="n">
         <v>2.12</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.15</v>
@@ -10506,7 +10506,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR46" t="n">
         <v>1.4</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.54</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.6899999999999999</v>
@@ -12904,7 +12904,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR57" t="n">
         <v>1.36</v>
@@ -13119,10 +13119,10 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13558,7 +13558,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR60" t="n">
         <v>1.65</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.92</v>
@@ -16392,7 +16392,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR73" t="n">
         <v>1.62</v>
@@ -16607,10 +16607,10 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.42</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.92</v>
@@ -17264,7 +17264,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -17697,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.38</v>
@@ -18136,7 +18136,7 @@
         <v>2</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR81" t="n">
         <v>1.26</v>
@@ -20534,7 +20534,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR92" t="n">
         <v>1.81</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.92</v>
@@ -21403,10 +21403,10 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR96" t="n">
         <v>1.47</v>
@@ -21621,7 +21621,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.42</v>
@@ -21842,7 +21842,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR98" t="n">
         <v>1.59</v>
@@ -22060,7 +22060,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR99" t="n">
         <v>2.14</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.31</v>
@@ -24891,10 +24891,10 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR112" t="n">
         <v>1.77</v>
@@ -25109,10 +25109,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25548,7 +25548,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.92</v>
@@ -26202,7 +26202,7 @@
         <v>2</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR118" t="n">
         <v>1.88</v>
@@ -28164,7 +28164,7 @@
         <v>2</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR127" t="n">
         <v>1.31</v>
@@ -28815,7 +28815,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.92</v>
@@ -29254,7 +29254,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.83</v>
@@ -30341,10 +30341,10 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR137" t="n">
         <v>1.3</v>
@@ -30995,7 +30995,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ140" t="n">
         <v>1</v>
@@ -31216,7 +31216,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31870,7 +31870,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -32957,7 +32957,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.15</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.92</v>
@@ -34050,7 +34050,7 @@
         <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR154" t="n">
         <v>1.8</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.83</v>
@@ -34922,7 +34922,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR158" t="n">
         <v>1.35</v>
@@ -35137,7 +35137,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.92</v>
@@ -35791,7 +35791,7 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.6899999999999999</v>
@@ -36666,7 +36666,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR166" t="n">
         <v>1.56</v>
@@ -37538,7 +37538,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR170" t="n">
         <v>1.36</v>
@@ -37971,7 +37971,7 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.83</v>
@@ -38407,7 +38407,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.62</v>
@@ -38625,7 +38625,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.6899999999999999</v>
@@ -39282,7 +39282,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR178" t="n">
         <v>1.59</v>
@@ -41462,7 +41462,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR188" t="n">
         <v>1.72</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.31</v>
@@ -41898,7 +41898,7 @@
         <v>2</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR190" t="n">
         <v>1.94</v>
@@ -42116,7 +42116,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR191" t="n">
         <v>1.56</v>
@@ -42331,7 +42331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.62</v>
@@ -42767,7 +42767,7 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.31</v>
@@ -42988,7 +42988,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR195" t="n">
         <v>1.36</v>
@@ -44075,7 +44075,7 @@
         <v>0.78</v>
       </c>
       <c r="AP200" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.83</v>
@@ -44950,7 +44950,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR204" t="n">
         <v>1.65</v>
@@ -45604,7 +45604,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR207" t="n">
         <v>1.71</v>
@@ -45822,7 +45822,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR208" t="n">
         <v>1.71</v>
@@ -46255,7 +46255,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.92</v>
@@ -46912,7 +46912,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR213" t="n">
         <v>1.4</v>
@@ -47130,7 +47130,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -47345,7 +47345,7 @@
         <v>1.7</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.38</v>
@@ -47566,7 +47566,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR216" t="n">
         <v>1.83</v>
@@ -48435,7 +48435,7 @@
         <v>1.2</v>
       </c>
       <c r="AP220" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.31</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.92</v>
@@ -48871,7 +48871,7 @@
         <v>1.09</v>
       </c>
       <c r="AP222" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.15</v>
@@ -49310,7 +49310,7 @@
         <v>2</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR224" t="n">
         <v>1.36</v>
@@ -49528,7 +49528,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR225" t="n">
         <v>1.66</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.92</v>
@@ -51269,7 +51269,7 @@
         <v>1.75</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.62</v>
@@ -51708,7 +51708,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR235" t="n">
         <v>1.6</v>
@@ -52798,7 +52798,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR240" t="n">
         <v>1.41</v>
@@ -53234,7 +53234,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR242" t="n">
         <v>1.4</v>
@@ -53449,7 +53449,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.54</v>
@@ -55193,7 +55193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ251" t="n">
         <v>1.31</v>
@@ -55426,31 +55426,31 @@
         <v>2.88</v>
       </c>
       <c r="AU252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV252" t="n">
         <v>1</v>
       </c>
       <c r="AW252" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX252" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY252" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA252" t="n">
         <v>5</v>
       </c>
-      <c r="AZ252" t="n">
+      <c r="BB252" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC252" t="n">
         <v>7</v>
-      </c>
-      <c r="BA252" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB252" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC252" t="n">
-        <v>5</v>
       </c>
       <c r="BD252" t="n">
         <v>1.65</v>
@@ -55644,19 +55644,19 @@
         <v>2.79</v>
       </c>
       <c r="AU253" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV253" t="n">
         <v>1</v>
       </c>
       <c r="AW253" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX253" t="n">
         <v>3</v>
       </c>
       <c r="AY253" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ253" t="n">
         <v>4</v>
@@ -55708,6 +55708,878 @@
       </c>
       <c r="BP253" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>7841285</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>45913.66666666666</v>
+      </c>
+      <c r="F254" t="n">
+        <v>26</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R254" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S254" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T254" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U254" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V254" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W254" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X254" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO254" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP254" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ254" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR254" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS254" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT254" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX254" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY254" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ254" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB254" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC254" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF254" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG254" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI254" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ254" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK254" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL254" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM254" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN254" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO254" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP254" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>7841283</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>45913.77083333334</v>
+      </c>
+      <c r="F255" t="n">
+        <v>26</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" t="n">
+        <v>1</v>
+      </c>
+      <c r="N255" t="n">
+        <v>2</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R255" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S255" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T255" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U255" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V255" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W255" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X255" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ255" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY255" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA255" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB255" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC255" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE255" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BF255" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI255" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ255" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK255" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL255" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM255" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN255" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO255" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP255" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>7841287</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>45914.66666666666</v>
+      </c>
+      <c r="F256" t="n">
+        <v>26</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" t="n">
+        <v>1</v>
+      </c>
+      <c r="L256" t="n">
+        <v>1</v>
+      </c>
+      <c r="M256" t="n">
+        <v>1</v>
+      </c>
+      <c r="N256" t="n">
+        <v>2</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R256" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S256" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T256" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V256" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W256" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X256" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY256" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA256" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB256" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC256" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE256" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF256" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BG256" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI256" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ256" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK256" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL256" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM256" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN256" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO256" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP256" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>7841289</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>45914.77083333334</v>
+      </c>
+      <c r="F257" t="n">
+        <v>26</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>2</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>2</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>['52', '80']</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R257" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S257" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T257" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U257" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V257" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W257" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X257" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ257" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW257" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX257" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY257" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ257" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA257" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB257" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC257" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE257" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF257" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG257" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH257" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI257" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ257" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK257" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL257" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM257" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN257" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO257" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP257" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP257"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.15</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.31</v>
@@ -2658,7 +2658,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.31</v>
@@ -3312,7 +3312,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.62</v>
@@ -5274,7 +5274,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5928,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.54</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.83</v>
@@ -7236,7 +7236,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR31" t="n">
         <v>1.94</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.31</v>
@@ -8544,7 +8544,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR37" t="n">
         <v>2.28</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.86</v>
@@ -9634,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR42" t="n">
         <v>2.35</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.62</v>
@@ -12032,7 +12032,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR53" t="n">
         <v>0.93</v>
@@ -12465,10 +12465,10 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.31</v>
@@ -13340,7 +13340,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR59" t="n">
         <v>1.44</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.86</v>
@@ -16171,10 +16171,10 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR72" t="n">
         <v>1.97</v>
@@ -16389,7 +16389,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.86</v>
@@ -16828,7 +16828,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17046,7 +17046,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.31</v>
@@ -17479,7 +17479,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.31</v>
@@ -17918,7 +17918,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR80" t="n">
         <v>1.73</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.85</v>
@@ -20752,7 +20752,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR93" t="n">
         <v>1.68</v>
@@ -20970,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.38</v>
@@ -21624,7 +21624,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.31</v>
@@ -22275,10 +22275,10 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR100" t="n">
         <v>1.47</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.38</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.62</v>
@@ -26420,7 +26420,7 @@
         <v>2</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR119" t="n">
         <v>1.9</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -26856,7 +26856,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR121" t="n">
         <v>1.92</v>
@@ -27510,7 +27510,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.6899999999999999</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.54</v>
@@ -28818,7 +28818,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR130" t="n">
         <v>1.56</v>
@@ -29251,7 +29251,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.62</v>
@@ -29472,7 +29472,7 @@
         <v>2</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR133" t="n">
         <v>1.92</v>
@@ -30562,7 +30562,7 @@
         <v>2</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR138" t="n">
         <v>1.81</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.38</v>
@@ -31431,7 +31431,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.6899999999999999</v>
@@ -32306,7 +32306,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -32521,7 +32521,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.92</v>
@@ -32742,7 +32742,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -33611,7 +33611,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.62</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.31</v>
@@ -35140,7 +35140,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR159" t="n">
         <v>1.43</v>
@@ -35576,7 +35576,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR161" t="n">
         <v>1.65</v>
@@ -36012,7 +36012,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR163" t="n">
         <v>1.21</v>
@@ -36227,7 +36227,7 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.31</v>
@@ -36445,7 +36445,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.31</v>
@@ -37320,7 +37320,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.54</v>
@@ -39936,7 +39936,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR181" t="n">
         <v>1.18</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.92</v>
@@ -40369,10 +40369,10 @@
         <v>1.25</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR183" t="n">
         <v>1.91</v>
@@ -40808,7 +40808,7 @@
         <v>2</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR185" t="n">
         <v>1.35</v>
@@ -41026,7 +41026,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.15</v>
@@ -43421,7 +43421,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.6899999999999999</v>
@@ -43642,7 +43642,7 @@
         <v>2</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR198" t="n">
         <v>1.74</v>
@@ -44511,10 +44511,10 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR202" t="n">
         <v>1.45</v>
@@ -45386,7 +45386,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR206" t="n">
         <v>1.82</v>
@@ -45819,7 +45819,7 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.85</v>
@@ -46040,7 +46040,7 @@
         <v>2</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR209" t="n">
         <v>1.85</v>
@@ -46473,7 +46473,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.31</v>
@@ -47781,7 +47781,7 @@
         <v>1</v>
       </c>
       <c r="AP217" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.85</v>
@@ -47999,7 +47999,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ218" t="n">
         <v>1</v>
@@ -48656,7 +48656,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR221" t="n">
         <v>1.61</v>
@@ -49092,7 +49092,7 @@
         <v>2</v>
       </c>
       <c r="AQ223" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR223" t="n">
         <v>1.87</v>
@@ -49743,10 +49743,10 @@
         <v>1.1</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR226" t="n">
         <v>1.91</v>
@@ -50179,7 +50179,7 @@
         <v>0.27</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.54</v>
@@ -50836,7 +50836,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR231" t="n">
         <v>1.66</v>
@@ -51487,7 +51487,7 @@
         <v>0.92</v>
       </c>
       <c r="AP234" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.85</v>
@@ -51926,7 +51926,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ236" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AR236" t="n">
         <v>1.84</v>
@@ -52141,10 +52141,10 @@
         <v>0.55</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR237" t="n">
         <v>1.78</v>
@@ -52577,7 +52577,7 @@
         <v>0.92</v>
       </c>
       <c r="AP239" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ239" t="n">
         <v>0.92</v>
@@ -52795,7 +52795,7 @@
         <v>0.83</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.86</v>
@@ -53016,7 +53016,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ241" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR241" t="n">
         <v>1.68</v>
@@ -53888,7 +53888,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AR245" t="n">
         <v>1.34</v>
@@ -55444,13 +55444,13 @@
         <v>10</v>
       </c>
       <c r="BA252" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB252" t="n">
         <v>2</v>
       </c>
       <c r="BC252" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD252" t="n">
         <v>1.65</v>
@@ -55650,13 +55650,13 @@
         <v>1</v>
       </c>
       <c r="AW253" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX253" t="n">
         <v>3</v>
       </c>
       <c r="AY253" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ253" t="n">
         <v>4</v>
@@ -56580,6 +56580,878 @@
       </c>
       <c r="BP257" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>7841290</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>45915.79166666666</v>
+      </c>
+      <c r="F258" t="n">
+        <v>26</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" t="n">
+        <v>2</v>
+      </c>
+      <c r="L258" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" t="n">
+        <v>2</v>
+      </c>
+      <c r="N258" t="n">
+        <v>3</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>['44', '46']</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R258" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S258" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T258" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U258" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V258" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W258" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X258" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ258" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU258" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV258" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX258" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY258" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA258" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB258" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC258" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE258" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="BF258" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG258" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH258" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI258" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ258" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BK258" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL258" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM258" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN258" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO258" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP258" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>7841288</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>45915.89583333334</v>
+      </c>
+      <c r="F259" t="n">
+        <v>26</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" t="n">
+        <v>2</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>2</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>['18', '80']</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R259" t="n">
+        <v>2</v>
+      </c>
+      <c r="S259" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T259" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U259" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="V259" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W259" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X259" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY259" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC259" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE259" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="BI259" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM259" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN259" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO259" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP259" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>7841284</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>45916.8125</v>
+      </c>
+      <c r="F260" t="n">
+        <v>26</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>1</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" t="n">
+        <v>2</v>
+      </c>
+      <c r="L260" t="n">
+        <v>2</v>
+      </c>
+      <c r="M260" t="n">
+        <v>1</v>
+      </c>
+      <c r="N260" t="n">
+        <v>3</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>['34', '81']</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R260" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S260" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U260" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V260" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X260" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU260" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY260" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA260" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB260" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC260" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE260" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI260" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO260" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP260" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>7841286</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>45916.89930555555</v>
+      </c>
+      <c r="F261" t="n">
+        <v>26</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" t="n">
+        <v>2</v>
+      </c>
+      <c r="M261" t="n">
+        <v>3</v>
+      </c>
+      <c r="N261" t="n">
+        <v>5</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>['48', '53']</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>['42', '58', '72']</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R261" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S261" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T261" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V261" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W261" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X261" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU261" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY261" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB261" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC261" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BE261" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI261" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO261" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP261" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.83</v>
@@ -5710,7 +5710,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.31</v>
@@ -10288,7 +10288,7 @@
         <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR45" t="n">
         <v>1.33</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.38</v>
@@ -14866,7 +14866,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR66" t="n">
         <v>1.45</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.31</v>
@@ -19444,7 +19444,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR87" t="n">
         <v>1.6</v>
@@ -19877,7 +19877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.6899999999999999</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.62</v>
@@ -24240,7 +24240,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR109" t="n">
         <v>1.15</v>
@@ -25766,7 +25766,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR116" t="n">
         <v>1.33</v>
@@ -27071,7 +27071,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.15</v>
@@ -30126,7 +30126,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR136" t="n">
         <v>1.97</v>
@@ -32739,7 +32739,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.08</v>
@@ -33832,7 +33832,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR153" t="n">
         <v>1.49</v>
@@ -35355,7 +35355,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.54</v>
@@ -39715,7 +39715,7 @@
         <v>1.13</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.31</v>
@@ -40154,7 +40154,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR182" t="n">
         <v>1.54</v>
@@ -42985,7 +42985,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.62</v>
@@ -45168,7 +45168,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR205" t="n">
         <v>1.71</v>
@@ -49964,7 +49964,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR227" t="n">
         <v>1.6</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.92</v>
@@ -53885,7 +53885,7 @@
         <v>1.27</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ245" t="n">
         <v>1.54</v>
@@ -54324,7 +54324,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR247" t="n">
         <v>1.65</v>
@@ -56522,13 +56522,13 @@
         <v>2</v>
       </c>
       <c r="AW257" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX257" t="n">
         <v>6</v>
       </c>
       <c r="AY257" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ257" t="n">
         <v>8</v>
@@ -56961,22 +56961,22 @@
         <v>11</v>
       </c>
       <c r="AX259" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY259" t="n">
         <v>13</v>
       </c>
       <c r="AZ259" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC259" t="n">
         <v>5</v>
-      </c>
-      <c r="BA259" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB259" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC259" t="n">
-        <v>2</v>
       </c>
       <c r="BD259" t="n">
         <v>1.28</v>
@@ -57071,12 +57071,12 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>['34', '81']</t>
+          <t>['33', '81']</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="Q260" t="n">
@@ -57176,25 +57176,25 @@
         <v>1</v>
       </c>
       <c r="AW260" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX260" t="n">
         <v>3</v>
       </c>
       <c r="AY260" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ260" t="n">
         <v>4</v>
       </c>
       <c r="BA260" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB260" t="n">
         <v>1</v>
       </c>
       <c r="BC260" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD260" t="n">
         <v>1.55</v>
@@ -57397,13 +57397,13 @@
         <v>8</v>
       </c>
       <c r="AX261" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY261" t="n">
         <v>13</v>
       </c>
       <c r="AZ261" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA261" t="n">
         <v>5</v>
@@ -57452,6 +57452,224 @@
       </c>
       <c r="BP261" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>7841301</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>45918.79166666666</v>
+      </c>
+      <c r="F262" t="n">
+        <v>27</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="n">
+        <v>1</v>
+      </c>
+      <c r="N262" t="n">
+        <v>2</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R262" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S262" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T262" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V262" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="W262" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X262" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY262" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA262" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB262" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC262" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BE262" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF262" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG262" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH262" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI262" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ262" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM262" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN262" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO262" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP262" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -57507,7 +57507,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
@@ -57615,13 +57615,13 @@
         <v>5</v>
       </c>
       <c r="AX262" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY262" t="n">
         <v>6</v>
       </c>
       <c r="AZ262" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA262" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.54</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR27" t="n">
         <v>1.86</v>
@@ -7890,7 +7890,7 @@
         <v>2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.31</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.54</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ67" t="n">
         <v>1</v>
@@ -15302,7 +15302,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -18572,7 +18572,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.85</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.15</v>
@@ -24676,7 +24676,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.86</v>
@@ -29036,7 +29036,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -30559,7 +30559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.46</v>
@@ -33178,7 +33178,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -34047,7 +34047,7 @@
         <v>0.86</v>
       </c>
       <c r="AP154" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.62</v>
@@ -36448,7 +36448,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -39061,7 +39061,7 @@
         <v>2</v>
       </c>
       <c r="AP177" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.38</v>
@@ -41680,7 +41680,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.85</v>
@@ -46476,7 +46476,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -46691,7 +46691,7 @@
         <v>1.64</v>
       </c>
       <c r="AP212" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.62</v>
@@ -52362,7 +52362,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
@@ -54757,7 +54757,7 @@
         <v>0.82</v>
       </c>
       <c r="AP249" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ249" t="n">
         <v>0.83</v>
@@ -55196,7 +55196,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR251" t="n">
         <v>1.49</v>
@@ -57670,6 +57670,224 @@
       </c>
       <c r="BP262" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>7841300</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>45919.79166666666</v>
+      </c>
+      <c r="F263" t="n">
+        <v>27</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S263" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="T263" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V263" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W263" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X263" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY263" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB263" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE263" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="BI263" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP263" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP263"/>
+  <dimension ref="A1:BP266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.46</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.08</v>
@@ -3748,7 +3748,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>1</v>
@@ -4184,7 +4184,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.93</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.92</v>
@@ -6582,7 +6582,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -7454,7 +7454,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.85</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.62</v>
@@ -10724,7 +10724,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.83</v>
@@ -12250,7 +12250,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR54" t="n">
         <v>1.59</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.85</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.83</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.62</v>
@@ -14648,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR65" t="n">
         <v>2</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.6899999999999999</v>
@@ -15956,7 +15956,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR71" t="n">
         <v>1.88</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ82" t="n">
         <v>1</v>
@@ -18790,7 +18790,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.15</v>
@@ -19226,7 +19226,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR86" t="n">
         <v>1.94</v>
@@ -19441,7 +19441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.93</v>
@@ -23150,7 +23150,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR104" t="n">
         <v>1.55</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.6899999999999999</v>
@@ -23801,10 +23801,10 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR107" t="n">
         <v>1.65</v>
@@ -24673,7 +24673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.21</v>
@@ -27507,7 +27507,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.54</v>
@@ -27728,7 +27728,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR125" t="n">
         <v>1.2</v>
@@ -28382,7 +28382,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR128" t="n">
         <v>1.74</v>
@@ -28597,7 +28597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.92</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.21</v>
@@ -31652,7 +31652,7 @@
         <v>2</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -32085,10 +32085,10 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR145" t="n">
         <v>1.63</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.54</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.31</v>
@@ -35358,7 +35358,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR160" t="n">
         <v>1.33</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.86</v>
@@ -36884,7 +36884,7 @@
         <v>2</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR167" t="n">
         <v>1.26</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.92</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.85</v>
@@ -38846,7 +38846,7 @@
         <v>2</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR176" t="n">
         <v>1.38</v>
@@ -39497,10 +39497,10 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR179" t="n">
         <v>1.34</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.85</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.31</v>
@@ -43203,7 +43203,7 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.38</v>
@@ -43860,7 +43860,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR199" t="n">
         <v>1.8</v>
@@ -44296,7 +44296,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR201" t="n">
         <v>1.52</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.93</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.86</v>
@@ -46909,7 +46909,7 @@
         <v>0.6</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.62</v>
@@ -47784,7 +47784,7 @@
         <v>2</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR217" t="n">
         <v>1.47</v>
@@ -49525,7 +49525,7 @@
         <v>0.64</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.62</v>
@@ -50182,7 +50182,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR228" t="n">
         <v>1.44</v>
@@ -50833,7 +50833,7 @@
         <v>0.3</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.46</v>
@@ -51490,7 +51490,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR234" t="n">
         <v>1.86</v>
@@ -51705,7 +51705,7 @@
         <v>0.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ235" t="n">
         <v>0.85</v>
@@ -53231,7 +53231,7 @@
         <v>1.18</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.31</v>
@@ -53452,7 +53452,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR243" t="n">
         <v>1.57</v>
@@ -54539,7 +54539,7 @@
         <v>1.55</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AQ248" t="n">
         <v>1.38</v>
@@ -57888,6 +57888,660 @@
       </c>
       <c r="BP263" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>7841293</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>45920.66666666666</v>
+      </c>
+      <c r="F264" t="n">
+        <v>27</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R264" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S264" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U264" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V264" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="W264" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X264" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU264" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY264" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA264" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC264" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE264" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG264" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH264" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI264" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BK264" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL264" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BM264" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN264" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO264" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BP264" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>7841296</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>45920.77083333334</v>
+      </c>
+      <c r="F265" t="n">
+        <v>27</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" t="n">
+        <v>2</v>
+      </c>
+      <c r="L265" t="n">
+        <v>2</v>
+      </c>
+      <c r="M265" t="n">
+        <v>2</v>
+      </c>
+      <c r="N265" t="n">
+        <v>4</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>['41', '90']</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>['10', '49']</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S265" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U265" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V265" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X265" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>31</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI265" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO265" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP265" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>7841298</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>45920.77083333334</v>
+      </c>
+      <c r="F266" t="n">
+        <v>27</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="n">
+        <v>1</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S266" t="n">
+        <v>4</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U266" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V266" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X266" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP266"/>
+  <dimension ref="A1:BP267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.62</v>
@@ -5056,7 +5056,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
         <v>2.72</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.62</v>
@@ -10942,7 +10942,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
         <v>1.9</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.46</v>
@@ -14212,7 +14212,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR63" t="n">
         <v>1.5</v>
@@ -15735,7 +15735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.92</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.5</v>
@@ -20316,7 +20316,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR91" t="n">
         <v>1.69</v>
@@ -24022,7 +24022,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR108" t="n">
         <v>1.47</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.93</v>
@@ -27725,7 +27725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.79</v>
@@ -29690,7 +29690,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.86</v>
@@ -34268,7 +34268,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.08</v>
@@ -37974,7 +37974,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR172" t="n">
         <v>1.66</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.85</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ193" t="n">
         <v>1</v>
@@ -44078,7 +44078,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -47127,7 +47127,7 @@
         <v>0.7</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.85</v>
@@ -50400,7 +50400,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR229" t="n">
         <v>1.56</v>
@@ -51051,7 +51051,7 @@
         <v>1.18</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.31</v>
@@ -54760,7 +54760,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ249" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR249" t="n">
         <v>1.78</v>
@@ -58113,7 +58113,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>7841296</v>
+        <v>7841298</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -58133,197 +58133,197 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="I265" t="n">
         <v>1</v>
       </c>
       <c r="J265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S265" t="n">
         <v>4</v>
       </c>
-      <c r="O265" t="inlineStr">
-        <is>
-          <t>['41', '90']</t>
-        </is>
-      </c>
-      <c r="P265" t="inlineStr">
-        <is>
-          <t>['10', '49']</t>
-        </is>
-      </c>
-      <c r="Q265" t="n">
+      <c r="T265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U265" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V265" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X265" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF265" t="n">
         <v>2.3</v>
-      </c>
-      <c r="R265" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S265" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T265" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U265" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V265" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="W265" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X265" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y265" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z265" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA265" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AB265" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC265" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD265" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE265" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF265" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AG265" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH265" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI265" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ265" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK265" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AL265" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AM265" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AN265" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO265" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP265" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ265" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR265" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS265" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AT265" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU265" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV265" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW265" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX265" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY265" t="n">
-        <v>31</v>
-      </c>
-      <c r="AZ265" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA265" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB265" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC265" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD265" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BE265" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF265" t="n">
-        <v>4.34</v>
       </c>
       <c r="BG265" t="n">
         <v>1.16</v>
       </c>
       <c r="BH265" t="n">
-        <v>4.5</v>
+        <v>3.97</v>
       </c>
       <c r="BI265" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BJ265" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="BK265" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BL265" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="BM265" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="BN265" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BO265" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BP265" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="266">
@@ -58331,7 +58331,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>7841298</v>
+        <v>7841296</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -58351,197 +58351,415 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="I266" t="n">
         <v>1</v>
       </c>
       <c r="J266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['41', '90']</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '49']</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R266" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="S266" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="T266" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U266" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="V266" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="W266" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="X266" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>31</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA266" t="n">
         <v>11</v>
       </c>
-      <c r="Y266" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z266" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA266" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB266" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AC266" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD266" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE266" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF266" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG266" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH266" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI266" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ266" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AK266" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL266" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AM266" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AN266" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO266" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AP266" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ266" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR266" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS266" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AT266" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU266" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV266" t="n">
+      <c r="BB266" t="n">
         <v>3</v>
       </c>
-      <c r="AW266" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX266" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY266" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ266" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA266" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB266" t="n">
+      <c r="BC266" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE266" t="n">
         <v>8</v>
       </c>
-      <c r="BC266" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD266" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BE266" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF266" t="n">
-        <v>2.3</v>
+        <v>4.34</v>
       </c>
       <c r="BG266" t="n">
         <v>1.16</v>
       </c>
       <c r="BH266" t="n">
-        <v>3.97</v>
+        <v>4.5</v>
       </c>
       <c r="BI266" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BJ266" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="BK266" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL266" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>7841295</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>45920.85416666666</v>
+      </c>
+      <c r="F267" t="n">
+        <v>27</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>1</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S267" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U267" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V267" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W267" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X267" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BI267" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM267" t="n">
         <v>2.28</v>
       </c>
-      <c r="BM266" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BN266" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BO266" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BP266" t="n">
-        <v>1.52</v>
+      <c r="BN267" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO267" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP267" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -58260,7 +58260,7 @@
         <v>2.85</v>
       </c>
       <c r="AU265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV265" t="n">
         <v>3</v>
@@ -58272,7 +58272,7 @@
         <v>15</v>
       </c>
       <c r="AY265" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ265" t="n">
         <v>18</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP267"/>
+  <dimension ref="A1:BP269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.93</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.85</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.21</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.46</v>
@@ -8108,7 +8108,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR35" t="n">
         <v>1.53</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.38</v>
@@ -8980,7 +8980,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.31</v>
@@ -11160,7 +11160,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -11814,7 +11814,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
         <v>2.13</v>
@@ -14430,7 +14430,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR64" t="n">
         <v>1.71</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.5</v>
@@ -15520,7 +15520,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.79</v>
@@ -19659,10 +19659,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR88" t="n">
         <v>1.88</v>
@@ -19880,7 +19880,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -22714,7 +22714,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR102" t="n">
         <v>1.21</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -23586,7 +23586,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR106" t="n">
         <v>1.68</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.92</v>
@@ -25984,7 +25984,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR117" t="n">
         <v>1.74</v>
@@ -26417,7 +26417,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.46</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.31</v>
@@ -27946,7 +27946,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -29469,7 +29469,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.85</v>
@@ -29908,7 +29908,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR135" t="n">
         <v>1.69</v>
@@ -31434,7 +31434,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR142" t="n">
         <v>1.84</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.21</v>
@@ -33614,7 +33614,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR152" t="n">
         <v>1.73</v>
@@ -34701,7 +34701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -35794,7 +35794,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR162" t="n">
         <v>1.64</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.15</v>
@@ -38410,7 +38410,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR174" t="n">
         <v>1.43</v>
@@ -38628,7 +38628,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR175" t="n">
         <v>1.47</v>
@@ -41023,7 +41023,7 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.54</v>
@@ -41895,7 +41895,7 @@
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.86</v>
@@ -42334,7 +42334,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR192" t="n">
         <v>1.47</v>
@@ -43424,7 +43424,7 @@
         <v>2</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.31</v>
@@ -46037,7 +46037,7 @@
         <v>1.22</v>
       </c>
       <c r="AP209" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.54</v>
@@ -46694,7 +46694,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR212" t="n">
         <v>1.78</v>
@@ -48220,7 +48220,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR219" t="n">
         <v>1.8</v>
@@ -49089,7 +49089,7 @@
         <v>1.1</v>
       </c>
       <c r="AP223" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.08</v>
@@ -51272,7 +51272,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AR233" t="n">
         <v>1.59</v>
@@ -53013,7 +53013,7 @@
         <v>1</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ241" t="n">
         <v>0.85</v>
@@ -54103,7 +54103,7 @@
         <v>1.25</v>
       </c>
       <c r="AP246" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.15</v>
@@ -54321,7 +54321,7 @@
         <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.93</v>
@@ -54978,7 +54978,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR250" t="n">
         <v>1.65</v>
@@ -58484,13 +58484,13 @@
         <v>6</v>
       </c>
       <c r="AW266" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX266" t="n">
         <v>6</v>
       </c>
       <c r="AY266" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AZ266" t="n">
         <v>12</v>
@@ -58760,6 +58760,442 @@
       </c>
       <c r="BP267" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>7841297</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>45921.66666666666</v>
+      </c>
+      <c r="F268" t="n">
+        <v>27</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>1</v>
+      </c>
+      <c r="L268" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R268" t="n">
+        <v>2</v>
+      </c>
+      <c r="S268" t="n">
+        <v>5</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U268" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V268" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X268" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>7841299</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>45921.66666666666</v>
+      </c>
+      <c r="F269" t="n">
+        <v>27</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>1</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>3</v>
+      </c>
+      <c r="R269" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S269" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U269" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V269" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X269" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO269" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP269" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP269"/>
+  <dimension ref="A1:BP273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.54</v>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.31</v>
@@ -2658,7 +2658,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.31</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.85</v>
@@ -4402,7 +4402,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.54</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR23" t="n">
         <v>1.23</v>
@@ -5928,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -6146,7 +6146,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR26" t="n">
         <v>1.36</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.64</v>
@@ -8326,7 +8326,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -10070,7 +10070,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR44" t="n">
         <v>1.6</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.64</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.5</v>
@@ -12468,7 +12468,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.85</v>
@@ -13776,7 +13776,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR61" t="n">
         <v>1.62</v>
@@ -13991,10 +13991,10 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR62" t="n">
         <v>1.27</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.93</v>
@@ -15738,7 +15738,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR70" t="n">
         <v>1.12</v>
@@ -16171,7 +16171,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.85</v>
@@ -17046,7 +17046,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -17697,10 +17697,10 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.21</v>
@@ -19008,7 +19008,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR85" t="n">
         <v>1.6</v>
@@ -20095,10 +20095,10 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.85</v>
@@ -20752,7 +20752,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR93" t="n">
         <v>1.68</v>
@@ -21188,7 +21188,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR95" t="n">
         <v>1.75</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.31</v>
@@ -22932,7 +22932,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR103" t="n">
         <v>2.01</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.79</v>
@@ -24019,7 +24019,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -24458,7 +24458,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR110" t="n">
         <v>1.88</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.85</v>
@@ -25330,7 +25330,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -25545,7 +25545,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.31</v>
@@ -27074,7 +27074,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR122" t="n">
         <v>1.13</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.64</v>
@@ -28600,7 +28600,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -28818,7 +28818,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR130" t="n">
         <v>1.56</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.5</v>
@@ -30780,7 +30780,7 @@
         <v>2</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -30995,7 +30995,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ140" t="n">
         <v>1</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.85</v>
@@ -32521,10 +32521,10 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR147" t="n">
         <v>1.59</v>
@@ -32742,7 +32742,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -32960,7 +32960,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ155" t="n">
         <v>1</v>
@@ -34483,10 +34483,10 @@
         <v>1.86</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR156" t="n">
         <v>1.7</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.46</v>
@@ -36012,7 +36012,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR163" t="n">
         <v>1.21</v>
@@ -36445,7 +36445,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.21</v>
@@ -37102,7 +37102,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR168" t="n">
         <v>1.68</v>
@@ -37756,7 +37756,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -38189,7 +38189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ173" t="n">
         <v>1</v>
@@ -39064,7 +39064,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR177" t="n">
         <v>1.8</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.62</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.93</v>
@@ -40372,7 +40372,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR183" t="n">
         <v>1.91</v>
@@ -40590,7 +40590,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR184" t="n">
         <v>1.84</v>
@@ -41244,7 +41244,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR187" t="n">
         <v>1.74</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.21</v>
@@ -43206,7 +43206,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.79</v>
@@ -44293,7 +44293,7 @@
         <v>0.3</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.5</v>
@@ -44511,7 +44511,7 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.46</v>
@@ -44732,7 +44732,7 @@
         <v>2</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR203" t="n">
         <v>1.34</v>
@@ -45386,7 +45386,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR206" t="n">
         <v>1.82</v>
@@ -46255,10 +46255,10 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR210" t="n">
         <v>1.66</v>
@@ -47348,7 +47348,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR215" t="n">
         <v>1.54</v>
@@ -47563,7 +47563,7 @@
         <v>0.82</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.86</v>
@@ -48874,7 +48874,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR222" t="n">
         <v>1.5</v>
@@ -49092,7 +49092,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR223" t="n">
         <v>1.87</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.93</v>
@@ -50179,7 +50179,7 @@
         <v>0.27</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.5</v>
@@ -50397,7 +50397,7 @@
         <v>0.8</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ229" t="n">
         <v>1</v>
@@ -50618,7 +50618,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR230" t="n">
         <v>1.33</v>
@@ -51923,10 +51923,10 @@
         <v>1</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR236" t="n">
         <v>1.84</v>
@@ -52580,7 +52580,7 @@
         <v>2</v>
       </c>
       <c r="AQ239" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR239" t="n">
         <v>1.52</v>
@@ -52795,7 +52795,7 @@
         <v>0.83</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.86</v>
@@ -53449,7 +53449,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.5</v>
@@ -54106,7 +54106,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR246" t="n">
         <v>1.84</v>
@@ -54542,7 +54542,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR248" t="n">
         <v>1.67</v>
@@ -54975,7 +54975,7 @@
         <v>0.75</v>
       </c>
       <c r="AP250" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ250" t="n">
         <v>0.64</v>
@@ -55632,7 +55632,7 @@
         <v>2</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR253" t="n">
         <v>1.45</v>
@@ -55847,7 +55847,7 @@
         <v>0.58</v>
       </c>
       <c r="AP254" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.62</v>
@@ -56719,10 +56719,10 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AR258" t="n">
         <v>1.33</v>
@@ -58484,13 +58484,13 @@
         <v>6</v>
       </c>
       <c r="AW266" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX266" t="n">
         <v>6</v>
       </c>
       <c r="AY266" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AZ266" t="n">
         <v>12</v>
@@ -58705,13 +58705,13 @@
         <v>9</v>
       </c>
       <c r="AX267" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY267" t="n">
         <v>12</v>
       </c>
       <c r="AZ267" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA267" t="n">
         <v>3</v>
@@ -58923,13 +58923,13 @@
         <v>14</v>
       </c>
       <c r="AX268" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY268" t="n">
         <v>16</v>
       </c>
       <c r="AZ268" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA268" t="n">
         <v>5</v>
@@ -59196,6 +59196,878 @@
       </c>
       <c r="BP269" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>7841292</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>45921.79166666666</v>
+      </c>
+      <c r="F270" t="n">
+        <v>27</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>1</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>1</v>
+      </c>
+      <c r="L270" t="n">
+        <v>2</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>['16', '83']</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R270" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S270" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U270" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V270" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X270" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY270" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA270" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB270" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI270" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ270" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK270" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL270" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM270" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN270" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO270" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP270" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>7841294</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>45921.85416666666</v>
+      </c>
+      <c r="F271" t="n">
+        <v>27</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S271" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T271" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U271" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V271" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W271" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X271" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC271" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI271" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM271" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN271" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO271" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP271" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>7841305</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>45923.8125</v>
+      </c>
+      <c r="F272" t="n">
+        <v>28</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1</v>
+      </c>
+      <c r="N272" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="R272" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S272" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T272" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U272" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V272" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W272" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X272" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY272" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA272" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB272" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC272" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BE272" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF272" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG272" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI272" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ272" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK272" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL272" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM272" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN272" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO272" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BP272" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>7841310</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>45923.89930555555</v>
+      </c>
+      <c r="F273" t="n">
+        <v>28</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" t="n">
+        <v>1</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="n">
+        <v>1</v>
+      </c>
+      <c r="N273" t="n">
+        <v>2</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R273" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S273" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T273" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U273" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V273" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W273" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X273" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC273" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE273" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BF273" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG273" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="BI273" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ273" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BK273" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL273" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM273" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN273" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO273" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP273" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP273"/>
+  <dimension ref="A1:BP281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>['36', '58']</t>
+          <t>['36', '59']</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.07</v>
+        <v>0.75</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.93</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
         <v>17</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.86</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.07</v>
@@ -2004,7 +2004,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -3094,7 +3094,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3106,22 +3106,22 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
         <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
         <v>7</v>
@@ -3312,7 +3312,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.5</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.79</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.36</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.64</v>
@@ -4838,7 +4838,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5716,10 +5716,10 @@
         <v>1.25</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AU24" t="n">
         <v>6</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.21</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6258,26 +6258,26 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>['5', '45+1', '45+3', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -6361,22 +6361,22 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.07</v>
+        <v>0.75</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AS27" t="n">
         <v>1.04</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV27" t="n">
         <v>1</v>
@@ -6385,13 +6385,13 @@
         <v>16</v>
       </c>
       <c r="AX27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA27" t="n">
         <v>5</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.5</v>
@@ -6800,7 +6800,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -7236,7 +7236,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR31" t="n">
         <v>1.94</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.79</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -7884,22 +7884,22 @@
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AU34" t="n">
         <v>3</v>
@@ -8111,13 +8111,13 @@
         <v>0.64</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AS35" t="n">
         <v>1.69</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="AU35" t="n">
         <v>4</v>
@@ -8544,7 +8544,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
         <v>2.28</v>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -8762,19 +8762,19 @@
         <v>2.07</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="AU38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV38" t="n">
         <v>3</v>
@@ -8783,13 +8783,13 @@
         <v>18</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA38" t="n">
         <v>8</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR40" t="n">
         <v>1.69</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ41" t="n">
         <v>1</v>
@@ -9634,16 +9634,16 @@
         <v>2.07</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AS42" t="n">
         <v>1.08</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.43</v>
+        <v>3.36</v>
       </c>
       <c r="AU42" t="n">
         <v>4</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -9843,34 +9843,34 @@
         <v>2.15</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AO43" t="n">
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.07</v>
+        <v>0.75</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AS43" t="n">
         <v>1.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="AU43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV43" t="n">
         <v>4</v>
       </c>
       <c r="AW43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX43" t="n">
         <v>7</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.07</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.93</v>
@@ -10294,10 +10294,10 @@
         <v>1.33</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="AU45" t="n">
         <v>4</v>
@@ -10506,7 +10506,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR46" t="n">
         <v>1.4</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.5</v>
@@ -12032,7 +12032,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR53" t="n">
         <v>0.93</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.79</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.21</v>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -12683,37 +12683,37 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.31</v>
+        <v>1</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AU56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW56" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ56" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA56" t="n">
         <v>2</v>
@@ -12904,16 +12904,16 @@
         <v>1.57</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AS57" t="n">
         <v>0.84</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AU57" t="n">
         <v>4</v>
@@ -13119,10 +13119,10 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13340,7 +13340,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR59" t="n">
         <v>1.44</v>
@@ -13555,10 +13555,10 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR60" t="n">
         <v>1.65</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.86</v>
@@ -13997,13 +13997,13 @@
         <v>1.07</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AS62" t="n">
         <v>1.7</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AU62" t="n">
         <v>7</v>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -14639,52 +14639,52 @@
         <v>2.1</v>
       </c>
       <c r="AN65" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.07</v>
+        <v>0.75</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.5</v>
       </c>
       <c r="AR65" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AS65" t="n">
         <v>1.15</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AU65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX65" t="n">
         <v>10</v>
       </c>
       <c r="AY65" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ65" t="n">
         <v>16</v>
       </c>
-      <c r="AZ65" t="n">
-        <v>14</v>
-      </c>
       <c r="BA65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB65" t="n">
         <v>5</v>
       </c>
       <c r="BC65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD65" t="n">
         <v>1.51</v>
@@ -14872,10 +14872,10 @@
         <v>1.45</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AU66" t="n">
         <v>8</v>
@@ -15087,13 +15087,13 @@
         <v>1</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AS67" t="n">
         <v>1.02</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="AU67" t="n">
         <v>3</v>
@@ -15296,22 +15296,22 @@
         <v>0.67</v>
       </c>
       <c r="AO68" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP68" t="n">
         <v>1.29</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AU68" t="n">
         <v>2</v>
@@ -16174,7 +16174,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR72" t="n">
         <v>1.97</v>
@@ -16389,10 +16389,10 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR73" t="n">
         <v>1.62</v>
@@ -16607,10 +16607,10 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -16825,10 +16825,10 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.21</v>
@@ -17261,10 +17261,10 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -17476,22 +17476,22 @@
         <v>2.33</v>
       </c>
       <c r="AO78" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.67</v>
+        <v>1.63</v>
       </c>
       <c r="AU78" t="n">
         <v>2</v>
@@ -17915,10 +17915,10 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR80" t="n">
         <v>1.73</v>
@@ -18133,10 +18133,10 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR81" t="n">
         <v>1.26</v>
@@ -18566,22 +18566,22 @@
         <v>1.75</v>
       </c>
       <c r="AO83" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP83" t="n">
         <v>1.57</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AU83" t="n">
         <v>4</v>
@@ -18796,10 +18796,10 @@
         <v>1.07</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AU84" t="n">
         <v>4</v>
@@ -19229,13 +19229,13 @@
         <v>0.79</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AS86" t="n">
         <v>1</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AU86" t="n">
         <v>6</v>
@@ -19450,10 +19450,10 @@
         <v>1.6</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="AU87" t="n">
         <v>5</v>
@@ -19653,25 +19653,25 @@
         <v>1.67</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.5</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
         <v>1.28</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.16</v>
+        <v>1.28</v>
       </c>
       <c r="AU88" t="n">
         <v>6</v>
@@ -20534,7 +20534,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR92" t="n">
         <v>1.81</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.21</v>
@@ -20967,10 +20967,10 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.36</v>
@@ -21403,10 +21403,10 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR96" t="n">
         <v>1.47</v>
@@ -21621,10 +21621,10 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -21839,10 +21839,10 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR98" t="n">
         <v>1.59</v>
@@ -22057,10 +22057,10 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR99" t="n">
         <v>2.14</v>
@@ -22275,10 +22275,10 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR100" t="n">
         <v>1.47</v>
@@ -22490,22 +22490,22 @@
         <v>0.5</v>
       </c>
       <c r="AO101" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP101" t="n">
         <v>0.79</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.29</v>
+        <v>2.07</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.93</v>
+        <v>3.71</v>
       </c>
       <c r="AU101" t="n">
         <v>6</v>
@@ -22935,13 +22935,13 @@
         <v>1.07</v>
       </c>
       <c r="AR103" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AS103" t="n">
         <v>1.49</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="AU103" t="n">
         <v>4</v>
@@ -23810,10 +23810,10 @@
         <v>1.65</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="AU107" t="n">
         <v>6</v>
@@ -24025,13 +24025,13 @@
         <v>1</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AS108" t="n">
         <v>1.37</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AU108" t="n">
         <v>1</v>
@@ -24246,10 +24246,10 @@
         <v>1.15</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AU109" t="n">
         <v>3</v>
@@ -24449,25 +24449,25 @@
         <v>1.57</v>
       </c>
       <c r="AN110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO110" t="n">
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.86</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AS110" t="n">
         <v>1.05</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AU110" t="n">
         <v>7</v>
@@ -24670,22 +24670,22 @@
         <v>1.2</v>
       </c>
       <c r="AO111" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AP111" t="n">
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AU111" t="n">
         <v>5</v>
@@ -24891,10 +24891,10 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR112" t="n">
         <v>1.77</v>
@@ -25112,7 +25112,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.36</v>
@@ -25548,16 +25548,16 @@
         <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AS115" t="n">
         <v>1.42</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AU115" t="n">
         <v>11</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.93</v>
@@ -25772,10 +25772,10 @@
         <v>1.33</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AU116" t="n">
         <v>5</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.5</v>
@@ -26202,16 +26202,16 @@
         <v>2.07</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AS118" t="n">
         <v>1.55</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="AU118" t="n">
         <v>6</v>
@@ -26411,25 +26411,25 @@
         <v>2.1</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO119" t="n">
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AS119" t="n">
         <v>1</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AU119" t="n">
         <v>11</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -26853,10 +26853,10 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR121" t="n">
         <v>1.92</v>
@@ -27286,22 +27286,22 @@
         <v>2.17</v>
       </c>
       <c r="AO123" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP123" t="n">
         <v>1.57</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="AU123" t="n">
         <v>2</v>
@@ -27510,7 +27510,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -28161,10 +28161,10 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR127" t="n">
         <v>1.31</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.5</v>
@@ -28388,10 +28388,10 @@
         <v>1.74</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="AU128" t="n">
         <v>6</v>
@@ -28815,7 +28815,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.21</v>
@@ -29030,22 +29030,22 @@
         <v>2.67</v>
       </c>
       <c r="AO131" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP131" t="n">
         <v>2.14</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU131" t="n">
         <v>4</v>
@@ -29251,10 +29251,10 @@
         <v>0.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29463,25 +29463,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AO133" t="n">
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AS133" t="n">
         <v>1.14</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="AU133" t="n">
         <v>6</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -29911,13 +29911,13 @@
         <v>1.5</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AS135" t="n">
         <v>1.19</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AU135" t="n">
         <v>3</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.93</v>
@@ -30132,10 +30132,10 @@
         <v>1.97</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AU136" t="n">
         <v>2</v>
@@ -30341,10 +30341,10 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR137" t="n">
         <v>1.3</v>
@@ -30562,16 +30562,16 @@
         <v>2.07</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AS138" t="n">
         <v>0.99</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AU138" t="n">
         <v>3</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.36</v>
@@ -31216,7 +31216,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31431,7 +31431,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.64</v>
@@ -31649,7 +31649,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.5</v>
@@ -31658,10 +31658,10 @@
         <v>1.28</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
@@ -31870,7 +31870,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -32306,7 +32306,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -32957,7 +32957,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.07</v>
@@ -33172,22 +33172,22 @@
         <v>2</v>
       </c>
       <c r="AO150" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP150" t="n">
         <v>1.57</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AU150" t="n">
         <v>1</v>
@@ -33390,22 +33390,22 @@
         <v>2.29</v>
       </c>
       <c r="AO151" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP151" t="n">
         <v>2.14</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AU151" t="n">
         <v>3</v>
@@ -33611,7 +33611,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.5</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.93</v>
@@ -33838,10 +33838,10 @@
         <v>1.49</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AU153" t="n">
         <v>5</v>
@@ -34050,16 +34050,16 @@
         <v>2.07</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS154" t="n">
         <v>1.48</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="AU154" t="n">
         <v>5</v>
@@ -34489,13 +34489,13 @@
         <v>1.36</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AS156" t="n">
         <v>1.34</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AU156" t="n">
         <v>2</v>
@@ -34695,25 +34695,25 @@
         <v>1.85</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AO157" t="n">
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AS157" t="n">
         <v>1.32</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="AU157" t="n">
         <v>8</v>
@@ -34919,10 +34919,10 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR158" t="n">
         <v>1.35</v>
@@ -35137,10 +35137,10 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
         <v>1.43</v>
@@ -35364,10 +35364,10 @@
         <v>1.33</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="AU160" t="n">
         <v>2</v>
@@ -35576,7 +35576,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR161" t="n">
         <v>1.65</v>
@@ -35791,7 +35791,7 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.64</v>
@@ -36224,22 +36224,22 @@
         <v>1.88</v>
       </c>
       <c r="AO164" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AT164" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AU164" t="n">
         <v>2</v>
@@ -36442,22 +36442,22 @@
         <v>1.71</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AP165" t="n">
         <v>1.36</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="AU165" t="n">
         <v>5</v>
@@ -36666,7 +36666,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR166" t="n">
         <v>1.56</v>
@@ -36881,7 +36881,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.79</v>
@@ -37317,10 +37317,10 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -37538,7 +37538,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR170" t="n">
         <v>1.36</v>
@@ -37971,7 +37971,7 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ172" t="n">
         <v>1</v>
@@ -38195,13 +38195,13 @@
         <v>1</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AS173" t="n">
         <v>1.31</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AU173" t="n">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.5</v>
@@ -38625,7 +38625,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.64</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.5</v>
@@ -38852,10 +38852,10 @@
         <v>1.38</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="AU176" t="n">
         <v>8</v>
@@ -39067,13 +39067,13 @@
         <v>1.36</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AS177" t="n">
         <v>1.29</v>
       </c>
       <c r="AT177" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AU177" t="n">
         <v>3</v>
@@ -39282,7 +39282,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR178" t="n">
         <v>1.59</v>
@@ -39712,22 +39712,22 @@
         <v>1.22</v>
       </c>
       <c r="AO180" t="n">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="AP180" t="n">
         <v>1.29</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AU180" t="n">
         <v>4</v>
@@ -39936,7 +39936,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR181" t="n">
         <v>1.18</v>
@@ -40160,10 +40160,10 @@
         <v>1.54</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AU182" t="n">
         <v>3</v>
@@ -40369,7 +40369,7 @@
         <v>1.25</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.21</v>
@@ -40587,7 +40587,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.86</v>
@@ -40805,10 +40805,10 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR185" t="n">
         <v>1.35</v>
@@ -41026,7 +41026,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.07</v>
@@ -41462,7 +41462,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR188" t="n">
         <v>1.72</v>
@@ -41674,22 +41674,22 @@
         <v>1.13</v>
       </c>
       <c r="AO189" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AP189" t="n">
         <v>0.79</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="AU189" t="n">
         <v>6</v>
@@ -41889,25 +41889,25 @@
         <v>1.95</v>
       </c>
       <c r="AN190" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AO190" t="n">
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AS190" t="n">
         <v>1.39</v>
       </c>
       <c r="AT190" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="AU190" t="n">
         <v>2</v>
@@ -42116,7 +42116,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR191" t="n">
         <v>1.56</v>
@@ -42331,7 +42331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.5</v>
@@ -42764,22 +42764,22 @@
         <v>1.67</v>
       </c>
       <c r="AO194" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AU194" t="n">
         <v>3</v>
@@ -42988,7 +42988,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR195" t="n">
         <v>1.36</v>
@@ -43421,7 +43421,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.64</v>
@@ -43642,16 +43642,16 @@
         <v>2.07</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AS198" t="n">
         <v>1.19</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AU198" t="n">
         <v>7</v>
@@ -43863,13 +43863,13 @@
         <v>0.79</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AS199" t="n">
         <v>1.07</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AU199" t="n">
         <v>5</v>
@@ -44075,7 +44075,7 @@
         <v>0.78</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ200" t="n">
         <v>1</v>
@@ -44302,10 +44302,10 @@
         <v>1.52</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AU201" t="n">
         <v>6</v>
@@ -44514,7 +44514,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR202" t="n">
         <v>1.45</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.07</v>
@@ -44950,7 +44950,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR204" t="n">
         <v>1.65</v>
@@ -45174,10 +45174,10 @@
         <v>1.71</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT205" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AU205" t="n">
         <v>3</v>
@@ -45383,7 +45383,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.21</v>
@@ -45604,7 +45604,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR207" t="n">
         <v>1.71</v>
@@ -45819,10 +45819,10 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR208" t="n">
         <v>1.71</v>
@@ -46031,25 +46031,25 @@
         <v>1.51</v>
       </c>
       <c r="AN209" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AO209" t="n">
         <v>1.22</v>
       </c>
       <c r="AP209" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AS209" t="n">
         <v>1.22</v>
       </c>
       <c r="AT209" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AU209" t="n">
         <v>9</v>
@@ -46470,22 +46470,22 @@
         <v>2.11</v>
       </c>
       <c r="AO211" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AT211" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="AU211" t="n">
         <v>6</v>
@@ -46697,13 +46697,13 @@
         <v>1.5</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AS212" t="n">
         <v>1.12</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AU212" t="n">
         <v>3</v>
@@ -46912,7 +46912,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR213" t="n">
         <v>1.4</v>
@@ -47130,7 +47130,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -47345,7 +47345,7 @@
         <v>1.7</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.36</v>
@@ -47566,16 +47566,16 @@
         <v>1.57</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AS216" t="n">
         <v>1.38</v>
       </c>
       <c r="AT216" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="AU216" t="n">
         <v>4</v>
@@ -47781,7 +47781,7 @@
         <v>1</v>
       </c>
       <c r="AP217" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.79</v>
@@ -47999,7 +47999,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ218" t="n">
         <v>1</v>
@@ -48217,7 +48217,7 @@
         <v>0.55</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.64</v>
@@ -48432,22 +48432,22 @@
         <v>1.1</v>
       </c>
       <c r="AO220" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AU220" t="n">
         <v>5</v>
@@ -48653,10 +48653,10 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR221" t="n">
         <v>1.61</v>
@@ -48871,7 +48871,7 @@
         <v>1.09</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.07</v>
@@ -49083,13 +49083,13 @@
         <v>1.75</v>
       </c>
       <c r="AN223" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AO223" t="n">
         <v>1.1</v>
       </c>
       <c r="AP223" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.21</v>
@@ -49307,10 +49307,10 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR224" t="n">
         <v>1.36</v>
@@ -49528,7 +49528,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR225" t="n">
         <v>1.66</v>
@@ -49743,10 +49743,10 @@
         <v>1.1</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR226" t="n">
         <v>1.91</v>
@@ -49970,10 +49970,10 @@
         <v>1.6</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT227" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AU227" t="n">
         <v>2</v>
@@ -50188,10 +50188,10 @@
         <v>1.44</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AT228" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AU228" t="n">
         <v>4</v>
@@ -50836,7 +50836,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR231" t="n">
         <v>1.66</v>
@@ -51048,22 +51048,22 @@
         <v>1.83</v>
       </c>
       <c r="AO232" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AP232" t="n">
         <v>1.57</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AT232" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AU232" t="n">
         <v>6</v>
@@ -51269,7 +51269,7 @@
         <v>1.75</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.5</v>
@@ -51487,7 +51487,7 @@
         <v>0.92</v>
       </c>
       <c r="AP234" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.79</v>
@@ -51708,7 +51708,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR235" t="n">
         <v>1.6</v>
@@ -52141,10 +52141,10 @@
         <v>0.55</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR237" t="n">
         <v>1.78</v>
@@ -52356,22 +52356,22 @@
         <v>1.73</v>
       </c>
       <c r="AO238" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="AU238" t="n">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>0.92</v>
       </c>
       <c r="AP239" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ239" t="n">
         <v>0.86</v>
@@ -52798,7 +52798,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR240" t="n">
         <v>1.41</v>
@@ -53016,7 +53016,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ241" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR241" t="n">
         <v>1.68</v>
@@ -53234,7 +53234,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR242" t="n">
         <v>1.4</v>
@@ -53458,10 +53458,10 @@
         <v>1.57</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="AU243" t="n">
         <v>6</v>
@@ -53667,7 +53667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ244" t="n">
         <v>1</v>
@@ -53888,7 +53888,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR245" t="n">
         <v>1.34</v>
@@ -54097,25 +54097,25 @@
         <v>1.75</v>
       </c>
       <c r="AN246" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AO246" t="n">
         <v>1.25</v>
       </c>
       <c r="AP246" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.07</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AS246" t="n">
         <v>1.24</v>
       </c>
       <c r="AT246" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="AU246" t="n">
         <v>5</v>
@@ -54330,10 +54330,10 @@
         <v>1.65</v>
       </c>
       <c r="AS247" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AT247" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="AU247" t="n">
         <v>4</v>
@@ -54763,13 +54763,13 @@
         <v>1</v>
       </c>
       <c r="AR249" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AS249" t="n">
         <v>1.25</v>
       </c>
       <c r="AT249" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AU249" t="n">
         <v>4</v>
@@ -55190,22 +55190,22 @@
         <v>2</v>
       </c>
       <c r="AO251" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR251" t="n">
         <v>1.49</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT251" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="AU251" t="n">
         <v>3</v>
@@ -55408,13 +55408,13 @@
         <v>1.58</v>
       </c>
       <c r="AO252" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
@@ -55629,7 +55629,7 @@
         <v>1.42</v>
       </c>
       <c r="AP253" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.36</v>
@@ -55850,7 +55850,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR254" t="n">
         <v>1.57</v>
@@ -56065,10 +56065,10 @@
         <v>1.33</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR255" t="n">
         <v>1.46</v>
@@ -56283,10 +56283,10 @@
         <v>0.85</v>
       </c>
       <c r="AP256" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ256" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR256" t="n">
         <v>1.58</v>
@@ -56501,10 +56501,10 @@
         <v>0.92</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR257" t="n">
         <v>1.47</v>
@@ -56937,10 +56937,10 @@
         <v>0.5</v>
       </c>
       <c r="AP259" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR259" t="n">
         <v>1.82</v>
@@ -57155,10 +57155,10 @@
         <v>0.92</v>
       </c>
       <c r="AP260" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR260" t="n">
         <v>1.73</v>
@@ -57373,10 +57373,10 @@
         <v>1.42</v>
       </c>
       <c r="AP261" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AR261" t="n">
         <v>1.53</v>
@@ -57600,10 +57600,10 @@
         <v>1.35</v>
       </c>
       <c r="AS262" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AU262" t="n">
         <v>1</v>
@@ -57806,22 +57806,22 @@
         <v>2</v>
       </c>
       <c r="AO263" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AP263" t="n">
         <v>2.07</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AU263" t="n">
         <v>4</v>
@@ -58254,10 +58254,10 @@
         <v>1.43</v>
       </c>
       <c r="AS265" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AT265" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AU265" t="n">
         <v>3</v>
@@ -58893,25 +58893,25 @@
         <v>1.91</v>
       </c>
       <c r="AN268" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO268" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="AP268" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AQ268" t="n">
         <v>0.64</v>
       </c>
       <c r="AR268" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AS268" t="n">
         <v>1.62</v>
       </c>
       <c r="AT268" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AU268" t="n">
         <v>2</v>
@@ -59341,13 +59341,13 @@
         <v>0.86</v>
       </c>
       <c r="AR270" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AS270" t="n">
         <v>1.12</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AU270" t="n">
         <v>6</v>
@@ -60068,6 +60068,1750 @@
       </c>
       <c r="BP273" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>7841303</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>45924.79166666666</v>
+      </c>
+      <c r="F274" t="n">
+        <v>28</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>2</v>
+      </c>
+      <c r="M274" t="n">
+        <v>2</v>
+      </c>
+      <c r="N274" t="n">
+        <v>4</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>['54', '70']</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>['46', '78']</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R274" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S274" t="n">
+        <v>4</v>
+      </c>
+      <c r="T274" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U274" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V274" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W274" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X274" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU274" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY274" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA274" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC274" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE274" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="BF274" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG274" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI274" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM274" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN274" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO274" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP274" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>7841308</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>45924.79166666666</v>
+      </c>
+      <c r="F275" t="n">
+        <v>28</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>2</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>2</v>
+      </c>
+      <c r="L275" t="n">
+        <v>3</v>
+      </c>
+      <c r="M275" t="n">
+        <v>2</v>
+      </c>
+      <c r="N275" t="n">
+        <v>5</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>['20', '43', '75']</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>['83', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S275" t="n">
+        <v>6</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U275" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V275" t="n">
+        <v>3</v>
+      </c>
+      <c r="W275" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X275" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX275" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY275" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ275" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB275" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC275" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE275" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG275" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH275" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BI275" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK275" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL275" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM275" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN275" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO275" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP275" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>7841309</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>45924.79166666666</v>
+      </c>
+      <c r="F276" t="n">
+        <v>28</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>1</v>
+      </c>
+      <c r="K276" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" t="n">
+        <v>3</v>
+      </c>
+      <c r="N276" t="n">
+        <v>3</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>['45+2', '77', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R276" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S276" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T276" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U276" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V276" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W276" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X276" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY276" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ276" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA276" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB276" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC276" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE276" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="BF276" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG276" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH276" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BI276" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ276" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK276" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL276" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM276" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN276" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO276" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BP276" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>7841307</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>45924.83333333334</v>
+      </c>
+      <c r="F277" t="n">
+        <v>28</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" t="n">
+        <v>2</v>
+      </c>
+      <c r="L277" t="n">
+        <v>2</v>
+      </c>
+      <c r="M277" t="n">
+        <v>1</v>
+      </c>
+      <c r="N277" t="n">
+        <v>3</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>['29', '76']</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R277" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S277" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="T277" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U277" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V277" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W277" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X277" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ277" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS277" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AT277" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU277" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY277" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ277" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA277" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB277" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC277" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD277" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE277" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BF277" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BG277" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH277" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI277" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ277" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK277" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL277" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM277" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN277" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO277" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP277" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>7841311</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>45924.89583333334</v>
+      </c>
+      <c r="F278" t="n">
+        <v>28</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" t="n">
+        <v>2</v>
+      </c>
+      <c r="M278" t="n">
+        <v>1</v>
+      </c>
+      <c r="N278" t="n">
+        <v>3</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>['14', '90+7']</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R278" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S278" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="T278" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U278" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V278" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W278" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X278" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI278" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK278" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO278" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ278" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS278" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT278" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU278" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW278" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX278" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY278" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ278" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA278" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB278" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC278" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD278" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE278" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF278" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG278" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH278" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI278" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ278" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK278" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL278" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM278" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN278" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO278" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP278" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>7841302</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>45925.79166666666</v>
+      </c>
+      <c r="F279" t="n">
+        <v>28</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Criciúma EC B</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>2</v>
+      </c>
+      <c r="K279" t="n">
+        <v>2</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" t="n">
+        <v>2</v>
+      </c>
+      <c r="N279" t="n">
+        <v>2</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>['33', '36']</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R279" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S279" t="n">
+        <v>5</v>
+      </c>
+      <c r="T279" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U279" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V279" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="W279" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X279" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT279" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX279" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY279" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ279" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA279" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB279" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC279" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD279" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE279" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF279" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BG279" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH279" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI279" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ279" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK279" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL279" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM279" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN279" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO279" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP279" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>7841304</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>45925.89583333334</v>
+      </c>
+      <c r="F280" t="n">
+        <v>28</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="n">
+        <v>1</v>
+      </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R280" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S280" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U280" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V280" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W280" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X280" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ280" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS280" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT280" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY280" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ280" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA280" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB280" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC280" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD280" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE280" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF280" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BG280" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH280" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI280" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ280" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK280" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL280" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM280" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BN280" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO280" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP280" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>7841306</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>45925.89930555555</v>
+      </c>
+      <c r="F281" t="n">
+        <v>28</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1</v>
+      </c>
+      <c r="N281" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R281" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S281" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T281" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U281" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V281" t="n">
+        <v>3</v>
+      </c>
+      <c r="W281" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X281" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO281" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP281" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR281" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS281" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT281" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU281" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW281" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX281" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY281" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ281" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA281" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB281" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC281" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD281" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE281" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BF281" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG281" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH281" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="BI281" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ281" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK281" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL281" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM281" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN281" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO281" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP281" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP281"/>
+  <dimension ref="A1:BP282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
         <v>1</v>
@@ -5710,7 +5710,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.64</v>
@@ -10288,7 +10288,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR45" t="n">
         <v>1.33</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.79</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.07</v>
@@ -14866,7 +14866,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR66" t="n">
         <v>1.45</v>
@@ -18569,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.29</v>
@@ -19444,7 +19444,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR87" t="n">
         <v>1.6</v>
@@ -24019,7 +24019,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -24240,7 +24240,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR109" t="n">
         <v>1.15</v>
@@ -25545,7 +25545,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.21</v>
@@ -25766,7 +25766,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR116" t="n">
         <v>1.33</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.5</v>
@@ -30126,7 +30126,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR136" t="n">
         <v>1.97</v>
@@ -33832,7 +33832,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR153" t="n">
         <v>1.49</v>
@@ -34483,7 +34483,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.36</v>
@@ -38189,7 +38189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ173" t="n">
         <v>1</v>
@@ -40154,7 +40154,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR182" t="n">
         <v>1.54</v>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.79</v>
@@ -45168,7 +45168,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR205" t="n">
         <v>1.71</v>
@@ -47563,7 +47563,7 @@
         <v>0.82</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.87</v>
@@ -49964,7 +49964,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR227" t="n">
         <v>1.6</v>
@@ -51923,7 +51923,7 @@
         <v>1</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.21</v>
@@ -54324,7 +54324,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR247" t="n">
         <v>1.65</v>
@@ -57594,7 +57594,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ262" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR262" t="n">
         <v>1.35</v>
@@ -59335,7 +59335,7 @@
         <v>0.92</v>
       </c>
       <c r="AP270" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ270" t="n">
         <v>0.86</v>
@@ -61112,13 +61112,13 @@
         <v>9</v>
       </c>
       <c r="BA278" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB278" t="n">
         <v>5</v>
       </c>
       <c r="BC278" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD278" t="n">
         <v>1.53</v>
@@ -61530,7 +61530,7 @@
         <v>3.23</v>
       </c>
       <c r="AU280" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV280" t="n">
         <v>4</v>
@@ -61539,13 +61539,13 @@
         <v>12</v>
       </c>
       <c r="AX280" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY280" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ280" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA280" t="n">
         <v>5</v>
@@ -61754,25 +61754,25 @@
         <v>7</v>
       </c>
       <c r="AW281" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX281" t="n">
         <v>8</v>
       </c>
       <c r="AY281" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ281" t="n">
         <v>15</v>
       </c>
       <c r="BA281" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB281" t="n">
         <v>2</v>
       </c>
       <c r="BC281" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD281" t="n">
         <v>1.64</v>
@@ -61812,6 +61812,224 @@
       </c>
       <c r="BP281" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>7841312</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>45927.85416666666</v>
+      </c>
+      <c r="F282" t="n">
+        <v>29</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>1</v>
+      </c>
+      <c r="L282" t="n">
+        <v>1</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="n">
+        <v>1</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R282" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S282" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="T282" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U282" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V282" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W282" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X282" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AH282" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI282" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK282" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO282" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP282" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ282" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS282" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT282" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX282" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY282" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ282" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA282" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB282" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC282" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD282" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE282" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BF282" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG282" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH282" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BI282" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ282" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK282" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BL282" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM282" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN282" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO282" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BP282" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP282"/>
+  <dimension ref="A1:BP285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.87</v>
@@ -1568,7 +1568,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.5</v>
@@ -4620,7 +4620,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.57</v>
@@ -6146,7 +6146,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR26" t="n">
         <v>1.36</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.29</v>
@@ -7454,7 +7454,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -8108,7 +8108,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR35" t="n">
         <v>1.6</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.5</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.64</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.21</v>
@@ -11160,7 +11160,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.43</v>
@@ -12250,7 +12250,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR54" t="n">
         <v>1.59</v>
@@ -13776,7 +13776,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR61" t="n">
         <v>1.62</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.5</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ67" t="n">
         <v>1</v>
@@ -15520,7 +15520,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -15735,10 +15735,10 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR70" t="n">
         <v>1.12</v>
@@ -15956,7 +15956,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR71" t="n">
         <v>1.88</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.5</v>
@@ -19223,10 +19223,10 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR86" t="n">
         <v>1.9</v>
@@ -19880,7 +19880,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20098,7 +20098,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.07</v>
@@ -23150,7 +23150,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR104" t="n">
         <v>1.55</v>
@@ -23586,7 +23586,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR106" t="n">
         <v>1.68</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.87</v>
@@ -24458,7 +24458,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR110" t="n">
         <v>1.9</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.87</v>
@@ -27725,10 +27725,10 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR125" t="n">
         <v>1.2</v>
@@ -27946,7 +27946,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -28600,7 +28600,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -30559,7 +30559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.43</v>
@@ -31434,7 +31434,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR142" t="n">
         <v>1.84</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.87</v>
@@ -32088,7 +32088,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR145" t="n">
         <v>1.63</v>
@@ -32524,7 +32524,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR147" t="n">
         <v>1.59</v>
@@ -34047,7 +34047,7 @@
         <v>0.86</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.57</v>
@@ -35794,7 +35794,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR162" t="n">
         <v>1.64</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.21</v>
@@ -36884,7 +36884,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR167" t="n">
         <v>1.26</v>
@@ -37102,7 +37102,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR168" t="n">
         <v>1.68</v>
@@ -38628,7 +38628,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR175" t="n">
         <v>1.47</v>
@@ -39061,7 +39061,7 @@
         <v>2</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.36</v>
@@ -39500,7 +39500,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR179" t="n">
         <v>1.34</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -40590,7 +40590,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR184" t="n">
         <v>1.84</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ193" t="n">
         <v>1</v>
@@ -43424,7 +43424,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ198" t="n">
         <v>1</v>
@@ -43860,7 +43860,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR199" t="n">
         <v>1.81</v>
@@ -46258,7 +46258,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR210" t="n">
         <v>1.66</v>
@@ -46691,7 +46691,7 @@
         <v>1.64</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.5</v>
@@ -47127,7 +47127,7 @@
         <v>0.7</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.79</v>
@@ -47784,7 +47784,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR217" t="n">
         <v>1.47</v>
@@ -48220,7 +48220,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR219" t="n">
         <v>1.8</v>
@@ -50618,7 +50618,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR230" t="n">
         <v>1.33</v>
@@ -51051,7 +51051,7 @@
         <v>1.5</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.6</v>
@@ -51490,7 +51490,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR234" t="n">
         <v>1.86</v>
@@ -52580,7 +52580,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ239" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR239" t="n">
         <v>1.52</v>
@@ -54757,7 +54757,7 @@
         <v>0.82</v>
       </c>
       <c r="AP249" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ249" t="n">
         <v>1</v>
@@ -54978,7 +54978,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR250" t="n">
         <v>1.65</v>
@@ -57809,7 +57809,7 @@
         <v>1.38</v>
       </c>
       <c r="AP263" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ263" t="n">
         <v>1.29</v>
@@ -58030,7 +58030,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ264" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="AR264" t="n">
         <v>1.63</v>
@@ -58681,7 +58681,7 @@
         <v>0.83</v>
       </c>
       <c r="AP267" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ267" t="n">
         <v>1</v>
@@ -58902,7 +58902,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR268" t="n">
         <v>1.8</v>
@@ -59338,7 +59338,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ270" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR270" t="n">
         <v>1.86</v>
@@ -62030,6 +62030,660 @@
       </c>
       <c r="BP282" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>7841317</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>45928.66666666666</v>
+      </c>
+      <c r="F283" t="n">
+        <v>29</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Criciúma EC B</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>2</v>
+      </c>
+      <c r="J283" t="n">
+        <v>2</v>
+      </c>
+      <c r="K283" t="n">
+        <v>4</v>
+      </c>
+      <c r="L283" t="n">
+        <v>2</v>
+      </c>
+      <c r="M283" t="n">
+        <v>4</v>
+      </c>
+      <c r="N283" t="n">
+        <v>6</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>['14', '45+4']</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>['31', '44', '68', '79']</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R283" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S283" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="T283" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U283" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V283" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W283" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X283" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO283" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP283" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AQ283" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR283" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS283" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT283" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU283" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV283" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX283" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY283" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ283" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA283" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB283" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC283" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD283" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE283" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF283" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG283" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH283" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BI283" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ283" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK283" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL283" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM283" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN283" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO283" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP283" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>7841320</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>45928.66666666666</v>
+      </c>
+      <c r="F284" t="n">
+        <v>29</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>1</v>
+      </c>
+      <c r="K284" t="n">
+        <v>1</v>
+      </c>
+      <c r="L284" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>2</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R284" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S284" t="n">
+        <v>6</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U284" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V284" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W284" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X284" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AN284" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO284" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ284" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR284" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS284" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT284" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU284" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY284" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ284" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA284" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB284" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC284" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD284" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE284" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF284" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG284" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH284" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="BI284" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK284" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL284" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM284" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN284" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO284" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP284" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>7841315</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>45928.75</v>
+      </c>
+      <c r="F285" t="n">
+        <v>29</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>2</v>
+      </c>
+      <c r="J285" t="n">
+        <v>1</v>
+      </c>
+      <c r="K285" t="n">
+        <v>3</v>
+      </c>
+      <c r="L285" t="n">
+        <v>4</v>
+      </c>
+      <c r="M285" t="n">
+        <v>2</v>
+      </c>
+      <c r="N285" t="n">
+        <v>6</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>['27', '35', '56', '75']</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>['24', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R285" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S285" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T285" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U285" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V285" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W285" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X285" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN285" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO285" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP285" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ285" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR285" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS285" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT285" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU285" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW285" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX285" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY285" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ285" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA285" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB285" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC285" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD285" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE285" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF285" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG285" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH285" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI285" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ285" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK285" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL285" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM285" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN285" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BO285" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP285" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP285"/>
+  <dimension ref="A1:BP287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.87</v>
@@ -2876,7 +2876,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -3094,7 +3094,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -3966,7 +3966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>1</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.64</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6258,26 +6258,26 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '45+3', '45+1', '87']</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR27" t="n">
         <v>1.65</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.21</v>
@@ -7884,13 +7884,13 @@
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -9416,7 +9416,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR41" t="n">
         <v>1.61</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -9843,13 +9843,13 @@
         <v>2.15</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AO43" t="n">
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.21</v>
@@ -11375,10 +11375,10 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR50" t="n">
         <v>1.42</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.36</v>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -12686,7 +12686,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -14639,13 +14639,13 @@
         <v>2.1</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.5</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.87</v>
@@ -15084,7 +15084,7 @@
         <v>2</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR67" t="n">
         <v>2.05</v>
@@ -15296,13 +15296,13 @@
         <v>0.67</v>
       </c>
       <c r="AO68" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -17476,22 +17476,22 @@
         <v>2.33</v>
       </c>
       <c r="AO78" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP78" t="n">
         <v>2.21</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.63</v>
+        <v>2.58</v>
       </c>
       <c r="AU78" t="n">
         <v>2</v>
@@ -18354,7 +18354,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR82" t="n">
         <v>1.73</v>
@@ -18566,13 +18566,13 @@
         <v>1.75</v>
       </c>
       <c r="AO83" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP83" t="n">
         <v>1.67</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR83" t="n">
         <v>1.53</v>
@@ -19653,25 +19653,25 @@
         <v>1.67</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO88" t="n">
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.5</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS88" t="n">
         <v>1.28</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.28</v>
+        <v>3.22</v>
       </c>
       <c r="AU88" t="n">
         <v>6</v>
@@ -19877,7 +19877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.6</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.87</v>
@@ -22490,22 +22490,22 @@
         <v>0.5</v>
       </c>
       <c r="AO101" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP101" t="n">
         <v>0.79</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.07</v>
+        <v>1.23</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.71</v>
+        <v>2.87</v>
       </c>
       <c r="AU101" t="n">
         <v>6</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.5</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.93</v>
@@ -23368,7 +23368,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR105" t="n">
         <v>1.6</v>
@@ -24449,25 +24449,25 @@
         <v>1.57</v>
       </c>
       <c r="AN110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO110" t="n">
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.87</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AS110" t="n">
         <v>1.05</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AU110" t="n">
         <v>7</v>
@@ -24670,13 +24670,13 @@
         <v>1.2</v>
       </c>
       <c r="AO111" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AP111" t="n">
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -26411,25 +26411,25 @@
         <v>2.1</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO119" t="n">
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.43</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AS119" t="n">
         <v>1</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AU119" t="n">
         <v>11</v>
@@ -26638,7 +26638,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR120" t="n">
         <v>1.52</v>
@@ -27071,7 +27071,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.07</v>
@@ -27286,22 +27286,22 @@
         <v>2.17</v>
       </c>
       <c r="AO123" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AP123" t="n">
         <v>1.57</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.03</v>
+        <v>2.74</v>
       </c>
       <c r="AU123" t="n">
         <v>2</v>
@@ -29030,13 +29030,13 @@
         <v>2.67</v>
       </c>
       <c r="AO131" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP131" t="n">
         <v>2.14</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -29463,25 +29463,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AO133" t="n">
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AS133" t="n">
         <v>1.14</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AU133" t="n">
         <v>6</v>
@@ -30998,7 +30998,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR140" t="n">
         <v>1.7</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.79</v>
@@ -32739,7 +32739,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.21</v>
@@ -33172,13 +33172,13 @@
         <v>2</v>
       </c>
       <c r="AO150" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP150" t="n">
         <v>1.57</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -33390,22 +33390,22 @@
         <v>2.29</v>
       </c>
       <c r="AO151" t="n">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP151" t="n">
         <v>2.14</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AU151" t="n">
         <v>3</v>
@@ -34695,25 +34695,25 @@
         <v>1.85</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AO157" t="n">
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AS157" t="n">
         <v>1.32</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AU157" t="n">
         <v>8</v>
@@ -35355,7 +35355,7 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.5</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.43</v>
@@ -36224,22 +36224,22 @@
         <v>1.88</v>
       </c>
       <c r="AO164" t="n">
-        <v>1.25</v>
+        <v>0.86</v>
       </c>
       <c r="AP164" t="n">
         <v>1.87</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AT164" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="AU164" t="n">
         <v>2</v>
@@ -36442,13 +36442,13 @@
         <v>1.71</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AP165" t="n">
         <v>1.36</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -38192,7 +38192,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR173" t="n">
         <v>1.71</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.57</v>
@@ -39712,22 +39712,22 @@
         <v>1.22</v>
       </c>
       <c r="AO180" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="AU180" t="n">
         <v>4</v>
@@ -41674,13 +41674,13 @@
         <v>1.13</v>
       </c>
       <c r="AO189" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AP189" t="n">
         <v>0.79</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -41889,25 +41889,25 @@
         <v>1.95</v>
       </c>
       <c r="AN190" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AO190" t="n">
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.87</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AS190" t="n">
         <v>1.39</v>
       </c>
       <c r="AT190" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="AU190" t="n">
         <v>2</v>
@@ -42552,7 +42552,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR193" t="n">
         <v>1.23</v>
@@ -42764,22 +42764,22 @@
         <v>1.67</v>
       </c>
       <c r="AO194" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP194" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AU194" t="n">
         <v>3</v>
@@ -42985,7 +42985,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.57</v>
@@ -44293,7 +44293,7 @@
         <v>0.3</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.5</v>
@@ -46031,25 +46031,25 @@
         <v>1.51</v>
       </c>
       <c r="AN209" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AO209" t="n">
         <v>1.22</v>
       </c>
       <c r="AP209" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.64</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AS209" t="n">
         <v>1.22</v>
       </c>
       <c r="AT209" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="AU209" t="n">
         <v>9</v>
@@ -46470,13 +46470,13 @@
         <v>2.11</v>
       </c>
       <c r="AO211" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AP211" t="n">
         <v>2.21</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -48002,7 +48002,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR218" t="n">
         <v>1.79</v>
@@ -48432,22 +48432,22 @@
         <v>1.1</v>
       </c>
       <c r="AO220" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AP220" t="n">
         <v>1.07</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AU220" t="n">
         <v>5</v>
@@ -49083,25 +49083,25 @@
         <v>1.75</v>
       </c>
       <c r="AN223" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AO223" t="n">
         <v>1.1</v>
       </c>
       <c r="AP223" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.21</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AS223" t="n">
         <v>1.13</v>
       </c>
       <c r="AT223" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AU223" t="n">
         <v>4</v>
@@ -50397,7 +50397,7 @@
         <v>0.8</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ229" t="n">
         <v>1</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.87</v>
@@ -51048,22 +51048,22 @@
         <v>1.83</v>
       </c>
       <c r="AO232" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AP232" t="n">
         <v>1.67</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT232" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AU232" t="n">
         <v>6</v>
@@ -52356,13 +52356,13 @@
         <v>1.73</v>
       </c>
       <c r="AO238" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AP238" t="n">
         <v>1.64</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
@@ -53670,7 +53670,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR244" t="n">
         <v>1.41</v>
@@ -53885,7 +53885,7 @@
         <v>1.27</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ245" t="n">
         <v>1.64</v>
@@ -54097,25 +54097,25 @@
         <v>1.75</v>
       </c>
       <c r="AN246" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AO246" t="n">
         <v>1.25</v>
       </c>
       <c r="AP246" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.07</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AS246" t="n">
         <v>1.24</v>
       </c>
       <c r="AT246" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AU246" t="n">
         <v>5</v>
@@ -54975,7 +54975,7 @@
         <v>0.75</v>
       </c>
       <c r="AP250" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ250" t="n">
         <v>0.6</v>
@@ -55190,13 +55190,13 @@
         <v>2</v>
       </c>
       <c r="AO251" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AP251" t="n">
         <v>1.79</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR251" t="n">
         <v>1.49</v>
@@ -55408,22 +55408,22 @@
         <v>1.58</v>
       </c>
       <c r="AO252" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AP252" t="n">
         <v>1.64</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AT252" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AU252" t="n">
         <v>2</v>
@@ -57591,7 +57591,7 @@
         <v>0.92</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AQ262" t="n">
         <v>0.87</v>
@@ -57806,13 +57806,13 @@
         <v>2</v>
       </c>
       <c r="AO263" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AP263" t="n">
         <v>2</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR263" t="n">
         <v>1.78</v>
@@ -58466,7 +58466,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ266" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR266" t="n">
         <v>1.65</v>
@@ -58893,25 +58893,25 @@
         <v>1.91</v>
       </c>
       <c r="AN268" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO268" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="AP268" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AQ268" t="n">
         <v>0.6</v>
       </c>
       <c r="AR268" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AS268" t="n">
         <v>1.62</v>
       </c>
       <c r="AT268" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="AU268" t="n">
         <v>2</v>
@@ -59553,7 +59553,7 @@
         <v>1.15</v>
       </c>
       <c r="AP271" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ271" t="n">
         <v>1.07</v>
@@ -61294,22 +61294,22 @@
         <v>2</v>
       </c>
       <c r="AO279" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP279" t="n">
         <v>1.86</v>
       </c>
       <c r="AQ279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR279" t="n">
         <v>1.52</v>
       </c>
       <c r="AS279" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="AT279" t="n">
-        <v>2.47</v>
+        <v>1.52</v>
       </c>
       <c r="AU279" t="n">
         <v>2</v>
@@ -62057,7 +62057,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -62163,25 +62163,25 @@
         <v>2.47</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.75</v>
+        <v>2.07</v>
       </c>
       <c r="AO283" t="n">
         <v>0.79</v>
       </c>
       <c r="AP283" t="n">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="AQ283" t="n">
         <v>0.93</v>
       </c>
       <c r="AR283" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AS283" t="n">
         <v>1.16</v>
       </c>
       <c r="AT283" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AU283" t="n">
         <v>5</v>
@@ -62683,6 +62683,442 @@
         <v>2.45</v>
       </c>
       <c r="BP285" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>7841321</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>45928.77083333334</v>
+      </c>
+      <c r="F286" t="n">
+        <v>29</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" t="n">
+        <v>2</v>
+      </c>
+      <c r="N286" t="n">
+        <v>3</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>['54', '60']</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>3</v>
+      </c>
+      <c r="R286" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S286" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T286" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U286" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="V286" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W286" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X286" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP286" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ286" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR286" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS286" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT286" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU286" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX286" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY286" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ286" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA286" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB286" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC286" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD286" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE286" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BF286" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BG286" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH286" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BI286" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ286" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK286" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL286" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM286" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN286" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO286" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP286" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>7841314</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>45928.85416666666</v>
+      </c>
+      <c r="F287" t="n">
+        <v>29</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>1</v>
+      </c>
+      <c r="J287" t="n">
+        <v>1</v>
+      </c>
+      <c r="K287" t="n">
+        <v>2</v>
+      </c>
+      <c r="L287" t="n">
+        <v>2</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1</v>
+      </c>
+      <c r="N287" t="n">
+        <v>3</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>['34', '69']</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R287" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S287" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T287" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U287" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V287" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W287" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X287" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI287" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK287" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AN287" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO287" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP287" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ287" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR287" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS287" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT287" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU287" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV287" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX287" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY287" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ287" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA287" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB287" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC287" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD287" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE287" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF287" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BG287" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH287" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BI287" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ287" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK287" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL287" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM287" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN287" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO287" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP287" t="n">
         <v>1.46</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP287"/>
+  <dimension ref="A1:BP291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.43</v>
@@ -1786,7 +1786,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.79</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.21</v>
@@ -3530,7 +3530,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.13</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR23" t="n">
         <v>1.23</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.87</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.87</v>
@@ -6582,7 +6582,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.43</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.36</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -8980,7 +8980,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -10070,7 +10070,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR44" t="n">
         <v>1.6</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.57</v>
@@ -10724,7 +10724,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR52" t="n">
         <v>2.13</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ59" t="n">
         <v>1</v>
@@ -13994,7 +13994,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR62" t="n">
         <v>1.29</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ63" t="n">
         <v>1</v>
@@ -14427,10 +14427,10 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR64" t="n">
         <v>1.71</v>
@@ -14648,7 +14648,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR65" t="n">
         <v>1.95</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.6</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.93</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.13</v>
@@ -18790,7 +18790,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19005,10 +19005,10 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR85" t="n">
         <v>1.6</v>
@@ -19441,7 +19441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.87</v>
@@ -19662,7 +19662,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR88" t="n">
         <v>1.94</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -22714,7 +22714,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR102" t="n">
         <v>1.21</v>
@@ -22932,7 +22932,7 @@
         <v>2</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR103" t="n">
         <v>1.98</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.13</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.6</v>
@@ -23801,10 +23801,10 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR107" t="n">
         <v>1.65</v>
@@ -24673,7 +24673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.13</v>
@@ -25984,7 +25984,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR117" t="n">
         <v>1.74</v>
@@ -27074,7 +27074,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR122" t="n">
         <v>1.13</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.31</v>
@@ -27507,7 +27507,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.64</v>
@@ -28382,7 +28382,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR128" t="n">
         <v>1.74</v>
@@ -28597,7 +28597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.87</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.13</v>
@@ -29908,7 +29908,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR135" t="n">
         <v>1.7</v>
@@ -31652,7 +31652,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -32085,7 +32085,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.93</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.64</v>
@@ -32960,7 +32960,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.13</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.31</v>
@@ -33614,7 +33614,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR152" t="n">
         <v>1.73</v>
@@ -35358,7 +35358,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR160" t="n">
         <v>1.33</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.87</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.87</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.79</v>
@@ -37753,10 +37753,10 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -38410,7 +38410,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR174" t="n">
         <v>1.43</v>
@@ -38846,7 +38846,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR176" t="n">
         <v>1.38</v>
@@ -39497,7 +39497,7 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ179" t="n">
         <v>0.93</v>
@@ -41023,7 +41023,7 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.64</v>
@@ -41244,7 +41244,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR187" t="n">
         <v>1.74</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.79</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.21</v>
@@ -42334,7 +42334,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR192" t="n">
         <v>1.47</v>
@@ -43203,7 +43203,7 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.36</v>
@@ -44296,7 +44296,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR201" t="n">
         <v>1.52</v>
@@ -44732,7 +44732,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR203" t="n">
         <v>1.34</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.21</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.87</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.87</v>
@@ -46694,7 +46694,7 @@
         <v>2</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR212" t="n">
         <v>1.77</v>
@@ -46909,7 +46909,7 @@
         <v>0.6</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.57</v>
@@ -48874,7 +48874,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR222" t="n">
         <v>1.5</v>
@@ -49525,7 +49525,7 @@
         <v>0.64</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.57</v>
@@ -50182,7 +50182,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR228" t="n">
         <v>1.44</v>
@@ -50833,7 +50833,7 @@
         <v>0.3</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.43</v>
@@ -51272,7 +51272,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR233" t="n">
         <v>1.59</v>
@@ -51705,7 +51705,7 @@
         <v>0.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ235" t="n">
         <v>0.79</v>
@@ -53013,7 +53013,7 @@
         <v>1</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ241" t="n">
         <v>1</v>
@@ -53231,7 +53231,7 @@
         <v>1.18</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.21</v>
@@ -53452,7 +53452,7 @@
         <v>0.79</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR243" t="n">
         <v>1.57</v>
@@ -54106,7 +54106,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR246" t="n">
         <v>1.86</v>
@@ -54321,7 +54321,7 @@
         <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.87</v>
@@ -54539,7 +54539,7 @@
         <v>1.55</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ248" t="n">
         <v>1.36</v>
@@ -58027,7 +58027,7 @@
         <v>0.85</v>
       </c>
       <c r="AP264" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ264" t="n">
         <v>0.93</v>
@@ -58245,10 +58245,10 @@
         <v>0.54</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR265" t="n">
         <v>1.43</v>
@@ -58463,7 +58463,7 @@
         <v>1</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ266" t="n">
         <v>1.13</v>
@@ -59117,10 +59117,10 @@
         <v>1.62</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ269" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR269" t="n">
         <v>1.62</v>
@@ -59556,7 +59556,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ271" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR271" t="n">
         <v>1.7</v>
@@ -63120,6 +63120,878 @@
       </c>
       <c r="BP287" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>7841318</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>45929.66666666666</v>
+      </c>
+      <c r="F288" t="n">
+        <v>29</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I288" t="n">
+        <v>1</v>
+      </c>
+      <c r="J288" t="n">
+        <v>1</v>
+      </c>
+      <c r="K288" t="n">
+        <v>2</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="n">
+        <v>3</v>
+      </c>
+      <c r="N288" t="n">
+        <v>4</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>['7', '84', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R288" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S288" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T288" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U288" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V288" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W288" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X288" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ288" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR288" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS288" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT288" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX288" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY288" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ288" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA288" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB288" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC288" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD288" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE288" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF288" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG288" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH288" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI288" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ288" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK288" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL288" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM288" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN288" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO288" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP288" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>7841319</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>45929.79166666666</v>
+      </c>
+      <c r="F289" t="n">
+        <v>29</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>1</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>2</v>
+      </c>
+      <c r="M289" t="n">
+        <v>1</v>
+      </c>
+      <c r="N289" t="n">
+        <v>3</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>['31', '81']</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R289" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S289" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="T289" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U289" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V289" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W289" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X289" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ289" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX289" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY289" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ289" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA289" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB289" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC289" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD289" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE289" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF289" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BG289" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH289" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BI289" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ289" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK289" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL289" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM289" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN289" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO289" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP289" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>7841316</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>45929.8125</v>
+      </c>
+      <c r="F290" t="n">
+        <v>29</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>2</v>
+      </c>
+      <c r="N290" t="n">
+        <v>2</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>['41', '80']</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R290" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S290" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="T290" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U290" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V290" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W290" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X290" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO290" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ290" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR290" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS290" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT290" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU290" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ290" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA290" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB290" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC290" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD290" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE290" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BF290" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG290" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH290" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="BI290" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ290" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK290" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL290" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM290" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN290" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO290" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP290" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>7841313</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>45930.89930555555</v>
+      </c>
+      <c r="F291" t="n">
+        <v>29</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R291" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S291" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="T291" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U291" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V291" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W291" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X291" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP291" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR291" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS291" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT291" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX291" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ291" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA291" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB291" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC291" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD291" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE291" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="BF291" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG291" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH291" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI291" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ291" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BK291" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL291" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM291" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN291" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO291" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP291" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -63056,13 +63056,13 @@
         <v>2.77</v>
       </c>
       <c r="AU287" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV287" t="n">
         <v>6</v>
       </c>
       <c r="AW287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX287" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP291"/>
+  <dimension ref="A1:BP296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.64</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.87</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.2</v>
@@ -2004,7 +2004,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.93</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.2</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.21</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.47</v>
@@ -7236,7 +7236,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR31" t="n">
         <v>1.94</v>
@@ -7669,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -8544,7 +8544,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR37" t="n">
         <v>2.28</v>
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -9198,7 +9198,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR40" t="n">
         <v>1.69</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.2</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.87</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.6</v>
@@ -12032,7 +12032,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR53" t="n">
         <v>0.93</v>
@@ -12686,7 +12686,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -12904,7 +12904,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR57" t="n">
         <v>1.4</v>
@@ -13340,7 +13340,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR59" t="n">
         <v>1.44</v>
@@ -13555,10 +13555,10 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR60" t="n">
         <v>1.65</v>
@@ -16174,7 +16174,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR72" t="n">
         <v>1.97</v>
@@ -16392,7 +16392,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR73" t="n">
         <v>1.62</v>
@@ -16610,7 +16610,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.64</v>
@@ -17479,10 +17479,10 @@
         <v>0.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -17697,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.36</v>
@@ -17918,7 +17918,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR80" t="n">
         <v>1.73</v>
@@ -18133,7 +18133,7 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.57</v>
@@ -20534,7 +20534,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR92" t="n">
         <v>1.81</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.21</v>
@@ -20967,10 +20967,10 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -21406,7 +21406,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR96" t="n">
         <v>1.47</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.21</v>
@@ -22278,7 +22278,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR100" t="n">
         <v>1.47</v>
@@ -22493,10 +22493,10 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.57</v>
@@ -25109,10 +25109,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.36</v>
@@ -26202,7 +26202,7 @@
         <v>2</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR118" t="n">
         <v>1.85</v>
@@ -26420,7 +26420,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR119" t="n">
         <v>1.94</v>
@@ -26856,7 +26856,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR121" t="n">
         <v>1.92</v>
@@ -27292,7 +27292,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -28161,10 +28161,10 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR127" t="n">
         <v>1.31</v>
@@ -29251,7 +29251,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.57</v>
@@ -29472,7 +29472,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR133" t="n">
         <v>1.96</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -30562,7 +30562,7 @@
         <v>2</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR138" t="n">
         <v>1.79</v>
@@ -30995,7 +30995,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.13</v>
@@ -31216,7 +31216,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31649,7 +31649,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.47</v>
@@ -31870,7 +31870,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -33396,7 +33396,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -33611,7 +33611,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.6</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.87</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ155" t="n">
         <v>1</v>
@@ -35140,7 +35140,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR159" t="n">
         <v>1.43</v>
@@ -35576,7 +35576,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR161" t="n">
         <v>1.65</v>
@@ -36230,7 +36230,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -36666,7 +36666,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR166" t="n">
         <v>1.56</v>
@@ -36881,7 +36881,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.93</v>
@@ -37538,7 +37538,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR170" t="n">
         <v>1.36</v>
@@ -38625,7 +38625,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.6</v>
@@ -39718,7 +39718,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -39936,7 +39936,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR181" t="n">
         <v>1.18</v>
@@ -40369,7 +40369,7 @@
         <v>1.25</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.21</v>
@@ -40805,10 +40805,10 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR185" t="n">
         <v>1.35</v>
@@ -41462,7 +41462,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR188" t="n">
         <v>1.72</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.13</v>
@@ -41898,7 +41898,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR190" t="n">
         <v>1.96</v>
@@ -42331,7 +42331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.6</v>
@@ -42770,7 +42770,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -43642,7 +43642,7 @@
         <v>2</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR198" t="n">
         <v>1.73</v>
@@ -44514,7 +44514,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR202" t="n">
         <v>1.45</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.2</v>
@@ -45604,7 +45604,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR207" t="n">
         <v>1.71</v>
@@ -45822,7 +45822,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR208" t="n">
         <v>1.71</v>
@@ -46255,7 +46255,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.87</v>
@@ -46473,7 +46473,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.13</v>
@@ -47130,7 +47130,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -47345,7 +47345,7 @@
         <v>1.7</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.36</v>
@@ -47566,7 +47566,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR216" t="n">
         <v>1.84</v>
@@ -48438,7 +48438,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -48656,7 +48656,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR221" t="n">
         <v>1.61</v>
@@ -49307,7 +49307,7 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.21</v>
@@ -49743,7 +49743,7 @@
         <v>1.1</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ226" t="n">
         <v>1.64</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.87</v>
@@ -50836,7 +50836,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR231" t="n">
         <v>1.66</v>
@@ -51054,7 +51054,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
@@ -51487,7 +51487,7 @@
         <v>0.92</v>
       </c>
       <c r="AP234" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.93</v>
@@ -51708,7 +51708,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR235" t="n">
         <v>1.6</v>
@@ -52144,7 +52144,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR237" t="n">
         <v>1.78</v>
@@ -52798,7 +52798,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR240" t="n">
         <v>1.41</v>
@@ -53016,7 +53016,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR241" t="n">
         <v>1.68</v>
@@ -53449,7 +53449,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.47</v>
@@ -53667,7 +53667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.13</v>
@@ -55193,7 +55193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ251" t="n">
         <v>1.13</v>
@@ -55414,7 +55414,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
@@ -55629,7 +55629,7 @@
         <v>1.42</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.36</v>
@@ -55847,7 +55847,7 @@
         <v>0.58</v>
       </c>
       <c r="AP254" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.57</v>
@@ -56065,7 +56065,7 @@
         <v>1.33</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ255" t="n">
         <v>1.21</v>
@@ -56286,7 +56286,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ256" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR256" t="n">
         <v>1.58</v>
@@ -56504,7 +56504,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR257" t="n">
         <v>1.47</v>
@@ -56937,10 +56937,10 @@
         <v>0.5</v>
       </c>
       <c r="AP259" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR259" t="n">
         <v>1.82</v>
@@ -57158,7 +57158,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ260" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR260" t="n">
         <v>1.73</v>
@@ -59771,7 +59771,7 @@
         <v>1.08</v>
       </c>
       <c r="AP272" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AQ272" t="n">
         <v>1.21</v>
@@ -60207,10 +60207,10 @@
         <v>0.86</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ274" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR274" t="n">
         <v>1.5</v>
@@ -60425,10 +60425,10 @@
         <v>0.85</v>
       </c>
       <c r="AP275" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ275" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR275" t="n">
         <v>1.77</v>
@@ -60864,7 +60864,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ277" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR277" t="n">
         <v>1.54</v>
@@ -61297,7 +61297,7 @@
         <v>0</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ279" t="n">
         <v>3</v>
@@ -61736,7 +61736,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR281" t="n">
         <v>1.53</v>
@@ -63992,6 +63992,1096 @@
       </c>
       <c r="BP291" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>7841325</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>45932.79166666666</v>
+      </c>
+      <c r="F292" t="n">
+        <v>30</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" t="n">
+        <v>1</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="n">
+        <v>1</v>
+      </c>
+      <c r="N292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R292" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S292" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T292" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U292" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V292" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W292" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X292" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK292" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AO292" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AP292" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ292" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS292" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT292" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU292" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW292" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX292" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY292" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ292" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA292" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB292" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC292" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD292" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE292" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF292" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG292" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH292" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI292" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ292" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK292" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL292" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM292" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN292" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO292" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP292" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>7841323</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>45932.89583333334</v>
+      </c>
+      <c r="F293" t="n">
+        <v>30</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>1</v>
+      </c>
+      <c r="L293" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1</v>
+      </c>
+      <c r="N293" t="n">
+        <v>2</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R293" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S293" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T293" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U293" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V293" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="W293" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X293" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN293" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO293" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ293" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR293" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS293" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT293" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU293" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW293" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX293" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY293" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ293" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA293" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB293" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC293" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD293" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE293" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF293" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG293" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH293" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI293" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ293" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK293" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL293" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM293" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN293" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO293" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP293" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>7841329</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>45933.79166666666</v>
+      </c>
+      <c r="F294" t="n">
+        <v>30</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>1</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1</v>
+      </c>
+      <c r="K294" t="n">
+        <v>2</v>
+      </c>
+      <c r="L294" t="n">
+        <v>2</v>
+      </c>
+      <c r="M294" t="n">
+        <v>2</v>
+      </c>
+      <c r="N294" t="n">
+        <v>4</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>['11', '59']</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>['42', '46']</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R294" t="n">
+        <v>2</v>
+      </c>
+      <c r="S294" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T294" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U294" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V294" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W294" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X294" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO294" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP294" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ294" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR294" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS294" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AT294" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU294" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY294" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ294" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA294" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB294" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC294" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD294" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE294" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF294" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BG294" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH294" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI294" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ294" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK294" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL294" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM294" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN294" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO294" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP294" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>7841322</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>45933.89583333334</v>
+      </c>
+      <c r="F295" t="n">
+        <v>30</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>2</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>2</v>
+      </c>
+      <c r="L295" t="n">
+        <v>2</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" t="n">
+        <v>2</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>['15', '37']</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R295" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S295" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T295" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U295" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V295" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="W295" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X295" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO295" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP295" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ295" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY295" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ295" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA295" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB295" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC295" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD295" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE295" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF295" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG295" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH295" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BI295" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ295" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK295" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL295" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM295" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN295" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO295" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP295" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>7841328</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>45933.89930555555</v>
+      </c>
+      <c r="F296" t="n">
+        <v>30</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>1</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>1</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>1</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R296" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S296" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T296" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U296" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V296" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W296" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X296" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP296" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ296" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR296" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS296" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT296" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU296" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW296" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX296" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY296" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ296" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA296" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB296" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC296" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD296" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE296" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF296" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG296" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH296" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BI296" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ296" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK296" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL296" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM296" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN296" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO296" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP296" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP296"/>
+  <dimension ref="A1:BP310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.47</v>
@@ -1132,7 +1132,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.73</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.88</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.93</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.6</v>
@@ -3748,7 +3748,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.13</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5492,7 +5492,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR23" t="n">
         <v>1.23</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.87</v>
@@ -5925,10 +5925,10 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR26" t="n">
         <v>1.36</v>
@@ -6364,7 +6364,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR27" t="n">
         <v>1.65</v>
@@ -6582,7 +6582,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -6797,10 +6797,10 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR30" t="n">
         <v>2.72</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.47</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -8108,7 +8108,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR35" t="n">
         <v>1.6</v>
@@ -8323,10 +8323,10 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.93</v>
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.88</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.13</v>
@@ -9634,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR42" t="n">
         <v>2.28</v>
@@ -9852,7 +9852,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR43" t="n">
         <v>2.02</v>
@@ -10070,7 +10070,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR44" t="n">
         <v>1.6</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.87</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR46" t="n">
         <v>1.4</v>
@@ -10724,7 +10724,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -10939,10 +10939,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR48" t="n">
         <v>1.9</v>
@@ -11160,7 +11160,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.13</v>
@@ -11593,10 +11593,10 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.6</v>
@@ -12247,10 +12247,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR54" t="n">
         <v>1.59</v>
@@ -12465,10 +12465,10 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -12683,10 +12683,10 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -13119,10 +13119,10 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.93</v>
@@ -13776,7 +13776,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR61" t="n">
         <v>1.62</v>
@@ -13994,7 +13994,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR62" t="n">
         <v>1.29</v>
@@ -14209,10 +14209,10 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR63" t="n">
         <v>1.5</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.6</v>
@@ -14648,7 +14648,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR65" t="n">
         <v>1.95</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.87</v>
@@ -15299,10 +15299,10 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -15517,10 +15517,10 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -15738,7 +15738,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR70" t="n">
         <v>1.12</v>
@@ -15953,10 +15953,10 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR71" t="n">
         <v>1.88</v>
@@ -16171,7 +16171,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.93</v>
@@ -16389,7 +16389,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.88</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.73</v>
@@ -16828,7 +16828,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17046,7 +17046,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -17261,10 +17261,10 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -17482,7 +17482,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -17700,7 +17700,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.47</v>
@@ -18133,10 +18133,10 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR81" t="n">
         <v>1.26</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.13</v>
@@ -18572,7 +18572,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR83" t="n">
         <v>1.53</v>
@@ -18790,7 +18790,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19005,10 +19005,10 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR85" t="n">
         <v>1.6</v>
@@ -19226,7 +19226,7 @@
         <v>2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR86" t="n">
         <v>1.9</v>
@@ -19441,7 +19441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.87</v>
@@ -19877,10 +19877,10 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20095,10 +20095,10 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -20313,10 +20313,10 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR91" t="n">
         <v>1.69</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.73</v>
@@ -20752,7 +20752,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR93" t="n">
         <v>1.68</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.93</v>
@@ -21185,10 +21185,10 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR95" t="n">
         <v>1.75</v>
@@ -21621,10 +21621,10 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -21842,7 +21842,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR98" t="n">
         <v>1.59</v>
@@ -22057,10 +22057,10 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR99" t="n">
         <v>2.14</v>
@@ -22275,7 +22275,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.47</v>
@@ -22496,7 +22496,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.6</v>
@@ -22932,7 +22932,7 @@
         <v>2</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR103" t="n">
         <v>1.98</v>
@@ -23147,10 +23147,10 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR104" t="n">
         <v>1.55</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.13</v>
@@ -23583,10 +23583,10 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR106" t="n">
         <v>1.68</v>
@@ -23801,10 +23801,10 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR107" t="n">
         <v>1.65</v>
@@ -24022,7 +24022,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR108" t="n">
         <v>1.49</v>
@@ -24458,7 +24458,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR110" t="n">
         <v>1.93</v>
@@ -24673,10 +24673,10 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -24894,7 +24894,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR112" t="n">
         <v>1.77</v>
@@ -25330,7 +25330,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -25548,7 +25548,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR115" t="n">
         <v>1.49</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.6</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.13</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.93</v>
@@ -27071,10 +27071,10 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR122" t="n">
         <v>1.13</v>
@@ -27289,10 +27289,10 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -27507,10 +27507,10 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -27728,7 +27728,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR125" t="n">
         <v>1.2</v>
@@ -27943,10 +27943,10 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.88</v>
@@ -28379,10 +28379,10 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR128" t="n">
         <v>1.74</v>
@@ -28597,10 +28597,10 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -28815,10 +28815,10 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR130" t="n">
         <v>1.56</v>
@@ -29033,10 +29033,10 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -29254,7 +29254,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29690,7 +29690,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.87</v>
@@ -30344,7 +30344,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR137" t="n">
         <v>1.3</v>
@@ -30777,10 +30777,10 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.73</v>
@@ -31431,10 +31431,10 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR142" t="n">
         <v>1.84</v>
@@ -31649,10 +31649,10 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -32085,10 +32085,10 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR145" t="n">
         <v>1.63</v>
@@ -32303,10 +32303,10 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -32521,10 +32521,10 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR147" t="n">
         <v>1.59</v>
@@ -32739,10 +32739,10 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -32957,10 +32957,10 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -33175,10 +33175,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -33393,10 +33393,10 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -34050,7 +34050,7 @@
         <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR154" t="n">
         <v>1.78</v>
@@ -34268,7 +34268,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -34486,7 +34486,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR156" t="n">
         <v>1.71</v>
@@ -34919,10 +34919,10 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR158" t="n">
         <v>1.35</v>
@@ -35355,10 +35355,10 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR160" t="n">
         <v>1.33</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.47</v>
@@ -35791,10 +35791,10 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR162" t="n">
         <v>1.64</v>
@@ -36012,7 +36012,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR163" t="n">
         <v>1.21</v>
@@ -36227,10 +36227,10 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -36445,10 +36445,10 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.88</v>
@@ -36881,10 +36881,10 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR167" t="n">
         <v>1.26</v>
@@ -37099,10 +37099,10 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR168" t="n">
         <v>1.68</v>
@@ -37317,10 +37317,10 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.73</v>
@@ -37753,10 +37753,10 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -37971,10 +37971,10 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR172" t="n">
         <v>1.66</v>
@@ -38628,7 +38628,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR175" t="n">
         <v>1.47</v>
@@ -38843,10 +38843,10 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR176" t="n">
         <v>1.38</v>
@@ -39064,7 +39064,7 @@
         <v>2</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR177" t="n">
         <v>1.79</v>
@@ -39279,10 +39279,10 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR178" t="n">
         <v>1.59</v>
@@ -39497,10 +39497,10 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR179" t="n">
         <v>1.34</v>
@@ -39715,10 +39715,10 @@
         <v>1.13</v>
       </c>
       <c r="AP180" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ180" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AQ180" t="n">
-        <v>1.29</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.87</v>
@@ -40372,7 +40372,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR183" t="n">
         <v>1.91</v>
@@ -40587,10 +40587,10 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR184" t="n">
         <v>1.84</v>
@@ -40805,7 +40805,7 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.47</v>
@@ -41023,10 +41023,10 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -41241,10 +41241,10 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR187" t="n">
         <v>1.74</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.73</v>
@@ -41680,7 +41680,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -42113,10 +42113,10 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR191" t="n">
         <v>1.56</v>
@@ -42767,10 +42767,10 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -42985,10 +42985,10 @@
         <v>0.67</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR195" t="n">
         <v>1.36</v>
@@ -43203,10 +43203,10 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -43421,10 +43421,10 @@
         <v>0.6</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -43860,7 +43860,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR199" t="n">
         <v>1.81</v>
@@ -44078,7 +44078,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -44293,10 +44293,10 @@
         <v>0.3</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR201" t="n">
         <v>1.52</v>
@@ -44511,7 +44511,7 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.47</v>
@@ -44729,10 +44729,10 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR203" t="n">
         <v>1.34</v>
@@ -44947,10 +44947,10 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR204" t="n">
         <v>1.65</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.87</v>
@@ -45383,10 +45383,10 @@
         <v>1.11</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR206" t="n">
         <v>1.82</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.88</v>
@@ -45819,7 +45819,7 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.73</v>
@@ -46040,7 +46040,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR209" t="n">
         <v>1.87</v>
@@ -46258,7 +46258,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR210" t="n">
         <v>1.66</v>
@@ -46476,7 +46476,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -46909,10 +46909,10 @@
         <v>0.6</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR213" t="n">
         <v>1.4</v>
@@ -47348,7 +47348,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR215" t="n">
         <v>1.54</v>
@@ -47781,10 +47781,10 @@
         <v>1</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR217" t="n">
         <v>1.47</v>
@@ -47999,7 +47999,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.13</v>
@@ -48217,10 +48217,10 @@
         <v>0.55</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR219" t="n">
         <v>1.8</v>
@@ -48438,7 +48438,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.93</v>
@@ -48874,7 +48874,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR222" t="n">
         <v>1.5</v>
@@ -49092,7 +49092,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR223" t="n">
         <v>1.89</v>
@@ -49307,10 +49307,10 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR224" t="n">
         <v>1.36</v>
@@ -49525,10 +49525,10 @@
         <v>0.64</v>
       </c>
       <c r="AP225" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR225" t="n">
         <v>1.66</v>
@@ -49746,7 +49746,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR226" t="n">
         <v>1.91</v>
@@ -50179,10 +50179,10 @@
         <v>0.27</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR228" t="n">
         <v>1.44</v>
@@ -50397,10 +50397,10 @@
         <v>0.8</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR229" t="n">
         <v>1.56</v>
@@ -50615,10 +50615,10 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR230" t="n">
         <v>1.33</v>
@@ -50833,7 +50833,7 @@
         <v>0.3</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.47</v>
@@ -51054,7 +51054,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
@@ -51269,7 +51269,7 @@
         <v>1.75</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.6</v>
@@ -51490,7 +51490,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR234" t="n">
         <v>1.86</v>
@@ -51705,7 +51705,7 @@
         <v>0.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ235" t="n">
         <v>0.73</v>
@@ -51926,7 +51926,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR236" t="n">
         <v>1.84</v>
@@ -52141,7 +52141,7 @@
         <v>0.55</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ237" t="n">
         <v>0.47</v>
@@ -52359,10 +52359,10 @@
         <v>1.18</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
@@ -52577,10 +52577,10 @@
         <v>0.92</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ239" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR239" t="n">
         <v>1.52</v>
@@ -52795,7 +52795,7 @@
         <v>0.83</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.88</v>
@@ -53013,7 +53013,7 @@
         <v>1</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ241" t="n">
         <v>0.93</v>
@@ -53231,10 +53231,10 @@
         <v>1.18</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR242" t="n">
         <v>1.4</v>
@@ -53452,7 +53452,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR243" t="n">
         <v>1.57</v>
@@ -53667,7 +53667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.13</v>
@@ -53885,10 +53885,10 @@
         <v>1.27</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR245" t="n">
         <v>1.34</v>
@@ -54106,7 +54106,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR246" t="n">
         <v>1.86</v>
@@ -54321,7 +54321,7 @@
         <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.87</v>
@@ -54539,10 +54539,10 @@
         <v>1.55</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR248" t="n">
         <v>1.67</v>
@@ -54760,7 +54760,7 @@
         <v>2</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR249" t="n">
         <v>1.76</v>
@@ -54975,10 +54975,10 @@
         <v>0.75</v>
       </c>
       <c r="AP250" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR250" t="n">
         <v>1.65</v>
@@ -55196,7 +55196,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR251" t="n">
         <v>1.49</v>
@@ -55411,10 +55411,10 @@
         <v>1.33</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
@@ -55629,10 +55629,10 @@
         <v>1.42</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR253" t="n">
         <v>1.45</v>
@@ -55850,7 +55850,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR254" t="n">
         <v>1.57</v>
@@ -56068,7 +56068,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR255" t="n">
         <v>1.46</v>
@@ -56283,7 +56283,7 @@
         <v>0.85</v>
       </c>
       <c r="AP256" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ256" t="n">
         <v>0.88</v>
@@ -56719,10 +56719,10 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR258" t="n">
         <v>1.33</v>
@@ -57155,7 +57155,7 @@
         <v>0.92</v>
       </c>
       <c r="AP260" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ260" t="n">
         <v>0.93</v>
@@ -57373,10 +57373,10 @@
         <v>1.42</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR261" t="n">
         <v>1.53</v>
@@ -57591,7 +57591,7 @@
         <v>0.92</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ262" t="n">
         <v>0.87</v>
@@ -57812,7 +57812,7 @@
         <v>2</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR263" t="n">
         <v>1.78</v>
@@ -58027,10 +58027,10 @@
         <v>0.85</v>
       </c>
       <c r="AP264" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ264" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR264" t="n">
         <v>1.63</v>
@@ -58245,10 +58245,10 @@
         <v>0.54</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR265" t="n">
         <v>1.43</v>
@@ -58463,7 +58463,7 @@
         <v>1</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ266" t="n">
         <v>1.13</v>
@@ -58684,7 +58684,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR267" t="n">
         <v>1.35</v>
@@ -58902,7 +58902,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR268" t="n">
         <v>1.84</v>
@@ -59117,7 +59117,7 @@
         <v>1.62</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ269" t="n">
         <v>1.6</v>
@@ -59338,7 +59338,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ270" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR270" t="n">
         <v>1.86</v>
@@ -59553,10 +59553,10 @@
         <v>1.15</v>
       </c>
       <c r="AP271" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ271" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR271" t="n">
         <v>1.7</v>
@@ -59774,7 +59774,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AR272" t="n">
         <v>1.56</v>
@@ -59989,10 +59989,10 @@
         <v>1.38</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR273" t="n">
         <v>1.32</v>
@@ -60646,7 +60646,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ276" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AR276" t="n">
         <v>1.45</v>
@@ -60861,7 +60861,7 @@
         <v>0.46</v>
       </c>
       <c r="AP277" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ277" t="n">
         <v>0.47</v>
@@ -61079,10 +61079,10 @@
         <v>1.31</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ278" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR278" t="n">
         <v>1.74</v>
@@ -61297,7 +61297,7 @@
         <v>0</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ279" t="n">
         <v>3</v>
@@ -61515,10 +61515,10 @@
         <v>0.62</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AQ280" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR280" t="n">
         <v>1.79</v>
@@ -61733,7 +61733,7 @@
         <v>0.85</v>
       </c>
       <c r="AP281" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ281" t="n">
         <v>0.93</v>
@@ -62172,7 +62172,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ283" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR283" t="n">
         <v>1.81</v>
@@ -62390,7 +62390,7 @@
         <v>2</v>
       </c>
       <c r="AQ284" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AR284" t="n">
         <v>1.8</v>
@@ -62608,7 +62608,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ285" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR285" t="n">
         <v>1.35</v>
@@ -62823,7 +62823,7 @@
         <v>1</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ286" t="n">
         <v>1.13</v>
@@ -63041,10 +63041,10 @@
         <v>1.21</v>
       </c>
       <c r="AP287" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ287" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR287" t="n">
         <v>1.68</v>
@@ -63259,10 +63259,10 @@
         <v>1.07</v>
       </c>
       <c r="AP288" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR288" t="n">
         <v>1.42</v>
@@ -63477,10 +63477,10 @@
         <v>0.5</v>
       </c>
       <c r="AP289" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR289" t="n">
         <v>1.56</v>
@@ -63695,7 +63695,7 @@
         <v>1.5</v>
       </c>
       <c r="AP290" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ290" t="n">
         <v>1.6</v>
@@ -63913,10 +63913,10 @@
         <v>1</v>
       </c>
       <c r="AP291" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AQ291" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR291" t="n">
         <v>1.66</v>
@@ -64352,7 +64352,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ293" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR293" t="n">
         <v>1.52</v>
@@ -64585,28 +64585,28 @@
         <v>5</v>
       </c>
       <c r="AV294" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW294" t="n">
         <v>17</v>
       </c>
       <c r="AX294" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY294" t="n">
         <v>22</v>
       </c>
       <c r="AZ294" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA294" t="n">
         <v>9</v>
       </c>
       <c r="BB294" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC294" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD294" t="n">
         <v>1.52</v>
@@ -64785,7 +64785,7 @@
         <v>0.79</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ295" t="n">
         <v>0.73</v>
@@ -65082,6 +65082,3058 @@
       </c>
       <c r="BP296" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>7841326</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>45934.66666666666</v>
+      </c>
+      <c r="F297" t="n">
+        <v>30</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" t="n">
+        <v>1</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R297" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S297" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T297" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U297" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V297" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W297" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X297" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH297" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI297" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ297" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK297" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM297" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN297" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO297" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP297" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ297" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR297" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS297" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT297" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU297" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW297" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX297" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY297" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ297" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA297" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB297" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC297" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD297" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE297" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BF297" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG297" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH297" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BI297" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ297" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BK297" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL297" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM297" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN297" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO297" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BP297" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>7841331</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>45934.77083333334</v>
+      </c>
+      <c r="F298" t="n">
+        <v>30</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" t="n">
+        <v>0</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R298" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S298" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T298" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U298" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V298" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W298" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X298" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI298" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK298" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM298" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN298" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO298" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP298" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ298" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR298" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS298" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV298" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW298" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX298" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY298" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ298" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA298" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB298" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC298" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD298" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE298" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF298" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG298" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH298" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI298" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ298" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BK298" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL298" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM298" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN298" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO298" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP298" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>7841330</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>45934.85416666666</v>
+      </c>
+      <c r="F299" t="n">
+        <v>30</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" t="n">
+        <v>2</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" t="n">
+        <v>3</v>
+      </c>
+      <c r="N299" t="n">
+        <v>4</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>['30', '90+1', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R299" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S299" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T299" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U299" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V299" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W299" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X299" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH299" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI299" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK299" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM299" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN299" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO299" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ299" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR299" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS299" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT299" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV299" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW299" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX299" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY299" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ299" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA299" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB299" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC299" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD299" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE299" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF299" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG299" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH299" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI299" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ299" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK299" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL299" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM299" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN299" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO299" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP299" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>7841327</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>45935.66666666666</v>
+      </c>
+      <c r="F300" t="n">
+        <v>30</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
+        <v>1</v>
+      </c>
+      <c r="N300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R300" t="n">
+        <v>2</v>
+      </c>
+      <c r="S300" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T300" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U300" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V300" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W300" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X300" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI300" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM300" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN300" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO300" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AP300" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ300" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR300" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS300" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT300" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU300" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW300" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX300" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY300" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ300" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA300" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB300" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC300" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD300" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE300" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BF300" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG300" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH300" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="BI300" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ300" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK300" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL300" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM300" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN300" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO300" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP300" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>7841324</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>45935.85416666666</v>
+      </c>
+      <c r="F301" t="n">
+        <v>30</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>2</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>2</v>
+      </c>
+      <c r="L301" t="n">
+        <v>3</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" t="n">
+        <v>3</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>['15', '45+4', '62']</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R301" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S301" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T301" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U301" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V301" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W301" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X301" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM301" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN301" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO301" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP301" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ301" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR301" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS301" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT301" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU301" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV301" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW301" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX301" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY301" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ301" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA301" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB301" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC301" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD301" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE301" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="BF301" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BG301" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH301" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BI301" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ301" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BK301" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL301" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM301" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BN301" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO301" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP301" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>7841338</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>45937.83333333334</v>
+      </c>
+      <c r="F302" t="n">
+        <v>31</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" t="n">
+        <v>1</v>
+      </c>
+      <c r="L302" t="n">
+        <v>2</v>
+      </c>
+      <c r="M302" t="n">
+        <v>1</v>
+      </c>
+      <c r="N302" t="n">
+        <v>3</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>['58', '86']</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="R302" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S302" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T302" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U302" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V302" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W302" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X302" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI302" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK302" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM302" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN302" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO302" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ302" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR302" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT302" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU302" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW302" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX302" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY302" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ302" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA302" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB302" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC302" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD302" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE302" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF302" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG302" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH302" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BI302" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ302" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK302" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL302" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM302" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN302" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO302" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP302" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>7841333</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>45937.89583333334</v>
+      </c>
+      <c r="F303" t="n">
+        <v>31</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>1</v>
+      </c>
+      <c r="J303" t="n">
+        <v>1</v>
+      </c>
+      <c r="K303" t="n">
+        <v>2</v>
+      </c>
+      <c r="L303" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" t="n">
+        <v>2</v>
+      </c>
+      <c r="N303" t="n">
+        <v>3</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>['28', '62']</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R303" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S303" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T303" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U303" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V303" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W303" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X303" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ303" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS303" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA303" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB303" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC303" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD303" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE303" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF303" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG303" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH303" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="BI303" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ303" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK303" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL303" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BM303" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN303" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BO303" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BP303" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>7841341</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>45937.89930555555</v>
+      </c>
+      <c r="F304" t="n">
+        <v>31</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" t="n">
+        <v>1</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" t="n">
+        <v>1</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="R304" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S304" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T304" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U304" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V304" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W304" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X304" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ304" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS304" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU304" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA304" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB304" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC304" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD304" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE304" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF304" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG304" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH304" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI304" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM304" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN304" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO304" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BP304" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>7841334</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>45938.79166666666</v>
+      </c>
+      <c r="F305" t="n">
+        <v>31</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1</v>
+      </c>
+      <c r="N305" t="n">
+        <v>1</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R305" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S305" t="n">
+        <v>4</v>
+      </c>
+      <c r="T305" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U305" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V305" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W305" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X305" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ305" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS305" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU305" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ305" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA305" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB305" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC305" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD305" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE305" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG305" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH305" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI305" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK305" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL305" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM305" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN305" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO305" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP305" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>7841337</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>45938.79166666666</v>
+      </c>
+      <c r="F306" t="n">
+        <v>31</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
+        <v>1</v>
+      </c>
+      <c r="J306" t="n">
+        <v>4</v>
+      </c>
+      <c r="K306" t="n">
+        <v>5</v>
+      </c>
+      <c r="L306" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" t="n">
+        <v>4</v>
+      </c>
+      <c r="N306" t="n">
+        <v>5</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>['15', '16', '44', '45+1']</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R306" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S306" t="n">
+        <v>5</v>
+      </c>
+      <c r="T306" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U306" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V306" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W306" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X306" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ306" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS306" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU306" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA306" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB306" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC306" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD306" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE306" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BG306" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH306" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI306" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK306" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL306" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM306" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN306" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO306" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP306" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>7841336</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>45938.875</v>
+      </c>
+      <c r="F307" t="n">
+        <v>31</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I307" t="n">
+        <v>1</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>1</v>
+      </c>
+      <c r="L307" t="n">
+        <v>3</v>
+      </c>
+      <c r="M307" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" t="n">
+        <v>3</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>['1', '60', '77']</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R307" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S307" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="T307" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U307" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V307" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W307" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X307" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ307" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS307" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU307" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ307" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA307" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB307" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC307" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD307" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE307" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BG307" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH307" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="BI307" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM307" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN307" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO307" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP307" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>7841339</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>45938.89583333334</v>
+      </c>
+      <c r="F308" t="n">
+        <v>31</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>1</v>
+      </c>
+      <c r="K308" t="n">
+        <v>1</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1</v>
+      </c>
+      <c r="N308" t="n">
+        <v>2</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R308" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S308" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T308" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U308" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V308" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W308" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X308" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ308" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS308" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT308" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ308" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA308" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB308" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC308" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD308" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE308" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF308" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BG308" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH308" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI308" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ308" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK308" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL308" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM308" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN308" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO308" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP308" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>7841340</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>45939.79166666666</v>
+      </c>
+      <c r="F309" t="n">
+        <v>31</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" t="n">
+        <v>1</v>
+      </c>
+      <c r="N309" t="n">
+        <v>1</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="R309" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S309" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T309" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U309" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V309" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W309" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X309" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ309" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR309" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS309" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT309" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV309" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW309" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX309" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY309" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ309" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA309" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB309" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC309" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD309" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE309" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF309" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG309" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH309" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BI309" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ309" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BK309" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL309" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM309" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN309" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO309" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP309" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>7841332</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>45939.8125</v>
+      </c>
+      <c r="F310" t="n">
+        <v>31</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="n">
+        <v>2</v>
+      </c>
+      <c r="M310" t="n">
+        <v>1</v>
+      </c>
+      <c r="N310" t="n">
+        <v>3</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>['74', '89']</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R310" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S310" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T310" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U310" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V310" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W310" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X310" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ310" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS310" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT310" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU310" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW310" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX310" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY310" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ310" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA310" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB310" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC310" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD310" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE310" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF310" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BG310" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH310" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BI310" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ310" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK310" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL310" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM310" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN310" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO310" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP310" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP310"/>
+  <dimension ref="A1:BP311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.73</v>
@@ -5274,7 +5274,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.6</v>
@@ -9634,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR42" t="n">
         <v>2.28</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.47</v>
@@ -12686,7 +12686,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -15735,7 +15735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.88</v>
@@ -16828,7 +16828,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17482,7 +17482,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.44</v>
@@ -21624,7 +21624,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -22496,7 +22496,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.87</v>
@@ -27292,7 +27292,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -27510,7 +27510,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -27725,7 +27725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.88</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.88</v>
@@ -32306,7 +32306,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -33396,7 +33396,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.25</v>
@@ -36230,7 +36230,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -37320,7 +37320,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -39718,7 +39718,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.93</v>
@@ -41026,7 +41026,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.13</v>
@@ -42770,7 +42770,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -46040,7 +46040,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR209" t="n">
         <v>1.87</v>
@@ -47127,7 +47127,7 @@
         <v>0.7</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.73</v>
@@ -48438,7 +48438,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -49534,10 +49534,10 @@
         <v>1.66</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AT225" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AU225" t="n">
         <v>1</v>
@@ -49746,16 +49746,16 @@
         <v>2.27</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AS226" t="n">
         <v>1.18</v>
       </c>
       <c r="AT226" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AU226" t="n">
         <v>2</v>
@@ -51051,10 +51051,10 @@
         <v>1.18</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
@@ -51275,13 +51275,13 @@
         <v>1.6</v>
       </c>
       <c r="AR233" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AS233" t="n">
         <v>1.12</v>
       </c>
       <c r="AT233" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AU233" t="n">
         <v>3</v>
@@ -51493,13 +51493,13 @@
         <v>0.88</v>
       </c>
       <c r="AR234" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AS234" t="n">
         <v>1.12</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="AU234" t="n">
         <v>4</v>
@@ -51929,13 +51929,13 @@
         <v>1.25</v>
       </c>
       <c r="AR236" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AS236" t="n">
         <v>1.09</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AU236" t="n">
         <v>7</v>
@@ -52368,10 +52368,10 @@
         <v>1.8</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU238" t="n">
         <v>8</v>
@@ -52804,10 +52804,10 @@
         <v>1.41</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU240" t="n">
         <v>1</v>
@@ -53022,10 +53022,10 @@
         <v>1.68</v>
       </c>
       <c r="AS241" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AT241" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AU241" t="n">
         <v>4</v>
@@ -53237,13 +53237,13 @@
         <v>1.33</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AS242" t="n">
         <v>1.13</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AU242" t="n">
         <v>3</v>
@@ -53888,16 +53888,16 @@
         <v>1.31</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR245" t="n">
         <v>1.34</v>
       </c>
       <c r="AS245" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AT245" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AU245" t="n">
         <v>4</v>
@@ -54327,13 +54327,13 @@
         <v>0.87</v>
       </c>
       <c r="AR247" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AS247" t="n">
         <v>1.33</v>
       </c>
       <c r="AT247" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="AU247" t="n">
         <v>4</v>
@@ -54766,10 +54766,10 @@
         <v>1.76</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT249" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AU249" t="n">
         <v>4</v>
@@ -54981,13 +54981,13 @@
         <v>0.75</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AS250" t="n">
         <v>1.64</v>
       </c>
       <c r="AT250" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AU250" t="n">
         <v>9</v>
@@ -55202,10 +55202,10 @@
         <v>1.49</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT251" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AU251" t="n">
         <v>3</v>
@@ -55414,7 +55414,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
@@ -55638,10 +55638,10 @@
         <v>1.45</v>
       </c>
       <c r="AS253" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AT253" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="AU253" t="n">
         <v>6</v>
@@ -55653,13 +55653,13 @@
         <v>18</v>
       </c>
       <c r="AX253" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY253" t="n">
         <v>24</v>
       </c>
       <c r="AZ253" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA253" t="n">
         <v>4</v>
@@ -55856,10 +55856,10 @@
         <v>1.57</v>
       </c>
       <c r="AS254" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AT254" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AU254" t="n">
         <v>1</v>
@@ -56289,13 +56289,13 @@
         <v>0.88</v>
       </c>
       <c r="AR256" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AS256" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT256" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AU256" t="n">
         <v>1</v>
@@ -56728,10 +56728,10 @@
         <v>1.33</v>
       </c>
       <c r="AS258" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT258" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AU258" t="n">
         <v>4</v>
@@ -56943,13 +56943,13 @@
         <v>0.47</v>
       </c>
       <c r="AR259" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AS259" t="n">
         <v>0.96</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU259" t="n">
         <v>2</v>
@@ -57164,10 +57164,10 @@
         <v>1.73</v>
       </c>
       <c r="AS260" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="AU260" t="n">
         <v>9</v>
@@ -57376,16 +57376,16 @@
         <v>1.93</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR261" t="n">
         <v>1.53</v>
       </c>
       <c r="AS261" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT261" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AU261" t="n">
         <v>5</v>
@@ -57815,13 +57815,13 @@
         <v>1.25</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="AU263" t="n">
         <v>4</v>
@@ -58036,10 +58036,10 @@
         <v>1.63</v>
       </c>
       <c r="AS264" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AT264" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AU264" t="n">
         <v>7</v>
@@ -58251,13 +58251,13 @@
         <v>0.44</v>
       </c>
       <c r="AR265" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AS265" t="n">
         <v>1.44</v>
       </c>
       <c r="AT265" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AU265" t="n">
         <v>3</v>
@@ -58469,13 +58469,13 @@
         <v>1.13</v>
       </c>
       <c r="AR266" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AS266" t="n">
         <v>1.25</v>
       </c>
       <c r="AT266" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU266" t="n">
         <v>6</v>
@@ -58681,7 +58681,7 @@
         <v>0.83</v>
       </c>
       <c r="AP267" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ267" t="n">
         <v>0.93</v>
@@ -58690,10 +58690,10 @@
         <v>1.35</v>
       </c>
       <c r="AS267" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT267" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AU267" t="n">
         <v>3</v>
@@ -58908,10 +58908,10 @@
         <v>1.84</v>
       </c>
       <c r="AS268" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AT268" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AU268" t="n">
         <v>2</v>
@@ -59341,13 +59341,13 @@
         <v>0.88</v>
       </c>
       <c r="AR270" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AS270" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AU270" t="n">
         <v>6</v>
@@ -59559,13 +59559,13 @@
         <v>1.31</v>
       </c>
       <c r="AR271" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AS271" t="n">
         <v>1.27</v>
       </c>
       <c r="AT271" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AU271" t="n">
         <v>3</v>
@@ -59780,10 +59780,10 @@
         <v>1.56</v>
       </c>
       <c r="AS272" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT272" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU272" t="n">
         <v>1</v>
@@ -59998,10 +59998,10 @@
         <v>1.32</v>
       </c>
       <c r="AS273" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AT273" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AU273" t="n">
         <v>5</v>
@@ -60216,10 +60216,10 @@
         <v>1.5</v>
       </c>
       <c r="AS274" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT274" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AU274" t="n">
         <v>7</v>
@@ -60431,13 +60431,13 @@
         <v>0.73</v>
       </c>
       <c r="AR275" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS275" t="n">
         <v>1.05</v>
       </c>
       <c r="AT275" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AU275" t="n">
         <v>5</v>
@@ -60646,16 +60646,16 @@
         <v>1.07</v>
       </c>
       <c r="AQ276" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR276" t="n">
         <v>1.45</v>
       </c>
       <c r="AS276" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT276" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AU276" t="n">
         <v>4</v>
@@ -60995,7 +60995,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>['14', '90+7']</t>
+          <t>['14', '90+8']</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
@@ -61190,7 +61190,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="I279" t="n">
@@ -61294,22 +61294,22 @@
         <v>2</v>
       </c>
       <c r="AO279" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AP279" t="n">
         <v>2</v>
       </c>
       <c r="AQ279" t="n">
-        <v>3</v>
+        <v>1.31</v>
       </c>
       <c r="AR279" t="n">
         <v>1.52</v>
       </c>
       <c r="AS279" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT279" t="n">
-        <v>1.52</v>
+        <v>2.53</v>
       </c>
       <c r="AU279" t="n">
         <v>2</v>
@@ -61521,13 +61521,13 @@
         <v>0.73</v>
       </c>
       <c r="AR280" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AS280" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AT280" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="AU280" t="n">
         <v>4</v>
@@ -61739,13 +61739,13 @@
         <v>0.93</v>
       </c>
       <c r="AR281" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AS281" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AT281" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AU281" t="n">
         <v>6</v>
@@ -61957,13 +61957,13 @@
         <v>0.87</v>
       </c>
       <c r="AR282" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AS282" t="n">
         <v>1.34</v>
       </c>
       <c r="AT282" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AU282" t="n">
         <v>3</v>
@@ -62178,10 +62178,10 @@
         <v>1.81</v>
       </c>
       <c r="AS283" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AT283" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AU283" t="n">
         <v>5</v>
@@ -62393,13 +62393,13 @@
         <v>0.88</v>
       </c>
       <c r="AR284" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AS284" t="n">
         <v>1.07</v>
       </c>
       <c r="AT284" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AU284" t="n">
         <v>5</v>
@@ -62605,7 +62605,7 @@
         <v>0.64</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ285" t="n">
         <v>0.75</v>
@@ -62614,10 +62614,10 @@
         <v>1.35</v>
       </c>
       <c r="AS285" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AT285" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="AU285" t="n">
         <v>7</v>
@@ -63047,13 +63047,13 @@
         <v>1.25</v>
       </c>
       <c r="AR287" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AS287" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AT287" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AU287" t="n">
         <v>6</v>
@@ -63265,13 +63265,13 @@
         <v>1.31</v>
       </c>
       <c r="AR288" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AS288" t="n">
         <v>1.23</v>
       </c>
       <c r="AT288" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="AU288" t="n">
         <v>3</v>
@@ -63701,13 +63701,13 @@
         <v>1.6</v>
       </c>
       <c r="AR290" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AS290" t="n">
         <v>1.16</v>
       </c>
       <c r="AT290" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AU290" t="n">
         <v>6</v>
@@ -63922,10 +63922,10 @@
         <v>1.66</v>
       </c>
       <c r="AS291" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT291" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AU291" t="n">
         <v>0</v>
@@ -64346,13 +64346,13 @@
         <v>1.79</v>
       </c>
       <c r="AO293" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AP293" t="n">
         <v>1.73</v>
       </c>
       <c r="AQ293" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR293" t="n">
         <v>1.52</v>
@@ -64573,13 +64573,13 @@
         <v>0.47</v>
       </c>
       <c r="AR294" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS294" t="n">
         <v>0.92</v>
       </c>
       <c r="AT294" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AU294" t="n">
         <v>5</v>
@@ -65009,13 +65009,13 @@
         <v>0.93</v>
       </c>
       <c r="AR296" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AS296" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT296" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AU296" t="n">
         <v>5</v>
@@ -65230,10 +65230,10 @@
         <v>1.52</v>
       </c>
       <c r="AS297" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT297" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AU297" t="n">
         <v>7</v>
@@ -65448,10 +65448,10 @@
         <v>1.77</v>
       </c>
       <c r="AS298" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT298" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AU298" t="n">
         <v>2</v>
@@ -65666,10 +65666,10 @@
         <v>1.34</v>
       </c>
       <c r="AS299" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AT299" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AU299" t="n">
         <v>2</v>
@@ -65881,13 +65881,13 @@
         <v>1.33</v>
       </c>
       <c r="AR300" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AS300" t="n">
         <v>1.06</v>
       </c>
       <c r="AT300" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AU300" t="n">
         <v>5</v>
@@ -66096,16 +66096,16 @@
         <v>1.94</v>
       </c>
       <c r="AQ301" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AR301" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AS301" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AT301" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AU301" t="n">
         <v>7</v>
@@ -66308,22 +66308,22 @@
         <v>1.4</v>
       </c>
       <c r="AO302" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AP302" t="n">
         <v>1.5</v>
       </c>
       <c r="AQ302" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR302" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AS302" t="n">
         <v>1</v>
       </c>
       <c r="AT302" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AU302" t="n">
         <v>5</v>
@@ -66538,10 +66538,10 @@
         <v>1.59</v>
       </c>
       <c r="AS303" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AT303" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AU303" t="n">
         <v>5</v>
@@ -66756,10 +66756,10 @@
         <v>1.29</v>
       </c>
       <c r="AS304" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT304" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AU304" t="n">
         <v>5</v>
@@ -66971,13 +66971,13 @@
         <v>1.25</v>
       </c>
       <c r="AR305" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AS305" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AT305" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AU305" t="n">
         <v>6</v>
@@ -67189,13 +67189,13 @@
         <v>1.25</v>
       </c>
       <c r="AR306" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AS306" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AT306" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AU306" t="n">
         <v>6</v>
@@ -67204,13 +67204,13 @@
         <v>5</v>
       </c>
       <c r="AW306" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX306" t="n">
         <v>2</v>
       </c>
       <c r="AY306" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ306" t="n">
         <v>7</v>
@@ -67407,13 +67407,13 @@
         <v>0.44</v>
       </c>
       <c r="AR307" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AS307" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AT307" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AU307" t="n">
         <v>8</v>
@@ -67625,13 +67625,13 @@
         <v>0.88</v>
       </c>
       <c r="AR308" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AS308" t="n">
         <v>1.02</v>
       </c>
       <c r="AT308" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AU308" t="n">
         <v>4</v>
@@ -67843,13 +67843,13 @@
         <v>1.31</v>
       </c>
       <c r="AR309" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AS309" t="n">
         <v>1.28</v>
       </c>
       <c r="AT309" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AU309" t="n">
         <v>2</v>
@@ -68064,10 +68064,10 @@
         <v>1.56</v>
       </c>
       <c r="AS310" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AT310" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AU310" t="n">
         <v>6</v>
@@ -68134,6 +68134,224 @@
       </c>
       <c r="BP310" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>7841335</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>45939.89930555555</v>
+      </c>
+      <c r="F311" t="n">
+        <v>31</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>1</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>1</v>
+      </c>
+      <c r="L311" t="n">
+        <v>2</v>
+      </c>
+      <c r="M311" t="n">
+        <v>1</v>
+      </c>
+      <c r="N311" t="n">
+        <v>3</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>['45+1', '73']</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R311" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S311" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T311" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U311" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V311" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W311" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X311" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ311" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS311" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT311" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU311" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV311" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY311" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA311" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB311" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC311" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD311" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BE311" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF311" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG311" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH311" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="BI311" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ311" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK311" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL311" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM311" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN311" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO311" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP311" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP311"/>
+  <dimension ref="A1:BP312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4402,7 +4402,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.75</v>
@@ -8326,7 +8326,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.44</v>
@@ -11596,7 +11596,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.88</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.25</v>
@@ -17700,7 +17700,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -21188,7 +21188,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR95" t="n">
         <v>1.75</v>
@@ -21403,7 +21403,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.88</v>
@@ -25330,7 +25330,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.87</v>
@@ -30341,7 +30341,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.33</v>
@@ -30780,7 +30780,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -34486,7 +34486,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR156" t="n">
         <v>1.71</v>
@@ -35137,7 +35137,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.93</v>
@@ -38407,7 +38407,7 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.6</v>
@@ -39064,7 +39064,7 @@
         <v>2</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR177" t="n">
         <v>1.79</v>
@@ -43206,7 +43206,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -44075,7 +44075,7 @@
         <v>0.78</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.93</v>
@@ -47348,7 +47348,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR215" t="n">
         <v>1.54</v>
@@ -48435,7 +48435,7 @@
         <v>1.2</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.31</v>
@@ -48871,7 +48871,7 @@
         <v>1.09</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.31</v>
@@ -54542,7 +54542,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR248" t="n">
         <v>1.67</v>
@@ -55632,7 +55632,7 @@
         <v>2</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR253" t="n">
         <v>1.45</v>
@@ -56501,7 +56501,7 @@
         <v>0.92</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ257" t="n">
         <v>0.73</v>
@@ -59992,7 +59992,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR273" t="n">
         <v>1.32</v>
@@ -60643,7 +60643,7 @@
         <v>1.54</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ276" t="n">
         <v>1.44</v>
@@ -64567,7 +64567,7 @@
         <v>0.43</v>
       </c>
       <c r="AP294" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ294" t="n">
         <v>0.47</v>
@@ -65442,7 +65442,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ298" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR298" t="n">
         <v>1.77</v>
@@ -68352,6 +68352,224 @@
       </c>
       <c r="BP311" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>7841349</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>45941.66666666666</v>
+      </c>
+      <c r="F312" t="n">
+        <v>32</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>1</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>1</v>
+      </c>
+      <c r="L312" t="n">
+        <v>1</v>
+      </c>
+      <c r="M312" t="n">
+        <v>1</v>
+      </c>
+      <c r="N312" t="n">
+        <v>2</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R312" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S312" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T312" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U312" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V312" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="W312" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X312" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK312" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AQ312" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR312" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS312" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT312" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV312" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW312" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX312" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY312" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ312" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA312" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB312" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC312" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD312" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE312" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF312" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG312" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH312" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI312" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ312" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK312" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL312" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM312" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN312" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO312" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP312" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="375">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -862,6 +862,12 @@
     <t>['5']</t>
   </si>
   <si>
+    <t>['47', '76', '86']</t>
+  </si>
+  <si>
+    <t>['12', '45+4']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1130,6 +1136,9 @@
   </si>
   <si>
     <t>['65']</t>
+  </si>
+  <si>
+    <t>['45', '53']</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP316"/>
+  <dimension ref="A1:BP318"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1953,7 +1962,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2159,7 +2168,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2649,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ6">
         <v>1.31</v>
@@ -2983,7 +2992,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3267,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ9">
         <v>0.88</v>
@@ -3601,7 +3610,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -4013,7 +4022,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -4219,7 +4228,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -5043,7 +5052,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -5249,7 +5258,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5742,7 +5751,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ21">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6073,7 +6082,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6691,7 +6700,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7181,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ28">
         <v>0.44</v>
@@ -7309,7 +7318,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7596,7 +7605,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ30">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR30">
         <v>2.72</v>
@@ -7721,7 +7730,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8957,7 +8966,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9859,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ41">
         <v>1.13</v>
@@ -9987,7 +9996,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -11223,7 +11232,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11304,7 +11313,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR48">
         <v>1.9</v>
@@ -11429,7 +11438,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -12537,7 +12546,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ54">
         <v>0.88</v>
@@ -13077,7 +13086,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13773,7 +13782,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ60">
         <v>0.88</v>
@@ -14394,7 +14403,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ63">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR63">
         <v>1.5</v>
@@ -14931,7 +14940,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15137,7 +15146,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -15343,7 +15352,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15961,7 +15970,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16991,7 +17000,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17481,7 +17490,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ78">
         <v>1.31</v>
@@ -17893,7 +17902,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ80">
         <v>0.44</v>
@@ -18845,7 +18854,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -20081,7 +20090,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -20162,7 +20171,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ91">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20287,7 +20296,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20493,7 +20502,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20905,7 +20914,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -21111,7 +21120,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21317,7 +21326,7 @@
         <v>160</v>
       </c>
       <c r="P97" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q97">
         <v>3.24</v>
@@ -21601,7 +21610,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ98">
         <v>1.33</v>
@@ -21807,7 +21816,7 @@
         <v>0</v>
       </c>
       <c r="AP99">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ99">
         <v>0.6899999999999999</v>
@@ -22965,7 +22974,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23664,7 +23673,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR108">
         <v>1.49</v>
@@ -24407,7 +24416,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24897,7 +24906,7 @@
         <v>2</v>
       </c>
       <c r="AP114">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ114">
         <v>1.31</v>
@@ -25231,7 +25240,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25849,7 +25858,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -26261,7 +26270,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26339,7 +26348,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ121">
         <v>0.93</v>
@@ -26879,7 +26888,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -28321,7 +28330,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28527,7 +28536,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28605,7 +28614,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ132">
         <v>0.6899999999999999</v>
@@ -28733,7 +28742,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -29020,7 +29029,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ134">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR134">
         <v>1.6</v>
@@ -29145,7 +29154,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29429,7 +29438,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ136">
         <v>0.8100000000000001</v>
@@ -29557,7 +29566,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29969,7 +29978,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q139">
         <v>3.02</v>
@@ -31617,7 +31626,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -32029,7 +32038,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -32725,7 +32734,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ152">
         <v>1.5</v>
@@ -33265,7 +33274,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33346,7 +33355,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ155">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR155">
         <v>1.69</v>
@@ -35119,7 +35128,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -35325,7 +35334,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35531,7 +35540,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35737,7 +35746,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -36149,7 +36158,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -36227,7 +36236,7 @@
         <v>1.43</v>
       </c>
       <c r="AP169">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ169">
         <v>1.44</v>
@@ -36848,7 +36857,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ172">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR172">
         <v>1.66</v>
@@ -37179,7 +37188,7 @@
         <v>199</v>
       </c>
       <c r="P174" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37591,7 +37600,7 @@
         <v>207</v>
       </c>
       <c r="P176" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q176">
         <v>2.8</v>
@@ -38003,7 +38012,7 @@
         <v>209</v>
       </c>
       <c r="P178" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q178">
         <v>2.93</v>
@@ -38209,7 +38218,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q179">
         <v>3.1</v>
@@ -38415,7 +38424,7 @@
         <v>97</v>
       </c>
       <c r="P180" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q180">
         <v>3.55</v>
@@ -39111,7 +39120,7 @@
         <v>1.25</v>
       </c>
       <c r="AP183">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ183">
         <v>1.25</v>
@@ -39317,7 +39326,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ184">
         <v>0.88</v>
@@ -39651,7 +39660,7 @@
         <v>214</v>
       </c>
       <c r="P186" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q186">
         <v>3.34</v>
@@ -40269,7 +40278,7 @@
         <v>111</v>
       </c>
       <c r="P189" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q189">
         <v>2.91</v>
@@ -40887,7 +40896,7 @@
         <v>98</v>
       </c>
       <c r="P192" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q192">
         <v>3.78</v>
@@ -41093,7 +41102,7 @@
         <v>97</v>
       </c>
       <c r="P193" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q193">
         <v>2.45</v>
@@ -41711,7 +41720,7 @@
         <v>218</v>
       </c>
       <c r="P196" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q196">
         <v>4.02</v>
@@ -41917,7 +41926,7 @@
         <v>219</v>
       </c>
       <c r="P197" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q197">
         <v>2.55</v>
@@ -42123,7 +42132,7 @@
         <v>111</v>
       </c>
       <c r="P198" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q198">
         <v>2.75</v>
@@ -42329,7 +42338,7 @@
         <v>163</v>
       </c>
       <c r="P199" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q199">
         <v>2.12</v>
@@ -42616,7 +42625,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ200">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR200">
         <v>1.37</v>
@@ -43565,7 +43574,7 @@
         <v>223</v>
       </c>
       <c r="P205" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q205">
         <v>2.2</v>
@@ -43849,7 +43858,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ206">
         <v>1.25</v>
@@ -44389,7 +44398,7 @@
         <v>226</v>
       </c>
       <c r="P209" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q209">
         <v>3.24</v>
@@ -44879,7 +44888,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ211">
         <v>1.25</v>
@@ -45007,7 +45016,7 @@
         <v>168</v>
       </c>
       <c r="P212" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q212">
         <v>3.2</v>
@@ -45213,7 +45222,7 @@
         <v>228</v>
       </c>
       <c r="P213" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q213">
         <v>3.44</v>
@@ -45419,7 +45428,7 @@
         <v>229</v>
       </c>
       <c r="P214" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q214">
         <v>2.3</v>
@@ -46243,7 +46252,7 @@
         <v>210</v>
       </c>
       <c r="P218" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q218">
         <v>2.33</v>
@@ -46527,7 +46536,7 @@
         <v>0.55</v>
       </c>
       <c r="AP219">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ219">
         <v>0.75</v>
@@ -47067,7 +47076,7 @@
         <v>97</v>
       </c>
       <c r="P222" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q222">
         <v>2.6</v>
@@ -47891,7 +47900,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q226">
         <v>3.1</v>
@@ -47969,7 +47978,7 @@
         <v>1.1</v>
       </c>
       <c r="AP226">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ226">
         <v>1.44</v>
@@ -48097,7 +48106,7 @@
         <v>229</v>
       </c>
       <c r="P227" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q227">
         <v>2.8</v>
@@ -48509,7 +48518,7 @@
         <v>206</v>
       </c>
       <c r="P229" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q229">
         <v>2.7</v>
@@ -48590,7 +48599,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ229">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR229">
         <v>1.56</v>
@@ -48921,7 +48930,7 @@
         <v>235</v>
       </c>
       <c r="P231" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q231">
         <v>2.38</v>
@@ -49617,7 +49626,7 @@
         <v>0.92</v>
       </c>
       <c r="AP234">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ234">
         <v>0.88</v>
@@ -49745,7 +49754,7 @@
         <v>238</v>
       </c>
       <c r="P235" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q235">
         <v>2.05</v>
@@ -49951,7 +49960,7 @@
         <v>239</v>
       </c>
       <c r="P236" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q236">
         <v>2.58</v>
@@ -50363,7 +50372,7 @@
         <v>97</v>
       </c>
       <c r="P238" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q238">
         <v>3</v>
@@ -50441,7 +50450,7 @@
         <v>1.18</v>
       </c>
       <c r="AP238">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ238">
         <v>1.25</v>
@@ -50569,7 +50578,7 @@
         <v>241</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q239">
         <v>2.6</v>
@@ -50775,7 +50784,7 @@
         <v>242</v>
       </c>
       <c r="P240" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -51187,7 +51196,7 @@
         <v>170</v>
       </c>
       <c r="P242" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51393,7 +51402,7 @@
         <v>98</v>
       </c>
       <c r="P243" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q243">
         <v>2.73</v>
@@ -51805,7 +51814,7 @@
         <v>245</v>
       </c>
       <c r="P245" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q245">
         <v>5.08</v>
@@ -52423,7 +52432,7 @@
         <v>247</v>
       </c>
       <c r="P248" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q248">
         <v>2.68</v>
@@ -52629,7 +52638,7 @@
         <v>248</v>
       </c>
       <c r="P249" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q249">
         <v>2.75</v>
@@ -52710,7 +52719,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ249">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR249">
         <v>1.76</v>
@@ -53325,7 +53334,7 @@
         <v>1.33</v>
       </c>
       <c r="AP252">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ252">
         <v>1.31</v>
@@ -54483,7 +54492,7 @@
         <v>121</v>
       </c>
       <c r="P258" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q258">
         <v>3.7</v>
@@ -54767,7 +54776,7 @@
         <v>0.5</v>
       </c>
       <c r="AP259">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ259">
         <v>0.44</v>
@@ -55101,7 +55110,7 @@
         <v>253</v>
       </c>
       <c r="P261" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q261">
         <v>3.3</v>
@@ -56131,7 +56140,7 @@
         <v>255</v>
       </c>
       <c r="P266" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q266">
         <v>2.3</v>
@@ -56418,7 +56427,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ267">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR267">
         <v>1.35</v>
@@ -57779,7 +57788,7 @@
         <v>257</v>
       </c>
       <c r="P274" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q274">
         <v>3.3</v>
@@ -57985,7 +57994,7 @@
         <v>258</v>
       </c>
       <c r="P275" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q275">
         <v>2.24</v>
@@ -58063,7 +58072,7 @@
         <v>0.85</v>
       </c>
       <c r="AP275">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ275">
         <v>0.73</v>
@@ -58191,7 +58200,7 @@
         <v>97</v>
       </c>
       <c r="P276" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q276">
         <v>4.35</v>
@@ -58681,7 +58690,7 @@
         <v>1.31</v>
       </c>
       <c r="AP278">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ278">
         <v>1.33</v>
@@ -58809,7 +58818,7 @@
         <v>97</v>
       </c>
       <c r="P279" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q279">
         <v>2.85</v>
@@ -59633,7 +59642,7 @@
         <v>262</v>
       </c>
       <c r="P283" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q283">
         <v>2.11</v>
@@ -60045,7 +60054,7 @@
         <v>264</v>
       </c>
       <c r="P285" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q285">
         <v>3.19</v>
@@ -60251,7 +60260,7 @@
         <v>265</v>
       </c>
       <c r="P286" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q286">
         <v>3</v>
@@ -60663,7 +60672,7 @@
         <v>267</v>
       </c>
       <c r="P288" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q288">
         <v>3.48</v>
@@ -61075,7 +61084,7 @@
         <v>97</v>
       </c>
       <c r="P290" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q290">
         <v>3.04</v>
@@ -61362,7 +61371,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ291">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR291">
         <v>1.66</v>
@@ -61487,7 +61496,7 @@
         <v>269</v>
       </c>
       <c r="P292" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q292">
         <v>3.62</v>
@@ -61899,7 +61908,7 @@
         <v>270</v>
       </c>
       <c r="P294" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62389,7 +62398,7 @@
         <v>1</v>
       </c>
       <c r="AP296">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ296">
         <v>0.93</v>
@@ -62801,7 +62810,7 @@
         <v>1.36</v>
       </c>
       <c r="AP298">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ298">
         <v>1.31</v>
@@ -62929,7 +62938,7 @@
         <v>133</v>
       </c>
       <c r="P299" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63547,7 +63556,7 @@
         <v>274</v>
       </c>
       <c r="P302" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q302">
         <v>3.61</v>
@@ -63753,7 +63762,7 @@
         <v>236</v>
       </c>
       <c r="P303" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q303">
         <v>2.64</v>
@@ -64371,7 +64380,7 @@
         <v>229</v>
       </c>
       <c r="P306" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q306">
         <v>2.62</v>
@@ -64783,7 +64792,7 @@
         <v>105</v>
       </c>
       <c r="P308" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q308">
         <v>2.6</v>
@@ -65276,7 +65285,7 @@
         <v>2</v>
       </c>
       <c r="AQ310">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR310">
         <v>1.56</v>
@@ -65401,7 +65410,7 @@
         <v>278</v>
       </c>
       <c r="P311" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q311">
         <v>3.95</v>
@@ -65706,13 +65715,13 @@
         <v>6</v>
       </c>
       <c r="AW312">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX312">
         <v>18</v>
       </c>
       <c r="AY312">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ312">
         <v>24</v>
@@ -66130,13 +66139,13 @@
         <v>10</v>
       </c>
       <c r="BA314">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB314">
         <v>1</v>
       </c>
       <c r="BC314">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD314">
         <v>1.55</v>
@@ -66225,7 +66234,7 @@
         <v>280</v>
       </c>
       <c r="P315" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q315">
         <v>2.68</v>
@@ -66588,6 +66597,418 @@
       </c>
       <c r="BP316">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="317" spans="1:68">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>7841351</v>
+      </c>
+      <c r="C317" t="s">
+        <v>68</v>
+      </c>
+      <c r="D317" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="2">
+        <v>45943.79166666666</v>
+      </c>
+      <c r="F317">
+        <v>32</v>
+      </c>
+      <c r="G317" t="s">
+        <v>77</v>
+      </c>
+      <c r="H317" t="s">
+        <v>79</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>0</v>
+      </c>
+      <c r="L317">
+        <v>3</v>
+      </c>
+      <c r="M317">
+        <v>0</v>
+      </c>
+      <c r="N317">
+        <v>3</v>
+      </c>
+      <c r="O317" t="s">
+        <v>282</v>
+      </c>
+      <c r="P317" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q317">
+        <v>3.26</v>
+      </c>
+      <c r="R317">
+        <v>1.93</v>
+      </c>
+      <c r="S317">
+        <v>3.5</v>
+      </c>
+      <c r="T317">
+        <v>1.48</v>
+      </c>
+      <c r="U317">
+        <v>2.44</v>
+      </c>
+      <c r="V317">
+        <v>3.35</v>
+      </c>
+      <c r="W317">
+        <v>1.27</v>
+      </c>
+      <c r="X317">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y317">
+        <v>1.01</v>
+      </c>
+      <c r="Z317">
+        <v>2.6</v>
+      </c>
+      <c r="AA317">
+        <v>2.9</v>
+      </c>
+      <c r="AB317">
+        <v>2.75</v>
+      </c>
+      <c r="AC317">
+        <v>1.04</v>
+      </c>
+      <c r="AD317">
+        <v>7.1</v>
+      </c>
+      <c r="AE317">
+        <v>1.4</v>
+      </c>
+      <c r="AF317">
+        <v>2.56</v>
+      </c>
+      <c r="AG317">
+        <v>2.38</v>
+      </c>
+      <c r="AH317">
+        <v>1.55</v>
+      </c>
+      <c r="AI317">
+        <v>1.97</v>
+      </c>
+      <c r="AJ317">
+        <v>1.75</v>
+      </c>
+      <c r="AK317">
+        <v>1.33</v>
+      </c>
+      <c r="AL317">
+        <v>1.3</v>
+      </c>
+      <c r="AM317">
+        <v>1.45</v>
+      </c>
+      <c r="AN317">
+        <v>1.6</v>
+      </c>
+      <c r="AO317">
+        <v>0.93</v>
+      </c>
+      <c r="AP317">
+        <v>1.69</v>
+      </c>
+      <c r="AQ317">
+        <v>0.88</v>
+      </c>
+      <c r="AR317">
+        <v>1.72</v>
+      </c>
+      <c r="AS317">
+        <v>1.16</v>
+      </c>
+      <c r="AT317">
+        <v>2.88</v>
+      </c>
+      <c r="AU317">
+        <v>8</v>
+      </c>
+      <c r="AV317">
+        <v>5</v>
+      </c>
+      <c r="AW317">
+        <v>4</v>
+      </c>
+      <c r="AX317">
+        <v>12</v>
+      </c>
+      <c r="AY317">
+        <v>12</v>
+      </c>
+      <c r="AZ317">
+        <v>17</v>
+      </c>
+      <c r="BA317">
+        <v>3</v>
+      </c>
+      <c r="BB317">
+        <v>2</v>
+      </c>
+      <c r="BC317">
+        <v>5</v>
+      </c>
+      <c r="BD317">
+        <v>1.95</v>
+      </c>
+      <c r="BE317">
+        <v>7.37</v>
+      </c>
+      <c r="BF317">
+        <v>2.48</v>
+      </c>
+      <c r="BG317">
+        <v>1.17</v>
+      </c>
+      <c r="BH317">
+        <v>3.9</v>
+      </c>
+      <c r="BI317">
+        <v>1.38</v>
+      </c>
+      <c r="BJ317">
+        <v>2.69</v>
+      </c>
+      <c r="BK317">
+        <v>1.7</v>
+      </c>
+      <c r="BL317">
+        <v>2.05</v>
+      </c>
+      <c r="BM317">
+        <v>2.09</v>
+      </c>
+      <c r="BN317">
+        <v>1.65</v>
+      </c>
+      <c r="BO317">
+        <v>2.72</v>
+      </c>
+      <c r="BP317">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="318" spans="1:68">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>7841348</v>
+      </c>
+      <c r="C318" t="s">
+        <v>68</v>
+      </c>
+      <c r="D318" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="2">
+        <v>45943.89583333334</v>
+      </c>
+      <c r="F318">
+        <v>32</v>
+      </c>
+      <c r="G318" t="s">
+        <v>74</v>
+      </c>
+      <c r="H318" t="s">
+        <v>76</v>
+      </c>
+      <c r="I318">
+        <v>2</v>
+      </c>
+      <c r="J318">
+        <v>1</v>
+      </c>
+      <c r="K318">
+        <v>3</v>
+      </c>
+      <c r="L318">
+        <v>2</v>
+      </c>
+      <c r="M318">
+        <v>2</v>
+      </c>
+      <c r="N318">
+        <v>4</v>
+      </c>
+      <c r="O318" t="s">
+        <v>283</v>
+      </c>
+      <c r="P318" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q318">
+        <v>2.11</v>
+      </c>
+      <c r="R318">
+        <v>2.14</v>
+      </c>
+      <c r="S318">
+        <v>6.3</v>
+      </c>
+      <c r="T318">
+        <v>1.38</v>
+      </c>
+      <c r="U318">
+        <v>2.77</v>
+      </c>
+      <c r="V318">
+        <v>2.77</v>
+      </c>
+      <c r="W318">
+        <v>1.38</v>
+      </c>
+      <c r="X318">
+        <v>7.1</v>
+      </c>
+      <c r="Y318">
+        <v>1.04</v>
+      </c>
+      <c r="Z318">
+        <v>1.59</v>
+      </c>
+      <c r="AA318">
+        <v>3.6</v>
+      </c>
+      <c r="AB318">
+        <v>5.3</v>
+      </c>
+      <c r="AC318">
+        <v>1.02</v>
+      </c>
+      <c r="AD318">
+        <v>9.85</v>
+      </c>
+      <c r="AE318">
+        <v>1.25</v>
+      </c>
+      <c r="AF318">
+        <v>3.28</v>
+      </c>
+      <c r="AG318">
+        <v>1.93</v>
+      </c>
+      <c r="AH318">
+        <v>1.83</v>
+      </c>
+      <c r="AI318">
+        <v>1.95</v>
+      </c>
+      <c r="AJ318">
+        <v>1.76</v>
+      </c>
+      <c r="AK318">
+        <v>1.23</v>
+      </c>
+      <c r="AL318">
+        <v>1.2</v>
+      </c>
+      <c r="AM318">
+        <v>2.36</v>
+      </c>
+      <c r="AN318">
+        <v>2.27</v>
+      </c>
+      <c r="AO318">
+        <v>1.13</v>
+      </c>
+      <c r="AP318">
+        <v>2.19</v>
+      </c>
+      <c r="AQ318">
+        <v>1.13</v>
+      </c>
+      <c r="AR318">
+        <v>1.74</v>
+      </c>
+      <c r="AS318">
+        <v>1.25</v>
+      </c>
+      <c r="AT318">
+        <v>2.99</v>
+      </c>
+      <c r="AU318">
+        <v>8</v>
+      </c>
+      <c r="AV318">
+        <v>6</v>
+      </c>
+      <c r="AW318">
+        <v>16</v>
+      </c>
+      <c r="AX318">
+        <v>13</v>
+      </c>
+      <c r="AY318">
+        <v>24</v>
+      </c>
+      <c r="AZ318">
+        <v>19</v>
+      </c>
+      <c r="BA318">
+        <v>8</v>
+      </c>
+      <c r="BB318">
+        <v>6</v>
+      </c>
+      <c r="BC318">
+        <v>14</v>
+      </c>
+      <c r="BD318">
+        <v>1.23</v>
+      </c>
+      <c r="BE318">
+        <v>10.6</v>
+      </c>
+      <c r="BF318">
+        <v>6.01</v>
+      </c>
+      <c r="BG318">
+        <v>1.11</v>
+      </c>
+      <c r="BH318">
+        <v>4.64</v>
+      </c>
+      <c r="BI318">
+        <v>1.29</v>
+      </c>
+      <c r="BJ318">
+        <v>3.08</v>
+      </c>
+      <c r="BK318">
+        <v>1.69</v>
+      </c>
+      <c r="BL318">
+        <v>2.27</v>
+      </c>
+      <c r="BM318">
+        <v>1.89</v>
+      </c>
+      <c r="BN318">
+        <v>1.81</v>
+      </c>
+      <c r="BO318">
+        <v>2.39</v>
+      </c>
+      <c r="BP318">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="377">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -868,6 +868,9 @@
     <t>['12', '45+4']</t>
   </si>
   <si>
+    <t>['52', '63']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1139,6 +1142,9 @@
   </si>
   <si>
     <t>['45', '53']</t>
+  </si>
+  <si>
+    <t>['17', '49', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP318"/>
+  <dimension ref="A1:BP321"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1962,7 +1968,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2040,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ3">
         <v>1.44</v>
@@ -2168,7 +2174,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2867,7 +2873,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ7">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2992,7 +2998,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3073,7 +3079,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3610,7 +3616,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3894,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ12">
         <v>1.31</v>
@@ -4022,7 +4028,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -4103,7 +4109,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ13">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4228,7 +4234,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4306,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ14">
         <v>1.5</v>
@@ -5052,7 +5058,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -5258,7 +5264,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -6082,7 +6088,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6160,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ23">
         <v>1.31</v>
@@ -6700,7 +6706,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -7318,7 +7324,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7399,7 +7405,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR29">
         <v>1.39</v>
@@ -7730,7 +7736,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8223,7 +8229,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ33">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
         <v>1.46</v>
@@ -8426,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ34">
         <v>1.25</v>
@@ -8632,7 +8638,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ35">
         <v>0.75</v>
@@ -8966,7 +8972,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9047,7 +9053,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ37">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR37">
         <v>2.28</v>
@@ -9996,7 +10002,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10283,7 +10289,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR43">
         <v>2.02</v>
@@ -11232,7 +11238,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11438,7 +11444,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11516,7 +11522,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ49">
         <v>0.75</v>
@@ -12958,7 +12964,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ56">
         <v>1.31</v>
@@ -13086,7 +13092,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13164,10 +13170,10 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ57">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR57">
         <v>1.4</v>
@@ -13579,7 +13585,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ59">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR59">
         <v>1.44</v>
@@ -14194,7 +14200,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ62">
         <v>1.31</v>
@@ -14940,7 +14946,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15146,7 +15152,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -15352,7 +15358,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15970,7 +15976,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16257,7 +16263,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ72">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR72">
         <v>1.97</v>
@@ -16460,7 +16466,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ73">
         <v>0.88</v>
@@ -16669,7 +16675,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ74">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR74">
         <v>1.47</v>
@@ -17000,7 +17006,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17287,7 +17293,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR77">
         <v>1.46</v>
@@ -17696,7 +17702,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ79">
         <v>1.31</v>
@@ -18520,7 +18526,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ83">
         <v>1.25</v>
@@ -18854,7 +18860,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -20090,7 +20096,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -20296,7 +20302,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20377,7 +20383,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ92">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
         <v>1.81</v>
@@ -20502,7 +20508,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20789,7 +20795,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR94">
         <v>1.26</v>
@@ -20914,7 +20920,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -21120,7 +21126,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21326,7 +21332,7 @@
         <v>160</v>
       </c>
       <c r="P97" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q97">
         <v>3.24</v>
@@ -21613,7 +21619,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR98">
         <v>1.59</v>
@@ -22022,7 +22028,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ100">
         <v>0.44</v>
@@ -22228,7 +22234,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ101">
         <v>1.31</v>
@@ -22974,7 +22980,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23670,7 +23676,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ108">
         <v>0.88</v>
@@ -24416,7 +24422,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24700,10 +24706,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ113">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR113">
         <v>1.73</v>
@@ -25112,10 +25118,10 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ115">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25240,7 +25246,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25858,7 +25864,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -26142,7 +26148,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ120">
         <v>1.13</v>
@@ -26270,7 +26276,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26351,7 +26357,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ121">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -26888,7 +26894,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -28330,7 +28336,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28536,7 +28542,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28742,7 +28748,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28823,7 +28829,7 @@
         <v>2</v>
       </c>
       <c r="AQ133">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR133">
         <v>1.96</v>
@@ -29154,7 +29160,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29232,7 +29238,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ135">
         <v>1.5</v>
@@ -29566,7 +29572,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29647,7 +29653,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR137">
         <v>1.3</v>
@@ -29978,7 +29984,7 @@
         <v>188</v>
       </c>
       <c r="P139" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q139">
         <v>3.02</v>
@@ -30056,7 +30062,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ139">
         <v>1.31</v>
@@ -30262,7 +30268,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ140">
         <v>1.13</v>
@@ -30471,7 +30477,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ141">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR141">
         <v>1.65</v>
@@ -31626,7 +31632,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -32038,7 +32044,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -33274,7 +33280,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33352,7 +33358,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ155">
         <v>0.88</v>
@@ -33558,7 +33564,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ156">
         <v>1.31</v>
@@ -33970,10 +33976,10 @@
         <v>1</v>
       </c>
       <c r="AP158">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ158">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR158">
         <v>1.35</v>
@@ -34179,7 +34185,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ159">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR159">
         <v>1.43</v>
@@ -35128,7 +35134,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -35334,7 +35340,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35540,7 +35546,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35746,7 +35752,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -36158,7 +36164,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -36445,7 +36451,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ170">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR170">
         <v>1.36</v>
@@ -37060,7 +37066,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ173">
         <v>1.13</v>
@@ -37188,7 +37194,7 @@
         <v>199</v>
       </c>
       <c r="P174" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q174">
         <v>3.25</v>
@@ -37600,7 +37606,7 @@
         <v>207</v>
       </c>
       <c r="P176" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q176">
         <v>2.8</v>
@@ -37678,7 +37684,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ176">
         <v>0.44</v>
@@ -38012,7 +38018,7 @@
         <v>209</v>
       </c>
       <c r="P178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q178">
         <v>2.93</v>
@@ -38218,7 +38224,7 @@
         <v>210</v>
       </c>
       <c r="P179" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q179">
         <v>3.1</v>
@@ -38424,7 +38430,7 @@
         <v>97</v>
       </c>
       <c r="P180" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q180">
         <v>3.55</v>
@@ -38711,7 +38717,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ181">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR181">
         <v>1.18</v>
@@ -39660,7 +39666,7 @@
         <v>214</v>
       </c>
       <c r="P186" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q186">
         <v>3.34</v>
@@ -40153,7 +40159,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ188">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR188">
         <v>1.72</v>
@@ -40278,7 +40284,7 @@
         <v>111</v>
       </c>
       <c r="P189" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q189">
         <v>2.91</v>
@@ -40356,7 +40362,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ189">
         <v>1.25</v>
@@ -40771,7 +40777,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ191">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR191">
         <v>1.56</v>
@@ -40896,7 +40902,7 @@
         <v>98</v>
       </c>
       <c r="P192" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q192">
         <v>3.78</v>
@@ -41102,7 +41108,7 @@
         <v>97</v>
       </c>
       <c r="P193" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q193">
         <v>2.45</v>
@@ -41720,7 +41726,7 @@
         <v>218</v>
       </c>
       <c r="P196" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q196">
         <v>4.02</v>
@@ -41926,7 +41932,7 @@
         <v>219</v>
       </c>
       <c r="P197" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q197">
         <v>2.55</v>
@@ -42004,7 +42010,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ197">
         <v>0.75</v>
@@ -42132,7 +42138,7 @@
         <v>111</v>
       </c>
       <c r="P198" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q198">
         <v>2.75</v>
@@ -42213,7 +42219,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ198">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR198">
         <v>1.73</v>
@@ -42338,7 +42344,7 @@
         <v>163</v>
       </c>
       <c r="P199" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q199">
         <v>2.12</v>
@@ -42416,7 +42422,7 @@
         <v>1</v>
       </c>
       <c r="AP199">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ199">
         <v>0.88</v>
@@ -43449,7 +43455,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ204">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR204">
         <v>1.65</v>
@@ -43574,7 +43580,7 @@
         <v>223</v>
       </c>
       <c r="P205" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q205">
         <v>2.2</v>
@@ -44273,7 +44279,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ208">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR208">
         <v>1.71</v>
@@ -44398,7 +44404,7 @@
         <v>226</v>
       </c>
       <c r="P209" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q209">
         <v>3.24</v>
@@ -44682,7 +44688,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ210">
         <v>0.88</v>
@@ -45016,7 +45022,7 @@
         <v>168</v>
       </c>
       <c r="P212" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q212">
         <v>3.2</v>
@@ -45222,7 +45228,7 @@
         <v>228</v>
       </c>
       <c r="P213" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q213">
         <v>3.44</v>
@@ -45428,7 +45434,7 @@
         <v>229</v>
       </c>
       <c r="P214" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q214">
         <v>2.3</v>
@@ -45509,7 +45515,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ214">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR214">
         <v>1.29</v>
@@ -45918,7 +45924,7 @@
         <v>0.82</v>
       </c>
       <c r="AP216">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ216">
         <v>0.88</v>
@@ -46124,7 +46130,7 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ217">
         <v>0.88</v>
@@ -46252,7 +46258,7 @@
         <v>210</v>
       </c>
       <c r="P218" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q218">
         <v>2.33</v>
@@ -46951,7 +46957,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ221">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR221">
         <v>1.61</v>
@@ -47076,7 +47082,7 @@
         <v>97</v>
       </c>
       <c r="P222" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q222">
         <v>2.6</v>
@@ -47569,7 +47575,7 @@
         <v>2</v>
       </c>
       <c r="AQ224">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR224">
         <v>1.36</v>
@@ -47900,7 +47906,7 @@
         <v>97</v>
       </c>
       <c r="P226" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q226">
         <v>3.1</v>
@@ -48106,7 +48112,7 @@
         <v>229</v>
       </c>
       <c r="P227" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q227">
         <v>2.8</v>
@@ -48184,7 +48190,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ227">
         <v>0.8100000000000001</v>
@@ -48518,7 +48524,7 @@
         <v>206</v>
       </c>
       <c r="P229" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q229">
         <v>2.7</v>
@@ -48930,7 +48936,7 @@
         <v>235</v>
       </c>
       <c r="P231" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q231">
         <v>2.38</v>
@@ -49754,7 +49760,7 @@
         <v>238</v>
       </c>
       <c r="P235" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q235">
         <v>2.05</v>
@@ -49835,7 +49841,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ235">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR235">
         <v>1.6</v>
@@ -49960,7 +49966,7 @@
         <v>239</v>
       </c>
       <c r="P236" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q236">
         <v>2.58</v>
@@ -50038,7 +50044,7 @@
         <v>1</v>
       </c>
       <c r="AP236">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ236">
         <v>1.25</v>
@@ -50372,7 +50378,7 @@
         <v>97</v>
       </c>
       <c r="P238" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q238">
         <v>3</v>
@@ -50578,7 +50584,7 @@
         <v>241</v>
       </c>
       <c r="P239" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q239">
         <v>2.6</v>
@@ -50656,7 +50662,7 @@
         <v>0.92</v>
       </c>
       <c r="AP239">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ239">
         <v>0.88</v>
@@ -50784,7 +50790,7 @@
         <v>242</v>
       </c>
       <c r="P240" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -51071,7 +51077,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ241">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR241">
         <v>1.68</v>
@@ -51196,7 +51202,7 @@
         <v>170</v>
       </c>
       <c r="P242" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q242">
         <v>2.88</v>
@@ -51277,7 +51283,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ242">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR242">
         <v>1.39</v>
@@ -51402,7 +51408,7 @@
         <v>98</v>
       </c>
       <c r="P243" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q243">
         <v>2.73</v>
@@ -51480,7 +51486,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ243">
         <v>0.44</v>
@@ -51814,7 +51820,7 @@
         <v>245</v>
       </c>
       <c r="P245" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q245">
         <v>5.08</v>
@@ -52432,7 +52438,7 @@
         <v>247</v>
       </c>
       <c r="P248" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q248">
         <v>2.68</v>
@@ -52638,7 +52644,7 @@
         <v>248</v>
       </c>
       <c r="P249" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q249">
         <v>2.75</v>
@@ -53746,7 +53752,7 @@
         <v>0.58</v>
       </c>
       <c r="AP254">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ254">
         <v>0.6899999999999999</v>
@@ -53955,7 +53961,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ255">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR255">
         <v>1.46</v>
@@ -54367,7 +54373,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ257">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR257">
         <v>1.47</v>
@@ -54492,7 +54498,7 @@
         <v>121</v>
       </c>
       <c r="P258" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q258">
         <v>3.7</v>
@@ -54985,7 +54991,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ260">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR260">
         <v>1.73</v>
@@ -55110,7 +55116,7 @@
         <v>253</v>
       </c>
       <c r="P261" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q261">
         <v>3.3</v>
@@ -55188,7 +55194,7 @@
         <v>1.42</v>
       </c>
       <c r="AP261">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ261">
         <v>1.44</v>
@@ -56140,7 +56146,7 @@
         <v>255</v>
       </c>
       <c r="P266" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q266">
         <v>2.3</v>
@@ -57042,7 +57048,7 @@
         <v>0.92</v>
       </c>
       <c r="AP270">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ270">
         <v>0.88</v>
@@ -57454,7 +57460,7 @@
         <v>1.08</v>
       </c>
       <c r="AP272">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ272">
         <v>1.25</v>
@@ -57788,7 +57794,7 @@
         <v>257</v>
       </c>
       <c r="P274" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q274">
         <v>3.3</v>
@@ -57994,7 +58000,7 @@
         <v>258</v>
       </c>
       <c r="P275" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q275">
         <v>2.24</v>
@@ -58075,7 +58081,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ275">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR275">
         <v>1.75</v>
@@ -58200,7 +58206,7 @@
         <v>97</v>
       </c>
       <c r="P276" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q276">
         <v>4.35</v>
@@ -58693,7 +58699,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ278">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR278">
         <v>1.74</v>
@@ -58818,7 +58824,7 @@
         <v>97</v>
       </c>
       <c r="P279" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q279">
         <v>2.85</v>
@@ -59308,10 +59314,10 @@
         <v>0.85</v>
       </c>
       <c r="AP281">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ281">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR281">
         <v>1.52</v>
@@ -59514,7 +59520,7 @@
         <v>0.93</v>
       </c>
       <c r="AP282">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ282">
         <v>0.8100000000000001</v>
@@ -59642,7 +59648,7 @@
         <v>262</v>
       </c>
       <c r="P283" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q283">
         <v>2.11</v>
@@ -60054,7 +60060,7 @@
         <v>264</v>
       </c>
       <c r="P285" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q285">
         <v>3.19</v>
@@ -60260,7 +60266,7 @@
         <v>265</v>
       </c>
       <c r="P286" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q286">
         <v>3</v>
@@ -60672,7 +60678,7 @@
         <v>267</v>
       </c>
       <c r="P288" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q288">
         <v>3.48</v>
@@ -61084,7 +61090,7 @@
         <v>97</v>
       </c>
       <c r="P290" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q290">
         <v>3.04</v>
@@ -61496,7 +61502,7 @@
         <v>269</v>
       </c>
       <c r="P292" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q292">
         <v>3.62</v>
@@ -61574,7 +61580,7 @@
         <v>0.87</v>
       </c>
       <c r="AP292">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AQ292">
         <v>0.88</v>
@@ -61908,7 +61914,7 @@
         <v>270</v>
       </c>
       <c r="P294" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62195,7 +62201,7 @@
         <v>2</v>
       </c>
       <c r="AQ295">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR295">
         <v>1.5</v>
@@ -62401,7 +62407,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ296">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR296">
         <v>1.77</v>
@@ -62604,7 +62610,7 @@
         <v>1.21</v>
       </c>
       <c r="AP297">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AQ297">
         <v>1.25</v>
@@ -62938,7 +62944,7 @@
         <v>133</v>
       </c>
       <c r="P299" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63225,7 +63231,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ300">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR300">
         <v>1.53</v>
@@ -63556,7 +63562,7 @@
         <v>274</v>
       </c>
       <c r="P302" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q302">
         <v>3.61</v>
@@ -63762,7 +63768,7 @@
         <v>236</v>
       </c>
       <c r="P303" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q303">
         <v>2.64</v>
@@ -64380,7 +64386,7 @@
         <v>229</v>
       </c>
       <c r="P306" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q306">
         <v>2.62</v>
@@ -64792,7 +64798,7 @@
         <v>105</v>
       </c>
       <c r="P308" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q308">
         <v>2.6</v>
@@ -65410,7 +65416,7 @@
         <v>278</v>
       </c>
       <c r="P311" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q311">
         <v>3.95</v>
@@ -66234,7 +66240,7 @@
         <v>280</v>
       </c>
       <c r="P315" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q315">
         <v>2.68</v>
@@ -66852,7 +66858,7 @@
         <v>283</v>
       </c>
       <c r="P318" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q318">
         <v>2.11</v>
@@ -67009,6 +67015,624 @@
       </c>
       <c r="BP318">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="319" spans="1:68">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>7841345</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="2">
+        <v>45944.8125</v>
+      </c>
+      <c r="F319">
+        <v>32</v>
+      </c>
+      <c r="G319" t="s">
+        <v>71</v>
+      </c>
+      <c r="H319" t="s">
+        <v>88</v>
+      </c>
+      <c r="I319">
+        <v>0</v>
+      </c>
+      <c r="J319">
+        <v>1</v>
+      </c>
+      <c r="K319">
+        <v>1</v>
+      </c>
+      <c r="L319">
+        <v>2</v>
+      </c>
+      <c r="M319">
+        <v>3</v>
+      </c>
+      <c r="N319">
+        <v>5</v>
+      </c>
+      <c r="O319" t="s">
+        <v>284</v>
+      </c>
+      <c r="P319" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q319">
+        <v>3.3</v>
+      </c>
+      <c r="R319">
+        <v>1.93</v>
+      </c>
+      <c r="S319">
+        <v>3.45</v>
+      </c>
+      <c r="T319">
+        <v>1.47</v>
+      </c>
+      <c r="U319">
+        <v>2.47</v>
+      </c>
+      <c r="V319">
+        <v>3.15</v>
+      </c>
+      <c r="W319">
+        <v>1.3</v>
+      </c>
+      <c r="X319">
+        <v>8.1</v>
+      </c>
+      <c r="Y319">
+        <v>1.02</v>
+      </c>
+      <c r="Z319">
+        <v>2.65</v>
+      </c>
+      <c r="AA319">
+        <v>2.95</v>
+      </c>
+      <c r="AB319">
+        <v>2.75</v>
+      </c>
+      <c r="AC319">
+        <v>1.03</v>
+      </c>
+      <c r="AD319">
+        <v>7.3</v>
+      </c>
+      <c r="AE319">
+        <v>1.4</v>
+      </c>
+      <c r="AF319">
+        <v>3.04</v>
+      </c>
+      <c r="AG319">
+        <v>2.15</v>
+      </c>
+      <c r="AH319">
+        <v>1.66</v>
+      </c>
+      <c r="AI319">
+        <v>1.9</v>
+      </c>
+      <c r="AJ319">
+        <v>1.83</v>
+      </c>
+      <c r="AK319">
+        <v>1.3</v>
+      </c>
+      <c r="AL319">
+        <v>1.3</v>
+      </c>
+      <c r="AM319">
+        <v>1.5</v>
+      </c>
+      <c r="AN319">
+        <v>0.8</v>
+      </c>
+      <c r="AO319">
+        <v>1.33</v>
+      </c>
+      <c r="AP319">
+        <v>0.75</v>
+      </c>
+      <c r="AQ319">
+        <v>1.44</v>
+      </c>
+      <c r="AR319">
+        <v>1.56</v>
+      </c>
+      <c r="AS319">
+        <v>1.05</v>
+      </c>
+      <c r="AT319">
+        <v>2.61</v>
+      </c>
+      <c r="AU319">
+        <v>6</v>
+      </c>
+      <c r="AV319">
+        <v>3</v>
+      </c>
+      <c r="AW319">
+        <v>10</v>
+      </c>
+      <c r="AX319">
+        <v>12</v>
+      </c>
+      <c r="AY319">
+        <v>16</v>
+      </c>
+      <c r="AZ319">
+        <v>15</v>
+      </c>
+      <c r="BA319">
+        <v>5</v>
+      </c>
+      <c r="BB319">
+        <v>2</v>
+      </c>
+      <c r="BC319">
+        <v>7</v>
+      </c>
+      <c r="BD319">
+        <v>1.5</v>
+      </c>
+      <c r="BE319">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="BF319">
+        <v>2.97</v>
+      </c>
+      <c r="BG319">
+        <v>1.07</v>
+      </c>
+      <c r="BH319">
+        <v>5.47</v>
+      </c>
+      <c r="BI319">
+        <v>1.22</v>
+      </c>
+      <c r="BJ319">
+        <v>3.5</v>
+      </c>
+      <c r="BK319">
+        <v>1.47</v>
+      </c>
+      <c r="BL319">
+        <v>2.59</v>
+      </c>
+      <c r="BM319">
+        <v>1.7</v>
+      </c>
+      <c r="BN319">
+        <v>2.05</v>
+      </c>
+      <c r="BO319">
+        <v>2</v>
+      </c>
+      <c r="BP319">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="320" spans="1:68">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>7841346</v>
+      </c>
+      <c r="C320" t="s">
+        <v>68</v>
+      </c>
+      <c r="D320" t="s">
+        <v>69</v>
+      </c>
+      <c r="E320" s="2">
+        <v>45944.8125</v>
+      </c>
+      <c r="F320">
+        <v>32</v>
+      </c>
+      <c r="G320" t="s">
+        <v>82</v>
+      </c>
+      <c r="H320" t="s">
+        <v>89</v>
+      </c>
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>0</v>
+      </c>
+      <c r="L320">
+        <v>1</v>
+      </c>
+      <c r="M320">
+        <v>1</v>
+      </c>
+      <c r="N320">
+        <v>2</v>
+      </c>
+      <c r="O320" t="s">
+        <v>235</v>
+      </c>
+      <c r="P320" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q320">
+        <v>2.16</v>
+      </c>
+      <c r="R320">
+        <v>2.08</v>
+      </c>
+      <c r="S320">
+        <v>5</v>
+      </c>
+      <c r="T320">
+        <v>1.41</v>
+      </c>
+      <c r="U320">
+        <v>2.66</v>
+      </c>
+      <c r="V320">
+        <v>2.95</v>
+      </c>
+      <c r="W320">
+        <v>1.35</v>
+      </c>
+      <c r="X320">
+        <v>7.4</v>
+      </c>
+      <c r="Y320">
+        <v>1.03</v>
+      </c>
+      <c r="Z320">
+        <v>1.58</v>
+      </c>
+      <c r="AA320">
+        <v>3.55</v>
+      </c>
+      <c r="AB320">
+        <v>5.2</v>
+      </c>
+      <c r="AC320">
+        <v>1.04</v>
+      </c>
+      <c r="AD320">
+        <v>8.5</v>
+      </c>
+      <c r="AE320">
+        <v>1.38</v>
+      </c>
+      <c r="AF320">
+        <v>3.13</v>
+      </c>
+      <c r="AG320">
+        <v>2.06</v>
+      </c>
+      <c r="AH320">
+        <v>1.72</v>
+      </c>
+      <c r="AI320">
+        <v>2.19</v>
+      </c>
+      <c r="AJ320">
+        <v>1.68</v>
+      </c>
+      <c r="AK320">
+        <v>1.22</v>
+      </c>
+      <c r="AL320">
+        <v>1.21</v>
+      </c>
+      <c r="AM320">
+        <v>2.19</v>
+      </c>
+      <c r="AN320">
+        <v>1.93</v>
+      </c>
+      <c r="AO320">
+        <v>0.73</v>
+      </c>
+      <c r="AP320">
+        <v>1.88</v>
+      </c>
+      <c r="AQ320">
+        <v>0.75</v>
+      </c>
+      <c r="AR320">
+        <v>1.53</v>
+      </c>
+      <c r="AS320">
+        <v>1.03</v>
+      </c>
+      <c r="AT320">
+        <v>2.56</v>
+      </c>
+      <c r="AU320">
+        <v>6</v>
+      </c>
+      <c r="AV320">
+        <v>4</v>
+      </c>
+      <c r="AW320">
+        <v>8</v>
+      </c>
+      <c r="AX320">
+        <v>10</v>
+      </c>
+      <c r="AY320">
+        <v>14</v>
+      </c>
+      <c r="AZ320">
+        <v>14</v>
+      </c>
+      <c r="BA320">
+        <v>6</v>
+      </c>
+      <c r="BB320">
+        <v>3</v>
+      </c>
+      <c r="BC320">
+        <v>9</v>
+      </c>
+      <c r="BD320">
+        <v>1.46</v>
+      </c>
+      <c r="BE320">
+        <v>7.5</v>
+      </c>
+      <c r="BF320">
+        <v>2.9</v>
+      </c>
+      <c r="BG320">
+        <v>1.16</v>
+      </c>
+      <c r="BH320">
+        <v>4.03</v>
+      </c>
+      <c r="BI320">
+        <v>1.36</v>
+      </c>
+      <c r="BJ320">
+        <v>2.76</v>
+      </c>
+      <c r="BK320">
+        <v>1.84</v>
+      </c>
+      <c r="BL320">
+        <v>2.08</v>
+      </c>
+      <c r="BM320">
+        <v>2.06</v>
+      </c>
+      <c r="BN320">
+        <v>1.68</v>
+      </c>
+      <c r="BO320">
+        <v>2.65</v>
+      </c>
+      <c r="BP320">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="321" spans="1:68">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>7841342</v>
+      </c>
+      <c r="C321" t="s">
+        <v>68</v>
+      </c>
+      <c r="D321" t="s">
+        <v>69</v>
+      </c>
+      <c r="E321" s="2">
+        <v>45944.89583333334</v>
+      </c>
+      <c r="F321">
+        <v>32</v>
+      </c>
+      <c r="G321" t="s">
+        <v>80</v>
+      </c>
+      <c r="H321" t="s">
+        <v>78</v>
+      </c>
+      <c r="I321">
+        <v>0</v>
+      </c>
+      <c r="J321">
+        <v>1</v>
+      </c>
+      <c r="K321">
+        <v>1</v>
+      </c>
+      <c r="L321">
+        <v>1</v>
+      </c>
+      <c r="M321">
+        <v>1</v>
+      </c>
+      <c r="N321">
+        <v>2</v>
+      </c>
+      <c r="O321" t="s">
+        <v>105</v>
+      </c>
+      <c r="P321" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q321">
+        <v>2.23</v>
+      </c>
+      <c r="R321">
+        <v>2.02</v>
+      </c>
+      <c r="S321">
+        <v>6.42</v>
+      </c>
+      <c r="T321">
+        <v>1.47</v>
+      </c>
+      <c r="U321">
+        <v>2.47</v>
+      </c>
+      <c r="V321">
+        <v>3.28</v>
+      </c>
+      <c r="W321">
+        <v>1.31</v>
+      </c>
+      <c r="X321">
+        <v>8.6</v>
+      </c>
+      <c r="Y321">
+        <v>1.01</v>
+      </c>
+      <c r="Z321">
+        <v>1.5</v>
+      </c>
+      <c r="AA321">
+        <v>3.25</v>
+      </c>
+      <c r="AB321">
+        <v>6</v>
+      </c>
+      <c r="AC321">
+        <v>1.03</v>
+      </c>
+      <c r="AD321">
+        <v>7.2</v>
+      </c>
+      <c r="AE321">
+        <v>1.4</v>
+      </c>
+      <c r="AF321">
+        <v>2.56</v>
+      </c>
+      <c r="AG321">
+        <v>2.33</v>
+      </c>
+      <c r="AH321">
+        <v>1.56</v>
+      </c>
+      <c r="AI321">
+        <v>2.32</v>
+      </c>
+      <c r="AJ321">
+        <v>1.6</v>
+      </c>
+      <c r="AK321">
+        <v>1.26</v>
+      </c>
+      <c r="AL321">
+        <v>1.2</v>
+      </c>
+      <c r="AM321">
+        <v>2.19</v>
+      </c>
+      <c r="AN321">
+        <v>1.67</v>
+      </c>
+      <c r="AO321">
+        <v>0.93</v>
+      </c>
+      <c r="AP321">
+        <v>1.63</v>
+      </c>
+      <c r="AQ321">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR321">
+        <v>1.73</v>
+      </c>
+      <c r="AS321">
+        <v>1.22</v>
+      </c>
+      <c r="AT321">
+        <v>2.95</v>
+      </c>
+      <c r="AU321">
+        <v>9</v>
+      </c>
+      <c r="AV321">
+        <v>5</v>
+      </c>
+      <c r="AW321">
+        <v>12</v>
+      </c>
+      <c r="AX321">
+        <v>7</v>
+      </c>
+      <c r="AY321">
+        <v>21</v>
+      </c>
+      <c r="AZ321">
+        <v>12</v>
+      </c>
+      <c r="BA321">
+        <v>10</v>
+      </c>
+      <c r="BB321">
+        <v>2</v>
+      </c>
+      <c r="BC321">
+        <v>12</v>
+      </c>
+      <c r="BD321">
+        <v>1.33</v>
+      </c>
+      <c r="BE321">
+        <v>8.5</v>
+      </c>
+      <c r="BF321">
+        <v>4.3</v>
+      </c>
+      <c r="BG321">
+        <v>1.16</v>
+      </c>
+      <c r="BH321">
+        <v>3.96</v>
+      </c>
+      <c r="BI321">
+        <v>1.37</v>
+      </c>
+      <c r="BJ321">
+        <v>2.72</v>
+      </c>
+      <c r="BK321">
+        <v>1.86</v>
+      </c>
+      <c r="BL321">
+        <v>2.06</v>
+      </c>
+      <c r="BM321">
+        <v>2.08</v>
+      </c>
+      <c r="BN321">
+        <v>1.67</v>
+      </c>
+      <c r="BO321">
+        <v>2.68</v>
+      </c>
+      <c r="BP321">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -70151,7 +70151,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -70035,28 +70035,28 @@
         <v>6</v>
       </c>
       <c r="AV319" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW319" t="n">
         <v>10</v>
       </c>
       <c r="AX319" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY319" t="n">
         <v>16</v>
       </c>
       <c r="AZ319" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA319" t="n">
         <v>5</v>
       </c>
       <c r="BB319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC319" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD319" t="n">
         <v>1.5</v>
@@ -70253,28 +70253,28 @@
         <v>6</v>
       </c>
       <c r="AV320" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW320" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX320" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY320" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ320" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA320" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB320" t="n">
         <v>6</v>
       </c>
-      <c r="BB320" t="n">
-        <v>3</v>
-      </c>
       <c r="BC320" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BD320" t="n">
         <v>1.46</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -68795,7 +68795,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>7841343</v>
+        <v>7841347</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -68815,12 +68815,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="I314" t="n">
@@ -68833,137 +68833,137 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['64', '76']</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="R314" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S314" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T314" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U314" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V314" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W314" t="n">
         <v>1.3</v>
       </c>
       <c r="X314" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z314" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AA314" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AB314" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="AC314" t="n">
         <v>1.1</v>
       </c>
       <c r="AD314" t="n">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="AE314" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF314" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG314" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH314" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI314" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AJ314" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AK314" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL314" t="n">
         <v>1.28</v>
       </c>
       <c r="AM314" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AN314" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="AP314" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AQ314" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR314" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AS314" t="n">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AT314" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU314" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW314" t="n">
         <v>9</v>
       </c>
       <c r="AX314" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY314" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ314" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA314" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC314" t="n">
         <v>7</v>
@@ -68972,40 +68972,40 @@
         <v>1.55</v>
       </c>
       <c r="BE314" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF314" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BG314" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BH314" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="BI314" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BJ314" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="BK314" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="BL314" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BM314" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BN314" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BO314" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP314" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="315">
@@ -69013,7 +69013,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>7841347</v>
+        <v>7841343</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -69033,12 +69033,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="I315" t="n">
@@ -69051,137 +69051,137 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>['64', '76']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="R315" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S315" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T315" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U315" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V315" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W315" t="n">
         <v>1.3</v>
       </c>
       <c r="X315" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Y315" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z315" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AA315" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AB315" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="AC315" t="n">
         <v>1.1</v>
       </c>
       <c r="AD315" t="n">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="AE315" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF315" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG315" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AH315" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI315" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AJ315" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AK315" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL315" t="n">
         <v>1.28</v>
       </c>
       <c r="AM315" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AN315" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="AP315" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AQ315" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AR315" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AS315" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="AT315" t="n">
-        <v>3.19</v>
+        <v>2.54</v>
       </c>
       <c r="AU315" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW315" t="n">
         <v>9</v>
       </c>
       <c r="AX315" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY315" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ315" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA315" t="n">
         <v>6</v>
       </c>
-      <c r="BA315" t="n">
-        <v>5</v>
-      </c>
       <c r="BB315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC315" t="n">
         <v>7</v>
@@ -69190,40 +69190,40 @@
         <v>1.55</v>
       </c>
       <c r="BE315" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF315" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="BG315" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BH315" t="n">
-        <v>3.62</v>
+        <v>3.77</v>
       </c>
       <c r="BI315" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BJ315" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BK315" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="BL315" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BM315" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BN315" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO315" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BP315" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="316">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP321"/>
+  <dimension ref="A1:BP322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,7 +2658,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.13</v>
@@ -5928,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR25" t="n">
         <v>1.28</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.9399999999999999</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.88</v>
@@ -12468,7 +12468,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR55" t="n">
         <v>1.63</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.75</v>
@@ -17046,7 +17046,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR76" t="n">
         <v>1.53</v>
@@ -19441,7 +19441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.8100000000000001</v>
@@ -20752,7 +20752,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR93" t="n">
         <v>1.68</v>
@@ -24673,7 +24673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.25</v>
@@ -28597,7 +28597,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.88</v>
@@ -28818,7 +28818,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR130" t="n">
         <v>1.56</v>
@@ -32303,7 +32303,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.44</v>
@@ -32742,7 +32742,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR148" t="n">
         <v>1.26</v>
@@ -36012,7 +36012,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR163" t="n">
         <v>1.21</v>
@@ -37535,7 +37535,7 @@
         <v>1</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.75</v>
@@ -39497,7 +39497,7 @@
         <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ179" t="n">
         <v>0.88</v>
@@ -40372,7 +40372,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR183" t="n">
         <v>1.91</v>
@@ -43203,7 +43203,7 @@
         <v>1.78</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.31</v>
@@ -45386,7 +45386,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR206" t="n">
         <v>1.82</v>
@@ -46909,7 +46909,7 @@
         <v>0.6</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.6899999999999999</v>
@@ -49092,7 +49092,7 @@
         <v>2</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR223" t="n">
         <v>1.89</v>
@@ -51926,7 +51926,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR236" t="n">
         <v>1.81</v>
@@ -53231,7 +53231,7 @@
         <v>1.18</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ242" t="n">
         <v>1.44</v>
@@ -56722,7 +56722,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR258" t="n">
         <v>1.33</v>
@@ -58245,7 +58245,7 @@
         <v>0.54</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ265" t="n">
         <v>0.44</v>
@@ -59774,7 +59774,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR272" t="n">
         <v>1.56</v>
@@ -63259,7 +63259,7 @@
         <v>1.07</v>
       </c>
       <c r="AP288" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ288" t="n">
         <v>1.31</v>
@@ -65224,7 +65224,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ297" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR297" t="n">
         <v>1.52</v>
@@ -66311,7 +66311,7 @@
         <v>1.4</v>
       </c>
       <c r="AP302" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ302" t="n">
         <v>1.31</v>
@@ -66968,7 +66968,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ305" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AR305" t="n">
         <v>1.62</v>
@@ -68795,7 +68795,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>7841347</v>
+        <v>7841343</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -68815,12 +68815,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="I314" t="n">
@@ -68833,137 +68833,137 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
+        <v>1</v>
+      </c>
+      <c r="M314" t="n">
+        <v>0</v>
+      </c>
+      <c r="N314" t="n">
+        <v>1</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q314" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R314" t="n">
         <v>2</v>
       </c>
-      <c r="M314" t="n">
-        <v>1</v>
-      </c>
-      <c r="N314" t="n">
-        <v>3</v>
-      </c>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>['64', '76']</t>
-        </is>
-      </c>
-      <c r="P314" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="Q314" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="R314" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S314" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T314" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U314" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V314" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W314" t="n">
         <v>1.3</v>
       </c>
       <c r="X314" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z314" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AA314" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AB314" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="AC314" t="n">
         <v>1.1</v>
       </c>
       <c r="AD314" t="n">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="AE314" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF314" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG314" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AH314" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI314" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AJ314" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AK314" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL314" t="n">
         <v>1.28</v>
       </c>
       <c r="AM314" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AN314" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="AP314" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ314" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR314" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT314" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU314" t="n">
         <v>2</v>
       </c>
-      <c r="AQ314" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR314" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS314" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT314" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AU314" t="n">
-        <v>4</v>
-      </c>
       <c r="AV314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW314" t="n">
         <v>9</v>
       </c>
       <c r="AX314" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY314" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ314" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA314" t="n">
         <v>6</v>
       </c>
-      <c r="BA314" t="n">
-        <v>5</v>
-      </c>
       <c r="BB314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC314" t="n">
         <v>7</v>
@@ -68972,40 +68972,40 @@
         <v>1.55</v>
       </c>
       <c r="BE314" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF314" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="BG314" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BH314" t="n">
-        <v>3.62</v>
+        <v>3.77</v>
       </c>
       <c r="BI314" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BJ314" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BK314" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="BL314" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BM314" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BN314" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO314" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BP314" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="315">
@@ -69013,7 +69013,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>7841343</v>
+        <v>7841347</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -69033,12 +69033,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="I315" t="n">
@@ -69051,137 +69051,137 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['64', '76']</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="R315" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S315" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T315" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U315" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V315" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W315" t="n">
         <v>1.3</v>
       </c>
       <c r="X315" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Y315" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z315" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AA315" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AB315" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="AC315" t="n">
         <v>1.1</v>
       </c>
       <c r="AD315" t="n">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="AE315" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF315" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG315" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH315" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI315" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AJ315" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AK315" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL315" t="n">
         <v>1.28</v>
       </c>
       <c r="AM315" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AN315" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="AP315" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AQ315" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR315" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AS315" t="n">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AT315" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU315" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW315" t="n">
         <v>9</v>
       </c>
       <c r="AX315" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY315" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ315" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA315" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC315" t="n">
         <v>7</v>
@@ -69190,40 +69190,40 @@
         <v>1.55</v>
       </c>
       <c r="BE315" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF315" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BG315" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BH315" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="BI315" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BJ315" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="BK315" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="BL315" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BM315" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BN315" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BO315" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP315" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="316">
@@ -70532,6 +70532,224 @@
       </c>
       <c r="BP321" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>7841358</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>45947.83333333334</v>
+      </c>
+      <c r="F322" t="n">
+        <v>33</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L322" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" t="n">
+        <v>0</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q322" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R322" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S322" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T322" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U322" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V322" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W322" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X322" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI322" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK322" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL322" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM322" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN322" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO322" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP322" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ322" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR322" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS322" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT322" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV322" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX322" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY322" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ322" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA322" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB322" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC322" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD322" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BE322" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF322" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG322" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH322" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI322" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ322" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK322" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL322" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM322" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN322" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO322" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP322" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP322"/>
+  <dimension ref="A1:BP323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.25</v>
@@ -6146,7 +6146,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR26" t="n">
         <v>1.36</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.88</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.24</v>
@@ -13776,7 +13776,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR61" t="n">
         <v>1.62</v>
@@ -15738,7 +15738,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR70" t="n">
         <v>1.12</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.44</v>
@@ -20098,7 +20098,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.31</v>
@@ -24458,7 +24458,7 @@
         <v>2</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR110" t="n">
         <v>1.93</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.5</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.44</v>
@@ -28600,7 +28600,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR129" t="n">
         <v>1.47</v>
@@ -31431,7 +31431,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.75</v>
@@ -32524,7 +32524,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR147" t="n">
         <v>1.59</v>
@@ -36227,7 +36227,7 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.31</v>
@@ -37102,7 +37102,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR168" t="n">
         <v>1.68</v>
@@ -40590,7 +40590,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR184" t="n">
         <v>1.84</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.31</v>
@@ -45819,7 +45819,7 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.75</v>
@@ -46258,7 +46258,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR210" t="n">
         <v>1.66</v>
@@ -47999,7 +47999,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.13</v>
@@ -50618,7 +50618,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR230" t="n">
         <v>1.33</v>
@@ -52141,7 +52141,7 @@
         <v>0.55</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ237" t="n">
         <v>0.44</v>
@@ -52580,7 +52580,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ239" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR239" t="n">
         <v>1.52</v>
@@ -57155,7 +57155,7 @@
         <v>0.92</v>
       </c>
       <c r="AP260" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ260" t="n">
         <v>0.9399999999999999</v>
@@ -59338,7 +59338,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ270" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR270" t="n">
         <v>1.81</v>
@@ -61515,7 +61515,7 @@
         <v>0.62</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ280" t="n">
         <v>0.6899999999999999</v>
@@ -62390,7 +62390,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ284" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR284" t="n">
         <v>1.78</v>
@@ -66093,7 +66093,7 @@
         <v>1.64</v>
       </c>
       <c r="AP301" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AQ301" t="n">
         <v>1.44</v>
@@ -67622,7 +67622,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ308" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR308" t="n">
         <v>1.53</v>
@@ -70750,6 +70750,224 @@
       </c>
       <c r="BP322" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>7841354</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>45948.66666666666</v>
+      </c>
+      <c r="F323" t="n">
+        <v>33</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
+        <v>0</v>
+      </c>
+      <c r="L323" t="n">
+        <v>1</v>
+      </c>
+      <c r="M323" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" t="n">
+        <v>1</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q323" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R323" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S323" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T323" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U323" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V323" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W323" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X323" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI323" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AK323" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL323" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM323" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN323" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO323" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ323" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR323" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS323" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT323" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU323" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV323" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW323" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX323" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY323" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ323" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA323" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB323" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC323" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD323" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE323" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BF323" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG323" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH323" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BI323" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ323" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK323" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL323" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM323" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN323" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO323" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BP323" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP323"/>
+  <dimension ref="A1:BP325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.75</v>
@@ -2876,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.6899999999999999</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR27" t="n">
         <v>1.65</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.44</v>
@@ -7890,7 +7890,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -8108,7 +8108,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR35" t="n">
         <v>1.6</v>
@@ -8323,7 +8323,7 @@
         <v>3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.31</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.5</v>
@@ -11160,7 +11160,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.44</v>
@@ -15302,7 +15302,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -15520,7 +15520,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -15735,7 +15735,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.82</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.88</v>
@@ -18572,7 +18572,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR83" t="n">
         <v>1.53</v>
@@ -18787,7 +18787,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.44</v>
@@ -19880,7 +19880,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.88</v>
@@ -23365,7 +23365,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.13</v>
@@ -23586,7 +23586,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR106" t="n">
         <v>1.68</v>
@@ -24237,7 +24237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.8100000000000001</v>
@@ -24676,7 +24676,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ123" t="n">
         <v>1.31</v>
@@ -27725,7 +27725,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.88</v>
@@ -27946,7 +27946,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -29036,7 +29036,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -31434,7 +31434,7 @@
         <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR142" t="n">
         <v>1.84</v>
@@ -31867,7 +31867,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.88</v>
@@ -33175,10 +33175,10 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -35794,7 +35794,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR162" t="n">
         <v>1.64</v>
@@ -36009,7 +36009,7 @@
         <v>1.29</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.24</v>
@@ -36448,7 +36448,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -37753,7 +37753,7 @@
         <v>0.88</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.31</v>
@@ -38628,7 +38628,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR175" t="n">
         <v>1.47</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.9399999999999999</v>
@@ -41023,7 +41023,7 @@
         <v>1.25</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.44</v>
@@ -41680,7 +41680,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.13</v>
@@ -43424,7 +43424,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.44</v>
@@ -46476,7 +46476,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -47127,7 +47127,7 @@
         <v>0.7</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.75</v>
@@ -48220,7 +48220,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR219" t="n">
         <v>1.8</v>
@@ -51051,7 +51051,7 @@
         <v>1.18</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.31</v>
@@ -52362,7 +52362,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
@@ -53013,7 +53013,7 @@
         <v>1</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ241" t="n">
         <v>0.9399999999999999</v>
@@ -54321,7 +54321,7 @@
         <v>0.92</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ247" t="n">
         <v>0.8100000000000001</v>
@@ -54978,7 +54978,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR250" t="n">
         <v>1.63</v>
@@ -55196,7 +55196,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR251" t="n">
         <v>1.49</v>
@@ -57812,7 +57812,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR263" t="n">
         <v>1.76</v>
@@ -58681,7 +58681,7 @@
         <v>0.83</v>
       </c>
       <c r="AP267" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ267" t="n">
         <v>0.88</v>
@@ -58902,7 +58902,7 @@
         <v>2</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR268" t="n">
         <v>1.84</v>
@@ -59117,7 +59117,7 @@
         <v>1.62</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ269" t="n">
         <v>1.5</v>
@@ -62605,10 +62605,10 @@
         <v>0.64</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ285" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR285" t="n">
         <v>1.35</v>
@@ -63044,7 +63044,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ287" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR287" t="n">
         <v>1.63</v>
@@ -63477,7 +63477,7 @@
         <v>0.5</v>
       </c>
       <c r="AP289" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ289" t="n">
         <v>0.44</v>
@@ -66532,7 +66532,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ303" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR303" t="n">
         <v>1.59</v>
@@ -67186,7 +67186,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ306" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR306" t="n">
         <v>1.53</v>
@@ -67619,7 +67619,7 @@
         <v>0.87</v>
       </c>
       <c r="AP308" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ308" t="n">
         <v>0.82</v>
@@ -68273,7 +68273,7 @@
         <v>1.53</v>
       </c>
       <c r="AP311" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ311" t="n">
         <v>1.44</v>
@@ -70968,6 +70968,442 @@
       </c>
       <c r="BP323" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>7841359</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>45948.77083333334</v>
+      </c>
+      <c r="F324" t="n">
+        <v>33</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>1</v>
+      </c>
+      <c r="K324" t="n">
+        <v>1</v>
+      </c>
+      <c r="L324" t="n">
+        <v>1</v>
+      </c>
+      <c r="M324" t="n">
+        <v>1</v>
+      </c>
+      <c r="N324" t="n">
+        <v>2</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q324" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R324" t="n">
+        <v>2</v>
+      </c>
+      <c r="S324" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T324" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U324" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V324" t="n">
+        <v>3</v>
+      </c>
+      <c r="W324" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X324" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH324" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI324" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK324" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM324" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN324" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO324" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP324" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ324" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR324" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS324" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT324" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AU324" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW324" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX324" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY324" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ324" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA324" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB324" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC324" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD324" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE324" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="BF324" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG324" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH324" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BI324" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ324" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK324" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL324" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM324" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BN324" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO324" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP324" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>7841355</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>45948.85416666666</v>
+      </c>
+      <c r="F325" t="n">
+        <v>33</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="I325" t="n">
+        <v>2</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="n">
+        <v>2</v>
+      </c>
+      <c r="L325" t="n">
+        <v>3</v>
+      </c>
+      <c r="M325" t="n">
+        <v>1</v>
+      </c>
+      <c r="N325" t="n">
+        <v>4</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>['14', '19', '74']</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q325" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R325" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S325" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T325" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U325" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V325" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W325" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X325" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH325" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI325" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ325" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK325" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL325" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM325" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN325" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO325" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP325" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ325" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR325" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS325" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT325" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU325" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV325" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW325" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX325" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY325" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ325" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA325" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB325" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC325" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD325" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE325" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF325" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG325" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH325" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI325" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ325" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK325" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL325" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BM325" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN325" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO325" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP325" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -71361,10 +71361,10 @@
         <v>3</v>
       </c>
       <c r="BB325" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC325" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD325" t="n">
         <v>1.66</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -68795,7 +68795,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>7841343</v>
+        <v>7841347</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -68815,12 +68815,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="I314" t="n">
@@ -68833,137 +68833,137 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['64', '76']</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="R314" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S314" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T314" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U314" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V314" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W314" t="n">
         <v>1.3</v>
       </c>
       <c r="X314" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z314" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AA314" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AB314" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="AC314" t="n">
         <v>1.1</v>
       </c>
       <c r="AD314" t="n">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="AE314" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF314" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG314" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH314" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI314" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AJ314" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AK314" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL314" t="n">
         <v>1.28</v>
       </c>
       <c r="AM314" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AN314" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="AP314" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AQ314" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR314" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AS314" t="n">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AT314" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU314" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW314" t="n">
         <v>9</v>
       </c>
       <c r="AX314" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY314" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ314" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA314" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC314" t="n">
         <v>7</v>
@@ -68972,40 +68972,40 @@
         <v>1.55</v>
       </c>
       <c r="BE314" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF314" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BG314" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BH314" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="BI314" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BJ314" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="BK314" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="BL314" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BM314" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BN314" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BO314" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP314" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="315">
@@ -69013,7 +69013,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>7841347</v>
+        <v>7841343</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -69033,12 +69033,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="I315" t="n">
@@ -69051,137 +69051,137 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>['64', '76']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="R315" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S315" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T315" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U315" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V315" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W315" t="n">
         <v>1.3</v>
       </c>
       <c r="X315" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Y315" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z315" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AA315" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AB315" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="AC315" t="n">
         <v>1.1</v>
       </c>
       <c r="AD315" t="n">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="AE315" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF315" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG315" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AH315" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI315" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AJ315" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AK315" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL315" t="n">
         <v>1.28</v>
       </c>
       <c r="AM315" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AN315" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="AP315" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AQ315" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AR315" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AS315" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="AT315" t="n">
-        <v>3.19</v>
+        <v>2.54</v>
       </c>
       <c r="AU315" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW315" t="n">
         <v>9</v>
       </c>
       <c r="AX315" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY315" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ315" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA315" t="n">
         <v>6</v>
       </c>
-      <c r="BA315" t="n">
-        <v>5</v>
-      </c>
       <c r="BB315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC315" t="n">
         <v>7</v>
@@ -69190,40 +69190,40 @@
         <v>1.55</v>
       </c>
       <c r="BE315" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF315" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="BG315" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BH315" t="n">
-        <v>3.62</v>
+        <v>3.77</v>
       </c>
       <c r="BI315" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BJ315" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BK315" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="BL315" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BM315" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BN315" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO315" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BP315" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="316">
@@ -70692,13 +70692,13 @@
         <v>5</v>
       </c>
       <c r="AW322" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX322" t="n">
         <v>5</v>
       </c>
       <c r="AY322" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ322" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP325"/>
+  <dimension ref="A1:BP329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.82</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.24</v>
@@ -3094,7 +3094,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.31</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.88</v>
@@ -5274,7 +5274,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.8100000000000001</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.24</v>
@@ -6582,7 +6582,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR28" t="n">
         <v>1.71</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.44</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.88</v>
@@ -8762,7 +8762,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -9634,7 +9634,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR42" t="n">
         <v>2.28</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.8100000000000001</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.6899999999999999</v>
@@ -10724,7 +10724,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR47" t="n">
         <v>2.09</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.31</v>
@@ -12686,7 +12686,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.6899999999999999</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.88</v>
@@ -14648,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR65" t="n">
         <v>1.95</v>
@@ -15299,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.18</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.75</v>
@@ -16828,7 +16828,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -17482,7 +17482,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -18133,7 +18133,7 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.6899999999999999</v>
@@ -18790,7 +18790,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.31</v>
@@ -19877,7 +19877,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.76</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.9399999999999999</v>
@@ -21621,10 +21621,10 @@
         <v>0.75</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -22496,7 +22496,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.5</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.76</v>
@@ -23804,7 +23804,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR107" t="n">
         <v>1.65</v>
@@ -27071,7 +27071,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.31</v>
@@ -27292,7 +27292,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -27507,10 +27507,10 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.88</v>
@@ -28382,7 +28382,7 @@
         <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR128" t="n">
         <v>1.74</v>
@@ -28815,7 +28815,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.24</v>
@@ -31649,10 +31649,10 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR143" t="n">
         <v>1.28</v>
@@ -32085,7 +32085,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.88</v>
@@ -32306,7 +32306,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -32739,7 +32739,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.24</v>
@@ -32957,7 +32957,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.31</v>
@@ -33396,7 +33396,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -35355,10 +35355,10 @@
         <v>0.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR160" t="n">
         <v>1.33</v>
@@ -35791,7 +35791,7 @@
         <v>0.63</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.76</v>
@@ -36230,7 +36230,7 @@
         <v>2</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -36881,7 +36881,7 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.88</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.82</v>
@@ -37320,7 +37320,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -37971,7 +37971,7 @@
         <v>0.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.88</v>
@@ -38846,7 +38846,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR176" t="n">
         <v>1.38</v>
@@ -39715,10 +39715,10 @@
         <v>1.13</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -40805,7 +40805,7 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.44</v>
@@ -41026,7 +41026,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.75</v>
@@ -42767,10 +42767,10 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -42985,7 +42985,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.6899999999999999</v>
@@ -44296,7 +44296,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR201" t="n">
         <v>1.52</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.31</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.88</v>
@@ -46040,7 +46040,7 @@
         <v>2</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR209" t="n">
         <v>1.87</v>
@@ -48438,7 +48438,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.9399999999999999</v>
@@ -49307,7 +49307,7 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.44</v>
@@ -49746,7 +49746,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR226" t="n">
         <v>1.9</v>
@@ -50182,7 +50182,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR228" t="n">
         <v>1.44</v>
@@ -50615,7 +50615,7 @@
         <v>1</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.82</v>
@@ -50833,7 +50833,7 @@
         <v>0.3</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.44</v>
@@ -51054,7 +51054,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
@@ -51269,7 +51269,7 @@
         <v>1.75</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.5</v>
@@ -53452,7 +53452,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR243" t="n">
         <v>1.57</v>
@@ -53667,7 +53667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.13</v>
@@ -53885,10 +53885,10 @@
         <v>1.27</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR245" t="n">
         <v>1.34</v>
@@ -54539,7 +54539,7 @@
         <v>1.55</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ248" t="n">
         <v>1.31</v>
@@ -55414,7 +55414,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
@@ -55629,7 +55629,7 @@
         <v>1.42</v>
       </c>
       <c r="AP253" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.31</v>
@@ -56283,7 +56283,7 @@
         <v>0.85</v>
       </c>
       <c r="AP256" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ256" t="n">
         <v>0.88</v>
@@ -57376,7 +57376,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR261" t="n">
         <v>1.53</v>
@@ -57591,7 +57591,7 @@
         <v>0.92</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ262" t="n">
         <v>0.8100000000000001</v>
@@ -58248,7 +58248,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR265" t="n">
         <v>1.42</v>
@@ -58463,7 +58463,7 @@
         <v>1</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ266" t="n">
         <v>1.13</v>
@@ -60646,7 +60646,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ276" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR276" t="n">
         <v>1.45</v>
@@ -60861,7 +60861,7 @@
         <v>0.46</v>
       </c>
       <c r="AP277" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ277" t="n">
         <v>0.44</v>
@@ -61297,10 +61297,10 @@
         <v>1.31</v>
       </c>
       <c r="AP279" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ279" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR279" t="n">
         <v>1.52</v>
@@ -62823,7 +62823,7 @@
         <v>1</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ286" t="n">
         <v>1.13</v>
@@ -63480,7 +63480,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR289" t="n">
         <v>1.56</v>
@@ -63695,7 +63695,7 @@
         <v>1.5</v>
       </c>
       <c r="AP290" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ290" t="n">
         <v>1.5</v>
@@ -64352,7 +64352,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ293" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR293" t="n">
         <v>1.52</v>
@@ -64785,7 +64785,7 @@
         <v>0.79</v>
       </c>
       <c r="AP295" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ295" t="n">
         <v>0.75</v>
@@ -65875,7 +65875,7 @@
         <v>1.21</v>
       </c>
       <c r="AP300" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ300" t="n">
         <v>1.44</v>
@@ -66096,7 +66096,7 @@
         <v>2</v>
       </c>
       <c r="AQ301" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR301" t="n">
         <v>1.78</v>
@@ -66314,7 +66314,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ302" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR302" t="n">
         <v>1.44</v>
@@ -66747,7 +66747,7 @@
         <v>0.93</v>
       </c>
       <c r="AP304" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ304" t="n">
         <v>0.88</v>
@@ -67183,7 +67183,7 @@
         <v>1.13</v>
       </c>
       <c r="AP306" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ306" t="n">
         <v>1.18</v>
@@ -67401,10 +67401,10 @@
         <v>0.47</v>
       </c>
       <c r="AP307" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ307" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR307" t="n">
         <v>1.7</v>
@@ -68055,7 +68055,7 @@
         <v>1</v>
       </c>
       <c r="AP310" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AQ310" t="n">
         <v>0.88</v>
@@ -68276,7 +68276,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ311" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AR311" t="n">
         <v>1.36</v>
@@ -71404,6 +71404,878 @@
       </c>
       <c r="BP325" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>7841356</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>45949.66666666666</v>
+      </c>
+      <c r="F326" t="n">
+        <v>33</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" t="n">
+        <v>1</v>
+      </c>
+      <c r="M326" t="n">
+        <v>1</v>
+      </c>
+      <c r="N326" t="n">
+        <v>2</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="Q326" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R326" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S326" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T326" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U326" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V326" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W326" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X326" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI326" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK326" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM326" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN326" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO326" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP326" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ326" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR326" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS326" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT326" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW326" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX326" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY326" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ326" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA326" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB326" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC326" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD326" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE326" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF326" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG326" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH326" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI326" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ326" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK326" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL326" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM326" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN326" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO326" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP326" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>7841357</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>45949.66666666666</v>
+      </c>
+      <c r="F327" t="n">
+        <v>33</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="I327" t="n">
+        <v>2</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" t="n">
+        <v>2</v>
+      </c>
+      <c r="L327" t="n">
+        <v>2</v>
+      </c>
+      <c r="M327" t="n">
+        <v>1</v>
+      </c>
+      <c r="N327" t="n">
+        <v>3</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>['5', '18']</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q327" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R327" t="n">
+        <v>2</v>
+      </c>
+      <c r="S327" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T327" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U327" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V327" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W327" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X327" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH327" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI327" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK327" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL327" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN327" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO327" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP327" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ327" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR327" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS327" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT327" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU327" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV327" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW327" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX327" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY327" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ327" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA327" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB327" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC327" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD327" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE327" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="BF327" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="BG327" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH327" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BI327" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ327" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK327" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL327" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM327" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN327" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO327" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BP327" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>7841352</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>45949.77083333334</v>
+      </c>
+      <c r="F328" t="n">
+        <v>33</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q328" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R328" t="n">
+        <v>2</v>
+      </c>
+      <c r="S328" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T328" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U328" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V328" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W328" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X328" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI328" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK328" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL328" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM328" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO328" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP328" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ328" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR328" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS328" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT328" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW328" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX328" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY328" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ328" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA328" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB328" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC328" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD328" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE328" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF328" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BG328" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH328" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI328" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ328" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BK328" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL328" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM328" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN328" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO328" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP328" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>7841361</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>45949.77083333334</v>
+      </c>
+      <c r="F329" t="n">
+        <v>33</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="I329" t="n">
+        <v>1</v>
+      </c>
+      <c r="J329" t="n">
+        <v>2</v>
+      </c>
+      <c r="K329" t="n">
+        <v>3</v>
+      </c>
+      <c r="L329" t="n">
+        <v>2</v>
+      </c>
+      <c r="M329" t="n">
+        <v>2</v>
+      </c>
+      <c r="N329" t="n">
+        <v>4</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>['29', '90+1']</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>['20', '45+4']</t>
+        </is>
+      </c>
+      <c r="Q329" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R329" t="n">
+        <v>2</v>
+      </c>
+      <c r="S329" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T329" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U329" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V329" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="W329" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X329" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH329" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI329" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK329" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL329" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM329" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN329" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO329" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP329" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ329" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR329" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS329" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT329" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU329" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV329" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW329" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX329" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY329" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ329" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA329" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB329" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC329" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD329" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE329" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="BF329" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG329" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH329" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI329" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ329" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BK329" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL329" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM329" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BN329" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO329" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP329" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP329"/>
+  <dimension ref="A1:BP330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.44</v>
@@ -1786,7 +1786,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR23" t="n">
         <v>1.23</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.82</v>
@@ -10070,7 +10070,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR44" t="n">
         <v>1.6</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.9399999999999999</v>
@@ -13994,7 +13994,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR62" t="n">
         <v>1.29</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.5</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.13</v>
@@ -19008,7 +19008,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR85" t="n">
         <v>1.6</v>
@@ -22932,7 +22932,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR103" t="n">
         <v>1.98</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.41</v>
@@ -27074,7 +27074,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR122" t="n">
         <v>1.13</v>
@@ -29033,7 +29033,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.18</v>
@@ -32960,7 +32960,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR149" t="n">
         <v>1.59</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.29</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.88</v>
@@ -37756,7 +37756,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR171" t="n">
         <v>1.57</v>
@@ -41244,7 +41244,7 @@
         <v>2</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR187" t="n">
         <v>1.74</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.44</v>
@@ -44732,7 +44732,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR203" t="n">
         <v>1.34</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.8100000000000001</v>
@@ -48874,7 +48874,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR222" t="n">
         <v>1.5</v>
@@ -49525,7 +49525,7 @@
         <v>0.64</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.6899999999999999</v>
@@ -51705,7 +51705,7 @@
         <v>0.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ235" t="n">
         <v>0.75</v>
@@ -54106,7 +54106,7 @@
         <v>2</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR246" t="n">
         <v>1.86</v>
@@ -58027,7 +58027,7 @@
         <v>0.85</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ264" t="n">
         <v>0.88</v>
@@ -59556,7 +59556,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ271" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR271" t="n">
         <v>1.67</v>
@@ -63262,7 +63262,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR288" t="n">
         <v>1.41</v>
@@ -63913,7 +63913,7 @@
         <v>1</v>
       </c>
       <c r="AP291" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ291" t="n">
         <v>0.88</v>
@@ -66529,7 +66529,7 @@
         <v>0.6</v>
       </c>
       <c r="AP303" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ303" t="n">
         <v>0.76</v>
@@ -67840,7 +67840,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ309" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR309" t="n">
         <v>1.32</v>
@@ -68795,7 +68795,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>7841347</v>
+        <v>7841343</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -68815,12 +68815,12 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="I314" t="n">
@@ -68833,137 +68833,137 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N314" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>['64', '76']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="R314" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S314" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T314" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U314" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V314" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="W314" t="n">
         <v>1.3</v>
       </c>
       <c r="X314" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Y314" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z314" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AA314" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AB314" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="AC314" t="n">
         <v>1.1</v>
       </c>
       <c r="AD314" t="n">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="AE314" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF314" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG314" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AH314" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI314" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AJ314" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AK314" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL314" t="n">
         <v>1.28</v>
       </c>
       <c r="AM314" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AN314" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AO314" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="AP314" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AQ314" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AR314" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AS314" t="n">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="AT314" t="n">
-        <v>3.19</v>
+        <v>2.54</v>
       </c>
       <c r="AU314" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW314" t="n">
         <v>9</v>
       </c>
       <c r="AX314" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY314" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ314" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA314" t="n">
         <v>6</v>
       </c>
-      <c r="BA314" t="n">
-        <v>5</v>
-      </c>
       <c r="BB314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC314" t="n">
         <v>7</v>
@@ -68972,40 +68972,40 @@
         <v>1.55</v>
       </c>
       <c r="BE314" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF314" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="BG314" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BH314" t="n">
-        <v>3.62</v>
+        <v>3.77</v>
       </c>
       <c r="BI314" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BJ314" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BK314" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="BL314" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BM314" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BN314" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO314" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BP314" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="315">
@@ -69013,7 +69013,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>7841343</v>
+        <v>7841347</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -69033,12 +69033,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="I315" t="n">
@@ -69051,137 +69051,137 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['64', '76']</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="R315" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S315" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T315" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U315" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V315" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W315" t="n">
         <v>1.3</v>
       </c>
       <c r="X315" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Y315" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z315" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AA315" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AB315" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="AC315" t="n">
         <v>1.1</v>
       </c>
       <c r="AD315" t="n">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="AE315" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF315" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG315" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AH315" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI315" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AJ315" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AK315" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL315" t="n">
         <v>1.28</v>
       </c>
       <c r="AM315" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AN315" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AO315" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="AP315" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AQ315" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR315" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AS315" t="n">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AT315" t="n">
-        <v>2.54</v>
+        <v>3.19</v>
       </c>
       <c r="AU315" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV315" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW315" t="n">
         <v>9</v>
       </c>
       <c r="AX315" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY315" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ315" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA315" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC315" t="n">
         <v>7</v>
@@ -69190,40 +69190,40 @@
         <v>1.55</v>
       </c>
       <c r="BE315" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF315" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BG315" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BH315" t="n">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="BI315" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BJ315" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="BK315" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="BL315" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BM315" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BN315" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BO315" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP315" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="316">
@@ -72233,10 +72233,10 @@
         <v>5</v>
       </c>
       <c r="BB329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC329" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD329" t="n">
         <v>2.17</v>
@@ -72276,6 +72276,224 @@
       </c>
       <c r="BP329" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>7841353</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="n">
+        <v>45949.85416666666</v>
+      </c>
+      <c r="F330" t="n">
+        <v>33</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>1</v>
+      </c>
+      <c r="K330" t="n">
+        <v>1</v>
+      </c>
+      <c r="L330" t="n">
+        <v>1</v>
+      </c>
+      <c r="M330" t="n">
+        <v>3</v>
+      </c>
+      <c r="N330" t="n">
+        <v>4</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>['4', '52', '87']</t>
+        </is>
+      </c>
+      <c r="Q330" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R330" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S330" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T330" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U330" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V330" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W330" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X330" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH330" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI330" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ330" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK330" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL330" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM330" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AN330" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO330" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP330" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ330" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR330" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS330" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT330" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV330" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW330" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX330" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY330" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ330" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA330" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB330" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC330" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD330" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE330" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF330" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG330" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH330" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BI330" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ330" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK330" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL330" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM330" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN330" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO330" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BP330" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -72233,10 +72233,10 @@
         <v>5</v>
       </c>
       <c r="BB329" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC329" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD329" t="n">
         <v>2.17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP330"/>
+  <dimension ref="A1:BP331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.44</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.88</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.5</v>
@@ -16171,7 +16171,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ72" t="n">
         <v>0.9399999999999999</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.75</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.76</v>
@@ -32521,7 +32521,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.82</v>
@@ -36445,7 +36445,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.18</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.8100000000000001</v>
@@ -44511,7 +44511,7 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.44</v>
@@ -50179,7 +50179,7 @@
         <v>0.27</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.41</v>
@@ -52795,7 +52795,7 @@
         <v>0.83</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.88</v>
@@ -56719,7 +56719,7 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ258" t="n">
         <v>1.24</v>
@@ -59989,7 +59989,7 @@
         <v>1.38</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.31</v>
@@ -65657,7 +65657,7 @@
         <v>0.57</v>
       </c>
       <c r="AP299" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ299" t="n">
         <v>0.6899999999999999</v>
@@ -67837,7 +67837,7 @@
         <v>1.2</v>
       </c>
       <c r="AP309" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ309" t="n">
         <v>1.41</v>
@@ -71346,13 +71346,13 @@
         <v>4</v>
       </c>
       <c r="AW325" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX325" t="n">
         <v>6</v>
       </c>
       <c r="AY325" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ325" t="n">
         <v>10</v>
@@ -72233,10 +72233,10 @@
         <v>5</v>
       </c>
       <c r="BB329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC329" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD329" t="n">
         <v>2.17</v>
@@ -72436,13 +72436,13 @@
         <v>6</v>
       </c>
       <c r="AW330" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AX330" t="n">
         <v>5</v>
       </c>
       <c r="AY330" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ330" t="n">
         <v>11</v>
@@ -72494,6 +72494,224 @@
       </c>
       <c r="BP330" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>7841360</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>45950.8125</v>
+      </c>
+      <c r="F331" t="n">
+        <v>33</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I331" t="n">
+        <v>1</v>
+      </c>
+      <c r="J331" t="n">
+        <v>2</v>
+      </c>
+      <c r="K331" t="n">
+        <v>3</v>
+      </c>
+      <c r="L331" t="n">
+        <v>2</v>
+      </c>
+      <c r="M331" t="n">
+        <v>2</v>
+      </c>
+      <c r="N331" t="n">
+        <v>4</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>['2', '66']</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>['15', '31']</t>
+        </is>
+      </c>
+      <c r="Q331" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R331" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S331" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T331" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U331" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V331" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W331" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X331" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AG331" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH331" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI331" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ331" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK331" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL331" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM331" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN331" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO331" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP331" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ331" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR331" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS331" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT331" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU331" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV331" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW331" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX331" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY331" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ331" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA331" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB331" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC331" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD331" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE331" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF331" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BG331" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH331" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BI331" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ331" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK331" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL331" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM331" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN331" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO331" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BP331" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -72218,13 +72218,13 @@
         <v>4</v>
       </c>
       <c r="AW329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX329" t="n">
         <v>10</v>
       </c>
       <c r="AY329" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ329" t="n">
         <v>14</v>
@@ -72436,13 +72436,13 @@
         <v>6</v>
       </c>
       <c r="AW330" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX330" t="n">
         <v>5</v>
       </c>
       <c r="AY330" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ330" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP331"/>
+  <dimension ref="A1:BP333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.9399999999999999</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.41</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.41</v>
@@ -6800,7 +6800,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR29" t="n">
         <v>1.39</v>
@@ -7672,7 +7672,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR33" t="n">
         <v>1.46</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.29</v>
@@ -9631,7 +9631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.41</v>
@@ -9852,7 +9852,7 @@
         <v>2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR43" t="n">
         <v>2.02</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.13</v>
@@ -12904,7 +12904,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR57" t="n">
         <v>1.4</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.8100000000000001</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.13</v>
@@ -16610,7 +16610,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR74" t="n">
         <v>1.47</v>
@@ -17264,7 +17264,7 @@
         <v>2</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR77" t="n">
         <v>1.46</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.88</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.82</v>
@@ -20534,7 +20534,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR92" t="n">
         <v>1.81</v>
@@ -21842,7 +21842,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR98" t="n">
         <v>1.59</v>
@@ -22929,7 +22929,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.41</v>
@@ -23147,7 +23147,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.88</v>
@@ -25112,7 +25112,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR113" t="n">
         <v>1.73</v>
@@ -25548,7 +25548,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR115" t="n">
         <v>1.49</v>
@@ -26199,7 +26199,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.88</v>
@@ -30344,7 +30344,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR137" t="n">
         <v>1.3</v>
@@ -30559,7 +30559,7 @@
         <v>0.17</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.44</v>
@@ -31213,10 +31213,10 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -34047,7 +34047,7 @@
         <v>0.86</v>
       </c>
       <c r="AP154" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.6899999999999999</v>
@@ -34922,7 +34922,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR158" t="n">
         <v>1.35</v>
@@ -35573,7 +35573,7 @@
         <v>0.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.44</v>
@@ -37538,7 +37538,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR170" t="n">
         <v>1.36</v>
@@ -39061,7 +39061,7 @@
         <v>2</v>
       </c>
       <c r="AP177" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.31</v>
@@ -39279,7 +39279,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ178" t="n">
         <v>0.6899999999999999</v>
@@ -41462,7 +41462,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR188" t="n">
         <v>1.72</v>
@@ -42116,7 +42116,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR191" t="n">
         <v>1.56</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.9399999999999999</v>
@@ -44293,7 +44293,7 @@
         <v>0.3</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.41</v>
@@ -44950,7 +44950,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR204" t="n">
         <v>1.65</v>
@@ -45822,7 +45822,7 @@
         <v>2</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR208" t="n">
         <v>1.71</v>
@@ -46691,7 +46691,7 @@
         <v>1.64</v>
       </c>
       <c r="AP212" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.5</v>
@@ -47130,7 +47130,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -49310,7 +49310,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR224" t="n">
         <v>1.36</v>
@@ -50397,7 +50397,7 @@
         <v>0.8</v>
       </c>
       <c r="AP229" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ229" t="n">
         <v>0.88</v>
@@ -51708,7 +51708,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR235" t="n">
         <v>1.6</v>
@@ -53234,7 +53234,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR242" t="n">
         <v>1.39</v>
@@ -54757,7 +54757,7 @@
         <v>0.82</v>
       </c>
       <c r="AP249" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ249" t="n">
         <v>0.88</v>
@@ -54975,7 +54975,7 @@
         <v>0.75</v>
       </c>
       <c r="AP250" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ250" t="n">
         <v>0.76</v>
@@ -56068,7 +56068,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR255" t="n">
         <v>1.46</v>
@@ -56504,7 +56504,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR257" t="n">
         <v>1.47</v>
@@ -57809,7 +57809,7 @@
         <v>1.31</v>
       </c>
       <c r="AP263" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ263" t="n">
         <v>1.18</v>
@@ -59553,7 +59553,7 @@
         <v>1.15</v>
       </c>
       <c r="AP271" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ271" t="n">
         <v>1.41</v>
@@ -60428,7 +60428,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ275" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR275" t="n">
         <v>1.75</v>
@@ -61082,7 +61082,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ278" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR278" t="n">
         <v>1.74</v>
@@ -62387,7 +62387,7 @@
         <v>0.86</v>
       </c>
       <c r="AP284" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ284" t="n">
         <v>0.82</v>
@@ -63041,7 +63041,7 @@
         <v>1.21</v>
       </c>
       <c r="AP287" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ287" t="n">
         <v>1.18</v>
@@ -64788,7 +64788,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ295" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR295" t="n">
         <v>1.5</v>
@@ -65878,7 +65878,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ300" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR300" t="n">
         <v>1.53</v>
@@ -66965,7 +66965,7 @@
         <v>1.13</v>
       </c>
       <c r="AP305" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ305" t="n">
         <v>1.24</v>
@@ -68709,7 +68709,7 @@
         <v>0.87</v>
       </c>
       <c r="AP313" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ313" t="n">
         <v>0.8100000000000001</v>
@@ -69363,7 +69363,7 @@
         <v>1.6</v>
       </c>
       <c r="AP316" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AQ316" t="n">
         <v>1.5</v>
@@ -70020,7 +70020,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ319" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR319" t="n">
         <v>1.56</v>
@@ -70238,7 +70238,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ320" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AR320" t="n">
         <v>1.53</v>
@@ -72712,6 +72712,442 @@
       </c>
       <c r="BP331" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>7841370</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>45954.79166666666</v>
+      </c>
+      <c r="F332" t="n">
+        <v>34</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K332" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" t="n">
+        <v>1</v>
+      </c>
+      <c r="M332" t="n">
+        <v>1</v>
+      </c>
+      <c r="N332" t="n">
+        <v>2</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="Q332" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R332" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S332" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T332" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U332" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V332" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W332" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X332" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH332" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI332" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ332" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK332" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL332" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM332" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN332" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO332" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ332" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR332" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS332" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT332" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU332" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV332" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW332" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY332" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ332" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA332" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB332" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC332" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD332" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BE332" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF332" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG332" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH332" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI332" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ332" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK332" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL332" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM332" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN332" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO332" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP332" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>7841364</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>45954.89930555555</v>
+      </c>
+      <c r="F333" t="n">
+        <v>34</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>2</v>
+      </c>
+      <c r="K333" t="n">
+        <v>2</v>
+      </c>
+      <c r="L333" t="n">
+        <v>1</v>
+      </c>
+      <c r="M333" t="n">
+        <v>3</v>
+      </c>
+      <c r="N333" t="n">
+        <v>4</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>['15', '43', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q333" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R333" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S333" t="n">
+        <v>5</v>
+      </c>
+      <c r="T333" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U333" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V333" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W333" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X333" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH333" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI333" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ333" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK333" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM333" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN333" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO333" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP333" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ333" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR333" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS333" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT333" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU333" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV333" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW333" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX333" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY333" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ333" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA333" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB333" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC333" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD333" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE333" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF333" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG333" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH333" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI333" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ333" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK333" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL333" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM333" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN333" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO333" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BP333" t="n">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -73102,13 +73102,13 @@
         <v>10</v>
       </c>
       <c r="BA333" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB333" t="n">
         <v>4</v>
       </c>
       <c r="BC333" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD333" t="n">
         <v>1.34</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP333"/>
+  <dimension ref="A1:BP335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.88</v>
@@ -3530,7 +3530,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.76</v>
@@ -4838,7 +4838,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -8980,7 +8980,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR39" t="n">
         <v>1.06</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.13</v>
@@ -10506,7 +10506,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR46" t="n">
         <v>1.4</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.41</v>
@@ -11814,7 +11814,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR52" t="n">
         <v>2.13</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.88</v>
@@ -13122,7 +13122,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR58" t="n">
         <v>1.35</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.82</v>
@@ -14430,7 +14430,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR64" t="n">
         <v>1.71</v>
@@ -17043,7 +17043,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.24</v>
@@ -17915,7 +17915,7 @@
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.44</v>
@@ -18136,7 +18136,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR81" t="n">
         <v>1.26</v>
@@ -19662,7 +19662,7 @@
         <v>2</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR88" t="n">
         <v>1.94</v>
@@ -21403,7 +21403,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.88</v>
@@ -22057,10 +22057,10 @@
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR99" t="n">
         <v>2.14</v>
@@ -22714,7 +22714,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR102" t="n">
         <v>1.21</v>
@@ -24894,7 +24894,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR112" t="n">
         <v>1.77</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.8100000000000001</v>
@@ -25984,7 +25984,7 @@
         <v>2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR117" t="n">
         <v>1.74</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.9399999999999999</v>
@@ -29254,7 +29254,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29908,7 +29908,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR135" t="n">
         <v>1.7</v>
@@ -30123,7 +30123,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.8100000000000001</v>
@@ -30341,7 +30341,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.53</v>
@@ -33614,7 +33614,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR152" t="n">
         <v>1.73</v>
@@ -34050,7 +34050,7 @@
         <v>2</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR154" t="n">
         <v>1.78</v>
@@ -35137,7 +35137,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.9399999999999999</v>
@@ -37317,7 +37317,7 @@
         <v>1.43</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.41</v>
@@ -38407,10 +38407,10 @@
         <v>1.56</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR174" t="n">
         <v>1.43</v>
@@ -39282,7 +39282,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ178" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR178" t="n">
         <v>1.59</v>
@@ -40587,7 +40587,7 @@
         <v>0.89</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.82</v>
@@ -42334,7 +42334,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR192" t="n">
         <v>1.47</v>
@@ -42988,7 +42988,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR195" t="n">
         <v>1.36</v>
@@ -44075,7 +44075,7 @@
         <v>0.78</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.88</v>
@@ -45383,7 +45383,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.24</v>
@@ -46694,7 +46694,7 @@
         <v>2</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR212" t="n">
         <v>1.77</v>
@@ -46912,7 +46912,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR213" t="n">
         <v>1.4</v>
@@ -48217,7 +48217,7 @@
         <v>0.55</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ219" t="n">
         <v>0.76</v>
@@ -48435,7 +48435,7 @@
         <v>1.2</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.29</v>
@@ -48871,7 +48871,7 @@
         <v>1.09</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.41</v>
@@ -49528,7 +49528,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR225" t="n">
         <v>1.66</v>
@@ -51272,7 +51272,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR233" t="n">
         <v>1.58</v>
@@ -52359,7 +52359,7 @@
         <v>1.18</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.18</v>
@@ -55411,7 +55411,7 @@
         <v>1.33</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ252" t="n">
         <v>1.29</v>
@@ -55850,7 +55850,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR254" t="n">
         <v>1.57</v>
@@ -56501,7 +56501,7 @@
         <v>0.92</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ257" t="n">
         <v>0.76</v>
@@ -59120,7 +59120,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ269" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR269" t="n">
         <v>1.62</v>
@@ -60643,7 +60643,7 @@
         <v>1.54</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ276" t="n">
         <v>1.41</v>
@@ -61079,7 +61079,7 @@
         <v>1.31</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ278" t="n">
         <v>1.53</v>
@@ -61518,7 +61518,7 @@
         <v>2</v>
       </c>
       <c r="AQ280" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR280" t="n">
         <v>1.78</v>
@@ -63698,7 +63698,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ290" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR290" t="n">
         <v>1.72</v>
@@ -64567,7 +64567,7 @@
         <v>0.43</v>
       </c>
       <c r="AP294" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ294" t="n">
         <v>0.44</v>
@@ -65439,7 +65439,7 @@
         <v>1.36</v>
       </c>
       <c r="AP298" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ298" t="n">
         <v>1.31</v>
@@ -65660,7 +65660,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ299" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR299" t="n">
         <v>1.34</v>
@@ -68491,7 +68491,7 @@
         <v>1.33</v>
       </c>
       <c r="AP312" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AQ312" t="n">
         <v>1.31</v>
@@ -69148,7 +69148,7 @@
         <v>2</v>
       </c>
       <c r="AQ315" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AR315" t="n">
         <v>1.8</v>
@@ -69366,7 +69366,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ316" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AR316" t="n">
         <v>1.62</v>
@@ -69581,7 +69581,7 @@
         <v>0.93</v>
       </c>
       <c r="AP317" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AQ317" t="n">
         <v>0.88</v>
@@ -73148,6 +73148,442 @@
       </c>
       <c r="BP333" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>7841369</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>45955.66666666666</v>
+      </c>
+      <c r="F334" t="n">
+        <v>34</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>0</v>
+      </c>
+      <c r="L334" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" t="n">
+        <v>2</v>
+      </c>
+      <c r="N334" t="n">
+        <v>2</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>['60', '74']</t>
+        </is>
+      </c>
+      <c r="Q334" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R334" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S334" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T334" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U334" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V334" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="W334" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X334" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH334" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI334" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ334" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK334" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM334" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN334" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO334" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ334" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR334" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS334" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT334" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV334" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW334" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX334" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY334" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ334" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA334" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB334" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC334" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD334" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE334" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF334" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG334" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH334" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="BI334" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ334" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK334" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL334" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BM334" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN334" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO334" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BP334" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>7841371</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>45955.66666666666</v>
+      </c>
+      <c r="F335" t="n">
+        <v>34</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>1</v>
+      </c>
+      <c r="K335" t="n">
+        <v>1</v>
+      </c>
+      <c r="L335" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" t="n">
+        <v>1</v>
+      </c>
+      <c r="N335" t="n">
+        <v>1</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q335" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R335" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S335" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T335" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U335" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V335" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W335" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X335" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH335" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI335" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ335" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK335" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM335" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN335" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO335" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP335" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ335" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR335" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS335" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT335" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU335" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW335" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX335" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY335" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ335" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA335" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB335" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC335" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD335" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE335" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF335" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG335" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH335" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="BI335" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ335" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK335" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL335" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM335" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN335" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO335" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BP335" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP335"/>
+  <dimension ref="A1:BP337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.41</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.8100000000000001</v>
@@ -3312,7 +3312,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.41</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.18</v>
@@ -8326,7 +8326,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR36" t="n">
         <v>1.81</v>
@@ -8544,7 +8544,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR37" t="n">
         <v>2.28</v>
@@ -9849,7 +9849,7 @@
         <v>1</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.53</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.76</v>
@@ -11596,7 +11596,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR51" t="n">
         <v>1.02</v>
@@ -13340,7 +13340,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR59" t="n">
         <v>1.44</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.41</v>
@@ -16174,7 +16174,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR72" t="n">
         <v>1.97</v>
@@ -17697,10 +17697,10 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR79" t="n">
         <v>1.54</v>
@@ -19659,7 +19659,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.59</v>
@@ -20970,7 +20970,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -21188,7 +21188,7 @@
         <v>2</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR95" t="n">
         <v>1.75</v>
@@ -22493,7 +22493,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.29</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.82</v>
@@ -25109,7 +25109,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.76</v>
@@ -25330,7 +25330,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR114" t="n">
         <v>1.58</v>
@@ -26417,7 +26417,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.44</v>
@@ -26856,7 +26856,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR121" t="n">
         <v>1.92</v>
@@ -29469,10 +29469,10 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR133" t="n">
         <v>1.96</v>
@@ -30780,7 +30780,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR139" t="n">
         <v>1.41</v>
@@ -30995,7 +30995,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.13</v>
@@ -34265,7 +34265,7 @@
         <v>0.86</v>
       </c>
       <c r="AP155" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.88</v>
@@ -34486,7 +34486,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR156" t="n">
         <v>1.71</v>
@@ -34701,7 +34701,7 @@
         <v>0.75</v>
       </c>
       <c r="AP157" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.13</v>
@@ -35140,7 +35140,7 @@
         <v>1</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR159" t="n">
         <v>1.43</v>
@@ -39064,7 +39064,7 @@
         <v>2</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR177" t="n">
         <v>1.79</v>
@@ -39936,7 +39936,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR181" t="n">
         <v>1.18</v>
@@ -41677,7 +41677,7 @@
         <v>1.33</v>
       </c>
       <c r="AP189" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.18</v>
@@ -41895,7 +41895,7 @@
         <v>1</v>
       </c>
       <c r="AP190" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.88</v>
@@ -43206,7 +43206,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -43642,7 +43642,7 @@
         <v>2</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR198" t="n">
         <v>1.73</v>
@@ -46037,7 +46037,7 @@
         <v>1.22</v>
       </c>
       <c r="AP209" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ209" t="n">
         <v>1.41</v>
@@ -46255,7 +46255,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.82</v>
@@ -47348,7 +47348,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR215" t="n">
         <v>1.54</v>
@@ -48656,7 +48656,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR221" t="n">
         <v>1.61</v>
@@ -49089,7 +49089,7 @@
         <v>1.1</v>
       </c>
       <c r="AP223" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ223" t="n">
         <v>1.24</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.8100000000000001</v>
@@ -53016,7 +53016,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ241" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR241" t="n">
         <v>1.68</v>
@@ -53449,7 +53449,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.41</v>
@@ -54103,7 +54103,7 @@
         <v>1.25</v>
       </c>
       <c r="AP246" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.41</v>
@@ -54542,7 +54542,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR248" t="n">
         <v>1.67</v>
@@ -55632,7 +55632,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR253" t="n">
         <v>1.45</v>
@@ -55847,7 +55847,7 @@
         <v>0.58</v>
       </c>
       <c r="AP254" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.82</v>
@@ -57158,7 +57158,7 @@
         <v>2</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR260" t="n">
         <v>1.73</v>
@@ -58899,7 +58899,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP268" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ268" t="n">
         <v>0.76</v>
@@ -59771,7 +59771,7 @@
         <v>1.08</v>
       </c>
       <c r="AP272" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ272" t="n">
         <v>1.24</v>
@@ -59992,7 +59992,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR273" t="n">
         <v>1.32</v>
@@ -61736,7 +61736,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ281" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR281" t="n">
         <v>1.52</v>
@@ -62169,7 +62169,7 @@
         <v>0.79</v>
       </c>
       <c r="AP283" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ283" t="n">
         <v>0.88</v>
@@ -64131,7 +64131,7 @@
         <v>0.87</v>
       </c>
       <c r="AP292" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ292" t="n">
         <v>0.88</v>
@@ -65006,7 +65006,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ296" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR296" t="n">
         <v>1.77</v>
@@ -65442,7 +65442,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ298" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR298" t="n">
         <v>1.77</v>
@@ -68494,7 +68494,7 @@
         <v>1</v>
       </c>
       <c r="AQ312" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AR312" t="n">
         <v>1.47</v>
@@ -69145,7 +69145,7 @@
         <v>0.73</v>
       </c>
       <c r="AP315" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ315" t="n">
         <v>0.82</v>
@@ -70017,7 +70017,7 @@
         <v>1.33</v>
       </c>
       <c r="AP319" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AQ319" t="n">
         <v>1.53</v>
@@ -70456,7 +70456,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ321" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="AR321" t="n">
         <v>1.73</v>
@@ -73584,6 +73584,442 @@
       </c>
       <c r="BP335" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>7841365</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>45955.77083333334</v>
+      </c>
+      <c r="F336" t="n">
+        <v>34</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>2</v>
+      </c>
+      <c r="K336" t="n">
+        <v>2</v>
+      </c>
+      <c r="L336" t="n">
+        <v>1</v>
+      </c>
+      <c r="M336" t="n">
+        <v>2</v>
+      </c>
+      <c r="N336" t="n">
+        <v>3</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>['18', '26']</t>
+        </is>
+      </c>
+      <c r="Q336" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R336" t="n">
+        <v>2</v>
+      </c>
+      <c r="S336" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T336" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U336" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V336" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W336" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X336" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AG336" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH336" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI336" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ336" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AK336" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL336" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM336" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN336" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO336" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AP336" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ336" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AR336" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS336" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT336" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU336" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV336" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW336" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX336" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY336" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ336" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA336" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB336" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC336" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD336" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE336" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF336" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BG336" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH336" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI336" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ336" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK336" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL336" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM336" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN336" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO336" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP336" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>7841367</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>45955.85416666666</v>
+      </c>
+      <c r="F337" t="n">
+        <v>34</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="I337" t="n">
+        <v>1</v>
+      </c>
+      <c r="J337" t="n">
+        <v>1</v>
+      </c>
+      <c r="K337" t="n">
+        <v>2</v>
+      </c>
+      <c r="L337" t="n">
+        <v>1</v>
+      </c>
+      <c r="M337" t="n">
+        <v>2</v>
+      </c>
+      <c r="N337" t="n">
+        <v>3</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>['9', '64']</t>
+        </is>
+      </c>
+      <c r="Q337" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R337" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S337" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T337" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U337" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V337" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W337" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X337" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD337" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF337" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG337" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH337" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI337" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ337" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK337" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL337" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM337" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO337" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP337" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ337" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR337" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS337" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT337" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU337" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV337" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW337" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX337" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY337" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ337" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA337" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB337" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC337" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD337" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE337" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF337" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BG337" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH337" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI337" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ337" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK337" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL337" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM337" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN337" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO337" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BP337" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP337"/>
+  <dimension ref="A1:BP339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.41</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.88</v>
@@ -3966,7 +3966,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.41</v>
@@ -7018,7 +7018,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR30" t="n">
         <v>2.72</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.76</v>
@@ -9416,7 +9416,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR41" t="n">
         <v>1.61</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.41</v>
@@ -10942,7 +10942,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR48" t="n">
         <v>1.9</v>
@@ -11378,7 +11378,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR50" t="n">
         <v>1.42</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.88</v>
@@ -14212,7 +14212,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR63" t="n">
         <v>1.5</v>
@@ -15084,7 +15084,7 @@
         <v>2</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR67" t="n">
         <v>2.05</v>
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.41</v>
@@ -17479,7 +17479,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.29</v>
@@ -18354,7 +18354,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR82" t="n">
         <v>1.73</v>
@@ -20316,7 +20316,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR91" t="n">
         <v>1.69</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.24</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.53</v>
@@ -23368,7 +23368,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR105" t="n">
         <v>1.6</v>
@@ -24022,7 +24022,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR108" t="n">
         <v>1.49</v>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.82</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.41</v>
@@ -26638,7 +26638,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR120" t="n">
         <v>1.52</v>
@@ -29251,7 +29251,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.82</v>
@@ -29687,10 +29687,10 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -30998,7 +30998,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR140" t="n">
         <v>1.7</v>
@@ -33611,7 +33611,7 @@
         <v>1.38</v>
       </c>
       <c r="AP152" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.59</v>
@@ -33829,7 +33829,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.8100000000000001</v>
@@ -34268,7 +34268,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR155" t="n">
         <v>1.69</v>
@@ -34704,7 +34704,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR157" t="n">
         <v>1.95</v>
@@ -37974,7 +37974,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR172" t="n">
         <v>1.66</v>
@@ -38192,7 +38192,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR173" t="n">
         <v>1.71</v>
@@ -38625,7 +38625,7 @@
         <v>0.67</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ175" t="n">
         <v>0.76</v>
@@ -40369,7 +40369,7 @@
         <v>1.25</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.24</v>
@@ -42331,7 +42331,7 @@
         <v>1.5</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.59</v>
@@ -42552,7 +42552,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR193" t="n">
         <v>1.23</v>
@@ -44078,7 +44078,7 @@
         <v>1</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -46473,7 +46473,7 @@
         <v>1.3</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.18</v>
@@ -47345,7 +47345,7 @@
         <v>1.7</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.41</v>
@@ -48002,7 +48002,7 @@
         <v>2</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR218" t="n">
         <v>1.79</v>
@@ -49743,7 +49743,7 @@
         <v>1.1</v>
       </c>
       <c r="AP226" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ226" t="n">
         <v>1.41</v>
@@ -50400,7 +50400,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR229" t="n">
         <v>1.56</v>
@@ -51487,7 +51487,7 @@
         <v>0.92</v>
       </c>
       <c r="AP234" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.88</v>
@@ -53670,7 +53670,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR244" t="n">
         <v>1.41</v>
@@ -54760,7 +54760,7 @@
         <v>2</v>
       </c>
       <c r="AQ249" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR249" t="n">
         <v>1.76</v>
@@ -55193,7 +55193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ251" t="n">
         <v>1.18</v>
@@ -56065,7 +56065,7 @@
         <v>1.33</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ255" t="n">
         <v>1.53</v>
@@ -56937,7 +56937,7 @@
         <v>0.5</v>
       </c>
       <c r="AP259" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ259" t="n">
         <v>0.44</v>
@@ -58466,7 +58466,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ266" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR266" t="n">
         <v>1.63</v>
@@ -58684,7 +58684,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ267" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR267" t="n">
         <v>1.35</v>
@@ -60207,7 +60207,7 @@
         <v>0.86</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ274" t="n">
         <v>0.88</v>
@@ -60425,7 +60425,7 @@
         <v>0.85</v>
       </c>
       <c r="AP275" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ275" t="n">
         <v>0.76</v>
@@ -62826,7 +62826,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ286" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR286" t="n">
         <v>1.3</v>
@@ -63916,7 +63916,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ291" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR291" t="n">
         <v>1.66</v>
@@ -64349,7 +64349,7 @@
         <v>1.43</v>
       </c>
       <c r="AP293" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ293" t="n">
         <v>1.29</v>
@@ -65003,7 +65003,7 @@
         <v>1</v>
       </c>
       <c r="AP296" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ296" t="n">
         <v>1.06</v>
@@ -68058,7 +68058,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ310" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR310" t="n">
         <v>1.56</v>
@@ -68927,7 +68927,7 @@
         <v>0.47</v>
       </c>
       <c r="AP314" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AQ314" t="n">
         <v>0.44</v>
@@ -69584,7 +69584,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ317" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AR317" t="n">
         <v>1.72</v>
@@ -69799,10 +69799,10 @@
         <v>1.13</v>
       </c>
       <c r="AP318" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ318" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR318" t="n">
         <v>1.74</v>
@@ -74020,6 +74020,442 @@
       </c>
       <c r="BP337" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>7841368</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>45956.66666666666</v>
+      </c>
+      <c r="F338" t="n">
+        <v>34</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" t="n">
+        <v>1</v>
+      </c>
+      <c r="K338" t="n">
+        <v>1</v>
+      </c>
+      <c r="L338" t="n">
+        <v>2</v>
+      </c>
+      <c r="M338" t="n">
+        <v>1</v>
+      </c>
+      <c r="N338" t="n">
+        <v>3</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>['76', '90']</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q338" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R338" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S338" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T338" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U338" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V338" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="W338" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X338" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG338" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH338" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI338" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ338" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK338" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL338" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM338" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN338" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO338" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP338" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ338" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR338" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS338" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT338" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU338" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV338" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW338" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX338" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY338" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ338" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA338" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB338" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC338" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD338" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE338" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF338" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG338" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH338" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI338" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ338" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK338" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL338" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM338" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN338" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO338" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP338" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>7841363</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>45956.77083333334</v>
+      </c>
+      <c r="F339" t="n">
+        <v>34</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="I339" t="n">
+        <v>2</v>
+      </c>
+      <c r="J339" t="n">
+        <v>1</v>
+      </c>
+      <c r="K339" t="n">
+        <v>3</v>
+      </c>
+      <c r="L339" t="n">
+        <v>2</v>
+      </c>
+      <c r="M339" t="n">
+        <v>2</v>
+      </c>
+      <c r="N339" t="n">
+        <v>4</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>['34', '43']</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>['45+1', '66']</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R339" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S339" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="T339" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U339" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V339" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W339" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X339" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG339" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH339" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI339" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AJ339" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK339" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL339" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM339" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN339" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO339" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP339" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ339" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR339" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS339" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT339" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU339" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV339" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW339" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX339" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY339" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ339" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA339" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB339" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC339" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD339" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE339" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="BF339" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG339" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH339" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BI339" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ339" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BK339" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL339" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM339" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN339" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO339" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP339" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP339"/>
+  <dimension ref="A1:BP341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.29</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.59</v>
@@ -5710,7 +5710,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR24" t="n">
         <v>1.25</v>
@@ -7236,7 +7236,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR31" t="n">
         <v>1.94</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.18</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.76</v>
@@ -10288,7 +10288,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR45" t="n">
         <v>1.33</v>
@@ -12032,7 +12032,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR53" t="n">
         <v>0.93</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.29</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.76</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.41</v>
@@ -14866,7 +14866,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR66" t="n">
         <v>1.45</v>
@@ -16389,7 +16389,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.88</v>
@@ -17918,7 +17918,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR80" t="n">
         <v>1.73</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.18</v>
@@ -19444,7 +19444,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR87" t="n">
         <v>1.6</v>
@@ -22275,10 +22275,10 @@
         <v>0.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR100" t="n">
         <v>1.47</v>
@@ -24019,7 +24019,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.82</v>
@@ -24240,7 +24240,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR109" t="n">
         <v>1.15</v>
@@ -25545,7 +25545,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.53</v>
@@ -25766,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR116" t="n">
         <v>1.33</v>
@@ -26420,7 +26420,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR119" t="n">
         <v>1.94</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.12</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.59</v>
@@ -30126,7 +30126,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR136" t="n">
         <v>1.97</v>
@@ -30562,7 +30562,7 @@
         <v>2</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR138" t="n">
         <v>1.79</v>
@@ -30777,7 +30777,7 @@
         <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.41</v>
@@ -33832,7 +33832,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR153" t="n">
         <v>1.49</v>
@@ -34483,7 +34483,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.41</v>
@@ -34919,7 +34919,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.53</v>
@@ -35576,7 +35576,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR161" t="n">
         <v>1.65</v>
@@ -38189,7 +38189,7 @@
         <v>0.67</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.12</v>
@@ -38843,7 +38843,7 @@
         <v>0.33</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.41</v>
@@ -40154,7 +40154,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR182" t="n">
         <v>1.54</v>
@@ -40808,7 +40808,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR185" t="n">
         <v>1.35</v>
@@ -43421,7 +43421,7 @@
         <v>0.6</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.76</v>
@@ -43857,7 +43857,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ199" t="n">
         <v>0.88</v>
@@ -44514,7 +44514,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR202" t="n">
         <v>1.45</v>
@@ -45168,7 +45168,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR205" t="n">
         <v>1.71</v>
@@ -47563,7 +47563,7 @@
         <v>0.82</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.88</v>
@@ -47781,7 +47781,7 @@
         <v>1</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.88</v>
@@ -49964,7 +49964,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR227" t="n">
         <v>1.6</v>
@@ -50836,7 +50836,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR231" t="n">
         <v>1.66</v>
@@ -51923,7 +51923,7 @@
         <v>1</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.24</v>
@@ -52144,7 +52144,7 @@
         <v>2</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR237" t="n">
         <v>1.78</v>
@@ -52577,7 +52577,7 @@
         <v>0.92</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ239" t="n">
         <v>0.82</v>
@@ -54324,7 +54324,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ247" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR247" t="n">
         <v>1.64</v>
@@ -56940,7 +56940,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ259" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR259" t="n">
         <v>1.79</v>
@@ -57373,7 +57373,7 @@
         <v>1.42</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ261" t="n">
         <v>1.41</v>
@@ -57594,7 +57594,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ262" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR262" t="n">
         <v>1.35</v>
@@ -59335,7 +59335,7 @@
         <v>0.92</v>
       </c>
       <c r="AP270" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ270" t="n">
         <v>0.82</v>
@@ -60864,7 +60864,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ277" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR277" t="n">
         <v>1.54</v>
@@ -61733,7 +61733,7 @@
         <v>0.85</v>
       </c>
       <c r="AP281" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ281" t="n">
         <v>1.06</v>
@@ -61951,10 +61951,10 @@
         <v>0.93</v>
       </c>
       <c r="AP282" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ282" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR282" t="n">
         <v>1.8</v>
@@ -64570,7 +64570,7 @@
         <v>1</v>
       </c>
       <c r="AQ294" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR294" t="n">
         <v>1.43</v>
@@ -65221,7 +65221,7 @@
         <v>1.21</v>
       </c>
       <c r="AP297" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ297" t="n">
         <v>1.24</v>
@@ -68712,7 +68712,7 @@
         <v>2</v>
       </c>
       <c r="AQ313" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AR313" t="n">
         <v>1.79</v>
@@ -68930,7 +68930,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ314" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AR314" t="n">
         <v>1.54</v>
@@ -70235,7 +70235,7 @@
         <v>0.73</v>
       </c>
       <c r="AP320" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AQ320" t="n">
         <v>0.76</v>
@@ -70453,7 +70453,7 @@
         <v>0.93</v>
       </c>
       <c r="AP321" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AQ321" t="n">
         <v>1.06</v>
@@ -73311,13 +73311,13 @@
         <v>3</v>
       </c>
       <c r="AX334" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY334" t="n">
         <v>5</v>
       </c>
       <c r="AZ334" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA334" t="n">
         <v>7</v>
@@ -73747,13 +73747,13 @@
         <v>13</v>
       </c>
       <c r="AX336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY336" t="n">
         <v>18</v>
       </c>
       <c r="AZ336" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA336" t="n">
         <v>5</v>
@@ -73956,13 +73956,13 @@
         <v>3.14</v>
       </c>
       <c r="AU337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV337" t="n">
         <v>6</v>
       </c>
       <c r="AW337" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX337" t="n">
         <v>7</v>
@@ -74180,13 +74180,13 @@
         <v>4</v>
       </c>
       <c r="AW338" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX338" t="n">
         <v>7</v>
       </c>
       <c r="AY338" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ338" t="n">
         <v>11</v>
@@ -74456,6 +74456,442 @@
       </c>
       <c r="BP339" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>7841366</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>45957.79166666666</v>
+      </c>
+      <c r="F340" t="n">
+        <v>34</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="I340" t="n">
+        <v>2</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K340" t="n">
+        <v>2</v>
+      </c>
+      <c r="L340" t="n">
+        <v>2</v>
+      </c>
+      <c r="M340" t="n">
+        <v>0</v>
+      </c>
+      <c r="N340" t="n">
+        <v>2</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>['7', '42']</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q340" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R340" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S340" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T340" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U340" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V340" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W340" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X340" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG340" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH340" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI340" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ340" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AK340" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL340" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM340" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN340" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO340" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP340" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AQ340" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR340" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS340" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT340" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU340" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV340" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW340" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX340" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY340" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ340" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA340" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB340" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC340" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD340" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE340" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF340" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG340" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH340" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI340" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ340" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK340" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL340" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM340" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN340" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO340" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP340" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>7841362</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>45957.89583333334</v>
+      </c>
+      <c r="F341" t="n">
+        <v>34</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="I341" t="n">
+        <v>1</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K341" t="n">
+        <v>1</v>
+      </c>
+      <c r="L341" t="n">
+        <v>2</v>
+      </c>
+      <c r="M341" t="n">
+        <v>0</v>
+      </c>
+      <c r="N341" t="n">
+        <v>2</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>['18', '71']</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R341" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S341" t="n">
+        <v>7</v>
+      </c>
+      <c r="T341" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U341" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V341" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W341" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X341" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG341" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH341" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI341" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AJ341" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK341" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL341" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM341" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AN341" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO341" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP341" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ341" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR341" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS341" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT341" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU341" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV341" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW341" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX341" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY341" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ341" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA341" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB341" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC341" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD341" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE341" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF341" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG341" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH341" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI341" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ341" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BK341" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL341" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM341" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN341" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO341" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP341" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP341"/>
+  <dimension ref="A1:BP344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.82</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.53</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.18</v>
@@ -3094,7 +3094,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.82</v>
@@ -7454,7 +7454,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR32" t="n">
         <v>1.04</v>
@@ -8108,7 +8108,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR35" t="n">
         <v>1.6</v>
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR38" t="n">
         <v>1.83</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.88</v>
@@ -10285,7 +10285,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.76</v>
@@ -11160,7 +11160,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR49" t="n">
         <v>1.34</v>
@@ -11811,7 +11811,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.59</v>
@@ -12250,7 +12250,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR54" t="n">
         <v>1.59</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.24</v>
@@ -12686,7 +12686,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR56" t="n">
         <v>1.65</v>
@@ -15520,7 +15520,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR69" t="n">
         <v>1.74</v>
@@ -15956,7 +15956,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR71" t="n">
         <v>1.88</v>
@@ -16171,7 +16171,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.06</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.53</v>
@@ -17482,7 +17482,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR78" t="n">
         <v>1.63</v>
@@ -18133,7 +18133,7 @@
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.82</v>
@@ -19226,7 +19226,7 @@
         <v>2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR86" t="n">
         <v>1.9</v>
@@ -19880,7 +19880,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR89" t="n">
         <v>1.14</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.76</v>
@@ -20967,7 +20967,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.06</v>
@@ -21185,7 +21185,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.41</v>
@@ -22496,7 +22496,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR101" t="n">
         <v>1.64</v>
@@ -23150,7 +23150,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR104" t="n">
         <v>1.55</v>
@@ -23586,7 +23586,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR106" t="n">
         <v>1.68</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.59</v>
@@ -27292,7 +27292,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR123" t="n">
         <v>1.6</v>
@@ -27728,7 +27728,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR125" t="n">
         <v>1.2</v>
@@ -27943,10 +27943,10 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR126" t="n">
         <v>1.75</v>
@@ -28161,7 +28161,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.88</v>
@@ -28379,7 +28379,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ128" t="n">
         <v>0.41</v>
@@ -31431,10 +31431,10 @@
         <v>0.71</v>
       </c>
       <c r="AP142" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR142" t="n">
         <v>1.84</v>
@@ -31649,7 +31649,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.41</v>
@@ -32088,7 +32088,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR145" t="n">
         <v>1.63</v>
@@ -32521,7 +32521,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.82</v>
@@ -33396,7 +33396,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR151" t="n">
         <v>1.59</v>
@@ -35794,7 +35794,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR162" t="n">
         <v>1.64</v>
@@ -36227,10 +36227,10 @@
         <v>0.86</v>
       </c>
       <c r="AP164" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR164" t="n">
         <v>1.83</v>
@@ -36445,7 +36445,7 @@
         <v>1.13</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.18</v>
@@ -36881,10 +36881,10 @@
         <v>0.75</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR167" t="n">
         <v>1.26</v>
@@ -38628,7 +38628,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR175" t="n">
         <v>1.47</v>
@@ -39500,7 +39500,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR179" t="n">
         <v>1.34</v>
@@ -39718,7 +39718,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR180" t="n">
         <v>1.31</v>
@@ -40151,7 +40151,7 @@
         <v>0.78</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.76</v>
@@ -40805,7 +40805,7 @@
         <v>0.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.41</v>
@@ -41241,7 +41241,7 @@
         <v>1.11</v>
       </c>
       <c r="AP187" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.41</v>
@@ -42770,7 +42770,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR194" t="n">
         <v>1.62</v>
@@ -43424,7 +43424,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -43860,7 +43860,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR199" t="n">
         <v>1.81</v>
@@ -44511,7 +44511,7 @@
         <v>0.33</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.41</v>
@@ -44729,7 +44729,7 @@
         <v>1.1</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.41</v>
@@ -45819,7 +45819,7 @@
         <v>0.78</v>
       </c>
       <c r="AP208" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.76</v>
@@ -47784,7 +47784,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR217" t="n">
         <v>1.47</v>
@@ -47999,7 +47999,7 @@
         <v>0.91</v>
       </c>
       <c r="AP218" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.12</v>
@@ -48220,7 +48220,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ219" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR219" t="n">
         <v>1.8</v>
@@ -48438,7 +48438,7 @@
         <v>1</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR220" t="n">
         <v>1.4</v>
@@ -49307,7 +49307,7 @@
         <v>1.2</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.53</v>
@@ -50179,7 +50179,7 @@
         <v>0.27</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.41</v>
@@ -51054,7 +51054,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR232" t="n">
         <v>1.33</v>
@@ -51490,7 +51490,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR234" t="n">
         <v>1.82</v>
@@ -52141,7 +52141,7 @@
         <v>0.55</v>
       </c>
       <c r="AP237" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ237" t="n">
         <v>0.41</v>
@@ -52795,7 +52795,7 @@
         <v>0.83</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.88</v>
@@ -53667,7 +53667,7 @@
         <v>1.08</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ244" t="n">
         <v>1.12</v>
@@ -54978,7 +54978,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR250" t="n">
         <v>1.63</v>
@@ -55414,7 +55414,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR252" t="n">
         <v>1.83</v>
@@ -55629,7 +55629,7 @@
         <v>1.42</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ253" t="n">
         <v>1.41</v>
@@ -56719,7 +56719,7 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ258" t="n">
         <v>1.24</v>
@@ -57155,7 +57155,7 @@
         <v>0.92</v>
       </c>
       <c r="AP260" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ260" t="n">
         <v>1.06</v>
@@ -58030,7 +58030,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ264" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR264" t="n">
         <v>1.63</v>
@@ -58902,7 +58902,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR268" t="n">
         <v>1.84</v>
@@ -59989,7 +59989,7 @@
         <v>1.38</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.41</v>
@@ -61297,10 +61297,10 @@
         <v>1.31</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ279" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR279" t="n">
         <v>1.52</v>
@@ -61515,7 +61515,7 @@
         <v>0.62</v>
       </c>
       <c r="AP280" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ280" t="n">
         <v>0.82</v>
@@ -62172,7 +62172,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ283" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR283" t="n">
         <v>1.81</v>
@@ -62608,7 +62608,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ285" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR285" t="n">
         <v>1.35</v>
@@ -64352,7 +64352,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ293" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR293" t="n">
         <v>1.52</v>
@@ -64785,7 +64785,7 @@
         <v>0.79</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ295" t="n">
         <v>0.76</v>
@@ -65657,7 +65657,7 @@
         <v>0.57</v>
       </c>
       <c r="AP299" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ299" t="n">
         <v>0.82</v>
@@ -66093,7 +66093,7 @@
         <v>1.64</v>
       </c>
       <c r="AP301" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ301" t="n">
         <v>1.41</v>
@@ -66314,7 +66314,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ302" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR302" t="n">
         <v>1.44</v>
@@ -66532,7 +66532,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ303" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR303" t="n">
         <v>1.59</v>
@@ -66750,7 +66750,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ304" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR304" t="n">
         <v>1.29</v>
@@ -67837,7 +67837,7 @@
         <v>1.2</v>
       </c>
       <c r="AP309" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ309" t="n">
         <v>1.41</v>
@@ -68055,7 +68055,7 @@
         <v>1</v>
       </c>
       <c r="AP310" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ310" t="n">
         <v>0.82</v>
@@ -70889,7 +70889,7 @@
         <v>0.88</v>
       </c>
       <c r="AP323" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ323" t="n">
         <v>0.82</v>
@@ -71110,7 +71110,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ324" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="AR324" t="n">
         <v>1.55</v>
@@ -71546,7 +71546,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ326" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR326" t="n">
         <v>1.73</v>
@@ -71979,7 +71979,7 @@
         <v>1.44</v>
       </c>
       <c r="AP328" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AQ328" t="n">
         <v>1.41</v>
@@ -72633,10 +72633,10 @@
         <v>0.88</v>
       </c>
       <c r="AP331" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ331" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AR331" t="n">
         <v>1.35</v>
@@ -74892,6 +74892,660 @@
       </c>
       <c r="BP341" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>7841372</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>45961.79166666666</v>
+      </c>
+      <c r="F342" t="n">
+        <v>35</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="I342" t="n">
+        <v>0</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L342" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q342" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R342" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S342" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T342" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U342" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V342" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W342" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X342" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG342" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH342" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI342" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ342" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK342" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL342" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM342" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AN342" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO342" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AP342" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ342" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AR342" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS342" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT342" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU342" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV342" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW342" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX342" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY342" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ342" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA342" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB342" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC342" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD342" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE342" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF342" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG342" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH342" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="BI342" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ342" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK342" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL342" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM342" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN342" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO342" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BP342" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>7841374</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>45961.79166666666</v>
+      </c>
+      <c r="F343" t="n">
+        <v>35</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>1</v>
+      </c>
+      <c r="K343" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" t="n">
+        <v>2</v>
+      </c>
+      <c r="M343" t="n">
+        <v>1</v>
+      </c>
+      <c r="N343" t="n">
+        <v>3</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>['61', '76']</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="Q343" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R343" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S343" t="n">
+        <v>5</v>
+      </c>
+      <c r="T343" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U343" t="n">
+        <v>3</v>
+      </c>
+      <c r="V343" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W343" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X343" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AG343" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH343" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI343" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ343" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK343" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL343" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM343" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN343" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO343" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP343" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ343" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR343" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS343" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT343" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU343" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV343" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW343" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX343" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY343" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ343" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA343" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB343" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC343" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD343" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE343" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF343" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG343" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH343" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI343" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ343" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK343" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL343" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM343" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN343" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO343" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BP343" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>7841380</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>45961.89930555555</v>
+      </c>
+      <c r="F344" t="n">
+        <v>35</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K344" t="n">
+        <v>0</v>
+      </c>
+      <c r="L344" t="n">
+        <v>0</v>
+      </c>
+      <c r="M344" t="n">
+        <v>0</v>
+      </c>
+      <c r="N344" t="n">
+        <v>0</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q344" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R344" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S344" t="n">
+        <v>3</v>
+      </c>
+      <c r="T344" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U344" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V344" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W344" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X344" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG344" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH344" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI344" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ344" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK344" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL344" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM344" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN344" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO344" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP344" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ344" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR344" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS344" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT344" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU344" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV344" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW344" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX344" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY344" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ344" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA344" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB344" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC344" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD344" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE344" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BF344" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BG344" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH344" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BI344" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ344" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK344" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL344" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM344" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN344" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO344" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP344" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie B_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP344"/>
+  <dimension ref="A1:BP346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.41</v>
@@ -1132,7 +1132,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.24</v>
@@ -2876,7 +2876,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR22" t="n">
         <v>1.56</v>
@@ -5707,7 +5707,7 @@
         <v>3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.76</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.82</v>
@@ -6364,7 +6364,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR27" t="n">
         <v>1.65</v>
@@ -7890,7 +7890,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR34" t="n">
         <v>2.11</v>
@@ -9634,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>2.28</v>
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.82</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.06</v>
@@ -14209,7 +14209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.82</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.59</v>
@@ -15302,7 +15302,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR68" t="n">
         <v>1.15</v>
@@ -16828,7 +16828,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR75" t="n">
         <v>1.74</v>
@@ -18351,7 +18351,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.12</v>
@@ -18572,7 +18572,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR83" t="n">
         <v>1.53</v>
@@ -19005,7 +19005,7 @@
         <v>1</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.41</v>
@@ -21624,7 +21624,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR97" t="n">
         <v>1.62</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.78</v>
@@ -23801,7 +23801,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.41</v>
@@ -24676,7 +24676,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR111" t="n">
         <v>1.55</v>
@@ -27507,10 +27507,10 @@
         <v>0.8</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR124" t="n">
         <v>1.64</v>
@@ -29033,10 +29033,10 @@
         <v>0.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR131" t="n">
         <v>1.6</v>
@@ -32085,7 +32085,7 @@
         <v>0.71</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.83</v>
@@ -32306,7 +32306,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR146" t="n">
         <v>1.44</v>
@@ -33178,7 +33178,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR150" t="n">
         <v>1.57</v>
@@ -33393,7 +33393,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.28</v>
@@ -36448,7 +36448,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR165" t="n">
         <v>1.6</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.88</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.82</v>
@@ -37320,7 +37320,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR169" t="n">
         <v>1.89</v>
@@ -41026,7 +41026,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR186" t="n">
         <v>1.69</v>
@@ -41459,7 +41459,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ188" t="n">
         <v>0.76</v>
@@ -41680,7 +41680,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR189" t="n">
         <v>1.65</v>
@@ -42113,7 +42113,7 @@
         <v>1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.53</v>
@@ -45165,7 +45165,7 @@
         <v>0.8</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ205" t="n">
         <v>0.76</v>
@@ -45601,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.88</v>
@@ -46040,7 +46040,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR209" t="n">
         <v>1.87</v>
@@ -46476,7 +46476,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR211" t="n">
         <v>1.88</v>
@@ -49525,7 +49525,7 @@
         <v>0.64</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ225" t="n">
         <v>0.82</v>
@@ -49746,7 +49746,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR226" t="n">
         <v>1.9</v>
@@ -50833,7 +50833,7 @@
         <v>0.3</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ231" t="n">
         <v>0.41</v>
@@ -51705,7 +51705,7 @@
         <v>0.73</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ235" t="n">
         <v>0.76</v>
@@ -52362,7 +52362,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR238" t="n">
         <v>1.8</v>
@@ -53888,7 +53888,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR245" t="n">
         <v>1.34</v>
@@ -54539,7 +54539,7 @@
         <v>1.55</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AQ248" t="n">
         <v>1.41</v>
@@ -55196,7 +55196,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR251" t="n">
         <v>1.49</v>
@@ -57376,7 +57376,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR261" t="n">
         <v>1.53</v>
@@ -57812,7 +57812,7 @@
         <v>2</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AR263" t="n">
         <v>1.76</v>
@@ -58027,7 +58027,7 @@
         <v>0.85</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AQ264" t="n">
         <v>0.83</v>
@@ -58463,7 +58463,7 @@
         <v>1</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.76</v>
+